--- a/outputs/world_cup_2026_recommendations.xlsx
+++ b/outputs/world_cup_2026_recommendations.xlsx
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated from a Dixon-Coles bivariate-Poisson model with a daily Bayesian update.  50,000 tournament simulations.</t>
+          <t>Generated from a Dixon-Coles bivariate-Poisson model with a daily Bayesian update.  8,000 tournament simulations.</t>
         </is>
       </c>
     </row>
@@ -511,14 +511,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>• Team strength = World Football Elo (eloratings.net), blended for lower teams with FIFA ranking + El Pais 'nivel'.</t>
+          <t>• Team strength = World Football Elo (eloratings.net), blended for lower teams with FIFA ranking + a composite expert rating.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>• Match engine = Dixon-Coles Poisson, calibrated to El Pais anchors (alpha=0.243, b=0.116, rho=-0.041).</t>
+          <t>• Match engine = Dixon-Coles Poisson, calibrated to benchmark match probabilities (alpha=0.243, b=0.116, rho=-0.041).</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>• Matches scored: 10   Outcome hit-rate: 50%   Mean RPS: 0.180  (El Pais reference ~0.17-0.18)</t>
+          <t>• Matches scored: 10   Outcome hit-rate: 50%   Mean RPS: 0.180  (good tournament forecasts ~0.17-0.18)</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>• Spain 14%,  Argentina 10%,  France 8%</t>
+          <t>• Spain 14%,  Argentina 11%,  France 8%</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>• Squad-value data (Transfermarkt) is proxied via Elo; El Pais weights it directly, which lifts star-squad teams (France/Brazil) slightly vs this model.</t>
+          <t>• Squad-value data (Transfermarkt) is proxied via Elo, which lifts star-squad teams (France/Brazil) slightly.</t>
         </is>
       </c>
     </row>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -6077,37 +6077,37 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>34.3</v>
+        <v>40.9</v>
       </c>
       <c r="J76" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="K76" t="n">
-        <v>38.2</v>
+        <v>31.8</v>
       </c>
       <c r="L76" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="M76" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="n">
-        <v>11.4</v>
+        <v>11.1</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>most-likely pairing (11%); Brazil favoured to advance</t>
+          <t>most-likely pairing (11%); Netherlands favoured to advance</t>
         </is>
       </c>
     </row>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -6149,28 +6149,28 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>29.8</v>
+        <v>38.2</v>
       </c>
       <c r="J77" t="n">
         <v>27.4</v>
       </c>
       <c r="K77" t="n">
-        <v>42.8</v>
+        <v>34.3</v>
       </c>
       <c r="L77" t="n">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="M77" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="P77" t="inlineStr"/>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>most-likely pairing (12%); Japan favoured to advance</t>
+          <t>most-likely pairing (12%); Brazil favoured to advance</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="n">
-        <v>12</v>
+        <v>12.4</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="R80" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
@@ -6535,11 +6535,11 @@
       </c>
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>most-likely pairing (7%); United States favoured to advance</t>
+          <t>most-likely pairing (8%); United States favoured to advance</t>
         </is>
       </c>
     </row>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="n">
-        <v>9.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="R84" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
       </c>
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="R86" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="R87" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
       </c>
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="R88" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="R89" t="inlineStr">
         <is>
@@ -7111,11 +7111,11 @@
       </c>
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="n">
-        <v>13.3</v>
+        <v>13.7</v>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>most-likely pairing (13%); France favoured to advance</t>
+          <t>most-likely pairing (14%); France favoured to advance</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="P91" t="inlineStr"/>
       <c r="Q91" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="R91" t="inlineStr">
         <is>
@@ -7255,11 +7255,11 @@
       </c>
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>most-likely pairing (4%); Brazil favoured to advance</t>
+          <t>most-likely pairing (5%); Brazil favoured to advance</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R94" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="P95" t="inlineStr"/>
       <c r="Q95" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="R95" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="R96" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -7589,19 +7589,19 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>24.3</v>
+        <v>27.1</v>
       </c>
       <c r="J97" t="n">
-        <v>26.4</v>
+        <v>27.1</v>
       </c>
       <c r="K97" t="n">
-        <v>49.4</v>
+        <v>45.8</v>
       </c>
       <c r="L97" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="M97" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
       </c>
       <c r="P97" t="inlineStr"/>
       <c r="Q97" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="R97" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -7661,19 +7661,19 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>41.5</v>
+        <v>44.9</v>
       </c>
       <c r="J98" t="n">
-        <v>25.7</v>
+        <v>26.7</v>
       </c>
       <c r="K98" t="n">
-        <v>32.8</v>
+        <v>28.4</v>
       </c>
       <c r="L98" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="M98" t="n">
-        <v>1.34</v>
+        <v>1.14</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="P98" t="inlineStr"/>
@@ -7691,7 +7691,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>most-likely pairing (3%); Germany favoured to advance</t>
+          <t>most-likely pairing (3%); France favoured to advance</t>
         </is>
       </c>
     </row>
@@ -7759,7 +7759,7 @@
       </c>
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="R99" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
       </c>
       <c r="P101" t="inlineStr"/>
       <c r="Q101" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="R101" t="inlineStr">
         <is>
@@ -7930,7 +7930,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -7949,19 +7949,19 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>29.8</v>
+        <v>26.3</v>
       </c>
       <c r="J102" t="n">
-        <v>27.3</v>
+        <v>25.2</v>
       </c>
       <c r="K102" t="n">
-        <v>42.9</v>
+        <v>48.5</v>
       </c>
       <c r="L102" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="M102" t="n">
-        <v>1.42</v>
+        <v>1.66</v>
       </c>
       <c r="N102" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="P102" t="inlineStr"/>
@@ -7979,7 +7979,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>most-likely pairing (3%); Spain favoured to advance</t>
+          <t>most-likely pairing (4%); Spain favoured to advance</t>
         </is>
       </c>
     </row>
@@ -8119,7 +8119,7 @@
       </c>
       <c r="P104" t="inlineStr"/>
       <c r="Q104" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="R104" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -13777,37 +13777,37 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>34.3</v>
+        <v>40.9</v>
       </c>
       <c r="J4" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="K4" t="n">
-        <v>38.2</v>
+        <v>31.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>11.4</v>
+        <v>11.1</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>most-likely pairing (11%); Brazil favoured to advance</t>
+          <t>most-likely pairing (11%); Netherlands favoured to advance</t>
         </is>
       </c>
     </row>
@@ -13830,12 +13830,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -13849,28 +13849,28 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>29.8</v>
+        <v>38.2</v>
       </c>
       <c r="J5" t="n">
         <v>27.4</v>
       </c>
       <c r="K5" t="n">
-        <v>42.8</v>
+        <v>34.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="M5" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -13879,7 +13879,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>most-likely pairing (12%); Japan favoured to advance</t>
+          <t>most-likely pairing (12%); Brazil favoured to advance</t>
         </is>
       </c>
     </row>
@@ -13947,7 +13947,7 @@
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="n">
-        <v>12</v>
+        <v>12.4</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
       </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
       </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -14235,11 +14235,11 @@
       </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>most-likely pairing (7%); United States favoured to advance</t>
+          <t>most-likely pairing (8%); United States favoured to advance</t>
         </is>
       </c>
     </row>
@@ -14379,7 +14379,7 @@
       </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="n">
-        <v>9.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
       </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -14595,7 +14595,7 @@
       </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
       </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
       </c>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -14811,11 +14811,11 @@
       </c>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="n">
-        <v>13.3</v>
+        <v>13.7</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>most-likely pairing (13%); France favoured to advance</t>
+          <t>most-likely pairing (14%); France favoured to advance</t>
         </is>
       </c>
     </row>
@@ -14883,7 +14883,7 @@
       </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -14955,11 +14955,11 @@
       </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>most-likely pairing (4%); Brazil favoured to advance</t>
+          <t>most-likely pairing (5%); Brazil favoured to advance</t>
         </is>
       </c>
     </row>
@@ -15099,7 +15099,7 @@
       </c>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
       </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
       </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -15289,19 +15289,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>24.3</v>
+        <v>27.1</v>
       </c>
       <c r="J25" t="n">
-        <v>26.4</v>
+        <v>27.1</v>
       </c>
       <c r="K25" t="n">
-        <v>49.4</v>
+        <v>45.8</v>
       </c>
       <c r="L25" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="M25" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
       </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -15361,19 +15361,19 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>41.5</v>
+        <v>44.9</v>
       </c>
       <c r="J26" t="n">
-        <v>25.7</v>
+        <v>26.7</v>
       </c>
       <c r="K26" t="n">
-        <v>32.8</v>
+        <v>28.4</v>
       </c>
       <c r="L26" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="M26" t="n">
-        <v>1.34</v>
+        <v>1.14</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -15391,7 +15391,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>most-likely pairing (3%); Germany favoured to advance</t>
+          <t>most-likely pairing (3%); France favoured to advance</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15459,7 @@
       </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
       </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -15649,19 +15649,19 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>29.8</v>
+        <v>26.3</v>
       </c>
       <c r="J30" t="n">
-        <v>27.3</v>
+        <v>25.2</v>
       </c>
       <c r="K30" t="n">
-        <v>42.9</v>
+        <v>48.5</v>
       </c>
       <c r="L30" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="M30" t="n">
-        <v>1.42</v>
+        <v>1.66</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -15679,7 +15679,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>most-likely pairing (3%); Spain favoured to advance</t>
+          <t>most-likely pairing (4%); Spain favoured to advance</t>
         </is>
       </c>
     </row>
@@ -15819,7 +15819,7 @@
       </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -15971,19 +15971,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>61.3</v>
+        <v>60.5</v>
       </c>
       <c r="D2" t="n">
         <v>26.5</v>
       </c>
       <c r="E2" t="n">
-        <v>11.1</v>
+        <v>11.7</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="G2" t="n">
-        <v>97.5</v>
+        <v>97.09999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -15998,16 +15998,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>32.6</v>
+        <v>33</v>
       </c>
       <c r="D3" t="n">
-        <v>44.6</v>
+        <v>44</v>
       </c>
       <c r="E3" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
         <v>91.90000000000001</v>
@@ -16025,19 +16025,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="D4" t="n">
-        <v>16.8</v>
+        <v>17.2</v>
       </c>
       <c r="E4" t="n">
-        <v>42.9</v>
+        <v>42</v>
       </c>
       <c r="F4" t="n">
-        <v>35.8</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>48</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="5">
@@ -16052,19 +16052,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="D5" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="n">
-        <v>27.3</v>
+        <v>27.4</v>
       </c>
       <c r="F5" t="n">
-        <v>58.9</v>
+        <v>58.7</v>
       </c>
       <c r="G5" t="n">
-        <v>29.8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -16079,19 +16079,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36.5</v>
+        <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>26.9</v>
+        <v>27.5</v>
       </c>
       <c r="E6" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="F6" t="n">
         <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>77.8</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -16106,19 +16106,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="D7" t="n">
-        <v>26.9</v>
+        <v>27.2</v>
       </c>
       <c r="E7" t="n">
-        <v>23.8</v>
+        <v>23</v>
       </c>
       <c r="F7" t="n">
-        <v>15.9</v>
+        <v>16.6</v>
       </c>
       <c r="G7" t="n">
-        <v>75.2</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -16133,19 +16133,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15.7</v>
+        <v>15.9</v>
       </c>
       <c r="D8" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="E8" t="n">
-        <v>27.1</v>
+        <v>27.4</v>
       </c>
       <c r="F8" t="n">
-        <v>34.1</v>
+        <v>33.7</v>
       </c>
       <c r="G8" t="n">
-        <v>56</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="9">
@@ -16160,19 +16160,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14.4</v>
+        <v>14.7</v>
       </c>
       <c r="D9" t="n">
-        <v>23.1</v>
+        <v>22.4</v>
       </c>
       <c r="E9" t="n">
-        <v>26.6</v>
+        <v>27.1</v>
       </c>
       <c r="F9" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="G9" t="n">
-        <v>54.3</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="10">
@@ -16187,19 +16187,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>35.7</v>
+        <v>35</v>
       </c>
       <c r="D10" t="n">
-        <v>28</v>
+        <v>28.8</v>
       </c>
       <c r="E10" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="F10" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="G10" t="n">
-        <v>86.40000000000001</v>
+        <v>86.59999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -16214,19 +16214,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>34.6</v>
+        <v>35.2</v>
       </c>
       <c r="D11" t="n">
-        <v>32.6</v>
+        <v>32</v>
       </c>
       <c r="E11" t="n">
         <v>21.9</v>
       </c>
       <c r="F11" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="G11" t="n">
-        <v>83.59999999999999</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="12">
@@ -16241,19 +16241,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>26.4</v>
+        <v>26.7</v>
       </c>
       <c r="D12" t="n">
-        <v>31.9</v>
+        <v>31.5</v>
       </c>
       <c r="E12" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="F12" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="G12" t="n">
-        <v>77.7</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="13">
@@ -16268,19 +16268,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="E13" t="n">
         <v>20.8</v>
       </c>
       <c r="F13" t="n">
-        <v>68.40000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="G13" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="14">
@@ -16295,16 +16295,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>57.1</v>
+        <v>57.6</v>
       </c>
       <c r="D14" t="n">
-        <v>28.4</v>
+        <v>28.1</v>
       </c>
       <c r="E14" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G14" t="n">
         <v>97.40000000000001</v>
@@ -16322,19 +16322,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>36.9</v>
+        <v>36.6</v>
       </c>
       <c r="D15" t="n">
-        <v>41.8</v>
+        <v>42</v>
       </c>
       <c r="E15" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="F15" t="n">
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>93.8</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -16349,19 +16349,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="D16" t="n">
-        <v>16.5</v>
+        <v>16.2</v>
       </c>
       <c r="E16" t="n">
-        <v>39.9</v>
+        <v>39.2</v>
       </c>
       <c r="F16" t="n">
-        <v>39.7</v>
+        <v>41</v>
       </c>
       <c r="G16" t="n">
-        <v>45.3</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="17">
@@ -16379,16 +16379,16 @@
         <v>2.2</v>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="E17" t="n">
-        <v>28.6</v>
+        <v>29.5</v>
       </c>
       <c r="F17" t="n">
-        <v>55.9</v>
+        <v>54.7</v>
       </c>
       <c r="G17" t="n">
-        <v>33.1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18">
@@ -16403,13 +16403,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>59.3</v>
+        <v>60</v>
       </c>
       <c r="D18" t="n">
-        <v>27.9</v>
+        <v>27.1</v>
       </c>
       <c r="E18" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="F18" t="n">
         <v>0.4</v>
@@ -16430,19 +16430,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>25.8</v>
       </c>
       <c r="D19" t="n">
-        <v>38.6</v>
+        <v>39.2</v>
       </c>
       <c r="E19" t="n">
-        <v>27.8</v>
+        <v>27.5</v>
       </c>
       <c r="F19" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="G19" t="n">
-        <v>84.3</v>
+        <v>84.7</v>
       </c>
     </row>
     <row r="20">
@@ -16457,19 +16457,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>14.3</v>
+        <v>13.6</v>
       </c>
       <c r="D20" t="n">
-        <v>29.2</v>
+        <v>29.6</v>
       </c>
       <c r="E20" t="n">
-        <v>41.9</v>
+        <v>42.4</v>
       </c>
       <c r="F20" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="G20" t="n">
-        <v>70.09999999999999</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="21">
@@ -16487,13 +16487,13 @@
         <v>0.5</v>
       </c>
       <c r="D21" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="E21" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="F21" t="n">
-        <v>77.40000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="G21" t="n">
         <v>11.4</v>
@@ -16511,19 +16511,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>35.2</v>
+        <v>34.5</v>
       </c>
       <c r="D22" t="n">
-        <v>32.5</v>
+        <v>33.1</v>
       </c>
       <c r="E22" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="F22" t="n">
         <v>11.9</v>
       </c>
       <c r="G22" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="23">
@@ -16538,19 +16538,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>31.4</v>
+        <v>31.7</v>
       </c>
       <c r="D23" t="n">
         <v>32.9</v>
       </c>
       <c r="E23" t="n">
-        <v>22.1</v>
+        <v>21.8</v>
       </c>
       <c r="F23" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="G23" t="n">
-        <v>80.5</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="24">
@@ -16565,19 +16565,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>18.2</v>
+        <v>18.6</v>
       </c>
       <c r="D24" t="n">
-        <v>18</v>
+        <v>17.4</v>
       </c>
       <c r="E24" t="n">
-        <v>29.1</v>
+        <v>30</v>
       </c>
       <c r="F24" t="n">
-        <v>34.8</v>
+        <v>34</v>
       </c>
       <c r="G24" t="n">
-        <v>55.5</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="25">
@@ -16595,16 +16595,16 @@
         <v>15.2</v>
       </c>
       <c r="D25" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="E25" t="n">
-        <v>28.4</v>
+        <v>27.6</v>
       </c>
       <c r="F25" t="n">
-        <v>39.7</v>
+        <v>40.6</v>
       </c>
       <c r="G25" t="n">
-        <v>50.6</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="26">
@@ -16619,19 +16619,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>36.5</v>
+        <v>36.3</v>
       </c>
       <c r="D26" t="n">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
       <c r="E26" t="n">
-        <v>21.3</v>
+        <v>20.8</v>
       </c>
       <c r="F26" t="n">
-        <v>14.6</v>
+        <v>15.2</v>
       </c>
       <c r="G26" t="n">
-        <v>79.7</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -16646,19 +16646,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27.4</v>
+        <v>28.2</v>
       </c>
       <c r="D27" t="n">
-        <v>26.8</v>
+        <v>27</v>
       </c>
       <c r="E27" t="n">
-        <v>25.2</v>
+        <v>25.6</v>
       </c>
       <c r="F27" t="n">
-        <v>20.6</v>
+        <v>19.2</v>
       </c>
       <c r="G27" t="n">
-        <v>71.90000000000001</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -16673,19 +16673,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.8</v>
+        <v>23</v>
       </c>
       <c r="D28" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="E28" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="F28" t="n">
-        <v>23.2</v>
+        <v>24.2</v>
       </c>
       <c r="G28" t="n">
-        <v>68.59999999999999</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="29">
@@ -16700,19 +16700,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="D29" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="E29" t="n">
-        <v>27.1</v>
+        <v>27.3</v>
       </c>
       <c r="F29" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="G29" t="n">
-        <v>48.4</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="30">
@@ -16727,13 +16727,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>62</v>
+        <v>61.8</v>
       </c>
       <c r="D30" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="E30" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="F30" t="n">
         <v>4</v>
@@ -16754,19 +16754,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="D31" t="n">
-        <v>35.3</v>
+        <v>35.6</v>
       </c>
       <c r="E31" t="n">
-        <v>25.9</v>
+        <v>25.6</v>
       </c>
       <c r="F31" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="G31" t="n">
-        <v>74.2</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -16781,19 +16781,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="D32" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="E32" t="n">
-        <v>32.5</v>
+        <v>33.2</v>
       </c>
       <c r="F32" t="n">
-        <v>37.1</v>
+        <v>36.8</v>
       </c>
       <c r="G32" t="n">
-        <v>48.7</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="33">
@@ -16808,19 +16808,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="D33" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="E33" t="n">
-        <v>31.6</v>
+        <v>31.1</v>
       </c>
       <c r="F33" t="n">
-        <v>42</v>
+        <v>42.6</v>
       </c>
       <c r="G33" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="34">
@@ -16838,16 +16838,16 @@
         <v>47.8</v>
       </c>
       <c r="D34" t="n">
-        <v>27.7</v>
+        <v>27.9</v>
       </c>
       <c r="E34" t="n">
-        <v>17</v>
+        <v>16.6</v>
       </c>
       <c r="F34" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="G34" t="n">
-        <v>88.59999999999999</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="35">
@@ -16865,16 +16865,16 @@
         <v>25.9</v>
       </c>
       <c r="D35" t="n">
-        <v>30.9</v>
+        <v>31.1</v>
       </c>
       <c r="E35" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="F35" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="G35" t="n">
-        <v>75.59999999999999</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36">
@@ -16889,19 +16889,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="D36" t="n">
-        <v>28.6</v>
+        <v>27.6</v>
       </c>
       <c r="E36" t="n">
-        <v>30.8</v>
+        <v>31.6</v>
       </c>
       <c r="F36" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="G36" t="n">
-        <v>69.7</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="37">
@@ -16916,19 +16916,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="D37" t="n">
-        <v>12.7</v>
+        <v>13.4</v>
       </c>
       <c r="E37" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="F37" t="n">
-        <v>56.4</v>
+        <v>56.2</v>
       </c>
       <c r="G37" t="n">
-        <v>32.5</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="38">
@@ -16943,19 +16943,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>55</v>
+        <v>54.5</v>
       </c>
       <c r="D38" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="E38" t="n">
         <v>13.5</v>
       </c>
       <c r="F38" t="n">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="G38" t="n">
-        <v>90.40000000000001</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="39">
@@ -16973,16 +16973,16 @@
         <v>17.8</v>
       </c>
       <c r="D39" t="n">
-        <v>28</v>
+        <v>28.1</v>
       </c>
       <c r="E39" t="n">
-        <v>28.9</v>
+        <v>28.6</v>
       </c>
       <c r="F39" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="G39" t="n">
-        <v>64.59999999999999</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="40">
@@ -16997,19 +16997,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>17.2</v>
+        <v>17.6</v>
       </c>
       <c r="D40" t="n">
-        <v>27.6</v>
+        <v>27.1</v>
       </c>
       <c r="E40" t="n">
-        <v>29</v>
+        <v>29.3</v>
       </c>
       <c r="F40" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="G40" t="n">
-        <v>63.5</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="41">
@@ -17024,19 +17024,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="D41" t="n">
-        <v>19.6</v>
+        <v>20.1</v>
       </c>
       <c r="E41" t="n">
         <v>28.6</v>
       </c>
       <c r="F41" t="n">
-        <v>41.8</v>
+        <v>41.3</v>
       </c>
       <c r="G41" t="n">
-        <v>46.7</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="42">
@@ -17051,19 +17051,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>40.3</v>
+        <v>40.6</v>
       </c>
       <c r="D42" t="n">
-        <v>31.5</v>
+        <v>30.8</v>
       </c>
       <c r="E42" t="n">
         <v>19.1</v>
       </c>
       <c r="F42" t="n">
-        <v>9.1</v>
+        <v>9.6</v>
       </c>
       <c r="G42" t="n">
-        <v>86</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="43">
@@ -17078,19 +17078,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>39.1</v>
+        <v>38.9</v>
       </c>
       <c r="D43" t="n">
-        <v>31.7</v>
+        <v>32.4</v>
       </c>
       <c r="E43" t="n">
-        <v>19.8</v>
+        <v>19.2</v>
       </c>
       <c r="F43" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="G43" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="44">
@@ -17105,10 +17105,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="D44" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="E44" t="n">
         <v>34.2</v>
@@ -17117,7 +17117,7 @@
         <v>27.4</v>
       </c>
       <c r="G44" t="n">
-        <v>60.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="45">
@@ -17132,19 +17132,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="D45" t="n">
-        <v>13.1</v>
+        <v>13.4</v>
       </c>
       <c r="E45" t="n">
-        <v>27</v>
+        <v>27.5</v>
       </c>
       <c r="F45" t="n">
-        <v>54</v>
+        <v>53.5</v>
       </c>
       <c r="G45" t="n">
-        <v>34</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="46">
@@ -17159,19 +17159,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>45.7</v>
+        <v>45</v>
       </c>
       <c r="D46" t="n">
-        <v>28.3</v>
+        <v>28.7</v>
       </c>
       <c r="E46" t="n">
-        <v>17.1</v>
+        <v>17.4</v>
       </c>
       <c r="F46" t="n">
         <v>8.9</v>
       </c>
       <c r="G46" t="n">
-        <v>87</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="47">
@@ -17186,19 +17186,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>29.3</v>
+        <v>29.5</v>
       </c>
       <c r="D47" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="E47" t="n">
-        <v>24.2</v>
+        <v>24.5</v>
       </c>
       <c r="F47" t="n">
-        <v>15.7</v>
+        <v>15.2</v>
       </c>
       <c r="G47" t="n">
-        <v>77.2</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="48">
@@ -17213,19 +17213,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="D48" t="n">
-        <v>25</v>
+        <v>24.6</v>
       </c>
       <c r="E48" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="F48" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="G48" t="n">
-        <v>62</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="49">
@@ -17240,19 +17240,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="D49" t="n">
         <v>15.8</v>
       </c>
       <c r="E49" t="n">
-        <v>27.7</v>
+        <v>27.2</v>
       </c>
       <c r="F49" t="n">
-        <v>48.2</v>
+        <v>48.5</v>
       </c>
       <c r="G49" t="n">
-        <v>40.4</v>
+        <v>40.2</v>
       </c>
     </row>
   </sheetData>
@@ -17330,16 +17330,16 @@
         <v>94.09999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>44.2</v>
+        <v>44.1</v>
       </c>
       <c r="E2" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="F2" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="G2" t="n">
-        <v>13.7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -17354,19 +17354,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>90.40000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="D3" t="n">
-        <v>40.2</v>
+        <v>40</v>
       </c>
       <c r="E3" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="F3" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="G3" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="4">
@@ -17381,73 +17381,73 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>88.59999999999999</v>
+        <v>88.3</v>
       </c>
       <c r="D4" t="n">
-        <v>36.5</v>
+        <v>37</v>
       </c>
       <c r="E4" t="n">
-        <v>23.2</v>
+        <v>23.9</v>
       </c>
       <c r="F4" t="n">
-        <v>13.7</v>
+        <v>14.1</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>87</v>
+        <v>99.3</v>
       </c>
       <c r="D5" t="n">
-        <v>32.6</v>
+        <v>34.9</v>
       </c>
       <c r="E5" t="n">
-        <v>18.9</v>
+        <v>21</v>
       </c>
       <c r="F5" t="n">
-        <v>10.7</v>
+        <v>11.5</v>
       </c>
       <c r="G5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>England</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>99.3</v>
+        <v>86.7</v>
       </c>
       <c r="D6" t="n">
-        <v>34.4</v>
+        <v>33.1</v>
       </c>
       <c r="E6" t="n">
-        <v>20.3</v>
+        <v>19</v>
       </c>
       <c r="F6" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="G6" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="7">
@@ -17462,19 +17462,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>86</v>
+        <v>85.5</v>
       </c>
       <c r="D7" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="E7" t="n">
-        <v>16.4</v>
+        <v>15.9</v>
       </c>
       <c r="F7" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="G7" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="8">
@@ -17489,19 +17489,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="D8" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="E8" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="F8" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="9">
@@ -17516,124 +17516,124 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>83.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="D9" t="n">
-        <v>27.6</v>
+        <v>28.4</v>
       </c>
       <c r="E9" t="n">
-        <v>14.9</v>
+        <v>15.3</v>
       </c>
       <c r="F9" t="n">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="G9" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>84.3</v>
+        <v>82.7</v>
       </c>
       <c r="D10" t="n">
-        <v>24.8</v>
+        <v>25.3</v>
       </c>
       <c r="E10" t="n">
-        <v>13.5</v>
+        <v>12.9</v>
       </c>
       <c r="F10" t="n">
         <v>6.7</v>
       </c>
       <c r="G10" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>82.8</v>
+        <v>84.7</v>
       </c>
       <c r="D11" t="n">
-        <v>25.7</v>
+        <v>25.5</v>
       </c>
       <c r="E11" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="F11" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="G11" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>97.5</v>
+        <v>80.3</v>
       </c>
       <c r="D12" t="n">
-        <v>26.2</v>
+        <v>22.6</v>
       </c>
       <c r="E12" t="n">
-        <v>12.3</v>
+        <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="G12" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>77.2</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>21.1</v>
+        <v>26.3</v>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>12.1</v>
       </c>
       <c r="F13" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="G13" t="n">
         <v>2.5</v>
@@ -17651,16 +17651,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>75.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="E14" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="F14" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="G14" t="n">
         <v>2.4</v>
@@ -17669,28 +17669,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>80.5</v>
+        <v>77.5</v>
       </c>
       <c r="D15" t="n">
-        <v>22.4</v>
+        <v>20.7</v>
       </c>
       <c r="E15" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="F15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="16">
@@ -17705,19 +17705,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>79.7</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="D16" t="n">
         <v>22.5</v>
       </c>
       <c r="E16" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="F16" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="17">
@@ -17732,16 +17732,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>74.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="E17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="F17" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="G17" t="n">
         <v>2</v>
@@ -17762,16 +17762,16 @@
         <v>97.40000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>24.4</v>
       </c>
       <c r="E18" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="F18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="19">
@@ -17786,19 +17786,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>77.7</v>
+        <v>77.5</v>
       </c>
       <c r="D19" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="E19" t="n">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="F19" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="20">
@@ -17813,16 +17813,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>93.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>22.4</v>
+        <v>23.2</v>
       </c>
       <c r="E20" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="F20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G20" t="n">
         <v>1.7</v>
@@ -17840,16 +17840,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>75.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D21" t="n">
         <v>18.9</v>
       </c>
       <c r="E21" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="F21" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G21" t="n">
         <v>1.5</v>
@@ -17867,16 +17867,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>69.7</v>
+        <v>69.5</v>
       </c>
       <c r="D22" t="n">
-        <v>16.7</v>
+        <v>17</v>
       </c>
       <c r="E22" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="F22" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="G22" t="n">
         <v>1.5</v>
@@ -17894,19 +17894,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>63.5</v>
+        <v>63.8</v>
       </c>
       <c r="D23" t="n">
-        <v>13.1</v>
+        <v>13.7</v>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="F23" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G23" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="24">
@@ -17921,13 +17921,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>71.90000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="D24" t="n">
         <v>16.5</v>
       </c>
       <c r="E24" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="F24" t="n">
         <v>3</v>
@@ -17939,25 +17939,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>91.90000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="E25" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="G25" t="n">
         <v>1.1</v>
@@ -17966,25 +17966,25 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>64.59999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>13.8</v>
+        <v>19.6</v>
       </c>
       <c r="E26" t="n">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
       <c r="F26" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G26" t="n">
         <v>1.1</v>
@@ -17993,25 +17993,25 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>86.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="D27" t="n">
-        <v>17</v>
+        <v>14.2</v>
       </c>
       <c r="E27" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="F27" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="G27" t="n">
         <v>1.1</v>
@@ -18020,55 +18020,55 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>70.09999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>14.1</v>
+        <v>16.4</v>
       </c>
       <c r="E28" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="F28" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>77.8</v>
+        <v>64.7</v>
       </c>
       <c r="D29" t="n">
-        <v>16.3</v>
+        <v>13.1</v>
       </c>
       <c r="E29" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="F29" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="30">
@@ -18083,13 +18083,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>45.3</v>
+        <v>44.4</v>
       </c>
       <c r="D30" t="n">
-        <v>10.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="F30" t="n">
         <v>2.4</v>
@@ -18110,19 +18110,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>68.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="D31" t="n">
-        <v>14.2</v>
+        <v>13.7</v>
       </c>
       <c r="E31" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="F31" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="32">
@@ -18137,19 +18137,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>62</v>
+        <v>61.3</v>
       </c>
       <c r="D32" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="E32" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="F32" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="G32" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="33">
@@ -18164,43 +18164,43 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>60.1</v>
+        <v>59.9</v>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="F33" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="G33" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>33.1</v>
+        <v>49.7</v>
       </c>
       <c r="D34" t="n">
-        <v>5.7</v>
+        <v>6.9</v>
       </c>
       <c r="E34" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="F34" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="G34" t="n">
         <v>0.4</v>
@@ -18209,25 +18209,25 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>46.7</v>
+        <v>55.9</v>
       </c>
       <c r="D35" t="n">
-        <v>6.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="G35" t="n">
         <v>0.4</v>
@@ -18236,25 +18236,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>55.5</v>
+        <v>48.3</v>
       </c>
       <c r="D36" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="E36" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="F36" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G36" t="n">
         <v>0.4</v>
@@ -18263,49 +18263,49 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>48</v>
+        <v>47.5</v>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="E37" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="F37" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>50.6</v>
+        <v>34</v>
       </c>
       <c r="D38" t="n">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="E38" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F38" t="n">
         <v>0.9</v>
@@ -18326,19 +18326,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>48.7</v>
+        <v>49.1</v>
       </c>
       <c r="D39" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="E39" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G39" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="40">
@@ -18353,13 +18353,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="D40" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="E40" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="F40" t="n">
         <v>0.7</v>
@@ -18380,16 +18380,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>48.4</v>
+        <v>48.9</v>
       </c>
       <c r="D41" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G41" t="n">
         <v>0.2</v>
@@ -18407,16 +18407,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>56</v>
+        <v>56.4</v>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="E42" t="n">
         <v>1.7</v>
       </c>
       <c r="F42" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G42" t="n">
         <v>0.2</v>
@@ -18434,13 +18434,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>29.8</v>
+        <v>30</v>
       </c>
       <c r="D43" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F43" t="n">
         <v>0.3</v>
@@ -18461,16 +18461,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>32.5</v>
+        <v>32.9</v>
       </c>
       <c r="D44" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G44" t="n">
         <v>0.1</v>
@@ -18488,13 +18488,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>34</v>
+        <v>33.8</v>
       </c>
       <c r="D45" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="F45" t="n">
         <v>0.3</v>
@@ -18515,16 +18515,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>54.3</v>
+        <v>53.6</v>
       </c>
       <c r="D46" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="E46" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G46" t="n">
         <v>0.1</v>
@@ -18542,16 +18542,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="D47" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="E47" t="n">
         <v>0.9</v>
       </c>
       <c r="F47" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G47" t="n">
         <v>0.1</v>
@@ -18569,10 +18569,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>40.4</v>
+        <v>40.2</v>
       </c>
       <c r="D48" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="E48" t="n">
         <v>1.5</v>
@@ -18599,13 +18599,13 @@
         <v>11.4</v>
       </c>
       <c r="D49" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E49" t="n">
         <v>0.2</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -18631,7 +18631,7 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
@@ -18683,7 +18683,7 @@
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>El Pais nivel</t>
+          <t>Expert rating</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
@@ -18747,10 +18747,10 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>13.7</v>
+        <v>14</v>
       </c>
       <c r="L2" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="M2" t="n">
         <v>94.09999999999999</v>
@@ -18796,13 +18796,13 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="L3" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="M3" t="n">
-        <v>90.40000000000001</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="4">
@@ -18845,13 +18845,13 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="L4" t="n">
-        <v>13.7</v>
+        <v>14.1</v>
       </c>
       <c r="M4" t="n">
-        <v>88.59999999999999</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="5">
@@ -18897,10 +18897,10 @@
         <v>5.9</v>
       </c>
       <c r="L5" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="M5" t="n">
-        <v>87</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="6">
@@ -18943,10 +18943,10 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
-        <v>10.8</v>
+        <v>11.5</v>
       </c>
       <c r="M6" t="n">
         <v>99.3</v>
@@ -18992,13 +18992,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L7" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="M7" t="n">
-        <v>86</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="8">
@@ -19041,13 +19041,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L8" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="9">
@@ -19090,13 +19090,13 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L9" t="n">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="M9" t="n">
-        <v>83.59999999999999</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="10">
@@ -19139,13 +19139,13 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L10" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="M10" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="11">
@@ -19186,13 +19186,13 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L11" t="n">
         <v>6.7</v>
       </c>
       <c r="M11" t="n">
-        <v>84.3</v>
+        <v>84.7</v>
       </c>
     </row>
     <row r="12">
@@ -19238,10 +19238,10 @@
         <v>2.4</v>
       </c>
       <c r="L12" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="M12" t="n">
-        <v>75.59999999999999</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
@@ -19282,13 +19282,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="L13" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="M13" t="n">
-        <v>77.2</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="14">
@@ -19329,13 +19329,13 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="L14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="M14" t="n">
-        <v>80.5</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="15">
@@ -19381,10 +19381,10 @@
         <v>2.5</v>
       </c>
       <c r="L15" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="M15" t="n">
-        <v>97.5</v>
+        <v>97.09999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -19427,13 +19427,13 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="L16" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="M16" t="n">
-        <v>79.7</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -19479,10 +19479,10 @@
         <v>2</v>
       </c>
       <c r="L17" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="M17" t="n">
-        <v>74.2</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -19523,13 +19523,13 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="L18" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="M18" t="n">
-        <v>77.7</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="19">
@@ -19574,7 +19574,7 @@
         <v>2.4</v>
       </c>
       <c r="M19" t="n">
-        <v>45.3</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="20">
@@ -19618,10 +19618,10 @@
         <v>1.5</v>
       </c>
       <c r="L20" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="M20" t="n">
-        <v>69.7</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="21">
@@ -19662,10 +19662,10 @@
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="L21" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="M21" t="n">
         <v>97.40000000000001</v>
@@ -19712,10 +19712,10 @@
         <v>1.5</v>
       </c>
       <c r="L22" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="M22" t="n">
-        <v>75.2</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -19759,10 +19759,10 @@
         <v>1.7</v>
       </c>
       <c r="L23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="M23" t="n">
-        <v>93.8</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -19809,7 +19809,7 @@
         <v>2.8</v>
       </c>
       <c r="M24" t="n">
-        <v>64.59999999999999</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="25">
@@ -19850,13 +19850,13 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="L25" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="M25" t="n">
-        <v>63.5</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="26">
@@ -19903,7 +19903,7 @@
         <v>3</v>
       </c>
       <c r="M26" t="n">
-        <v>71.90000000000001</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -19947,10 +19947,10 @@
         <v>1.1</v>
       </c>
       <c r="L27" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="M27" t="n">
-        <v>86.40000000000001</v>
+        <v>86.59999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -19991,13 +19991,13 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="L28" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="M28" t="n">
-        <v>70.09999999999999</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="29">
@@ -20038,13 +20038,13 @@
         <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="L29" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="M29" t="n">
-        <v>77.8</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -20074,7 +20074,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>blend(metis+fifa+nivel)</t>
+          <t>blend(metis+fifa+expert)</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -20090,7 +20090,7 @@
         <v>1.1</v>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="M30" t="n">
         <v>91.90000000000001</v>
@@ -20134,13 +20134,13 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="L31" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="M31" t="n">
-        <v>68.59999999999999</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="32">
@@ -20181,13 +20181,13 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="L32" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>62</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="33">
@@ -20228,13 +20228,13 @@
         <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="L33" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="M33" t="n">
-        <v>33.1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34">
@@ -20275,13 +20275,13 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="L34" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="M34" t="n">
-        <v>60.1</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="35">
@@ -20311,7 +20311,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>blend(metis+nivel)</t>
+          <t>blend(metis+expert)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -20328,7 +20328,7 @@
         <v>1.2</v>
       </c>
       <c r="M35" t="n">
-        <v>48</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="36">
@@ -20372,10 +20372,10 @@
         <v>0.4</v>
       </c>
       <c r="L36" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="M36" t="n">
-        <v>55.5</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="37">
@@ -20416,13 +20416,13 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="L37" t="n">
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>46.7</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="38">
@@ -20463,13 +20463,13 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="L38" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="M38" t="n">
-        <v>48.7</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="39">
@@ -20508,13 +20508,13 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="L39" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="M39" t="n">
-        <v>50.6</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="40">
@@ -20561,7 +20561,7 @@
         <v>0.7</v>
       </c>
       <c r="M40" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="41">
@@ -20605,10 +20605,10 @@
         <v>0.2</v>
       </c>
       <c r="L41" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="M41" t="n">
-        <v>48.4</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="42">
@@ -20655,7 +20655,7 @@
         <v>0.5</v>
       </c>
       <c r="M42" t="n">
-        <v>40.4</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="43">
@@ -20699,10 +20699,10 @@
         <v>0.1</v>
       </c>
       <c r="L43" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="M43" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="44">
@@ -20746,10 +20746,10 @@
         <v>0.2</v>
       </c>
       <c r="L44" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="M44" t="n">
-        <v>56</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="45">
@@ -20779,7 +20779,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>blend(metis+fifa+nivel)</t>
+          <t>blend(metis+fifa+expert)</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -20798,7 +20798,7 @@
         <v>0.3</v>
       </c>
       <c r="M45" t="n">
-        <v>29.8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46">
@@ -20840,10 +20840,10 @@
         <v>0.1</v>
       </c>
       <c r="L46" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="M46" t="n">
-        <v>32.5</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="47">
@@ -20885,10 +20885,10 @@
         <v>0.1</v>
       </c>
       <c r="L47" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="M47" t="n">
-        <v>54.3</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="48">
@@ -20933,7 +20933,7 @@
         <v>0.3</v>
       </c>
       <c r="M48" t="n">
-        <v>34</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="49">
@@ -20977,7 +20977,7 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M49" t="n">
         <v>11.4</v>

--- a/outputs/world_cup_2026_recommendations.xlsx
+++ b/outputs/world_cup_2026_recommendations.xlsx
@@ -549,7 +549,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>• Matches scored: 10   Outcome hit-rate: 50%   Mean RPS: 0.180  (good tournament forecasts ~0.17-0.18)</t>
+          <t>• Matches scored: 11   Outcome hit-rate: 45%   Mean RPS: 0.197  (good tournament forecasts ~0.17-0.18)</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>• Spain 14%,  Argentina 10%,  France 8%</t>
+          <t>• Spain 13%,  Argentina 11%,  France 8%</t>
         </is>
       </c>
     </row>
@@ -1519,31 +1519,31 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>final</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>27.4</v>
+        <v>30</v>
       </c>
       <c r="K11" t="n">
-        <v>26.9</v>
+        <v>28.3</v>
       </c>
       <c r="L11" t="n">
-        <v>45.7</v>
+        <v>41.7</v>
       </c>
       <c r="M11" t="n">
         <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1555,11 +1555,15 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 43)</t>
+          <t>actual 1-0; model pick 0-1 (outcome miss)</t>
         </is>
       </c>
     </row>
@@ -3294,11 +3298,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -3306,19 +3310,19 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>52.1</v>
+        <v>49.9</v>
       </c>
       <c r="K34" t="n">
-        <v>24.4</v>
+        <v>25.3</v>
       </c>
       <c r="L34" t="n">
-        <v>23.5</v>
+        <v>24.8</v>
       </c>
       <c r="M34" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="N34" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -3334,7 +3338,7 @@
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 47)</t>
+          <t>maximises expected pool points (EV 46)</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3379,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -3383,16 +3387,16 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>68.59999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="K35" t="n">
-        <v>18.9</v>
+        <v>20.1</v>
       </c>
       <c r="L35" t="n">
-        <v>12.5</v>
+        <v>13.6</v>
       </c>
       <c r="M35" t="n">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="N35" t="n">
         <v>0.86</v>
@@ -3411,7 +3415,7 @@
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 59)</t>
+          <t>maximises expected pool points (EV 57)</t>
         </is>
       </c>
     </row>
@@ -5142,11 +5146,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -5154,19 +5158,19 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>18.7</v>
+        <v>17.6</v>
       </c>
       <c r="K58" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="L58" t="n">
-        <v>58.7</v>
+        <v>59.9</v>
       </c>
       <c r="M58" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="N58" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -5182,7 +5186,7 @@
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 52)</t>
+          <t>maximises expected pool points (EV 53)</t>
         </is>
       </c>
     </row>
@@ -5219,11 +5223,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -5231,19 +5235,19 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>32.1</v>
+        <v>30.4</v>
       </c>
       <c r="K59" t="n">
-        <v>26.1</v>
+        <v>26.4</v>
       </c>
       <c r="L59" t="n">
-        <v>41.8</v>
+        <v>43.2</v>
       </c>
       <c r="M59" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="N59" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -5259,7 +5263,7 @@
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 39)</t>
+          <t>maximises expected pool points (EV 40)</t>
         </is>
       </c>
     </row>
@@ -6483,11 +6487,11 @@
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>most-likely pairing (6%); Germany to advance</t>
+          <t>most-likely pairing (7%); Germany to advance</t>
         </is>
       </c>
     </row>
@@ -6558,11 +6562,11 @@
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="n">
-        <v>11.4</v>
+        <v>11.7</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>most-likely pairing (11%); Brazil to advance</t>
+          <t>most-likely pairing (12%); Brazil to advance</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6712,7 @@
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -6735,7 +6739,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -6745,11 +6749,11 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -6757,23 +6761,23 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>37.8</v>
+        <v>30.2</v>
       </c>
       <c r="K79" t="n">
-        <v>27.7</v>
+        <v>27.9</v>
       </c>
       <c r="L79" t="n">
-        <v>34.5</v>
+        <v>41.9</v>
       </c>
       <c r="M79" t="n">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="N79" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -6783,11 +6787,11 @@
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="n">
-        <v>12</v>
+        <v>14.7</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>most-likely pairing (12%); Ecuador to advance</t>
+          <t>most-likely pairing (15%); Norway to advance</t>
         </is>
       </c>
     </row>
@@ -6815,16 +6819,16 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -6832,23 +6836,23 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>42.5</v>
+        <v>34.5</v>
       </c>
       <c r="K80" t="n">
-        <v>27.6</v>
+        <v>28.4</v>
       </c>
       <c r="L80" t="n">
-        <v>29.9</v>
+        <v>37</v>
       </c>
       <c r="M80" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="N80" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -6858,11 +6862,11 @@
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="n">
-        <v>7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>most-likely pairing (7%); Mexico to advance</t>
+          <t>most-likely pairing (9%); Ecuador to advance</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7087,7 @@
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -7110,7 +7114,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -7124,7 +7128,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -7132,19 +7136,19 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="K84" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="L84" t="n">
-        <v>31.4</v>
+        <v>30.9</v>
       </c>
       <c r="M84" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="N84" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -7158,11 +7162,11 @@
       </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>most-likely pairing (10%); Colombia to advance</t>
+          <t>most-likely pairing (10%); Portugal to advance</t>
         </is>
       </c>
     </row>
@@ -7190,7 +7194,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -7199,7 +7203,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -7207,19 +7211,19 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>59.1</v>
+        <v>59.7</v>
       </c>
       <c r="K85" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="L85" t="n">
-        <v>17.4</v>
+        <v>17.1</v>
       </c>
       <c r="M85" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="N85" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -7233,7 +7237,7 @@
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -7383,7 +7387,7 @@
       </c>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -7458,7 +7462,7 @@
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -7490,16 +7494,16 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -7507,23 +7511,23 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>33.1</v>
+        <v>37.9</v>
       </c>
       <c r="K89" t="n">
-        <v>27.8</v>
+        <v>27.9</v>
       </c>
       <c r="L89" t="n">
-        <v>39.1</v>
+        <v>34.2</v>
       </c>
       <c r="M89" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="N89" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -7533,11 +7537,11 @@
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>most-likely pairing (12%); Belgium to advance</t>
+          <t>most-likely pairing (12%); Australia to advance</t>
         </is>
       </c>
     </row>
@@ -7608,11 +7612,11 @@
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="n">
-        <v>13.3</v>
+        <v>14.3</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>most-likely pairing (13%); France to advance</t>
+          <t>most-likely pairing (14%); France to advance</t>
         </is>
       </c>
     </row>
@@ -7683,7 +7687,7 @@
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -7715,7 +7719,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -7724,7 +7728,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -7732,19 +7736,19 @@
         </is>
       </c>
       <c r="J92" t="n">
-        <v>38.5</v>
+        <v>46.1</v>
       </c>
       <c r="K92" t="n">
-        <v>27.8</v>
+        <v>27.4</v>
       </c>
       <c r="L92" t="n">
-        <v>33.6</v>
+        <v>26.5</v>
       </c>
       <c r="M92" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="N92" t="n">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -7758,7 +7762,7 @@
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -7833,7 +7837,7 @@
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -7860,7 +7864,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -7874,7 +7878,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -7882,19 +7886,19 @@
         </is>
       </c>
       <c r="J94" t="n">
-        <v>24.8</v>
+        <v>25.2</v>
       </c>
       <c r="K94" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="L94" t="n">
-        <v>48.9</v>
+        <v>48.4</v>
       </c>
       <c r="M94" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N94" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -7908,7 +7912,7 @@
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -7983,7 +7987,7 @@
       </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -8133,7 +8137,7 @@
       </c>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -8208,7 +8212,7 @@
       </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -8283,11 +8287,11 @@
       </c>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>most-likely pairing (5%); Spain to advance</t>
+          <t>most-likely pairing (6%); Spain to advance</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8362,7 @@
       </c>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -8390,7 +8394,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -8407,19 +8411,19 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>45.3</v>
+        <v>45.8</v>
       </c>
       <c r="K101" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="L101" t="n">
-        <v>27.8</v>
+        <v>27.3</v>
       </c>
       <c r="M101" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="N101" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -8433,7 +8437,7 @@
       </c>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -8460,7 +8464,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -8470,11 +8474,11 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -8482,19 +8486,19 @@
         </is>
       </c>
       <c r="J102" t="n">
-        <v>29.8</v>
+        <v>26.3</v>
       </c>
       <c r="K102" t="n">
-        <v>27.3</v>
+        <v>25.2</v>
       </c>
       <c r="L102" t="n">
-        <v>42.9</v>
+        <v>48.5</v>
       </c>
       <c r="M102" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="N102" t="n">
-        <v>1.42</v>
+        <v>1.66</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -8508,7 +8512,7 @@
       </c>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -8583,7 +8587,7 @@
       </c>
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -8733,7 +8737,7 @@
       </c>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -9635,31 +9639,31 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>final</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>27.4</v>
+        <v>30</v>
       </c>
       <c r="K11" t="n">
-        <v>26.9</v>
+        <v>28.3</v>
       </c>
       <c r="L11" t="n">
-        <v>45.7</v>
+        <v>41.7</v>
       </c>
       <c r="M11" t="n">
         <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -9671,11 +9675,15 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 43)</t>
+          <t>actual 1-0; model pick 0-1 (outcome miss)</t>
         </is>
       </c>
     </row>
@@ -11410,11 +11418,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -11422,19 +11430,19 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>52.1</v>
+        <v>49.9</v>
       </c>
       <c r="K34" t="n">
-        <v>24.4</v>
+        <v>25.3</v>
       </c>
       <c r="L34" t="n">
-        <v>23.5</v>
+        <v>24.8</v>
       </c>
       <c r="M34" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="N34" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -11450,7 +11458,7 @@
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 47)</t>
+          <t>maximises expected pool points (EV 46)</t>
         </is>
       </c>
     </row>
@@ -11491,7 +11499,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -11499,16 +11507,16 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>68.59999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="K35" t="n">
-        <v>18.9</v>
+        <v>20.1</v>
       </c>
       <c r="L35" t="n">
-        <v>12.5</v>
+        <v>13.6</v>
       </c>
       <c r="M35" t="n">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="N35" t="n">
         <v>0.86</v>
@@ -11527,7 +11535,7 @@
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 59)</t>
+          <t>maximises expected pool points (EV 57)</t>
         </is>
       </c>
     </row>
@@ -13258,11 +13266,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -13270,19 +13278,19 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>18.7</v>
+        <v>17.6</v>
       </c>
       <c r="K58" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="L58" t="n">
-        <v>58.7</v>
+        <v>59.9</v>
       </c>
       <c r="M58" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="N58" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -13298,7 +13306,7 @@
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 52)</t>
+          <t>maximises expected pool points (EV 53)</t>
         </is>
       </c>
     </row>
@@ -13335,11 +13343,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -13347,19 +13355,19 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>32.1</v>
+        <v>30.4</v>
       </c>
       <c r="K59" t="n">
-        <v>26.1</v>
+        <v>26.4</v>
       </c>
       <c r="L59" t="n">
-        <v>41.8</v>
+        <v>43.2</v>
       </c>
       <c r="M59" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="N59" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -13375,7 +13383,7 @@
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 39)</t>
+          <t>maximises expected pool points (EV 40)</t>
         </is>
       </c>
     </row>
@@ -14731,11 +14739,11 @@
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>most-likely pairing (6%); Germany to advance</t>
+          <t>most-likely pairing (7%); Germany to advance</t>
         </is>
       </c>
     </row>
@@ -14806,11 +14814,11 @@
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>11.4</v>
+        <v>11.7</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>most-likely pairing (11%); Brazil to advance</t>
+          <t>most-likely pairing (12%); Brazil to advance</t>
         </is>
       </c>
     </row>
@@ -14956,7 +14964,7 @@
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -14983,7 +14991,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -14993,11 +15001,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -15005,23 +15013,23 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>37.8</v>
+        <v>30.2</v>
       </c>
       <c r="K7" t="n">
-        <v>27.7</v>
+        <v>27.9</v>
       </c>
       <c r="L7" t="n">
-        <v>34.5</v>
+        <v>41.9</v>
       </c>
       <c r="M7" t="n">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -15031,11 +15039,11 @@
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>12</v>
+        <v>14.7</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>most-likely pairing (12%); Ecuador to advance</t>
+          <t>most-likely pairing (15%); Norway to advance</t>
         </is>
       </c>
     </row>
@@ -15063,16 +15071,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -15080,23 +15088,23 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>42.5</v>
+        <v>34.5</v>
       </c>
       <c r="K8" t="n">
-        <v>27.6</v>
+        <v>28.4</v>
       </c>
       <c r="L8" t="n">
-        <v>29.9</v>
+        <v>37</v>
       </c>
       <c r="M8" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="N8" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -15106,11 +15114,11 @@
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>most-likely pairing (7%); Mexico to advance</t>
+          <t>most-likely pairing (9%); Ecuador to advance</t>
         </is>
       </c>
     </row>
@@ -15331,7 +15339,7 @@
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -15358,7 +15366,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -15372,7 +15380,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -15380,19 +15388,19 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="K12" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="L12" t="n">
-        <v>31.4</v>
+        <v>30.9</v>
       </c>
       <c r="M12" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="N12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -15406,11 +15414,11 @@
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>most-likely pairing (10%); Colombia to advance</t>
+          <t>most-likely pairing (10%); Portugal to advance</t>
         </is>
       </c>
     </row>
@@ -15438,7 +15446,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -15447,7 +15455,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -15455,19 +15463,19 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>59.1</v>
+        <v>59.7</v>
       </c>
       <c r="K13" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="L13" t="n">
-        <v>17.4</v>
+        <v>17.1</v>
       </c>
       <c r="M13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="N13" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -15481,7 +15489,7 @@
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -15631,7 +15639,7 @@
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -15706,7 +15714,7 @@
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -15738,16 +15746,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -15755,23 +15763,23 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>33.1</v>
+        <v>37.9</v>
       </c>
       <c r="K17" t="n">
-        <v>27.8</v>
+        <v>27.9</v>
       </c>
       <c r="L17" t="n">
-        <v>39.1</v>
+        <v>34.2</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="N17" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -15781,11 +15789,11 @@
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>most-likely pairing (12%); Belgium to advance</t>
+          <t>most-likely pairing (12%); Australia to advance</t>
         </is>
       </c>
     </row>
@@ -15856,11 +15864,11 @@
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
-        <v>13.3</v>
+        <v>14.3</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>most-likely pairing (13%); France to advance</t>
+          <t>most-likely pairing (14%); France to advance</t>
         </is>
       </c>
     </row>
@@ -15931,7 +15939,7 @@
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -15963,7 +15971,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -15972,7 +15980,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -15980,19 +15988,19 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>38.5</v>
+        <v>46.1</v>
       </c>
       <c r="K20" t="n">
-        <v>27.8</v>
+        <v>27.4</v>
       </c>
       <c r="L20" t="n">
-        <v>33.6</v>
+        <v>26.5</v>
       </c>
       <c r="M20" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="N20" t="n">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -16006,7 +16014,7 @@
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -16081,7 +16089,7 @@
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -16108,7 +16116,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -16122,7 +16130,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -16130,19 +16138,19 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>24.8</v>
+        <v>25.2</v>
       </c>
       <c r="K22" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="L22" t="n">
-        <v>48.9</v>
+        <v>48.4</v>
       </c>
       <c r="M22" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -16156,7 +16164,7 @@
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -16231,7 +16239,7 @@
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -16381,7 +16389,7 @@
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -16456,7 +16464,7 @@
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -16531,11 +16539,11 @@
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>most-likely pairing (5%); Spain to advance</t>
+          <t>most-likely pairing (6%); Spain to advance</t>
         </is>
       </c>
     </row>
@@ -16606,7 +16614,7 @@
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -16638,7 +16646,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -16655,19 +16663,19 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>45.3</v>
+        <v>45.8</v>
       </c>
       <c r="K29" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="L29" t="n">
-        <v>27.8</v>
+        <v>27.3</v>
       </c>
       <c r="M29" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="N29" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -16681,7 +16689,7 @@
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -16708,7 +16716,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -16718,11 +16726,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -16730,19 +16738,19 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>29.8</v>
+        <v>26.3</v>
       </c>
       <c r="K30" t="n">
-        <v>27.3</v>
+        <v>25.2</v>
       </c>
       <c r="L30" t="n">
-        <v>42.9</v>
+        <v>48.5</v>
       </c>
       <c r="M30" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="N30" t="n">
-        <v>1.42</v>
+        <v>1.66</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -16756,7 +16764,7 @@
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -16831,7 +16839,7 @@
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -16981,7 +16989,7 @@
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -17061,13 +17069,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>61.3</v>
+        <v>61.1</v>
       </c>
       <c r="D2" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="E2" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="F2" t="n">
         <v>1.1</v>
@@ -17091,16 +17099,16 @@
         <v>32.6</v>
       </c>
       <c r="D3" t="n">
-        <v>44.6</v>
+        <v>44.4</v>
       </c>
       <c r="E3" t="n">
-        <v>18.7</v>
+        <v>19</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>91.90000000000001</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="4">
@@ -17115,19 +17123,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="D4" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="E4" t="n">
         <v>42.9</v>
       </c>
       <c r="F4" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="G4" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="5">
@@ -17145,16 +17153,16 @@
         <v>1.7</v>
       </c>
       <c r="D5" t="n">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="E5" t="n">
-        <v>27.3</v>
+        <v>26.9</v>
       </c>
       <c r="F5" t="n">
-        <v>58.9</v>
+        <v>59</v>
       </c>
       <c r="G5" t="n">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="6">
@@ -17172,16 +17180,16 @@
         <v>36.5</v>
       </c>
       <c r="D6" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="E6" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="G6" t="n">
-        <v>77.8</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="7">
@@ -17196,19 +17204,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="D7" t="n">
         <v>26.9</v>
       </c>
       <c r="E7" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="F7" t="n">
         <v>15.9</v>
       </c>
       <c r="G7" t="n">
-        <v>75.2</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="8">
@@ -17226,7 +17234,7 @@
         <v>15.7</v>
       </c>
       <c r="D8" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="E8" t="n">
         <v>27.1</v>
@@ -17235,7 +17243,7 @@
         <v>34.1</v>
       </c>
       <c r="G8" t="n">
-        <v>56</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="9">
@@ -17250,19 +17258,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="D9" t="n">
         <v>23.1</v>
       </c>
       <c r="E9" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="F9" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="G9" t="n">
-        <v>54.3</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="10">
@@ -17277,19 +17285,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="D10" t="n">
-        <v>28</v>
+        <v>27.8</v>
       </c>
       <c r="E10" t="n">
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
       <c r="F10" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="G10" t="n">
-        <v>86.40000000000001</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11">
@@ -17307,16 +17315,16 @@
         <v>34.6</v>
       </c>
       <c r="D11" t="n">
-        <v>32.6</v>
+        <v>32.8</v>
       </c>
       <c r="E11" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="F11" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="G11" t="n">
-        <v>83.59999999999999</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="12">
@@ -17337,13 +17345,13 @@
         <v>31.9</v>
       </c>
       <c r="E12" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="F12" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="G12" t="n">
-        <v>77.7</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="13">
@@ -17364,13 +17372,13 @@
         <v>7.5</v>
       </c>
       <c r="E13" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="F13" t="n">
-        <v>68.40000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="G13" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="14">
@@ -17385,16 +17393,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>57.1</v>
+        <v>57.3</v>
       </c>
       <c r="D14" t="n">
-        <v>28.4</v>
+        <v>28.2</v>
       </c>
       <c r="E14" t="n">
         <v>13.2</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G14" t="n">
         <v>97.40000000000001</v>
@@ -17412,19 +17420,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="D15" t="n">
-        <v>41.8</v>
+        <v>41.5</v>
       </c>
       <c r="E15" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G15" t="n">
-        <v>93.8</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="16">
@@ -17439,19 +17447,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="D16" t="n">
-        <v>16.5</v>
+        <v>16.8</v>
       </c>
       <c r="E16" t="n">
-        <v>39.9</v>
+        <v>39.5</v>
       </c>
       <c r="F16" t="n">
-        <v>39.7</v>
+        <v>40</v>
       </c>
       <c r="G16" t="n">
-        <v>45.3</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="17">
@@ -17466,19 +17474,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="E17" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="F17" t="n">
-        <v>55.9</v>
+        <v>55.5</v>
       </c>
       <c r="G17" t="n">
-        <v>33.1</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="18">
@@ -17493,19 +17501,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>59.3</v>
+        <v>63.7</v>
       </c>
       <c r="D18" t="n">
-        <v>27.9</v>
+        <v>23.5</v>
       </c>
       <c r="E18" t="n">
         <v>12.5</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G18" t="n">
-        <v>99.3</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -17516,23 +17524,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>38.6</v>
+        <v>46.8</v>
       </c>
       <c r="E19" t="n">
-        <v>27.8</v>
+        <v>19.8</v>
       </c>
       <c r="F19" t="n">
-        <v>7.6</v>
+        <v>1.4</v>
       </c>
       <c r="G19" t="n">
-        <v>84.3</v>
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -17543,23 +17551,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>14.3</v>
+        <v>3.8</v>
       </c>
       <c r="D20" t="n">
-        <v>29.2</v>
+        <v>25.5</v>
       </c>
       <c r="E20" t="n">
-        <v>41.9</v>
+        <v>53.6</v>
       </c>
       <c r="F20" t="n">
-        <v>14.6</v>
+        <v>17.1</v>
       </c>
       <c r="G20" t="n">
-        <v>70.09999999999999</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21">
@@ -17580,13 +17588,13 @@
         <v>4.3</v>
       </c>
       <c r="E21" t="n">
-        <v>17.8</v>
+        <v>14.1</v>
       </c>
       <c r="F21" t="n">
-        <v>77.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="G21" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="22">
@@ -17601,16 +17609,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="D22" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="E22" t="n">
         <v>20.4</v>
       </c>
       <c r="F22" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="G22" t="n">
         <v>82.8</v>
@@ -17628,19 +17636,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>31.4</v>
+        <v>31.1</v>
       </c>
       <c r="D23" t="n">
-        <v>32.9</v>
+        <v>33.2</v>
       </c>
       <c r="E23" t="n">
         <v>22.1</v>
       </c>
       <c r="F23" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="G23" t="n">
-        <v>80.5</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="24">
@@ -17655,10 +17663,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="D24" t="n">
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="E24" t="n">
         <v>29.1</v>
@@ -17667,7 +17675,7 @@
         <v>34.8</v>
       </c>
       <c r="G24" t="n">
-        <v>55.5</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="25">
@@ -17682,19 +17690,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>15.2</v>
+        <v>15.5</v>
       </c>
       <c r="D25" t="n">
-        <v>16.6</v>
+        <v>16.3</v>
       </c>
       <c r="E25" t="n">
-        <v>28.4</v>
+        <v>28.3</v>
       </c>
       <c r="F25" t="n">
-        <v>39.7</v>
+        <v>39.8</v>
       </c>
       <c r="G25" t="n">
-        <v>50.6</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="26">
@@ -17712,16 +17720,16 @@
         <v>36.5</v>
       </c>
       <c r="D26" t="n">
-        <v>27.6</v>
+        <v>27.4</v>
       </c>
       <c r="E26" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="F26" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="G26" t="n">
-        <v>79.7</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="27">
@@ -17736,19 +17744,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27.4</v>
+        <v>27.1</v>
       </c>
       <c r="D27" t="n">
-        <v>26.8</v>
+        <v>27.5</v>
       </c>
       <c r="E27" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="F27" t="n">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
       <c r="G27" t="n">
-        <v>71.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -17763,19 +17771,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="D28" t="n">
-        <v>26.6</v>
+        <v>26.2</v>
       </c>
       <c r="E28" t="n">
         <v>26.4</v>
       </c>
       <c r="F28" t="n">
-        <v>23.2</v>
+        <v>23.5</v>
       </c>
       <c r="G28" t="n">
-        <v>68.59999999999999</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="29">
@@ -17790,19 +17798,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="D29" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="E29" t="n">
-        <v>27.1</v>
+        <v>27.3</v>
       </c>
       <c r="F29" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="G29" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="30">
@@ -17817,19 +17825,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>62</v>
+        <v>61.9</v>
       </c>
       <c r="D30" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="E30" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G30" t="n">
-        <v>94.09999999999999</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -17844,19 +17852,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="D31" t="n">
-        <v>35.3</v>
+        <v>35.7</v>
       </c>
       <c r="E31" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="F31" t="n">
-        <v>16.9</v>
+        <v>16.7</v>
       </c>
       <c r="G31" t="n">
-        <v>74.2</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32">
@@ -17874,16 +17882,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="E32" t="n">
-        <v>32.5</v>
+        <v>32.9</v>
       </c>
       <c r="F32" t="n">
-        <v>37.1</v>
+        <v>36.9</v>
       </c>
       <c r="G32" t="n">
-        <v>48.7</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="33">
@@ -17898,19 +17906,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="D33" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="E33" t="n">
-        <v>31.6</v>
+        <v>31.2</v>
       </c>
       <c r="F33" t="n">
-        <v>42</v>
+        <v>42.3</v>
       </c>
       <c r="G33" t="n">
-        <v>44</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="34">
@@ -17925,13 +17933,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
       <c r="D34" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="E34" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="F34" t="n">
         <v>7.4</v>
@@ -17952,19 +17960,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>25.9</v>
+        <v>26.1</v>
       </c>
       <c r="D35" t="n">
-        <v>30.9</v>
+        <v>31.3</v>
       </c>
       <c r="E35" t="n">
-        <v>27</v>
+        <v>27.2</v>
       </c>
       <c r="F35" t="n">
-        <v>16.1</v>
+        <v>15.4</v>
       </c>
       <c r="G35" t="n">
-        <v>75.59999999999999</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -17979,19 +17987,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="D36" t="n">
-        <v>28.6</v>
+        <v>28.3</v>
       </c>
       <c r="E36" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="F36" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="G36" t="n">
-        <v>69.7</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="37">
@@ -18006,19 +18014,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="D37" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="E37" t="n">
-        <v>25.1</v>
+        <v>24.8</v>
       </c>
       <c r="F37" t="n">
-        <v>56.4</v>
+        <v>57.1</v>
       </c>
       <c r="G37" t="n">
-        <v>32.5</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="38">
@@ -18036,16 +18044,16 @@
         <v>55</v>
       </c>
       <c r="D38" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="E38" t="n">
         <v>13.5</v>
       </c>
       <c r="F38" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="G38" t="n">
-        <v>90.40000000000001</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -18066,13 +18074,13 @@
         <v>28</v>
       </c>
       <c r="E39" t="n">
-        <v>28.9</v>
+        <v>28.6</v>
       </c>
       <c r="F39" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="G39" t="n">
-        <v>64.59999999999999</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="40">
@@ -18093,13 +18101,13 @@
         <v>27.6</v>
       </c>
       <c r="E40" t="n">
-        <v>29</v>
+        <v>29.2</v>
       </c>
       <c r="F40" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="G40" t="n">
-        <v>63.5</v>
+        <v>63.2</v>
       </c>
     </row>
     <row r="41">
@@ -18117,16 +18125,16 @@
         <v>10</v>
       </c>
       <c r="D41" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="E41" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="F41" t="n">
-        <v>41.8</v>
+        <v>41.4</v>
       </c>
       <c r="G41" t="n">
-        <v>46.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="42">
@@ -18141,19 +18149,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>40.3</v>
+        <v>39.9</v>
       </c>
       <c r="D42" t="n">
         <v>31.5</v>
       </c>
       <c r="E42" t="n">
-        <v>19.1</v>
+        <v>19.5</v>
       </c>
       <c r="F42" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="G42" t="n">
-        <v>86</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="43">
@@ -18168,16 +18176,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>39.1</v>
+        <v>39.5</v>
       </c>
       <c r="D43" t="n">
         <v>31.7</v>
       </c>
       <c r="E43" t="n">
-        <v>19.8</v>
+        <v>19.4</v>
       </c>
       <c r="F43" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G43" t="n">
         <v>85.59999999999999</v>
@@ -18195,19 +18203,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="D44" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="E44" t="n">
         <v>34.2</v>
       </c>
       <c r="F44" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="G44" t="n">
-        <v>60.1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45">
@@ -18222,19 +18230,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="D45" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="n">
-        <v>27</v>
+        <v>26.8</v>
       </c>
       <c r="F45" t="n">
-        <v>54</v>
+        <v>54.3</v>
       </c>
       <c r="G45" t="n">
-        <v>34</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="46">
@@ -18249,19 +18257,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>45.7</v>
+        <v>45.9</v>
       </c>
       <c r="D46" t="n">
-        <v>28.3</v>
+        <v>28.5</v>
       </c>
       <c r="E46" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="F46" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="G46" t="n">
-        <v>87</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -18276,19 +18284,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="D47" t="n">
-        <v>30.8</v>
+        <v>30.5</v>
       </c>
       <c r="E47" t="n">
-        <v>24.2</v>
+        <v>24.7</v>
       </c>
       <c r="F47" t="n">
-        <v>15.7</v>
+        <v>15.4</v>
       </c>
       <c r="G47" t="n">
-        <v>77.2</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -18306,16 +18314,16 @@
         <v>16.8</v>
       </c>
       <c r="D48" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="E48" t="n">
-        <v>31</v>
+        <v>30.8</v>
       </c>
       <c r="F48" t="n">
         <v>27.2</v>
       </c>
       <c r="G48" t="n">
-        <v>62</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="49">
@@ -18330,19 +18338,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="D49" t="n">
         <v>15.8</v>
       </c>
       <c r="E49" t="n">
-        <v>27.7</v>
+        <v>27.4</v>
       </c>
       <c r="F49" t="n">
-        <v>48.2</v>
+        <v>48.8</v>
       </c>
       <c r="G49" t="n">
-        <v>40.4</v>
+        <v>39.6</v>
       </c>
     </row>
   </sheetData>
@@ -18417,19 +18425,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>94.09999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>44.2</v>
+        <v>44.1</v>
       </c>
       <c r="E2" t="n">
-        <v>31.8</v>
+        <v>31.2</v>
       </c>
       <c r="F2" t="n">
-        <v>21.3</v>
+        <v>20.7</v>
       </c>
       <c r="G2" t="n">
-        <v>13.7</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="3">
@@ -18444,19 +18452,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>90.40000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>40.2</v>
+        <v>40.4</v>
       </c>
       <c r="E3" t="n">
         <v>27.1</v>
       </c>
       <c r="F3" t="n">
-        <v>17.1</v>
+        <v>17.4</v>
       </c>
       <c r="G3" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="4">
@@ -18474,16 +18482,16 @@
         <v>88.59999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="E4" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="F4" t="n">
-        <v>13.7</v>
+        <v>13.4</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5">
@@ -18498,19 +18506,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>87</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>32.6</v>
+        <v>32.4</v>
       </c>
       <c r="E5" t="n">
-        <v>18.9</v>
+        <v>19.4</v>
       </c>
       <c r="F5" t="n">
-        <v>10.7</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="6">
@@ -18525,19 +18533,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>99.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>34.4</v>
+        <v>34.7</v>
       </c>
       <c r="E6" t="n">
-        <v>20.3</v>
+        <v>20.8</v>
       </c>
       <c r="F6" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="7">
@@ -18552,19 +18560,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>86</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="E7" t="n">
-        <v>16.4</v>
+        <v>16.7</v>
       </c>
       <c r="F7" t="n">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="8">
@@ -18585,13 +18593,13 @@
         <v>28.8</v>
       </c>
       <c r="E8" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="F8" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="9">
@@ -18606,40 +18614,40 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>83.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="D9" t="n">
-        <v>27.6</v>
+        <v>27.9</v>
       </c>
       <c r="E9" t="n">
         <v>14.9</v>
       </c>
       <c r="F9" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="G9" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>84.3</v>
+        <v>82.8</v>
       </c>
       <c r="D10" t="n">
-        <v>24.8</v>
+        <v>26</v>
       </c>
       <c r="E10" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="F10" t="n">
         <v>6.7</v>
@@ -18651,160 +18659,160 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>82.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>25.7</v>
+        <v>22.1</v>
       </c>
       <c r="E11" t="n">
-        <v>13</v>
+        <v>11.4</v>
       </c>
       <c r="F11" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="G11" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>97.5</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>26.2</v>
+        <v>20.4</v>
       </c>
       <c r="E12" t="n">
-        <v>12.3</v>
+        <v>10.4</v>
       </c>
       <c r="F12" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>77.2</v>
+        <v>97.5</v>
       </c>
       <c r="D13" t="n">
-        <v>21.1</v>
+        <v>26.7</v>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>12.4</v>
       </c>
       <c r="F13" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>75.59999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="D14" t="n">
-        <v>21.1</v>
+        <v>22.4</v>
       </c>
       <c r="E14" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="F14" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>80.5</v>
+        <v>79.3</v>
       </c>
       <c r="D15" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="E15" t="n">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="F15" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>79.7</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>22.5</v>
+        <v>18.7</v>
       </c>
       <c r="E16" t="n">
-        <v>10.1</v>
+        <v>9.4</v>
       </c>
       <c r="F16" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="G16" t="n">
         <v>2.1</v>
@@ -18822,16 +18830,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>74.2</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
-        <v>17.8</v>
+        <v>17.6</v>
       </c>
       <c r="E17" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="G17" t="n">
         <v>2</v>
@@ -18852,13 +18860,13 @@
         <v>97.40000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="E18" t="n">
         <v>10.4</v>
       </c>
       <c r="F18" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="G18" t="n">
         <v>2</v>
@@ -18876,16 +18884,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>77.7</v>
+        <v>77.8</v>
       </c>
       <c r="D19" t="n">
-        <v>19.8</v>
+        <v>20.1</v>
       </c>
       <c r="E19" t="n">
         <v>9.4</v>
       </c>
       <c r="F19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G19" t="n">
         <v>1.9</v>
@@ -18903,13 +18911,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>93.8</v>
+        <v>93.3</v>
       </c>
       <c r="D20" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="E20" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="F20" t="n">
         <v>4.2</v>
@@ -18930,16 +18938,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>75.2</v>
+        <v>75.3</v>
       </c>
       <c r="D21" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="E21" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="F21" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="G21" t="n">
         <v>1.5</v>
@@ -18957,13 +18965,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>69.7</v>
+        <v>69.5</v>
       </c>
       <c r="D22" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E22" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F22" t="n">
         <v>3.6</v>
@@ -18975,163 +18983,163 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>63.5</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>13.1</v>
+        <v>18.8</v>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="F23" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="G23" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>71.90000000000001</v>
+        <v>64.2</v>
       </c>
       <c r="D24" t="n">
-        <v>16.5</v>
+        <v>13.7</v>
       </c>
       <c r="E24" t="n">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G24" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>91.90000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="D25" t="n">
-        <v>19.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="n">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G25" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>64.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>13.8</v>
+        <v>16.3</v>
       </c>
       <c r="E26" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="F26" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>86.40000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="D27" t="n">
-        <v>17</v>
+        <v>19.3</v>
       </c>
       <c r="E27" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="F27" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>70.09999999999999</v>
+        <v>44.9</v>
       </c>
       <c r="D28" t="n">
-        <v>14.1</v>
+        <v>10.2</v>
       </c>
       <c r="E28" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="F28" t="n">
         <v>2.4</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="29">
@@ -19146,16 +19154,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>77.8</v>
+        <v>77.2</v>
       </c>
       <c r="D29" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="E29" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="F29" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -19164,25 +19172,25 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>45.3</v>
+        <v>86</v>
       </c>
       <c r="D30" t="n">
-        <v>10.3</v>
+        <v>17.4</v>
       </c>
       <c r="E30" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="F30" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
@@ -19200,16 +19208,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>68.59999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="D31" t="n">
-        <v>14.2</v>
+        <v>13.8</v>
       </c>
       <c r="E31" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="F31" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G31" t="n">
         <v>0.9</v>
@@ -19227,10 +19235,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>62</v>
+        <v>61.8</v>
       </c>
       <c r="D32" t="n">
-        <v>11.3</v>
+        <v>11</v>
       </c>
       <c r="E32" t="n">
         <v>4.7</v>
@@ -19254,13 +19262,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>60.1</v>
+        <v>60</v>
       </c>
       <c r="D33" t="n">
         <v>10</v>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="F33" t="n">
         <v>1.6</v>
@@ -19281,10 +19289,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>33.1</v>
+        <v>33.5</v>
       </c>
       <c r="D34" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="E34" t="n">
         <v>2.6</v>
@@ -19293,58 +19301,58 @@
         <v>1.1</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>46.7</v>
+        <v>55.3</v>
       </c>
       <c r="D35" t="n">
-        <v>6.9</v>
+        <v>9.5</v>
       </c>
       <c r="E35" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="G35" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>55.5</v>
+        <v>47.9</v>
       </c>
       <c r="D36" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="E36" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="F36" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G36" t="n">
         <v>0.4</v>
@@ -19353,28 +19361,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>48</v>
+        <v>48.9</v>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="E37" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="F37" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="38">
@@ -19389,16 +19397,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>50.6</v>
+        <v>50.1</v>
       </c>
       <c r="D38" t="n">
         <v>7.6</v>
       </c>
       <c r="E38" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
         <v>0.3</v>
@@ -19407,25 +19415,25 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>48.7</v>
+        <v>46.5</v>
       </c>
       <c r="D39" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="E39" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
         <v>0.3</v>
@@ -19443,7 +19451,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>44</v>
+        <v>43.8</v>
       </c>
       <c r="D40" t="n">
         <v>5.2</v>
@@ -19452,7 +19460,7 @@
         <v>1.9</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G40" t="n">
         <v>0.2</v>
@@ -19470,13 +19478,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="D41" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="F41" t="n">
         <v>0.6</v>
@@ -19488,46 +19496,46 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>56</v>
+        <v>29.6</v>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="E42" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="F42" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G42" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>29.8</v>
+        <v>31.6</v>
       </c>
       <c r="D43" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="E43" t="n">
         <v>1</v>
@@ -19542,25 +19550,25 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>32.5</v>
+        <v>33.6</v>
       </c>
       <c r="D44" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G44" t="n">
         <v>0.1</v>
@@ -19569,25 +19577,25 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>34</v>
+        <v>54.4</v>
       </c>
       <c r="D45" t="n">
-        <v>2.9</v>
+        <v>5.4</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G45" t="n">
         <v>0.1</v>
@@ -19596,25 +19604,25 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>54.3</v>
+        <v>24.3</v>
       </c>
       <c r="D46" t="n">
-        <v>5.4</v>
+        <v>2.8</v>
       </c>
       <c r="E46" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G46" t="n">
         <v>0.1</v>
@@ -19623,25 +19631,25 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>24.4</v>
+        <v>39.6</v>
       </c>
       <c r="D47" t="n">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="F47" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="G47" t="n">
         <v>0.1</v>
@@ -19650,22 +19658,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>40.4</v>
+        <v>55.9</v>
       </c>
       <c r="D48" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="E48" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="F48" t="n">
         <v>0.5</v>
@@ -19686,7 +19694,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="D49" t="n">
         <v>0.8</v>
@@ -19695,7 +19703,7 @@
         <v>0.2</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -19837,13 +19845,13 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>13.7</v>
+        <v>13.4</v>
       </c>
       <c r="L2" t="n">
-        <v>21.3</v>
+        <v>20.7</v>
       </c>
       <c r="M2" t="n">
-        <v>94.09999999999999</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -19886,13 +19894,13 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="L3" t="n">
-        <v>17.1</v>
+        <v>17.4</v>
       </c>
       <c r="M3" t="n">
-        <v>90.40000000000001</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -19935,10 +19943,10 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="L4" t="n">
-        <v>13.7</v>
+        <v>13.4</v>
       </c>
       <c r="M4" t="n">
         <v>88.59999999999999</v>
@@ -19984,13 +19992,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="L5" t="n">
-        <v>10.7</v>
+        <v>11</v>
       </c>
       <c r="M5" t="n">
-        <v>87</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -20033,13 +20041,13 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="L6" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="M6" t="n">
-        <v>99.3</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -20082,13 +20090,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L7" t="n">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>86</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -20131,10 +20139,10 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M8" t="n">
         <v>85.59999999999999</v>
@@ -20180,13 +20188,13 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="M9" t="n">
-        <v>83.59999999999999</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="10">
@@ -20229,10 +20237,10 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="L10" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="M10" t="n">
         <v>82.8</v>
@@ -20258,10 +20266,10 @@
         <v>1938</v>
       </c>
       <c r="E11" t="n">
-        <v>1938</v>
+        <v>1916</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -20273,16 +20281,16 @@
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="L11" t="n">
-        <v>6.7</v>
+        <v>4.6</v>
       </c>
       <c r="M11" t="n">
-        <v>84.3</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12">
@@ -20325,13 +20333,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="L12" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="M12" t="n">
-        <v>75.59999999999999</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -20372,13 +20380,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="L13" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="M13" t="n">
-        <v>77.2</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -20419,13 +20427,13 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="L14" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="M14" t="n">
-        <v>80.5</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="15">
@@ -20468,10 +20476,10 @@
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="L15" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M15" t="n">
         <v>97.5</v>
@@ -20517,13 +20525,13 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="L16" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>79.7</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="17">
@@ -20569,10 +20577,10 @@
         <v>2</v>
       </c>
       <c r="L17" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="M17" t="n">
-        <v>74.2</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -20616,10 +20624,10 @@
         <v>1.9</v>
       </c>
       <c r="L18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="M18" t="n">
-        <v>77.7</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="19">
@@ -20658,13 +20666,13 @@
         <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="L19" t="n">
         <v>2.4</v>
       </c>
       <c r="M19" t="n">
-        <v>45.3</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="20">
@@ -20711,7 +20719,7 @@
         <v>3.6</v>
       </c>
       <c r="M20" t="n">
-        <v>69.7</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="21">
@@ -20755,7 +20763,7 @@
         <v>2</v>
       </c>
       <c r="L21" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="M21" t="n">
         <v>97.40000000000001</v>
@@ -20802,10 +20810,10 @@
         <v>1.5</v>
       </c>
       <c r="L22" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="M22" t="n">
-        <v>75.2</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="23">
@@ -20852,7 +20860,7 @@
         <v>4.2</v>
       </c>
       <c r="M23" t="n">
-        <v>93.8</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="24">
@@ -20893,13 +20901,13 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="L24" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="M24" t="n">
-        <v>64.59999999999999</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="25">
@@ -20943,36 +20951,36 @@
         <v>1.2</v>
       </c>
       <c r="L25" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="M25" t="n">
-        <v>63.5</v>
+        <v>63.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AFC</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1824</v>
+        <v>1806</v>
       </c>
       <c r="E26" t="n">
-        <v>1824</v>
+        <v>1828</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -20980,46 +20988,46 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="L26" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="M26" t="n">
-        <v>71.90000000000001</v>
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UEFA</t>
+          <t>AFC</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1805</v>
+        <v>1824</v>
       </c>
       <c r="E27" t="n">
-        <v>1815</v>
+        <v>1824</v>
       </c>
       <c r="F27" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -21027,46 +21035,46 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="L27" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="M27" t="n">
-        <v>86.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>UEFA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="E28" t="n">
-        <v>1806</v>
+        <v>1815</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -21074,20 +21082,20 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="M28" t="n">
-        <v>70.09999999999999</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29">
@@ -21131,10 +21139,10 @@
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="M29" t="n">
-        <v>77.8</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="30">
@@ -21177,13 +21185,13 @@
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="L30" t="n">
         <v>3</v>
       </c>
       <c r="M30" t="n">
-        <v>91.90000000000001</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="31">
@@ -21227,10 +21235,10 @@
         <v>0.9</v>
       </c>
       <c r="L31" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="M31" t="n">
-        <v>68.59999999999999</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="32">
@@ -21277,7 +21285,7 @@
         <v>1.9</v>
       </c>
       <c r="M32" t="n">
-        <v>62</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="33">
@@ -21318,13 +21326,13 @@
         <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="L33" t="n">
         <v>1.1</v>
       </c>
       <c r="M33" t="n">
-        <v>33.1</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="34">
@@ -21371,7 +21379,7 @@
         <v>1.6</v>
       </c>
       <c r="M34" t="n">
-        <v>60.1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35">
@@ -21418,7 +21426,7 @@
         <v>1.2</v>
       </c>
       <c r="M35" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="36">
@@ -21459,13 +21467,13 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="L36" t="n">
         <v>1.3</v>
       </c>
       <c r="M36" t="n">
-        <v>55.5</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="37">
@@ -21506,13 +21514,13 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="L37" t="n">
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>46.7</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="38">
@@ -21556,10 +21564,10 @@
         <v>0.3</v>
       </c>
       <c r="L38" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="M38" t="n">
-        <v>48.7</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="39">
@@ -21601,10 +21609,10 @@
         <v>0.3</v>
       </c>
       <c r="L39" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>50.6</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="40">
@@ -21648,10 +21656,10 @@
         <v>0.2</v>
       </c>
       <c r="L40" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="M40" t="n">
-        <v>44</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="41">
@@ -21698,7 +21706,7 @@
         <v>0.6</v>
       </c>
       <c r="M41" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="42">
@@ -21745,7 +21753,7 @@
         <v>0.5</v>
       </c>
       <c r="M42" t="n">
-        <v>40.4</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="43">
@@ -21792,7 +21800,7 @@
         <v>0.3</v>
       </c>
       <c r="M43" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="44">
@@ -21833,13 +21841,13 @@
         <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L44" t="n">
         <v>0.5</v>
       </c>
       <c r="M44" t="n">
-        <v>56</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="45">
@@ -21888,7 +21896,7 @@
         <v>0.3</v>
       </c>
       <c r="M45" t="n">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="46">
@@ -21933,7 +21941,7 @@
         <v>0.3</v>
       </c>
       <c r="M46" t="n">
-        <v>32.5</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="47">
@@ -21978,7 +21986,7 @@
         <v>0.4</v>
       </c>
       <c r="M47" t="n">
-        <v>54.3</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="48">
@@ -22020,10 +22028,10 @@
         <v>0.1</v>
       </c>
       <c r="L48" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="M48" t="n">
-        <v>34</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="49">
@@ -22067,10 +22075,10 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M49" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
     </row>
   </sheetData>
@@ -22084,7 +22092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -22481,37 +22489,74 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Ivory Coast 1-0 Ecuador</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.2738762749141564</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2691027275042267</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.4570209975816171</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.3680619281815189</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Netherlands 2-2 Japan</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E12" t="n">
         <v>0.3911107030923358</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F12" t="n">
         <v>0.2764517043235625</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G12" t="n">
         <v>0.3324375925841019</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H12" t="n">
         <v>0.1317411675182472</v>
       </c>
-      <c r="I11" t="b">
+      <c r="I12" t="b">
         <v>0</v>
       </c>
     </row>

--- a/outputs/world_cup_2026_recommendations.xlsx
+++ b/outputs/world_cup_2026_recommendations.xlsx
@@ -549,7 +549,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>• Matches scored: 11   Outcome hit-rate: 45%   Mean RPS: 0.197  (good tournament forecasts ~0.17-0.18)</t>
+          <t>• Matches scored: 12   Outcome hit-rate: 42%   Mean RPS: 0.205  (good tournament forecasts ~0.17-0.18)</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>• Spain 13%,  Argentina 11%,  France 8%</t>
+          <t>• Spain 14%,  Argentina 11%,  France 8%</t>
         </is>
       </c>
     </row>
@@ -1681,35 +1681,35 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>final</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>33.8</v>
+        <v>44.3</v>
       </c>
       <c r="K13" t="n">
-        <v>27.7</v>
+        <v>25.4</v>
       </c>
       <c r="L13" t="n">
-        <v>38.5</v>
+        <v>30.4</v>
       </c>
       <c r="M13" t="n">
-        <v>1.23</v>
+        <v>1.61</v>
       </c>
       <c r="N13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1717,11 +1717,15 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>5-1</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 37)</t>
+          <t>actual 5-1; model pick 2-1 (outcome hit)</t>
         </is>
       </c>
     </row>
@@ -3452,11 +3456,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -3464,19 +3468,19 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>54.5</v>
+        <v>50.6</v>
       </c>
       <c r="K36" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="L36" t="n">
         <v>24.6</v>
       </c>
-      <c r="L36" t="n">
-        <v>20.9</v>
-      </c>
       <c r="M36" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="N36" t="n">
-        <v>0.99</v>
+        <v>1.13</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -3492,7 +3496,7 @@
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 50)</t>
+          <t>maximises expected pool points (EV 46)</t>
         </is>
       </c>
     </row>
@@ -3529,11 +3533,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -3541,19 +3545,19 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>25</v>
+        <v>21.3</v>
       </c>
       <c r="K37" t="n">
-        <v>25.9</v>
+        <v>23.7</v>
       </c>
       <c r="L37" t="n">
-        <v>49</v>
+        <v>54.9</v>
       </c>
       <c r="M37" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N37" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -3569,7 +3573,7 @@
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 46)</t>
+          <t>maximises expected pool points (EV 49)</t>
         </is>
       </c>
     </row>
@@ -5300,11 +5304,11 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -5312,19 +5316,19 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>51.6</v>
+        <v>47.6</v>
       </c>
       <c r="K60" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="L60" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M60" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="N60" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -5340,7 +5344,7 @@
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 48)</t>
+          <t>maximises expected pool points (EV 44)</t>
         </is>
       </c>
     </row>
@@ -5377,11 +5381,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -5389,19 +5393,19 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>22.8</v>
+        <v>19.2</v>
       </c>
       <c r="K61" t="n">
-        <v>25.3</v>
+        <v>22.9</v>
       </c>
       <c r="L61" t="n">
-        <v>51.9</v>
+        <v>57.9</v>
       </c>
       <c r="M61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N61" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -5417,7 +5421,7 @@
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 48)</t>
+          <t>maximises expected pool points (EV 52)</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6373,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -6378,7 +6382,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -6386,19 +6390,19 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>35.9</v>
+        <v>32.6</v>
       </c>
       <c r="K74" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="L74" t="n">
-        <v>36.3</v>
+        <v>39.7</v>
       </c>
       <c r="M74" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="N74" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -6416,7 +6420,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>most-likely pairing (12%); Canada to advance</t>
+          <t>most-likely pairing (12%); Switzerland to advance</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6518,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6528,7 +6532,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -6536,19 +6540,19 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>34.3</v>
+        <v>23</v>
       </c>
       <c r="K76" t="n">
-        <v>27.4</v>
+        <v>24.9</v>
       </c>
       <c r="L76" t="n">
-        <v>38.2</v>
+        <v>52.2</v>
       </c>
       <c r="M76" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="N76" t="n">
-        <v>1.34</v>
+        <v>1.71</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -6562,7 +6566,7 @@
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="n">
-        <v>11.7</v>
+        <v>12.2</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -6637,7 +6641,7 @@
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="n">
-        <v>11.9</v>
+        <v>12.3</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -6712,7 +6716,7 @@
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -6787,11 +6791,11 @@
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="n">
-        <v>14.7</v>
+        <v>14.4</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>most-likely pairing (15%); Norway to advance</t>
+          <t>most-likely pairing (14%); Norway to advance</t>
         </is>
       </c>
     </row>
@@ -6862,7 +6866,7 @@
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -6937,7 +6941,7 @@
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -7012,11 +7016,11 @@
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="n">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>most-likely pairing (7%); United States to advance</t>
+          <t>most-likely pairing (8%); United States to advance</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7091,7 @@
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -7114,7 +7118,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -7128,7 +7132,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -7136,19 +7140,19 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>41.6</v>
+        <v>41.1</v>
       </c>
       <c r="K84" t="n">
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
       <c r="L84" t="n">
-        <v>30.9</v>
+        <v>31.4</v>
       </c>
       <c r="M84" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="N84" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -7166,7 +7170,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>most-likely pairing (10%); Portugal to advance</t>
+          <t>most-likely pairing (10%); Colombia to advance</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7198,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -7203,7 +7207,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -7211,19 +7215,19 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>59.7</v>
+        <v>59.1</v>
       </c>
       <c r="K85" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="L85" t="n">
-        <v>17.1</v>
+        <v>17.4</v>
       </c>
       <c r="M85" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="N85" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -7237,7 +7241,7 @@
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -7269,12 +7273,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H86" t="n">
@@ -7286,23 +7290,23 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>36.7</v>
+        <v>34.7</v>
       </c>
       <c r="K86" t="n">
         <v>27.9</v>
       </c>
       <c r="L86" t="n">
-        <v>35.3</v>
+        <v>37.4</v>
       </c>
       <c r="M86" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="N86" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -7312,11 +7316,11 @@
       </c>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>most-likely pairing (4%); Canada to advance</t>
+          <t>most-likely pairing (4%); Iran to advance</t>
         </is>
       </c>
     </row>
@@ -7387,11 +7391,11 @@
       </c>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="n">
-        <v>19.7</v>
+        <v>19.3</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>most-likely pairing (20%); Argentina to advance</t>
+          <t>most-likely pairing (19%); Argentina to advance</t>
         </is>
       </c>
     </row>
@@ -7494,16 +7498,16 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -7511,23 +7515,23 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>37.9</v>
+        <v>33.1</v>
       </c>
       <c r="K89" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="L89" t="n">
-        <v>34.2</v>
+        <v>39.1</v>
       </c>
       <c r="M89" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="N89" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -7537,11 +7541,11 @@
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>most-likely pairing (12%); Australia to advance</t>
+          <t>most-likely pairing (12%); Belgium to advance</t>
         </is>
       </c>
     </row>
@@ -7612,7 +7616,7 @@
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -7687,7 +7691,7 @@
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -7762,7 +7766,7 @@
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -7837,7 +7841,7 @@
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -7864,7 +7868,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -7878,7 +7882,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -7886,19 +7890,19 @@
         </is>
       </c>
       <c r="J94" t="n">
-        <v>25.2</v>
+        <v>24.8</v>
       </c>
       <c r="K94" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="L94" t="n">
-        <v>48.4</v>
+        <v>48.9</v>
       </c>
       <c r="M94" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N94" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -7912,7 +7916,7 @@
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -7987,7 +7991,7 @@
       </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -8062,7 +8066,7 @@
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -8137,7 +8141,7 @@
       </c>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -8212,7 +8216,7 @@
       </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -8287,11 +8291,11 @@
       </c>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>most-likely pairing (6%); Spain to advance</t>
+          <t>most-likely pairing (5%); Spain to advance</t>
         </is>
       </c>
     </row>
@@ -8362,7 +8366,7 @@
       </c>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -8394,7 +8398,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -8411,19 +8415,19 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>45.8</v>
+        <v>45.3</v>
       </c>
       <c r="K101" t="n">
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="L101" t="n">
-        <v>27.3</v>
+        <v>27.8</v>
       </c>
       <c r="M101" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="N101" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -8437,7 +8441,7 @@
       </c>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -8512,7 +8516,7 @@
       </c>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -8587,7 +8591,7 @@
       </c>
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -8662,7 +8666,7 @@
       </c>
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -8737,7 +8741,7 @@
       </c>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -9801,35 +9805,35 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>final</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>33.8</v>
+        <v>44.3</v>
       </c>
       <c r="K13" t="n">
-        <v>27.7</v>
+        <v>25.4</v>
       </c>
       <c r="L13" t="n">
-        <v>38.5</v>
+        <v>30.4</v>
       </c>
       <c r="M13" t="n">
-        <v>1.23</v>
+        <v>1.61</v>
       </c>
       <c r="N13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -9837,11 +9841,15 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>5-1</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 37)</t>
+          <t>actual 5-1; model pick 2-1 (outcome hit)</t>
         </is>
       </c>
     </row>
@@ -11572,11 +11580,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -11584,19 +11592,19 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>54.5</v>
+        <v>50.6</v>
       </c>
       <c r="K36" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="L36" t="n">
         <v>24.6</v>
       </c>
-      <c r="L36" t="n">
-        <v>20.9</v>
-      </c>
       <c r="M36" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="N36" t="n">
-        <v>0.99</v>
+        <v>1.13</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -11612,7 +11620,7 @@
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 50)</t>
+          <t>maximises expected pool points (EV 46)</t>
         </is>
       </c>
     </row>
@@ -11649,11 +11657,11 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -11661,19 +11669,19 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>25</v>
+        <v>21.3</v>
       </c>
       <c r="K37" t="n">
-        <v>25.9</v>
+        <v>23.7</v>
       </c>
       <c r="L37" t="n">
-        <v>49</v>
+        <v>54.9</v>
       </c>
       <c r="M37" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N37" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -11689,7 +11697,7 @@
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 46)</t>
+          <t>maximises expected pool points (EV 49)</t>
         </is>
       </c>
     </row>
@@ -13420,11 +13428,11 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -13432,19 +13440,19 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>51.6</v>
+        <v>47.6</v>
       </c>
       <c r="K60" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="L60" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M60" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="N60" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -13460,7 +13468,7 @@
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 48)</t>
+          <t>maximises expected pool points (EV 44)</t>
         </is>
       </c>
     </row>
@@ -13497,11 +13505,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -13509,19 +13517,19 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>22.8</v>
+        <v>19.2</v>
       </c>
       <c r="K61" t="n">
-        <v>25.3</v>
+        <v>22.9</v>
       </c>
       <c r="L61" t="n">
-        <v>51.9</v>
+        <v>57.9</v>
       </c>
       <c r="M61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N61" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -13537,7 +13545,7 @@
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 48)</t>
+          <t>maximises expected pool points (EV 52)</t>
         </is>
       </c>
     </row>
@@ -14621,7 +14629,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -14630,7 +14638,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -14638,19 +14646,19 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>35.9</v>
+        <v>32.6</v>
       </c>
       <c r="K2" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="L2" t="n">
-        <v>36.3</v>
+        <v>39.7</v>
       </c>
       <c r="M2" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="N2" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -14668,7 +14676,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>most-likely pairing (12%); Canada to advance</t>
+          <t>most-likely pairing (12%); Switzerland to advance</t>
         </is>
       </c>
     </row>
@@ -14766,7 +14774,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -14780,7 +14788,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -14788,19 +14796,19 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>34.3</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>27.4</v>
+        <v>24.9</v>
       </c>
       <c r="L4" t="n">
-        <v>38.2</v>
+        <v>52.2</v>
       </c>
       <c r="M4" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>1.34</v>
+        <v>1.71</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -14814,7 +14822,7 @@
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>11.7</v>
+        <v>12.2</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -14889,7 +14897,7 @@
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>11.9</v>
+        <v>12.3</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -14964,7 +14972,7 @@
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -15039,11 +15047,11 @@
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>14.7</v>
+        <v>14.4</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>most-likely pairing (15%); Norway to advance</t>
+          <t>most-likely pairing (14%); Norway to advance</t>
         </is>
       </c>
     </row>
@@ -15114,7 +15122,7 @@
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -15189,7 +15197,7 @@
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -15264,11 +15272,11 @@
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>most-likely pairing (7%); United States to advance</t>
+          <t>most-likely pairing (8%); United States to advance</t>
         </is>
       </c>
     </row>
@@ -15339,7 +15347,7 @@
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -15366,7 +15374,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -15380,7 +15388,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -15388,19 +15396,19 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>41.6</v>
+        <v>41.1</v>
       </c>
       <c r="K12" t="n">
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
       <c r="L12" t="n">
-        <v>30.9</v>
+        <v>31.4</v>
       </c>
       <c r="M12" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="N12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -15418,7 +15426,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>most-likely pairing (10%); Portugal to advance</t>
+          <t>most-likely pairing (10%); Colombia to advance</t>
         </is>
       </c>
     </row>
@@ -15446,7 +15454,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -15455,7 +15463,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -15463,19 +15471,19 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>59.7</v>
+        <v>59.1</v>
       </c>
       <c r="K13" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="L13" t="n">
-        <v>17.1</v>
+        <v>17.4</v>
       </c>
       <c r="M13" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="N13" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -15489,7 +15497,7 @@
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -15521,12 +15529,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -15538,23 +15546,23 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>36.7</v>
+        <v>34.7</v>
       </c>
       <c r="K14" t="n">
         <v>27.9</v>
       </c>
       <c r="L14" t="n">
-        <v>35.3</v>
+        <v>37.4</v>
       </c>
       <c r="M14" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="N14" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -15564,11 +15572,11 @@
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>most-likely pairing (4%); Canada to advance</t>
+          <t>most-likely pairing (4%); Iran to advance</t>
         </is>
       </c>
     </row>
@@ -15639,11 +15647,11 @@
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
-        <v>19.7</v>
+        <v>19.3</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>most-likely pairing (20%); Argentina to advance</t>
+          <t>most-likely pairing (19%); Argentina to advance</t>
         </is>
       </c>
     </row>
@@ -15746,16 +15754,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -15763,23 +15771,23 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>37.9</v>
+        <v>33.1</v>
       </c>
       <c r="K17" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="L17" t="n">
-        <v>34.2</v>
+        <v>39.1</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="N17" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -15789,11 +15797,11 @@
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>most-likely pairing (12%); Australia to advance</t>
+          <t>most-likely pairing (12%); Belgium to advance</t>
         </is>
       </c>
     </row>
@@ -15864,7 +15872,7 @@
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -15939,7 +15947,7 @@
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -16014,7 +16022,7 @@
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -16089,7 +16097,7 @@
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -16116,7 +16124,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -16130,7 +16138,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -16138,19 +16146,19 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>25.2</v>
+        <v>24.8</v>
       </c>
       <c r="K22" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="L22" t="n">
-        <v>48.4</v>
+        <v>48.9</v>
       </c>
       <c r="M22" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N22" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -16164,7 +16172,7 @@
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -16239,7 +16247,7 @@
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -16314,7 +16322,7 @@
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -16389,7 +16397,7 @@
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -16464,7 +16472,7 @@
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -16539,11 +16547,11 @@
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>most-likely pairing (6%); Spain to advance</t>
+          <t>most-likely pairing (5%); Spain to advance</t>
         </is>
       </c>
     </row>
@@ -16614,7 +16622,7 @@
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -16646,7 +16654,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -16663,19 +16671,19 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>45.8</v>
+        <v>45.3</v>
       </c>
       <c r="K29" t="n">
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="L29" t="n">
-        <v>27.3</v>
+        <v>27.8</v>
       </c>
       <c r="M29" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="N29" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -16689,7 +16697,7 @@
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -16764,7 +16772,7 @@
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -16839,7 +16847,7 @@
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -16914,7 +16922,7 @@
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -16989,7 +16997,7 @@
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -17069,19 +17077,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>61.1</v>
+        <v>61.9</v>
       </c>
       <c r="D2" t="n">
-        <v>26.6</v>
+        <v>26.2</v>
       </c>
       <c r="E2" t="n">
-        <v>11.2</v>
+        <v>10.7</v>
       </c>
       <c r="F2" t="n">
         <v>1.1</v>
       </c>
       <c r="G2" t="n">
-        <v>97.5</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -17096,19 +17104,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>32.6</v>
+        <v>32</v>
       </c>
       <c r="D3" t="n">
-        <v>44.4</v>
+        <v>44.8</v>
       </c>
       <c r="E3" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>91.8</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="4">
@@ -17123,19 +17131,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="D4" t="n">
-        <v>16.6</v>
+        <v>16.3</v>
       </c>
       <c r="E4" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="F4" t="n">
-        <v>35.9</v>
+        <v>36.5</v>
       </c>
       <c r="G4" t="n">
-        <v>47.9</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="5">
@@ -17153,16 +17161,16 @@
         <v>1.7</v>
       </c>
       <c r="D5" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="E5" t="n">
-        <v>26.9</v>
+        <v>27.3</v>
       </c>
       <c r="F5" t="n">
-        <v>59</v>
+        <v>58.4</v>
       </c>
       <c r="G5" t="n">
-        <v>29.6</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="6">
@@ -17177,19 +17185,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36.5</v>
+        <v>36.9</v>
       </c>
       <c r="D6" t="n">
-        <v>26.8</v>
+        <v>26.6</v>
       </c>
       <c r="E6" t="n">
         <v>22.5</v>
       </c>
       <c r="F6" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="G6" t="n">
-        <v>77.2</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="7">
@@ -17204,19 +17212,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>33.3</v>
+        <v>33.1</v>
       </c>
       <c r="D7" t="n">
-        <v>26.9</v>
+        <v>27.1</v>
       </c>
       <c r="E7" t="n">
-        <v>23.9</v>
+        <v>23.5</v>
       </c>
       <c r="F7" t="n">
-        <v>15.9</v>
+        <v>16.3</v>
       </c>
       <c r="G7" t="n">
-        <v>75.3</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -17231,19 +17239,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="D8" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="E8" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="F8" t="n">
-        <v>34.1</v>
+        <v>33.8</v>
       </c>
       <c r="G8" t="n">
-        <v>55.9</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="9">
@@ -17258,19 +17266,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="D9" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="E9" t="n">
-        <v>26.5</v>
+        <v>26.8</v>
       </c>
       <c r="F9" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="G9" t="n">
-        <v>54.4</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10">
@@ -17285,19 +17293,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>35.6</v>
+        <v>36</v>
       </c>
       <c r="D10" t="n">
-        <v>27.8</v>
+        <v>27.6</v>
       </c>
       <c r="E10" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="F10" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="G10" t="n">
-        <v>86</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -17318,13 +17326,13 @@
         <v>32.8</v>
       </c>
       <c r="E11" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="F11" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="G11" t="n">
-        <v>83.5</v>
+        <v>83.59999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -17339,19 +17347,19 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E12" t="n">
         <v>26.4</v>
       </c>
-      <c r="D12" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="E12" t="n">
-        <v>26.6</v>
-      </c>
       <c r="F12" t="n">
-        <v>15</v>
+        <v>15.3</v>
       </c>
       <c r="G12" t="n">
-        <v>77.8</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="13">
@@ -17372,13 +17380,13 @@
         <v>7.5</v>
       </c>
       <c r="E13" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="F13" t="n">
-        <v>68.5</v>
+        <v>68.3</v>
       </c>
       <c r="G13" t="n">
-        <v>24.3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
@@ -17393,13 +17401,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>57.3</v>
+        <v>57.6</v>
       </c>
       <c r="D14" t="n">
-        <v>28.2</v>
+        <v>28</v>
       </c>
       <c r="E14" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="F14" t="n">
         <v>1.3</v>
@@ -17420,19 +17428,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>36.8</v>
+        <v>36.2</v>
       </c>
       <c r="D15" t="n">
-        <v>41.5</v>
+        <v>42</v>
       </c>
       <c r="E15" t="n">
         <v>18.6</v>
       </c>
       <c r="F15" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G15" t="n">
-        <v>93.3</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16">
@@ -17447,16 +17455,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="E16" t="n">
-        <v>39.5</v>
+        <v>39.8</v>
       </c>
       <c r="F16" t="n">
-        <v>40</v>
+        <v>39.8</v>
       </c>
       <c r="G16" t="n">
         <v>44.9</v>
@@ -17477,16 +17485,16 @@
         <v>2.3</v>
       </c>
       <c r="D17" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="E17" t="n">
-        <v>28.7</v>
+        <v>28.5</v>
       </c>
       <c r="F17" t="n">
-        <v>55.5</v>
+        <v>55.7</v>
       </c>
       <c r="G17" t="n">
-        <v>33.5</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="18">
@@ -17501,13 +17509,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>63.7</v>
+        <v>63.8</v>
       </c>
       <c r="D18" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="E18" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="F18" t="n">
         <v>0.3</v>
@@ -17531,13 +17539,13 @@
         <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>46.8</v>
+        <v>47</v>
       </c>
       <c r="E19" t="n">
-        <v>19.8</v>
+        <v>19.5</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="G19" t="n">
         <v>94.09999999999999</v>
@@ -17558,16 +17566,16 @@
         <v>3.8</v>
       </c>
       <c r="D20" t="n">
-        <v>25.5</v>
+        <v>25.1</v>
       </c>
       <c r="E20" t="n">
-        <v>53.6</v>
+        <v>54.3</v>
       </c>
       <c r="F20" t="n">
-        <v>17.1</v>
+        <v>16.8</v>
       </c>
       <c r="G20" t="n">
-        <v>67</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -17582,19 +17590,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D21" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="E21" t="n">
-        <v>14.1</v>
+        <v>13.9</v>
       </c>
       <c r="F21" t="n">
-        <v>81.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
@@ -17605,23 +17613,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>35.1</v>
+        <v>36.9</v>
       </c>
       <c r="D22" t="n">
-        <v>32.6</v>
+        <v>26.8</v>
       </c>
       <c r="E22" t="n">
-        <v>20.4</v>
+        <v>32.7</v>
       </c>
       <c r="F22" t="n">
-        <v>11.8</v>
+        <v>3.6</v>
       </c>
       <c r="G22" t="n">
-        <v>82.8</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -17632,23 +17640,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>31.1</v>
+        <v>32</v>
       </c>
       <c r="D23" t="n">
-        <v>33.2</v>
+        <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>22.1</v>
+        <v>23</v>
       </c>
       <c r="F23" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="G23" t="n">
-        <v>80.3</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="24">
@@ -17659,23 +17667,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>18.3</v>
+        <v>28.5</v>
       </c>
       <c r="D24" t="n">
-        <v>17.8</v>
+        <v>33.6</v>
       </c>
       <c r="E24" t="n">
-        <v>29.1</v>
+        <v>25</v>
       </c>
       <c r="F24" t="n">
-        <v>34.8</v>
+        <v>12.9</v>
       </c>
       <c r="G24" t="n">
-        <v>55.3</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -17686,23 +17694,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>15.5</v>
+        <v>2.6</v>
       </c>
       <c r="D25" t="n">
-        <v>16.3</v>
+        <v>5.7</v>
       </c>
       <c r="E25" t="n">
-        <v>28.3</v>
+        <v>19.3</v>
       </c>
       <c r="F25" t="n">
-        <v>39.8</v>
+        <v>72.5</v>
       </c>
       <c r="G25" t="n">
-        <v>50.1</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="26">
@@ -17720,16 +17728,16 @@
         <v>36.5</v>
       </c>
       <c r="D26" t="n">
-        <v>27.4</v>
+        <v>27.8</v>
       </c>
       <c r="E26" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="F26" t="n">
         <v>14.8</v>
       </c>
       <c r="G26" t="n">
-        <v>79.3</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="27">
@@ -17744,19 +17752,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="D27" t="n">
-        <v>27.5</v>
+        <v>27.2</v>
       </c>
       <c r="E27" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="F27" t="n">
-        <v>20.3</v>
+        <v>20.6</v>
       </c>
       <c r="G27" t="n">
-        <v>72.09999999999999</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="28">
@@ -17771,16 +17779,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="D28" t="n">
-        <v>26.2</v>
+        <v>26.4</v>
       </c>
       <c r="E28" t="n">
         <v>26.4</v>
       </c>
       <c r="F28" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="G28" t="n">
         <v>68.2</v>
@@ -17798,19 +17806,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="D29" t="n">
-        <v>18.8</v>
+        <v>18.5</v>
       </c>
       <c r="E29" t="n">
-        <v>27.3</v>
+        <v>27.7</v>
       </c>
       <c r="F29" t="n">
-        <v>41.4</v>
+        <v>41.6</v>
       </c>
       <c r="G29" t="n">
-        <v>48.3</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="30">
@@ -17825,7 +17833,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>61.9</v>
+        <v>62.1</v>
       </c>
       <c r="D30" t="n">
         <v>23.9</v>
@@ -17834,10 +17842,10 @@
         <v>10.1</v>
       </c>
       <c r="F30" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="G30" t="n">
-        <v>93.90000000000001</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31">
@@ -17852,19 +17860,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="D31" t="n">
-        <v>35.7</v>
+        <v>35.3</v>
       </c>
       <c r="E31" t="n">
-        <v>25.8</v>
+        <v>26.2</v>
       </c>
       <c r="F31" t="n">
-        <v>16.7</v>
+        <v>16.9</v>
       </c>
       <c r="G31" t="n">
-        <v>74</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -17882,16 +17890,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="E32" t="n">
-        <v>32.9</v>
+        <v>32.7</v>
       </c>
       <c r="F32" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="G32" t="n">
-        <v>48.9</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="33">
@@ -17906,19 +17914,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="D33" t="n">
         <v>19</v>
       </c>
       <c r="E33" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="F33" t="n">
-        <v>42.3</v>
+        <v>42.5</v>
       </c>
       <c r="G33" t="n">
-        <v>43.8</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="34">
@@ -17933,19 +17941,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
       <c r="D34" t="n">
-        <v>27.8</v>
+        <v>28.2</v>
       </c>
       <c r="E34" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="F34" t="n">
         <v>7.4</v>
       </c>
       <c r="G34" t="n">
-        <v>88.59999999999999</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="35">
@@ -17960,19 +17968,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="D35" t="n">
-        <v>31.3</v>
+        <v>31</v>
       </c>
       <c r="E35" t="n">
         <v>27.2</v>
       </c>
       <c r="F35" t="n">
-        <v>15.4</v>
+        <v>15.8</v>
       </c>
       <c r="G35" t="n">
-        <v>76.09999999999999</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="36">
@@ -17987,19 +17995,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="D36" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="E36" t="n">
-        <v>31.2</v>
+        <v>30.7</v>
       </c>
       <c r="F36" t="n">
-        <v>20.1</v>
+        <v>20.5</v>
       </c>
       <c r="G36" t="n">
-        <v>69.5</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="37">
@@ -18014,19 +18022,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="D37" t="n">
         <v>12.6</v>
       </c>
       <c r="E37" t="n">
-        <v>24.8</v>
+        <v>25.5</v>
       </c>
       <c r="F37" t="n">
-        <v>57.1</v>
+        <v>56.3</v>
       </c>
       <c r="G37" t="n">
-        <v>31.6</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="38">
@@ -18041,19 +18049,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>55</v>
+        <v>54.8</v>
       </c>
       <c r="D38" t="n">
-        <v>24.6</v>
+        <v>25.4</v>
       </c>
       <c r="E38" t="n">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="F38" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="G38" t="n">
-        <v>90.09999999999999</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="39">
@@ -18068,19 +18076,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="D39" t="n">
-        <v>28</v>
+        <v>27.6</v>
       </c>
       <c r="E39" t="n">
-        <v>28.6</v>
+        <v>29</v>
       </c>
       <c r="F39" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="G39" t="n">
-        <v>64.2</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="40">
@@ -18095,19 +18103,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="D40" t="n">
-        <v>27.6</v>
+        <v>27.3</v>
       </c>
       <c r="E40" t="n">
-        <v>29.2</v>
+        <v>29</v>
       </c>
       <c r="F40" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="G40" t="n">
-        <v>63.2</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="41">
@@ -18122,19 +18130,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="D41" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="E41" t="n">
         <v>28.7</v>
       </c>
       <c r="F41" t="n">
-        <v>41.4</v>
+        <v>41.7</v>
       </c>
       <c r="G41" t="n">
-        <v>46.5</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="42">
@@ -18149,19 +18157,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>39.9</v>
+        <v>40.3</v>
       </c>
       <c r="D42" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="E42" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="F42" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>85.90000000000001</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="43">
@@ -18176,19 +18184,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>39.5</v>
+        <v>39.1</v>
       </c>
       <c r="D43" t="n">
         <v>31.7</v>
       </c>
       <c r="E43" t="n">
-        <v>19.4</v>
+        <v>19.7</v>
       </c>
       <c r="F43" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="G43" t="n">
-        <v>85.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -18203,19 +18211,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="D44" t="n">
-        <v>23.5</v>
+        <v>23.9</v>
       </c>
       <c r="E44" t="n">
         <v>34.2</v>
       </c>
       <c r="F44" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="G44" t="n">
-        <v>60</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="45">
@@ -18230,19 +18238,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="E45" t="n">
-        <v>26.8</v>
+        <v>27</v>
       </c>
       <c r="F45" t="n">
-        <v>54.3</v>
+        <v>54</v>
       </c>
       <c r="G45" t="n">
-        <v>33.6</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="46">
@@ -18257,19 +18265,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
       <c r="D46" t="n">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
       <c r="E46" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="F46" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>87.40000000000001</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47">
@@ -18284,19 +18292,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="D47" t="n">
-        <v>30.5</v>
+        <v>30.8</v>
       </c>
       <c r="E47" t="n">
-        <v>24.7</v>
+        <v>24.3</v>
       </c>
       <c r="F47" t="n">
-        <v>15.4</v>
+        <v>15.6</v>
       </c>
       <c r="G47" t="n">
-        <v>77.09999999999999</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="48">
@@ -18311,19 +18319,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="D48" t="n">
-        <v>25.2</v>
+        <v>24.8</v>
       </c>
       <c r="E48" t="n">
-        <v>30.8</v>
+        <v>31.1</v>
       </c>
       <c r="F48" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="G48" t="n">
-        <v>61.8</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="49">
@@ -18338,19 +18346,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="E49" t="n">
-        <v>27.4</v>
+        <v>27.6</v>
       </c>
       <c r="F49" t="n">
-        <v>48.8</v>
+        <v>48.2</v>
       </c>
       <c r="G49" t="n">
-        <v>39.6</v>
+        <v>40.1</v>
       </c>
     </row>
   </sheetData>
@@ -18425,19 +18433,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>93.90000000000001</v>
+        <v>94</v>
       </c>
       <c r="D2" t="n">
-        <v>44.1</v>
+        <v>44.3</v>
       </c>
       <c r="E2" t="n">
-        <v>31.2</v>
+        <v>31.5</v>
       </c>
       <c r="F2" t="n">
-        <v>20.7</v>
+        <v>21.2</v>
       </c>
       <c r="G2" t="n">
-        <v>13.4</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="3">
@@ -18452,19 +18460,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>90.09999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="D3" t="n">
-        <v>40.4</v>
+        <v>40.2</v>
       </c>
       <c r="E3" t="n">
         <v>27.1</v>
       </c>
       <c r="F3" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="G3" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="4">
@@ -18479,16 +18487,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>88.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="D4" t="n">
-        <v>36.6</v>
+        <v>36.4</v>
       </c>
       <c r="E4" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="F4" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="G4" t="n">
         <v>7.8</v>
@@ -18506,19 +18514,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>87.40000000000001</v>
+        <v>87</v>
       </c>
       <c r="D5" t="n">
-        <v>32.4</v>
+        <v>31.9</v>
       </c>
       <c r="E5" t="n">
-        <v>19.4</v>
+        <v>18.9</v>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>10.6</v>
       </c>
       <c r="G5" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="6">
@@ -18539,10 +18547,10 @@
         <v>34.7</v>
       </c>
       <c r="E6" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="G6" t="n">
         <v>5.8</v>
@@ -18560,19 +18568,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>85.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="D7" t="n">
-        <v>29.5</v>
+        <v>29</v>
       </c>
       <c r="E7" t="n">
-        <v>16.7</v>
+        <v>16.1</v>
       </c>
       <c r="F7" t="n">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="8">
@@ -18587,19 +18595,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>85.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="E8" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="F8" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="9">
@@ -18614,19 +18622,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>83.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="E9" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="F9" t="n">
         <v>7.6</v>
       </c>
       <c r="G9" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -18641,127 +18649,127 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>82.8</v>
+        <v>83.3</v>
       </c>
       <c r="D10" t="n">
-        <v>26</v>
+        <v>26.3</v>
       </c>
       <c r="E10" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="F10" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="G10" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>76.09999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>22.1</v>
+        <v>22.6</v>
       </c>
       <c r="E11" t="n">
-        <v>11.4</v>
+        <v>11.1</v>
       </c>
       <c r="F11" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>77.09999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>20.4</v>
+        <v>26.5</v>
       </c>
       <c r="E12" t="n">
-        <v>10.4</v>
+        <v>12.4</v>
       </c>
       <c r="F12" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="G12" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>97.5</v>
+        <v>75.8</v>
       </c>
       <c r="D13" t="n">
-        <v>26.7</v>
+        <v>21.7</v>
       </c>
       <c r="E13" t="n">
-        <v>12.4</v>
+        <v>11.3</v>
       </c>
       <c r="F13" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>80.3</v>
+        <v>76.8</v>
       </c>
       <c r="D14" t="n">
-        <v>22.4</v>
+        <v>20.8</v>
       </c>
       <c r="E14" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="F14" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="15">
@@ -18776,7 +18784,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>79.3</v>
+        <v>79.5</v>
       </c>
       <c r="D15" t="n">
         <v>22.2</v>
@@ -18803,19 +18811,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>18.7</v>
+        <v>18.4</v>
       </c>
       <c r="E16" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="17">
@@ -18830,10 +18838,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>17.6</v>
+        <v>17.9</v>
       </c>
       <c r="E17" t="n">
         <v>9.199999999999999</v>
@@ -18860,16 +18868,16 @@
         <v>97.40000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>25.2</v>
+        <v>24.8</v>
       </c>
       <c r="E18" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="F18" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="19">
@@ -18884,19 +18892,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>77.8</v>
+        <v>77.3</v>
       </c>
       <c r="D19" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="E19" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="F19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G19" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="20">
@@ -18911,19 +18919,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>93.3</v>
+        <v>93</v>
       </c>
       <c r="D20" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="E20" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F20" t="n">
         <v>4.2</v>
       </c>
       <c r="G20" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="21">
@@ -18938,16 +18946,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>75.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>18.7</v>
+        <v>18.3</v>
       </c>
       <c r="E21" t="n">
         <v>7.8</v>
       </c>
       <c r="F21" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G21" t="n">
         <v>1.5</v>
@@ -18965,16 +18973,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>69.5</v>
+        <v>69.2</v>
       </c>
       <c r="D22" t="n">
-        <v>17.4</v>
+        <v>17</v>
       </c>
       <c r="E22" t="n">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="F22" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="G22" t="n">
         <v>1.5</v>
@@ -18995,13 +19003,13 @@
         <v>94.09999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="E23" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="F23" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G23" t="n">
         <v>1.4</v>
@@ -19010,22 +19018,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>64.2</v>
+        <v>71.7</v>
       </c>
       <c r="D24" t="n">
-        <v>13.7</v>
+        <v>16.2</v>
       </c>
       <c r="E24" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="F24" t="n">
         <v>2.9</v>
@@ -19037,7 +19045,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -19046,13 +19054,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>63.2</v>
+        <v>63.8</v>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.5</v>
       </c>
       <c r="E25" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="F25" t="n">
         <v>2.9</v>
@@ -19064,25 +19072,25 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>72.09999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>16.3</v>
+        <v>17.4</v>
       </c>
       <c r="E26" t="n">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G26" t="n">
         <v>1.2</v>
@@ -19091,25 +19099,25 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>91.8</v>
+        <v>62.9</v>
       </c>
       <c r="D27" t="n">
-        <v>19.3</v>
+        <v>13.3</v>
       </c>
       <c r="E27" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G27" t="n">
         <v>1.2</v>
@@ -19118,25 +19126,25 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>44.9</v>
+        <v>91.5</v>
       </c>
       <c r="D28" t="n">
-        <v>10.2</v>
+        <v>19.2</v>
       </c>
       <c r="E28" t="n">
-        <v>5.1</v>
+        <v>7.7</v>
       </c>
       <c r="F28" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
         <v>1.1</v>
@@ -19145,25 +19153,25 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>77.2</v>
+        <v>44.9</v>
       </c>
       <c r="D29" t="n">
-        <v>16.5</v>
+        <v>10.4</v>
       </c>
       <c r="E29" t="n">
-        <v>6.3</v>
+        <v>5.1</v>
       </c>
       <c r="F29" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -19172,25 +19180,25 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>86</v>
+        <v>77.3</v>
       </c>
       <c r="D30" t="n">
-        <v>17.4</v>
+        <v>16.3</v>
       </c>
       <c r="E30" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
       <c r="F30" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
@@ -19199,52 +19207,52 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>68.2</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>13.8</v>
+        <v>16.3</v>
       </c>
       <c r="E31" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="F31" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>61.8</v>
+        <v>68.2</v>
       </c>
       <c r="D32" t="n">
-        <v>11</v>
+        <v>13.7</v>
       </c>
       <c r="E32" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="F32" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="G32" t="n">
         <v>0.8</v>
@@ -19253,79 +19261,79 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>60</v>
+        <v>61.2</v>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>11.3</v>
       </c>
       <c r="E33" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="F33" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="G33" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>33.5</v>
+        <v>59.9</v>
       </c>
       <c r="D34" t="n">
-        <v>5.9</v>
+        <v>10.1</v>
       </c>
       <c r="E34" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="F34" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>55.3</v>
+        <v>33.1</v>
       </c>
       <c r="D35" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="F35" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="G35" t="n">
         <v>0.5</v>
@@ -19343,13 +19351,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>47.9</v>
+        <v>46.7</v>
       </c>
       <c r="D36" t="n">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="F36" t="n">
         <v>1.2</v>
@@ -19361,52 +19369,52 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>48.9</v>
+        <v>46.2</v>
       </c>
       <c r="D37" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="E37" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>50.1</v>
+        <v>48.7</v>
       </c>
       <c r="D38" t="n">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="E38" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G38" t="n">
         <v>0.3</v>
@@ -19415,46 +19423,46 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>46.5</v>
+        <v>43.1</v>
       </c>
       <c r="D39" t="n">
-        <v>6.9</v>
+        <v>5</v>
       </c>
       <c r="E39" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="G39" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>43.8</v>
+        <v>47.7</v>
       </c>
       <c r="D40" t="n">
-        <v>5.2</v>
+        <v>6.1</v>
       </c>
       <c r="E40" t="n">
         <v>1.9</v>
@@ -19469,49 +19477,49 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>48.3</v>
+        <v>29.9</v>
       </c>
       <c r="D41" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="E41" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>29.6</v>
+        <v>17.9</v>
       </c>
       <c r="D42" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="E42" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="F42" t="n">
         <v>0.3</v>
@@ -19532,13 +19540,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>31.6</v>
+        <v>32.1</v>
       </c>
       <c r="D43" t="n">
         <v>3.4</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="F43" t="n">
         <v>0.3</v>
@@ -19559,13 +19567,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>33.6</v>
+        <v>33.7</v>
       </c>
       <c r="D44" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="E44" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F44" t="n">
         <v>0.2</v>
@@ -19586,13 +19594,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>54.4</v>
+        <v>54</v>
       </c>
       <c r="D45" t="n">
         <v>5.4</v>
       </c>
       <c r="E45" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F45" t="n">
         <v>0.4</v>
@@ -19613,10 +19621,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>24.3</v>
+        <v>24</v>
       </c>
       <c r="D46" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="E46" t="n">
         <v>0.9</v>
@@ -19640,10 +19648,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>39.6</v>
+        <v>40.1</v>
       </c>
       <c r="D47" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="E47" t="n">
         <v>1.4</v>
@@ -19667,10 +19675,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>55.9</v>
+        <v>56.2</v>
       </c>
       <c r="D48" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="E48" t="n">
         <v>1.7</v>
@@ -19694,10 +19702,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="D49" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E49" t="n">
         <v>0.2</v>
@@ -19845,13 +19853,13 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>13.4</v>
+        <v>13.7</v>
       </c>
       <c r="L2" t="n">
-        <v>20.7</v>
+        <v>21.2</v>
       </c>
       <c r="M2" t="n">
-        <v>93.90000000000001</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3">
@@ -19894,13 +19902,13 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="L3" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="M3" t="n">
-        <v>90.09999999999999</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="4">
@@ -19946,10 +19954,10 @@
         <v>7.8</v>
       </c>
       <c r="L4" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="M4" t="n">
-        <v>88.59999999999999</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="5">
@@ -19992,13 +20000,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="L5" t="n">
-        <v>11</v>
+        <v>10.6</v>
       </c>
       <c r="M5" t="n">
-        <v>87.40000000000001</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6">
@@ -20044,7 +20052,7 @@
         <v>5.8</v>
       </c>
       <c r="L6" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="M6" t="n">
         <v>99.40000000000001</v>
@@ -20090,13 +20098,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L7" t="n">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>85.90000000000001</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="8">
@@ -20139,13 +20147,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L8" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>85.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -20188,13 +20196,13 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
         <v>7.6</v>
       </c>
       <c r="M9" t="n">
-        <v>83.5</v>
+        <v>83.59999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -20237,13 +20245,13 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="L10" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="M10" t="n">
-        <v>82.8</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="11">
@@ -20284,13 +20292,13 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="L11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="M11" t="n">
-        <v>67</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -20333,13 +20341,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="L12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="M12" t="n">
-        <v>76.09999999999999</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="13">
@@ -20380,13 +20388,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="L13" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="M13" t="n">
-        <v>77.09999999999999</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="14">
@@ -20427,13 +20435,13 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="L14" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="M14" t="n">
-        <v>80.3</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -20476,13 +20484,13 @@
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="L15" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="M15" t="n">
-        <v>97.5</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -20531,7 +20539,7 @@
         <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>79.3</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="17">
@@ -20580,7 +20588,7 @@
         <v>4.5</v>
       </c>
       <c r="M17" t="n">
-        <v>74</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -20621,13 +20629,13 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="L18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="M18" t="n">
-        <v>77.8</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="19">
@@ -20666,10 +20674,10 @@
         <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="M19" t="n">
         <v>44.9</v>
@@ -20716,10 +20724,10 @@
         <v>1.5</v>
       </c>
       <c r="L20" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="M20" t="n">
-        <v>69.5</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="21">
@@ -20760,10 +20768,10 @@
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="L21" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="M21" t="n">
         <v>97.40000000000001</v>
@@ -20810,10 +20818,10 @@
         <v>1.5</v>
       </c>
       <c r="L22" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="M22" t="n">
-        <v>75.3</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -20854,13 +20862,13 @@
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="L23" t="n">
         <v>4.2</v>
       </c>
       <c r="M23" t="n">
-        <v>93.3</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24">
@@ -20901,13 +20909,13 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="L24" t="n">
         <v>2.9</v>
       </c>
       <c r="M24" t="n">
-        <v>64.2</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="25">
@@ -20954,7 +20962,7 @@
         <v>2.9</v>
       </c>
       <c r="M25" t="n">
-        <v>63.2</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="26">
@@ -20998,7 +21006,7 @@
         <v>1.4</v>
       </c>
       <c r="L26" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="M26" t="n">
         <v>94.09999999999999</v>
@@ -21042,13 +21050,13 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="L27" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="M27" t="n">
-        <v>72.09999999999999</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="28">
@@ -21089,13 +21097,13 @@
         <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L28" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="M28" t="n">
-        <v>86</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -21139,10 +21147,10 @@
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="M29" t="n">
-        <v>77.2</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="30">
@@ -21185,13 +21193,13 @@
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="L30" t="n">
         <v>3</v>
       </c>
       <c r="M30" t="n">
-        <v>91.8</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="31">
@@ -21232,10 +21240,10 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="L31" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="M31" t="n">
         <v>68.2</v>
@@ -21282,10 +21290,10 @@
         <v>0.8</v>
       </c>
       <c r="L32" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>61.8</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="33">
@@ -21332,148 +21340,146 @@
         <v>1.1</v>
       </c>
       <c r="M33" t="n">
-        <v>33.5</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AFC</t>
+          <t>UEFA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1759</v>
+        <v>1703</v>
       </c>
       <c r="E34" t="n">
-        <v>1759</v>
+        <v>1766</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>blend(metis+fifa)</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>50</v>
-      </c>
+          <t>blend(metis)</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="L34" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="M34" t="n">
-        <v>60</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>UEFA</t>
+          <t>AFC</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1764</v>
+        <v>1759</v>
       </c>
       <c r="E35" t="n">
-        <v>1750</v>
+        <v>1759</v>
       </c>
       <c r="F35" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>blend(metis+expert)</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="n">
-        <v>61</v>
-      </c>
+          <t>blend(metis+fifa)</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>50</v>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="L35" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="M35" t="n">
-        <v>47.9</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>UEFA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1737</v>
+        <v>1764</v>
       </c>
       <c r="E36" t="n">
-        <v>1737</v>
+        <v>1750</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>blend(metis+fifa)</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>40</v>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>blend(metis+expert)</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>61</v>
+      </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="L36" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="M36" t="n">
-        <v>55.3</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="37">
@@ -21514,13 +21520,13 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="L37" t="n">
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>46.5</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="38">
@@ -21564,81 +21570,83 @@
         <v>0.3</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="M38" t="n">
-        <v>48.9</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>UEFA</t>
+          <t>AFC</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1703</v>
+        <v>1676</v>
       </c>
       <c r="E39" t="n">
-        <v>1703</v>
+        <v>1676</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>blend(metis)</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>blend(metis+fifa)</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>60</v>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="M39" t="n">
-        <v>50.1</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AFC</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1676</v>
+        <v>1737</v>
       </c>
       <c r="E40" t="n">
-        <v>1676</v>
+        <v>1673</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>-64</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -21646,20 +21654,20 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L40" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="M40" t="n">
-        <v>43.8</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="41">
@@ -21706,7 +21714,7 @@
         <v>0.6</v>
       </c>
       <c r="M41" t="n">
-        <v>48.3</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="42">
@@ -21753,7 +21761,7 @@
         <v>0.5</v>
       </c>
       <c r="M42" t="n">
-        <v>39.6</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="43">
@@ -21800,7 +21808,7 @@
         <v>0.3</v>
       </c>
       <c r="M43" t="n">
-        <v>24.3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="44">
@@ -21847,7 +21855,7 @@
         <v>0.5</v>
       </c>
       <c r="M44" t="n">
-        <v>55.9</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="45">
@@ -21896,7 +21904,7 @@
         <v>0.3</v>
       </c>
       <c r="M45" t="n">
-        <v>29.6</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="46">
@@ -21941,7 +21949,7 @@
         <v>0.3</v>
       </c>
       <c r="M46" t="n">
-        <v>31.6</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="47">
@@ -21986,7 +21994,7 @@
         <v>0.4</v>
       </c>
       <c r="M47" t="n">
-        <v>54.4</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48">
@@ -22031,7 +22039,7 @@
         <v>0.2</v>
       </c>
       <c r="M48" t="n">
-        <v>33.6</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="49">
@@ -22078,7 +22086,7 @@
         <v>0.1</v>
       </c>
       <c r="M49" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -22092,7 +22100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -22560,6 +22568,43 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sweden 5-1 Tunisia</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3379351884295246</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2767432920907087</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.3853215194797665</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2934012440470226</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/world_cup_2026_recommendations.xlsx
+++ b/outputs/world_cup_2026_recommendations.xlsx
@@ -549,7 +549,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>• Matches scored: 12   Outcome hit-rate: 42%   Mean RPS: 0.205  (good tournament forecasts ~0.17-0.18)</t>
+          <t>• Matches scored: 16   Outcome hit-rate: 31%   Mean RPS: 0.197  (good tournament forecasts ~0.17-0.18)</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>• Spain 14%,  Argentina 11%,  France 8%</t>
+          <t>• Spain 11%,  Argentina 11%,  France 8%</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1770,23 +1770,23 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>final</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>43.2</v>
+        <v>42.3</v>
       </c>
       <c r="K14" t="n">
-        <v>27.3</v>
+        <v>27.7</v>
       </c>
       <c r="L14" t="n">
-        <v>29.5</v>
+        <v>30</v>
       </c>
       <c r="M14" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="N14" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1798,11 +1798,15 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 41)</t>
+          <t>actual 1-1; model pick 1-0 (outcome miss)</t>
         </is>
       </c>
     </row>
@@ -1839,31 +1843,31 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>final</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>48.3</v>
+        <v>47.8</v>
       </c>
       <c r="K15" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="L15" t="n">
         <v>26.4</v>
       </c>
-      <c r="L15" t="n">
-        <v>25.3</v>
-      </c>
       <c r="M15" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="N15" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1875,11 +1879,15 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 45)</t>
+          <t>actual 2-2; model pick 1-0 (outcome miss)</t>
         </is>
       </c>
     </row>
@@ -1916,31 +1924,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>final</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>22.4</v>
+        <v>23.5</v>
       </c>
       <c r="K16" t="n">
-        <v>25.6</v>
+        <v>26.3</v>
       </c>
       <c r="L16" t="n">
-        <v>52</v>
+        <v>50.2</v>
       </c>
       <c r="M16" t="n">
         <v>0.99</v>
       </c>
       <c r="N16" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1952,11 +1960,15 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 48)</t>
+          <t>actual 1-1; model pick 0-1 (outcome miss)</t>
         </is>
       </c>
     </row>
@@ -1993,31 +2005,31 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>final</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>68.90000000000001</v>
+        <v>64</v>
       </c>
       <c r="K17" t="n">
-        <v>19.5</v>
+        <v>22.6</v>
       </c>
       <c r="L17" t="n">
-        <v>11.6</v>
+        <v>13.4</v>
       </c>
       <c r="M17" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="N17" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -2026,14 +2038,18 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr"/>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 60)</t>
+          <t>actual 0-0; model pick 1-0 (outcome miss)</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3630,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -3622,19 +3638,19 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>41.1</v>
+        <v>41.5</v>
       </c>
       <c r="K38" t="n">
-        <v>27.5</v>
+        <v>27.2</v>
       </c>
       <c r="L38" t="n">
-        <v>31.4</v>
+        <v>31.2</v>
       </c>
       <c r="M38" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="N38" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -3650,7 +3666,7 @@
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 39)</t>
+          <t>maximises expected pool points (EV 40)</t>
         </is>
       </c>
     </row>
@@ -3699,19 +3715,19 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>27</v>
+        <v>27.3</v>
       </c>
       <c r="K39" t="n">
-        <v>26.8</v>
+        <v>26.6</v>
       </c>
       <c r="L39" t="n">
         <v>46.1</v>
       </c>
       <c r="M39" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N39" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -3768,7 +3784,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -3776,19 +3792,19 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>71.2</v>
+        <v>67.8</v>
       </c>
       <c r="K40" t="n">
-        <v>18.4</v>
+        <v>20.5</v>
       </c>
       <c r="L40" t="n">
-        <v>10.4</v>
+        <v>11.7</v>
       </c>
       <c r="M40" t="n">
-        <v>2.23</v>
+        <v>2.03</v>
       </c>
       <c r="N40" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -3804,7 +3820,7 @@
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 61)</t>
+          <t>maximises expected pool points (EV 59)</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3861,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -3853,19 +3869,19 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>49.5</v>
+        <v>46.4</v>
       </c>
       <c r="K41" t="n">
-        <v>26.2</v>
+        <v>27.7</v>
       </c>
       <c r="L41" t="n">
-        <v>24.3</v>
+        <v>25.9</v>
       </c>
       <c r="M41" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="N41" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -3881,7 +3897,7 @@
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 46)</t>
+          <t>maximises expected pool points (EV 44)</t>
         </is>
       </c>
     </row>
@@ -5462,7 +5478,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -5470,16 +5486,16 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>34.1</v>
+        <v>35.1</v>
       </c>
       <c r="K62" t="n">
-        <v>27.7</v>
+        <v>27.5</v>
       </c>
       <c r="L62" t="n">
-        <v>38.2</v>
+        <v>37.4</v>
       </c>
       <c r="M62" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="N62" t="n">
         <v>1.32</v>
@@ -5498,7 +5514,7 @@
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 37)</t>
+          <t>maximises expected pool points (EV 36)</t>
         </is>
       </c>
     </row>
@@ -5547,16 +5563,16 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="K63" t="n">
         <v>25.2</v>
       </c>
       <c r="L63" t="n">
-        <v>53.6</v>
+        <v>52.9</v>
       </c>
       <c r="M63" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="N63" t="n">
         <v>1.68</v>
@@ -5616,7 +5632,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -5624,19 +5640,19 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="K64" t="n">
-        <v>27.7</v>
+        <v>28.6</v>
       </c>
       <c r="L64" t="n">
-        <v>33.8</v>
+        <v>32.7</v>
       </c>
       <c r="M64" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="N64" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -5652,7 +5668,7 @@
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 37)</t>
+          <t>maximises expected pool points (EV 38)</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5709,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -5701,19 +5717,19 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>19.8</v>
+        <v>20.3</v>
       </c>
       <c r="K65" t="n">
-        <v>24.6</v>
+        <v>25.8</v>
       </c>
       <c r="L65" t="n">
-        <v>55.7</v>
+        <v>53.9</v>
       </c>
       <c r="M65" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="N65" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -5722,14 +5738,14 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 51)</t>
+          <t>maximises expected pool points (EV 50)</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6432,7 @@
       </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -6491,7 +6507,7 @@
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -6566,7 +6582,7 @@
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -6641,7 +6657,7 @@
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -6716,7 +6732,7 @@
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -6791,7 +6807,7 @@
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -6866,7 +6882,7 @@
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="n">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -6941,7 +6957,7 @@
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="n">
-        <v>9.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -7016,7 +7032,7 @@
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -7065,19 +7081,19 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>46.7</v>
+        <v>46.2</v>
       </c>
       <c r="K83" t="n">
-        <v>26.6</v>
+        <v>26.8</v>
       </c>
       <c r="L83" t="n">
-        <v>26.7</v>
+        <v>26.9</v>
       </c>
       <c r="M83" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="N83" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -7091,7 +7107,7 @@
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -7166,7 +7182,7 @@
       </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="n">
-        <v>9.699999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -7207,7 +7223,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -7215,19 +7231,19 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>59.1</v>
+        <v>56.7</v>
       </c>
       <c r="K85" t="n">
-        <v>23.4</v>
+        <v>24.8</v>
       </c>
       <c r="L85" t="n">
-        <v>17.4</v>
+        <v>18.5</v>
       </c>
       <c r="M85" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="N85" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -7241,11 +7257,11 @@
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="n">
-        <v>17.1</v>
+        <v>14.5</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>most-likely pairing (17%); Spain to advance</t>
+          <t>most-likely pairing (14%); Spain to advance</t>
         </is>
       </c>
     </row>
@@ -7273,16 +7289,16 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -7290,23 +7306,23 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>34.7</v>
+        <v>36.3</v>
       </c>
       <c r="K86" t="n">
-        <v>27.9</v>
+        <v>28.1</v>
       </c>
       <c r="L86" t="n">
-        <v>37.4</v>
+        <v>35.6</v>
       </c>
       <c r="M86" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="N86" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -7316,11 +7332,11 @@
       </c>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>most-likely pairing (4%); Iran to advance</t>
+          <t>most-likely pairing (4%); Canada to advance</t>
         </is>
       </c>
     </row>
@@ -7348,7 +7364,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -7357,7 +7373,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -7365,19 +7381,19 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>52.5</v>
+        <v>63.5</v>
       </c>
       <c r="K87" t="n">
-        <v>25.4</v>
+        <v>22.3</v>
       </c>
       <c r="L87" t="n">
-        <v>22</v>
+        <v>14.2</v>
       </c>
       <c r="M87" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="N87" t="n">
-        <v>0.98</v>
+        <v>0.78</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
@@ -7386,16 +7402,16 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="n">
-        <v>19.3</v>
+        <v>15.5</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>most-likely pairing (19%); Argentina to advance</t>
+          <t>most-likely pairing (15%); Argentina to advance</t>
         </is>
       </c>
     </row>
@@ -7466,7 +7482,7 @@
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -7498,12 +7514,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H89" t="n">
@@ -7515,23 +7531,23 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>33.1</v>
+        <v>39.6</v>
       </c>
       <c r="K89" t="n">
-        <v>27.8</v>
+        <v>27.9</v>
       </c>
       <c r="L89" t="n">
-        <v>39.1</v>
+        <v>32.5</v>
       </c>
       <c r="M89" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="N89" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -7545,7 +7561,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>most-likely pairing (12%); Belgium to advance</t>
+          <t>most-likely pairing (12%); Australia to advance</t>
         </is>
       </c>
     </row>
@@ -7691,7 +7707,7 @@
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -7882,7 +7898,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -7890,19 +7906,19 @@
         </is>
       </c>
       <c r="J94" t="n">
-        <v>24.8</v>
+        <v>25.8</v>
       </c>
       <c r="K94" t="n">
-        <v>26.3</v>
+        <v>27.4</v>
       </c>
       <c r="L94" t="n">
-        <v>48.9</v>
+        <v>46.7</v>
       </c>
       <c r="M94" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N94" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -7916,11 +7932,11 @@
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="n">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>most-likely pairing (8%); Spain to advance</t>
+          <t>most-likely pairing (7%); Spain to advance</t>
         </is>
       </c>
     </row>
@@ -7965,19 +7981,19 @@
         </is>
       </c>
       <c r="J95" t="n">
-        <v>34</v>
+        <v>34.3</v>
       </c>
       <c r="K95" t="n">
-        <v>27</v>
+        <v>27.2</v>
       </c>
       <c r="L95" t="n">
-        <v>39</v>
+        <v>38.6</v>
       </c>
       <c r="M95" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="N95" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -7991,11 +8007,11 @@
       </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>most-likely pairing (8%); Belgium to advance</t>
+          <t>most-likely pairing (7%); Belgium to advance</t>
         </is>
       </c>
     </row>
@@ -8066,7 +8082,7 @@
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -8173,7 +8189,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -8182,7 +8198,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -8190,19 +8206,19 @@
         </is>
       </c>
       <c r="J98" t="n">
-        <v>41.5</v>
+        <v>39.1</v>
       </c>
       <c r="K98" t="n">
-        <v>25.7</v>
+        <v>26.4</v>
       </c>
       <c r="L98" t="n">
-        <v>32.8</v>
+        <v>34.5</v>
       </c>
       <c r="M98" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="N98" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -8216,7 +8232,7 @@
       </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -8257,7 +8273,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -8265,19 +8281,19 @@
         </is>
       </c>
       <c r="J99" t="n">
-        <v>58.9</v>
+        <v>56.5</v>
       </c>
       <c r="K99" t="n">
-        <v>23</v>
+        <v>24.4</v>
       </c>
       <c r="L99" t="n">
-        <v>18</v>
+        <v>19.1</v>
       </c>
       <c r="M99" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="N99" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -8286,16 +8302,16 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>most-likely pairing (5%); Spain to advance</t>
+          <t>most-likely pairing (4%); Spain to advance</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8457,7 @@
       </c>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -8478,11 +8494,11 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -8490,19 +8506,19 @@
         </is>
       </c>
       <c r="J102" t="n">
-        <v>26.3</v>
+        <v>27.5</v>
       </c>
       <c r="K102" t="n">
-        <v>25.2</v>
+        <v>26.2</v>
       </c>
       <c r="L102" t="n">
-        <v>48.5</v>
+        <v>46.3</v>
       </c>
       <c r="M102" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="N102" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -8516,7 +8532,7 @@
       </c>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -8632,7 +8648,7 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -8640,19 +8656,19 @@
         </is>
       </c>
       <c r="J104" t="n">
-        <v>39.1</v>
+        <v>37.3</v>
       </c>
       <c r="K104" t="n">
-        <v>27.6</v>
+        <v>28.5</v>
       </c>
       <c r="L104" t="n">
-        <v>33.2</v>
+        <v>34.2</v>
       </c>
       <c r="M104" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="N104" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -8707,7 +8723,7 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -8715,19 +8731,19 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>39.1</v>
+        <v>37.3</v>
       </c>
       <c r="K105" t="n">
-        <v>27.6</v>
+        <v>28.5</v>
       </c>
       <c r="L105" t="n">
-        <v>33.2</v>
+        <v>34.2</v>
       </c>
       <c r="M105" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="N105" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
@@ -8741,7 +8757,7 @@
       </c>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -9886,7 +9902,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -9894,23 +9910,23 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>final</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>43.2</v>
+        <v>42.3</v>
       </c>
       <c r="K14" t="n">
-        <v>27.3</v>
+        <v>27.7</v>
       </c>
       <c r="L14" t="n">
-        <v>29.5</v>
+        <v>30</v>
       </c>
       <c r="M14" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="N14" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -9922,11 +9938,15 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 41)</t>
+          <t>actual 1-1; model pick 1-0 (outcome miss)</t>
         </is>
       </c>
     </row>
@@ -9963,31 +9983,31 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>final</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>48.3</v>
+        <v>47.8</v>
       </c>
       <c r="K15" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="L15" t="n">
         <v>26.4</v>
       </c>
-      <c r="L15" t="n">
-        <v>25.3</v>
-      </c>
       <c r="M15" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="N15" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -9999,11 +10019,15 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 45)</t>
+          <t>actual 2-2; model pick 1-0 (outcome miss)</t>
         </is>
       </c>
     </row>
@@ -10040,31 +10064,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>final</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>22.4</v>
+        <v>23.5</v>
       </c>
       <c r="K16" t="n">
-        <v>25.6</v>
+        <v>26.3</v>
       </c>
       <c r="L16" t="n">
-        <v>52</v>
+        <v>50.2</v>
       </c>
       <c r="M16" t="n">
         <v>0.99</v>
       </c>
       <c r="N16" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -10076,11 +10100,15 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 48)</t>
+          <t>actual 1-1; model pick 0-1 (outcome miss)</t>
         </is>
       </c>
     </row>
@@ -10117,31 +10145,31 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>final</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>68.90000000000001</v>
+        <v>64</v>
       </c>
       <c r="K17" t="n">
-        <v>19.5</v>
+        <v>22.6</v>
       </c>
       <c r="L17" t="n">
-        <v>11.6</v>
+        <v>13.4</v>
       </c>
       <c r="M17" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="N17" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -10150,14 +10178,18 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr"/>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 60)</t>
+          <t>actual 0-0; model pick 1-0 (outcome miss)</t>
         </is>
       </c>
     </row>
@@ -11738,7 +11770,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -11746,19 +11778,19 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>41.1</v>
+        <v>41.5</v>
       </c>
       <c r="K38" t="n">
-        <v>27.5</v>
+        <v>27.2</v>
       </c>
       <c r="L38" t="n">
-        <v>31.4</v>
+        <v>31.2</v>
       </c>
       <c r="M38" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="N38" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -11774,7 +11806,7 @@
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 39)</t>
+          <t>maximises expected pool points (EV 40)</t>
         </is>
       </c>
     </row>
@@ -11823,19 +11855,19 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>27</v>
+        <v>27.3</v>
       </c>
       <c r="K39" t="n">
-        <v>26.8</v>
+        <v>26.6</v>
       </c>
       <c r="L39" t="n">
         <v>46.1</v>
       </c>
       <c r="M39" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N39" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -11892,7 +11924,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -11900,19 +11932,19 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>71.2</v>
+        <v>67.8</v>
       </c>
       <c r="K40" t="n">
-        <v>18.4</v>
+        <v>20.5</v>
       </c>
       <c r="L40" t="n">
-        <v>10.4</v>
+        <v>11.7</v>
       </c>
       <c r="M40" t="n">
-        <v>2.23</v>
+        <v>2.03</v>
       </c>
       <c r="N40" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -11928,7 +11960,7 @@
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 61)</t>
+          <t>maximises expected pool points (EV 59)</t>
         </is>
       </c>
     </row>
@@ -11969,7 +12001,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -11977,19 +12009,19 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>49.5</v>
+        <v>46.4</v>
       </c>
       <c r="K41" t="n">
-        <v>26.2</v>
+        <v>27.7</v>
       </c>
       <c r="L41" t="n">
-        <v>24.3</v>
+        <v>25.9</v>
       </c>
       <c r="M41" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="N41" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -12005,7 +12037,7 @@
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 46)</t>
+          <t>maximises expected pool points (EV 44)</t>
         </is>
       </c>
     </row>
@@ -13586,7 +13618,7 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -13594,16 +13626,16 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>34.1</v>
+        <v>35.1</v>
       </c>
       <c r="K62" t="n">
-        <v>27.7</v>
+        <v>27.5</v>
       </c>
       <c r="L62" t="n">
-        <v>38.2</v>
+        <v>37.4</v>
       </c>
       <c r="M62" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="N62" t="n">
         <v>1.32</v>
@@ -13622,7 +13654,7 @@
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 37)</t>
+          <t>maximises expected pool points (EV 36)</t>
         </is>
       </c>
     </row>
@@ -13671,16 +13703,16 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="K63" t="n">
         <v>25.2</v>
       </c>
       <c r="L63" t="n">
-        <v>53.6</v>
+        <v>52.9</v>
       </c>
       <c r="M63" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="N63" t="n">
         <v>1.68</v>
@@ -13740,7 +13772,7 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -13748,19 +13780,19 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="K64" t="n">
-        <v>27.7</v>
+        <v>28.6</v>
       </c>
       <c r="L64" t="n">
-        <v>33.8</v>
+        <v>32.7</v>
       </c>
       <c r="M64" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="N64" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -13776,7 +13808,7 @@
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 37)</t>
+          <t>maximises expected pool points (EV 38)</t>
         </is>
       </c>
     </row>
@@ -13817,7 +13849,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -13825,19 +13857,19 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>19.8</v>
+        <v>20.3</v>
       </c>
       <c r="K65" t="n">
-        <v>24.6</v>
+        <v>25.8</v>
       </c>
       <c r="L65" t="n">
-        <v>55.7</v>
+        <v>53.9</v>
       </c>
       <c r="M65" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="N65" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -13846,14 +13878,14 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 51)</t>
+          <t>maximises expected pool points (EV 50)</t>
         </is>
       </c>
     </row>
@@ -14672,7 +14704,7 @@
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -14747,7 +14779,7 @@
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -14822,7 +14854,7 @@
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -14897,7 +14929,7 @@
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -14972,7 +15004,7 @@
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -15047,7 +15079,7 @@
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -15122,7 +15154,7 @@
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -15197,7 +15229,7 @@
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>9.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -15272,7 +15304,7 @@
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -15321,19 +15353,19 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>46.7</v>
+        <v>46.2</v>
       </c>
       <c r="K11" t="n">
-        <v>26.6</v>
+        <v>26.8</v>
       </c>
       <c r="L11" t="n">
-        <v>26.7</v>
+        <v>26.9</v>
       </c>
       <c r="M11" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="N11" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -15347,7 +15379,7 @@
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -15422,7 +15454,7 @@
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
-        <v>9.699999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -15463,7 +15495,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -15471,19 +15503,19 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>59.1</v>
+        <v>56.7</v>
       </c>
       <c r="K13" t="n">
-        <v>23.4</v>
+        <v>24.8</v>
       </c>
       <c r="L13" t="n">
-        <v>17.4</v>
+        <v>18.5</v>
       </c>
       <c r="M13" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -15497,11 +15529,11 @@
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
-        <v>17.1</v>
+        <v>14.5</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>most-likely pairing (17%); Spain to advance</t>
+          <t>most-likely pairing (14%); Spain to advance</t>
         </is>
       </c>
     </row>
@@ -15529,16 +15561,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -15546,23 +15578,23 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>34.7</v>
+        <v>36.3</v>
       </c>
       <c r="K14" t="n">
-        <v>27.9</v>
+        <v>28.1</v>
       </c>
       <c r="L14" t="n">
-        <v>37.4</v>
+        <v>35.6</v>
       </c>
       <c r="M14" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="N14" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -15572,11 +15604,11 @@
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>most-likely pairing (4%); Iran to advance</t>
+          <t>most-likely pairing (4%); Canada to advance</t>
         </is>
       </c>
     </row>
@@ -15604,7 +15636,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -15613,7 +15645,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -15621,19 +15653,19 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>52.5</v>
+        <v>63.5</v>
       </c>
       <c r="K15" t="n">
-        <v>25.4</v>
+        <v>22.3</v>
       </c>
       <c r="L15" t="n">
-        <v>22</v>
+        <v>14.2</v>
       </c>
       <c r="M15" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="N15" t="n">
-        <v>0.98</v>
+        <v>0.78</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -15642,16 +15674,16 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
-        <v>19.3</v>
+        <v>15.5</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>most-likely pairing (19%); Argentina to advance</t>
+          <t>most-likely pairing (15%); Argentina to advance</t>
         </is>
       </c>
     </row>
@@ -15722,7 +15754,7 @@
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -15754,12 +15786,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -15771,23 +15803,23 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>33.1</v>
+        <v>39.6</v>
       </c>
       <c r="K17" t="n">
-        <v>27.8</v>
+        <v>27.9</v>
       </c>
       <c r="L17" t="n">
-        <v>39.1</v>
+        <v>32.5</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="N17" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -15801,7 +15833,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>most-likely pairing (12%); Belgium to advance</t>
+          <t>most-likely pairing (12%); Australia to advance</t>
         </is>
       </c>
     </row>
@@ -15947,7 +15979,7 @@
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -16138,7 +16170,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -16146,19 +16178,19 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>24.8</v>
+        <v>25.8</v>
       </c>
       <c r="K22" t="n">
-        <v>26.3</v>
+        <v>27.4</v>
       </c>
       <c r="L22" t="n">
-        <v>48.9</v>
+        <v>46.7</v>
       </c>
       <c r="M22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -16172,11 +16204,11 @@
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>most-likely pairing (8%); Spain to advance</t>
+          <t>most-likely pairing (7%); Spain to advance</t>
         </is>
       </c>
     </row>
@@ -16221,19 +16253,19 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>34</v>
+        <v>34.3</v>
       </c>
       <c r="K23" t="n">
-        <v>27</v>
+        <v>27.2</v>
       </c>
       <c r="L23" t="n">
-        <v>39</v>
+        <v>38.6</v>
       </c>
       <c r="M23" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="N23" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -16247,11 +16279,11 @@
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>most-likely pairing (8%); Belgium to advance</t>
+          <t>most-likely pairing (7%); Belgium to advance</t>
         </is>
       </c>
     </row>
@@ -16322,7 +16354,7 @@
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -16429,7 +16461,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -16438,7 +16470,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -16446,19 +16478,19 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>41.5</v>
+        <v>39.1</v>
       </c>
       <c r="K26" t="n">
-        <v>25.7</v>
+        <v>26.4</v>
       </c>
       <c r="L26" t="n">
-        <v>32.8</v>
+        <v>34.5</v>
       </c>
       <c r="M26" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="N26" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -16472,7 +16504,7 @@
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -16513,7 +16545,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -16521,19 +16553,19 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>58.9</v>
+        <v>56.5</v>
       </c>
       <c r="K27" t="n">
-        <v>23</v>
+        <v>24.4</v>
       </c>
       <c r="L27" t="n">
-        <v>18</v>
+        <v>19.1</v>
       </c>
       <c r="M27" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="N27" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -16542,16 +16574,16 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>most-likely pairing (5%); Spain to advance</t>
+          <t>most-likely pairing (4%); Spain to advance</t>
         </is>
       </c>
     </row>
@@ -16697,7 +16729,7 @@
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -16734,11 +16766,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -16746,19 +16778,19 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>26.3</v>
+        <v>27.5</v>
       </c>
       <c r="K30" t="n">
-        <v>25.2</v>
+        <v>26.2</v>
       </c>
       <c r="L30" t="n">
-        <v>48.5</v>
+        <v>46.3</v>
       </c>
       <c r="M30" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="N30" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -16772,7 +16804,7 @@
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -16888,7 +16920,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -16896,19 +16928,19 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>39.1</v>
+        <v>37.3</v>
       </c>
       <c r="K32" t="n">
-        <v>27.6</v>
+        <v>28.5</v>
       </c>
       <c r="L32" t="n">
-        <v>33.2</v>
+        <v>34.2</v>
       </c>
       <c r="M32" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="N32" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -16963,7 +16995,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -16971,19 +17003,19 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>39.1</v>
+        <v>37.3</v>
       </c>
       <c r="K33" t="n">
-        <v>27.6</v>
+        <v>28.5</v>
       </c>
       <c r="L33" t="n">
-        <v>33.2</v>
+        <v>34.2</v>
       </c>
       <c r="M33" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="N33" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -16997,7 +17029,7 @@
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -17077,19 +17109,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>61.9</v>
+        <v>61</v>
       </c>
       <c r="D2" t="n">
-        <v>26.2</v>
+        <v>27</v>
       </c>
       <c r="E2" t="n">
-        <v>10.7</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>97.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="3">
@@ -17104,19 +17136,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
+        <v>32.6</v>
       </c>
       <c r="D3" t="n">
-        <v>44.8</v>
+        <v>44.5</v>
       </c>
       <c r="E3" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>91.5</v>
+        <v>91.90000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -17131,19 +17163,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="D4" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="E4" t="n">
         <v>42.8</v>
       </c>
       <c r="F4" t="n">
-        <v>36.5</v>
+        <v>36.3</v>
       </c>
       <c r="G4" t="n">
-        <v>46.7</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="5">
@@ -17158,16 +17190,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="D5" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="E5" t="n">
         <v>27.3</v>
       </c>
       <c r="F5" t="n">
-        <v>58.4</v>
+        <v>58.7</v>
       </c>
       <c r="G5" t="n">
         <v>29.9</v>
@@ -17185,19 +17217,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="D6" t="n">
         <v>26.6</v>
       </c>
       <c r="E6" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="F6" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>77.3</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -17212,19 +17244,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>33.1</v>
+        <v>32.7</v>
       </c>
       <c r="D7" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="E7" t="n">
-        <v>23.5</v>
+        <v>24</v>
       </c>
       <c r="F7" t="n">
-        <v>16.3</v>
+        <v>16.1</v>
       </c>
       <c r="G7" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="8">
@@ -17239,19 +17271,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="D8" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="E8" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="F8" t="n">
-        <v>33.8</v>
+        <v>34.1</v>
       </c>
       <c r="G8" t="n">
-        <v>56.2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9">
@@ -17266,19 +17298,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14.4</v>
+        <v>14.8</v>
       </c>
       <c r="D9" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="E9" t="n">
-        <v>26.8</v>
+        <v>26.4</v>
       </c>
       <c r="F9" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="G9" t="n">
-        <v>54</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="10">
@@ -17293,19 +17325,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="D10" t="n">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
       <c r="E10" t="n">
-        <v>30.9</v>
+        <v>30.7</v>
       </c>
       <c r="F10" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="G10" t="n">
-        <v>86.09999999999999</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="11">
@@ -17320,10 +17352,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>34.6</v>
+        <v>34.4</v>
       </c>
       <c r="D11" t="n">
-        <v>32.8</v>
+        <v>33.1</v>
       </c>
       <c r="E11" t="n">
         <v>21.9</v>
@@ -17332,7 +17364,7 @@
         <v>10.7</v>
       </c>
       <c r="G11" t="n">
-        <v>83.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -17347,19 +17379,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>26.1</v>
+        <v>26.5</v>
       </c>
       <c r="D12" t="n">
-        <v>32.1</v>
+        <v>31.9</v>
       </c>
       <c r="E12" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="F12" t="n">
-        <v>15.3</v>
+        <v>15</v>
       </c>
       <c r="G12" t="n">
-        <v>77.3</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="13">
@@ -17374,19 +17406,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="D13" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="E13" t="n">
         <v>20.9</v>
       </c>
       <c r="F13" t="n">
-        <v>68.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="14">
@@ -17401,19 +17433,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>57.6</v>
+        <v>57.4</v>
       </c>
       <c r="D14" t="n">
         <v>28</v>
       </c>
       <c r="E14" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="G14" t="n">
-        <v>97.40000000000001</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="15">
@@ -17428,19 +17460,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>36.2</v>
+        <v>36.6</v>
       </c>
       <c r="D15" t="n">
-        <v>42</v>
+        <v>41.4</v>
       </c>
       <c r="E15" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="F15" t="n">
         <v>3.3</v>
       </c>
       <c r="G15" t="n">
-        <v>93</v>
+        <v>93.09999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -17455,19 +17487,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="D16" t="n">
-        <v>16.5</v>
+        <v>17.1</v>
       </c>
       <c r="E16" t="n">
-        <v>39.8</v>
+        <v>39.6</v>
       </c>
       <c r="F16" t="n">
-        <v>39.8</v>
+        <v>39.6</v>
       </c>
       <c r="G16" t="n">
-        <v>44.9</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="17">
@@ -17485,16 +17517,16 @@
         <v>2.3</v>
       </c>
       <c r="D17" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="E17" t="n">
         <v>28.5</v>
       </c>
       <c r="F17" t="n">
-        <v>55.7</v>
+        <v>55.8</v>
       </c>
       <c r="G17" t="n">
-        <v>33.1</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="18">
@@ -17509,13 +17541,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>63.8</v>
+        <v>63.6</v>
       </c>
       <c r="D18" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="E18" t="n">
-        <v>12.2</v>
+        <v>12.6</v>
       </c>
       <c r="F18" t="n">
         <v>0.3</v>
@@ -17536,19 +17568,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>32.3</v>
       </c>
       <c r="D19" t="n">
-        <v>47</v>
+        <v>46.7</v>
       </c>
       <c r="E19" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G19" t="n">
-        <v>94.09999999999999</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="20">
@@ -17563,19 +17595,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="D20" t="n">
-        <v>25.1</v>
+        <v>25.7</v>
       </c>
       <c r="E20" t="n">
-        <v>54.3</v>
+        <v>54.1</v>
       </c>
       <c r="F20" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="G20" t="n">
-        <v>67.09999999999999</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="21">
@@ -17593,16 +17625,16 @@
         <v>0.4</v>
       </c>
       <c r="D21" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="F21" t="n">
-        <v>81.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="22">
@@ -17620,16 +17652,16 @@
         <v>36.9</v>
       </c>
       <c r="D22" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="E22" t="n">
-        <v>32.7</v>
+        <v>33</v>
       </c>
       <c r="F22" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G22" t="n">
-        <v>93.40000000000001</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="23">
@@ -17644,19 +17676,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>32</v>
+        <v>32.2</v>
       </c>
       <c r="D23" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="E23" t="n">
         <v>23</v>
       </c>
       <c r="F23" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="G23" t="n">
-        <v>83.3</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="24">
@@ -17671,19 +17703,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="D24" t="n">
-        <v>33.6</v>
+        <v>33.8</v>
       </c>
       <c r="E24" t="n">
         <v>25</v>
       </c>
       <c r="F24" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="G24" t="n">
-        <v>80.90000000000001</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="25">
@@ -17701,16 +17733,16 @@
         <v>2.6</v>
       </c>
       <c r="D25" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="E25" t="n">
-        <v>19.3</v>
+        <v>19</v>
       </c>
       <c r="F25" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="G25" t="n">
-        <v>17.9</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="26">
@@ -17725,19 +17757,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>36.5</v>
+        <v>34.3</v>
       </c>
       <c r="D26" t="n">
-        <v>27.8</v>
+        <v>27.5</v>
       </c>
       <c r="E26" t="n">
-        <v>21</v>
+        <v>21.5</v>
       </c>
       <c r="F26" t="n">
-        <v>14.8</v>
+        <v>16.7</v>
       </c>
       <c r="G26" t="n">
-        <v>79.5</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="27">
@@ -17748,23 +17780,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27.2</v>
+        <v>25.7</v>
       </c>
       <c r="D27" t="n">
-        <v>27.2</v>
+        <v>28</v>
       </c>
       <c r="E27" t="n">
-        <v>24.9</v>
+        <v>23.6</v>
       </c>
       <c r="F27" t="n">
-        <v>20.6</v>
+        <v>22.6</v>
       </c>
       <c r="G27" t="n">
-        <v>71.7</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="28">
@@ -17775,23 +17807,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.1</v>
+        <v>25.1</v>
       </c>
       <c r="D28" t="n">
-        <v>26.4</v>
+        <v>23.9</v>
       </c>
       <c r="E28" t="n">
-        <v>26.4</v>
+        <v>27.8</v>
       </c>
       <c r="F28" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="G28" t="n">
-        <v>68.2</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="29">
@@ -17806,19 +17838,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>12.3</v>
+        <v>14.9</v>
       </c>
       <c r="D29" t="n">
-        <v>18.5</v>
+        <v>20.6</v>
       </c>
       <c r="E29" t="n">
-        <v>27.7</v>
+        <v>27</v>
       </c>
       <c r="F29" t="n">
-        <v>41.6</v>
+        <v>37.5</v>
       </c>
       <c r="G29" t="n">
-        <v>47.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30">
@@ -17833,19 +17865,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>62.1</v>
+        <v>52.6</v>
       </c>
       <c r="D30" t="n">
-        <v>23.9</v>
+        <v>24.8</v>
       </c>
       <c r="E30" t="n">
-        <v>10.1</v>
+        <v>15.3</v>
       </c>
       <c r="F30" t="n">
-        <v>3.9</v>
+        <v>7.3</v>
       </c>
       <c r="G30" t="n">
-        <v>94</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="31">
@@ -17860,19 +17892,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="D31" t="n">
-        <v>35.3</v>
+        <v>26.6</v>
       </c>
       <c r="E31" t="n">
-        <v>26.2</v>
+        <v>29.9</v>
       </c>
       <c r="F31" t="n">
-        <v>16.9</v>
+        <v>21.8</v>
       </c>
       <c r="G31" t="n">
-        <v>73.59999999999999</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="32">
@@ -17887,19 +17919,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="D32" t="n">
-        <v>21.7</v>
+        <v>28.6</v>
       </c>
       <c r="E32" t="n">
-        <v>32.7</v>
+        <v>25.9</v>
       </c>
       <c r="F32" t="n">
-        <v>36.8</v>
+        <v>30.9</v>
       </c>
       <c r="G32" t="n">
-        <v>48.7</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="33">
@@ -17914,19 +17946,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7.5</v>
+        <v>11.2</v>
       </c>
       <c r="D33" t="n">
-        <v>19</v>
+        <v>19.9</v>
       </c>
       <c r="E33" t="n">
-        <v>31.1</v>
+        <v>28.9</v>
       </c>
       <c r="F33" t="n">
-        <v>42.5</v>
+        <v>40</v>
       </c>
       <c r="G33" t="n">
-        <v>43.1</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="34">
@@ -17944,16 +17976,16 @@
         <v>47.8</v>
       </c>
       <c r="D34" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="E34" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="F34" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="G34" t="n">
-        <v>88.8</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -17968,7 +18000,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>26</v>
+        <v>26.2</v>
       </c>
       <c r="D35" t="n">
         <v>31</v>
@@ -17977,7 +18009,7 @@
         <v>27.2</v>
       </c>
       <c r="F35" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="G35" t="n">
         <v>75.8</v>
@@ -17995,16 +18027,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="D36" t="n">
         <v>28.2</v>
       </c>
       <c r="E36" t="n">
-        <v>30.7</v>
+        <v>31.1</v>
       </c>
       <c r="F36" t="n">
-        <v>20.5</v>
+        <v>20.2</v>
       </c>
       <c r="G36" t="n">
         <v>69.2</v>
@@ -18022,19 +18054,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="D37" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="n">
-        <v>25.5</v>
+        <v>25.2</v>
       </c>
       <c r="F37" t="n">
-        <v>56.3</v>
+        <v>56.8</v>
       </c>
       <c r="G37" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38">
@@ -18049,19 +18081,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>54.8</v>
+        <v>54.7</v>
       </c>
       <c r="D38" t="n">
         <v>25.4</v>
       </c>
       <c r="E38" t="n">
-        <v>13.2</v>
+        <v>13.4</v>
       </c>
       <c r="F38" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="G38" t="n">
-        <v>90.5</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -18076,19 +18108,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>17.9</v>
+        <v>18.2</v>
       </c>
       <c r="D39" t="n">
-        <v>27.6</v>
+        <v>27.4</v>
       </c>
       <c r="E39" t="n">
-        <v>29</v>
+        <v>28.8</v>
       </c>
       <c r="F39" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="G39" t="n">
-        <v>63.8</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="40">
@@ -18103,19 +18135,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="D40" t="n">
-        <v>27.3</v>
+        <v>27.5</v>
       </c>
       <c r="E40" t="n">
-        <v>29</v>
+        <v>29.3</v>
       </c>
       <c r="F40" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="G40" t="n">
-        <v>62.9</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="41">
@@ -18136,13 +18168,13 @@
         <v>19.7</v>
       </c>
       <c r="E41" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="F41" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="G41" t="n">
-        <v>46.2</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="42">
@@ -18157,19 +18189,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>40.3</v>
+        <v>40.8</v>
       </c>
       <c r="D42" t="n">
-        <v>31.4</v>
+        <v>31</v>
       </c>
       <c r="E42" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="F42" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="G42" t="n">
-        <v>85.7</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -18184,19 +18216,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>39.1</v>
+        <v>38.8</v>
       </c>
       <c r="D43" t="n">
-        <v>31.7</v>
+        <v>32.2</v>
       </c>
       <c r="E43" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="F43" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>85.40000000000001</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="44">
@@ -18211,19 +18243,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="D44" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="E44" t="n">
-        <v>34.2</v>
+        <v>34</v>
       </c>
       <c r="F44" t="n">
-        <v>27.2</v>
+        <v>27.6</v>
       </c>
       <c r="G44" t="n">
-        <v>59.9</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="45">
@@ -18238,19 +18270,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="D45" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="E45" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="F45" t="n">
         <v>54</v>
       </c>
       <c r="G45" t="n">
-        <v>33.7</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="46">
@@ -18265,19 +18297,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>45.8</v>
+        <v>46.5</v>
       </c>
       <c r="D46" t="n">
-        <v>28.3</v>
+        <v>28</v>
       </c>
       <c r="E46" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="F46" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="G46" t="n">
-        <v>87</v>
+        <v>87.09999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -18292,19 +18324,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="D47" t="n">
-        <v>30.8</v>
+        <v>31.1</v>
       </c>
       <c r="E47" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="F47" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="G47" t="n">
-        <v>76.8</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -18319,19 +18351,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>16.7</v>
+        <v>16.3</v>
       </c>
       <c r="D48" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="E48" t="n">
-        <v>31.1</v>
+        <v>31.4</v>
       </c>
       <c r="F48" t="n">
-        <v>27.3</v>
+        <v>27.4</v>
       </c>
       <c r="G48" t="n">
-        <v>61.2</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="49">
@@ -18346,19 +18378,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="D49" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="E49" t="n">
-        <v>27.6</v>
+        <v>27.4</v>
       </c>
       <c r="F49" t="n">
-        <v>48.2</v>
+        <v>48.6</v>
       </c>
       <c r="G49" t="n">
-        <v>40.1</v>
+        <v>39.7</v>
       </c>
     </row>
   </sheetData>
@@ -18433,19 +18465,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>94</v>
+        <v>88.5</v>
       </c>
       <c r="D2" t="n">
-        <v>44.3</v>
+        <v>39.4</v>
       </c>
       <c r="E2" t="n">
-        <v>31.5</v>
+        <v>27.5</v>
       </c>
       <c r="F2" t="n">
-        <v>21.2</v>
+        <v>17.8</v>
       </c>
       <c r="G2" t="n">
-        <v>13.7</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="3">
@@ -18460,16 +18492,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>90.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>40.2</v>
+        <v>41.2</v>
       </c>
       <c r="E3" t="n">
-        <v>27.1</v>
+        <v>27.6</v>
       </c>
       <c r="F3" t="n">
-        <v>17.3</v>
+        <v>17.6</v>
       </c>
       <c r="G3" t="n">
         <v>10.8</v>
@@ -18487,19 +18519,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>88.8</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>36.4</v>
+        <v>37</v>
       </c>
       <c r="E4" t="n">
-        <v>23.2</v>
+        <v>23.5</v>
       </c>
       <c r="F4" t="n">
-        <v>13.5</v>
+        <v>13.9</v>
       </c>
       <c r="G4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -18514,19 +18546,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>87</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>31.9</v>
+        <v>32.6</v>
       </c>
       <c r="E5" t="n">
-        <v>18.9</v>
+        <v>19.4</v>
       </c>
       <c r="F5" t="n">
-        <v>10.6</v>
+        <v>10.9</v>
       </c>
       <c r="G5" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="6">
@@ -18544,16 +18576,16 @@
         <v>99.40000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>34.7</v>
+        <v>33.8</v>
       </c>
       <c r="E6" t="n">
-        <v>20.6</v>
+        <v>20.2</v>
       </c>
       <c r="F6" t="n">
         <v>10.9</v>
       </c>
       <c r="G6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="7">
@@ -18568,19 +18600,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>85.7</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>29</v>
+        <v>29.8</v>
       </c>
       <c r="E7" t="n">
-        <v>16.1</v>
+        <v>16.7</v>
       </c>
       <c r="F7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="G7" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="8">
@@ -18595,19 +18627,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>85.40000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="D8" t="n">
-        <v>28.9</v>
+        <v>29.1</v>
       </c>
       <c r="E8" t="n">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="F8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="9">
@@ -18622,16 +18654,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>83.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="D9" t="n">
         <v>28</v>
       </c>
       <c r="E9" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="F9" t="n">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
@@ -18649,100 +18681,100 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>83.3</v>
+        <v>83.5</v>
       </c>
       <c r="D10" t="n">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
       <c r="E10" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="F10" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="G10" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>80.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="D11" t="n">
-        <v>22.6</v>
+        <v>22</v>
       </c>
       <c r="E11" t="n">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="F11" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="G11" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>97.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="D12" t="n">
-        <v>26.5</v>
+        <v>22.5</v>
       </c>
       <c r="E12" t="n">
-        <v>12.4</v>
+        <v>10.9</v>
       </c>
       <c r="F12" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>75.8</v>
+        <v>97.5</v>
       </c>
       <c r="D13" t="n">
-        <v>21.7</v>
+        <v>26</v>
       </c>
       <c r="E13" t="n">
-        <v>11.3</v>
+        <v>12.4</v>
       </c>
       <c r="F13" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="14">
@@ -18757,13 +18789,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>76.8</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>20.8</v>
+        <v>21.4</v>
       </c>
       <c r="E14" t="n">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="F14" t="n">
         <v>5.4</v>
@@ -18775,133 +18807,133 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>79.5</v>
+        <v>67.2</v>
       </c>
       <c r="D15" t="n">
-        <v>22.2</v>
+        <v>19</v>
       </c>
       <c r="E15" t="n">
-        <v>10.4</v>
+        <v>9.4</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>67.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="D16" t="n">
-        <v>18.4</v>
+        <v>21.3</v>
       </c>
       <c r="E16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="F16" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="G16" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>73.59999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9</v>
+        <v>25.4</v>
       </c>
       <c r="E17" t="n">
-        <v>9.199999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="F17" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>97.40000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="D18" t="n">
-        <v>24.8</v>
+        <v>20</v>
       </c>
       <c r="E18" t="n">
-        <v>10.2</v>
+        <v>9.4</v>
       </c>
       <c r="F18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G18" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>77.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>20.2</v>
+        <v>22.4</v>
       </c>
       <c r="E19" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="G19" t="n">
         <v>1.8</v>
@@ -18910,28 +18942,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>93</v>
+        <v>63.9</v>
       </c>
       <c r="D20" t="n">
-        <v>22.1</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="n">
-        <v>9.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="F20" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="G20" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="21">
@@ -18946,19 +18978,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="D21" t="n">
-        <v>18.3</v>
+        <v>18.6</v>
       </c>
       <c r="E21" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G21" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="22">
@@ -18976,16 +19008,16 @@
         <v>69.2</v>
       </c>
       <c r="D22" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="E22" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="F22" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="G22" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="23">
@@ -19000,52 +19032,52 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>94.09999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="D23" t="n">
-        <v>18.9</v>
+        <v>19.2</v>
       </c>
       <c r="E23" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="F23" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G23" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="D24" t="n">
-        <v>16.2</v>
+        <v>14.8</v>
       </c>
       <c r="E24" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="F24" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="G24" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -19054,19 +19086,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>63.8</v>
+        <v>63.4</v>
       </c>
       <c r="D25" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="E25" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="F25" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="26">
@@ -19081,16 +19113,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>86.09999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="D26" t="n">
         <v>17.4</v>
       </c>
       <c r="E26" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="F26" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G26" t="n">
         <v>1.2</v>
@@ -19099,25 +19131,25 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>62.9</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>13.3</v>
+        <v>19.6</v>
       </c>
       <c r="E27" t="n">
-        <v>6.2</v>
+        <v>7.7</v>
       </c>
       <c r="F27" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="G27" t="n">
         <v>1.2</v>
@@ -19126,25 +19158,25 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>91.5</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>19.2</v>
+        <v>16.5</v>
       </c>
       <c r="E28" t="n">
-        <v>7.7</v>
+        <v>6.5</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G28" t="n">
         <v>1.1</v>
@@ -19162,16 +19194,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>44.9</v>
+        <v>45.4</v>
       </c>
       <c r="D29" t="n">
         <v>10.4</v>
       </c>
       <c r="E29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="F29" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -19180,79 +19212,79 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>77.3</v>
+        <v>63.7</v>
       </c>
       <c r="D30" t="n">
-        <v>16.3</v>
+        <v>13.7</v>
       </c>
       <c r="E30" t="n">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
       <c r="F30" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>93.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="D31" t="n">
-        <v>16.3</v>
+        <v>14.4</v>
       </c>
       <c r="E31" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="F31" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="G31" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>68.2</v>
+        <v>93.3</v>
       </c>
       <c r="D32" t="n">
-        <v>13.7</v>
+        <v>16.3</v>
       </c>
       <c r="E32" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="F32" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="G32" t="n">
         <v>0.8</v>
@@ -19270,16 +19302,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>61.2</v>
+        <v>61.4</v>
       </c>
       <c r="D33" t="n">
         <v>11.3</v>
       </c>
       <c r="E33" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="G33" t="n">
         <v>0.8</v>
@@ -19288,52 +19320,52 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>59.9</v>
+        <v>47.2</v>
       </c>
       <c r="D34" t="n">
-        <v>10.1</v>
+        <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="F34" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="G34" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>33.1</v>
+        <v>59.5</v>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>10.1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="F35" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="G35" t="n">
         <v>0.5</v>
@@ -19342,25 +19374,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>46.7</v>
+        <v>46.4</v>
       </c>
       <c r="D36" t="n">
-        <v>8.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="E36" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="F36" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="G36" t="n">
         <v>0.4</v>
@@ -19369,25 +19401,25 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>46.2</v>
+        <v>60.7</v>
       </c>
       <c r="D37" t="n">
-        <v>6.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G37" t="n">
         <v>0.4</v>
@@ -19396,28 +19428,28 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>48.7</v>
+        <v>33.3</v>
       </c>
       <c r="D38" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="E38" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="G38" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="39">
@@ -19432,16 +19464,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>43.1</v>
+        <v>46.7</v>
       </c>
       <c r="D39" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="E39" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G39" t="n">
         <v>0.2</v>
@@ -19459,16 +19491,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>47.7</v>
+        <v>50</v>
       </c>
       <c r="D40" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="E40" t="n">
         <v>1.9</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G40" t="n">
         <v>0.2</v>
@@ -19477,22 +19509,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>29.9</v>
+        <v>18.5</v>
       </c>
       <c r="D41" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F41" t="n">
         <v>0.3</v>
@@ -19504,22 +19536,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>17.9</v>
+        <v>29.9</v>
       </c>
       <c r="D42" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="E42" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="F42" t="n">
         <v>0.3</v>
@@ -19540,7 +19572,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="D43" t="n">
         <v>3.4</v>
@@ -19567,16 +19599,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>33.7</v>
+        <v>33.9</v>
       </c>
       <c r="D44" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
         <v>0.9</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G44" t="n">
         <v>0.1</v>
@@ -19594,10 +19626,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>54</v>
+        <v>54.4</v>
       </c>
       <c r="D45" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="E45" t="n">
         <v>1.5</v>
@@ -19621,10 +19653,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="D46" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="E46" t="n">
         <v>0.9</v>
@@ -19648,13 +19680,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>40.1</v>
+        <v>39.7</v>
       </c>
       <c r="D47" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="E47" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="F47" t="n">
         <v>0.5</v>
@@ -19675,13 +19707,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>56.2</v>
+        <v>56</v>
       </c>
       <c r="D48" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="E48" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="F48" t="n">
         <v>0.5</v>
@@ -19702,7 +19734,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="D49" t="n">
         <v>0.7</v>
@@ -19711,7 +19743,7 @@
         <v>0.2</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -19833,10 +19865,10 @@
         <v>2157</v>
       </c>
       <c r="E2" t="n">
-        <v>2157</v>
+        <v>2137</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -19850,16 +19882,16 @@
         <v>90</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>13.7</v>
+        <v>11.4</v>
       </c>
       <c r="L2" t="n">
-        <v>21.2</v>
+        <v>17.8</v>
       </c>
       <c r="M2" t="n">
-        <v>94</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="3">
@@ -19905,10 +19937,10 @@
         <v>10.8</v>
       </c>
       <c r="L3" t="n">
-        <v>17.3</v>
+        <v>17.6</v>
       </c>
       <c r="M3" t="n">
-        <v>90.5</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -19951,13 +19983,13 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
-        <v>13.5</v>
+        <v>13.9</v>
       </c>
       <c r="M4" t="n">
-        <v>88.8</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -20000,13 +20032,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="L5" t="n">
-        <v>10.6</v>
+        <v>10.9</v>
       </c>
       <c r="M5" t="n">
-        <v>87</v>
+        <v>87.09999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -20049,7 +20081,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L6" t="n">
         <v>10.9</v>
@@ -20098,13 +20130,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="M7" t="n">
-        <v>85.7</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -20147,13 +20179,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="L8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>85.40000000000001</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="9">
@@ -20199,10 +20231,10 @@
         <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="M9" t="n">
-        <v>83.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -20245,13 +20277,13 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="L10" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="M10" t="n">
-        <v>83.3</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="11">
@@ -20295,10 +20327,10 @@
         <v>2.2</v>
       </c>
       <c r="L11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="M11" t="n">
-        <v>67.09999999999999</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="12">
@@ -20341,10 +20373,10 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="L12" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="M12" t="n">
         <v>75.8</v>
@@ -20394,7 +20426,7 @@
         <v>5.4</v>
       </c>
       <c r="M13" t="n">
-        <v>76.8</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -20435,13 +20467,13 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="L14" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="M14" t="n">
-        <v>80.90000000000001</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="15">
@@ -20484,13 +20516,13 @@
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="L15" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="M15" t="n">
-        <v>97.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="16">
@@ -20513,10 +20545,10 @@
         <v>1894</v>
       </c>
       <c r="E16" t="n">
-        <v>1894</v>
+        <v>1890</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -20530,16 +20562,16 @@
         <v>77</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="M16" t="n">
-        <v>79.5</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="17">
@@ -20562,10 +20594,10 @@
         <v>1892</v>
       </c>
       <c r="E17" t="n">
-        <v>1892</v>
+        <v>1882</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -20579,16 +20611,16 @@
         <v>77</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="L17" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="M17" t="n">
-        <v>73.59999999999999</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="18">
@@ -20629,13 +20661,13 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="M18" t="n">
-        <v>77.3</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="19">
@@ -20677,10 +20709,10 @@
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="M19" t="n">
-        <v>44.9</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="20">
@@ -20721,10 +20753,10 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="L20" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="M20" t="n">
         <v>69.2</v>
@@ -20768,13 +20800,13 @@
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="L21" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="M21" t="n">
-        <v>97.40000000000001</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="22">
@@ -20815,13 +20847,13 @@
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="L22" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="M22" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="23">
@@ -20865,10 +20897,10 @@
         <v>1.8</v>
       </c>
       <c r="L23" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="M23" t="n">
-        <v>93</v>
+        <v>93.09999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -20909,13 +20941,13 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="L24" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="M24" t="n">
-        <v>63.8</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="25">
@@ -20956,13 +20988,13 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="L25" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>62.9</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="26">
@@ -21003,13 +21035,13 @@
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="L26" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="M26" t="n">
-        <v>94.09999999999999</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="27">
@@ -21032,10 +21064,10 @@
         <v>1824</v>
       </c>
       <c r="E27" t="n">
-        <v>1824</v>
+        <v>1816</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -21047,16 +21079,16 @@
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="L27" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="M27" t="n">
-        <v>71.7</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="28">
@@ -21100,10 +21132,10 @@
         <v>1.2</v>
       </c>
       <c r="L28" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="M28" t="n">
-        <v>86.09999999999999</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="29">
@@ -21144,13 +21176,13 @@
         <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="L29" t="n">
         <v>2.6</v>
       </c>
       <c r="M29" t="n">
-        <v>77.3</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -21193,13 +21225,13 @@
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="M30" t="n">
-        <v>91.5</v>
+        <v>91.90000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -21222,10 +21254,10 @@
         <v>1795</v>
       </c>
       <c r="E31" t="n">
-        <v>1795</v>
+        <v>1800</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -21237,16 +21269,16 @@
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L31" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="M31" t="n">
-        <v>68.2</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="32">
@@ -21290,10 +21322,10 @@
         <v>0.8</v>
       </c>
       <c r="L32" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="M32" t="n">
-        <v>61.2</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="33">
@@ -21334,13 +21366,13 @@
         <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="L33" t="n">
         <v>1.1</v>
       </c>
       <c r="M33" t="n">
-        <v>33.1</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="34">
@@ -21382,10 +21414,10 @@
         <v>0.8</v>
       </c>
       <c r="L34" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="M34" t="n">
-        <v>93.40000000000001</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="35">
@@ -21426,13 +21458,13 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="L35" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="M35" t="n">
-        <v>59.9</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="36">
@@ -21473,39 +21505,39 @@
         <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="L36" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="M36" t="n">
-        <v>46.7</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AFC</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1728</v>
+        <v>1710</v>
       </c>
       <c r="E37" t="n">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -21513,43 +21545,43 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>0.4</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="M37" t="n">
-        <v>46.2</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>AFC</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1710</v>
+        <v>1728</v>
       </c>
       <c r="E38" t="n">
-        <v>1710</v>
+        <v>1728</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -21560,20 +21592,20 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="L38" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="M38" t="n">
-        <v>48.7</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="39">
@@ -21596,10 +21628,10 @@
         <v>1676</v>
       </c>
       <c r="E39" t="n">
-        <v>1676</v>
+        <v>1686</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -21611,16 +21643,16 @@
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
         <v>0.2</v>
       </c>
       <c r="L39" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="M39" t="n">
-        <v>43.1</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="40">
@@ -21667,7 +21699,7 @@
         <v>0.3</v>
       </c>
       <c r="M40" t="n">
-        <v>17.9</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="41">
@@ -21690,10 +21722,10 @@
         <v>1657</v>
       </c>
       <c r="E41" t="n">
-        <v>1657</v>
+        <v>1665</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -21705,16 +21737,16 @@
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>0.2</v>
       </c>
       <c r="L41" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="M41" t="n">
-        <v>47.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42">
@@ -21761,7 +21793,7 @@
         <v>0.5</v>
       </c>
       <c r="M42" t="n">
-        <v>40.1</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="43">
@@ -21808,7 +21840,7 @@
         <v>0.3</v>
       </c>
       <c r="M43" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="44">
@@ -21855,7 +21887,7 @@
         <v>0.5</v>
       </c>
       <c r="M44" t="n">
-        <v>56.2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="45">
@@ -21949,7 +21981,7 @@
         <v>0.3</v>
       </c>
       <c r="M46" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47">
@@ -21994,7 +22026,7 @@
         <v>0.4</v>
       </c>
       <c r="M47" t="n">
-        <v>54</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="48">
@@ -22036,10 +22068,10 @@
         <v>0.1</v>
       </c>
       <c r="L48" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="M48" t="n">
-        <v>33.7</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="49">
@@ -22083,10 +22115,10 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
     </row>
   </sheetData>
@@ -22100,7 +22132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -22605,6 +22637,154 @@
         <v>0</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Belgium 1-1 Egypt</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.4323227858568852</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.2726912470817157</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.2949859670613991</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1369598559671035</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Iran 2-2 New Zealand</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.4832027730434736</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.2642809230535665</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.25251630390296</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1486247018068573</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Saudi Arabia 1-1 Uruguay</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.2240862560806894</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2558123361101832</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.5201014078091272</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1603600622846482</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Spain 0-0 Cape Verde</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.6889149405831398</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1951539809620534</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.1159310784548069</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.2440219051551828</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/world_cup_2026_recommendations.xlsx
+++ b/outputs/world_cup_2026_recommendations.xlsx
@@ -549,7 +549,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>• Matches scored: 16   Outcome hit-rate: 31%   Mean RPS: 0.197  (good tournament forecasts ~0.17-0.18)</t>
+          <t>• Matches scored: 22   Outcome hit-rate: 45%   Mean RPS: 0.187  (good tournament forecasts ~0.17-0.18)</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>• Spain 11%,  Argentina 11%,  France 8%</t>
+          <t>• Argentina 14%,  Spain 11%,  France 10%</t>
         </is>
       </c>
     </row>
@@ -2086,28 +2086,28 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>final</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K18" t="n">
-        <v>25.8</v>
+        <v>24.2</v>
       </c>
       <c r="L18" t="n">
-        <v>23.2</v>
+        <v>20.8</v>
       </c>
       <c r="M18" t="n">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="N18" t="n">
         <v>1.01</v>
@@ -2122,11 +2122,15 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 47)</t>
+          <t>actual 3-1; model pick 1-0 (outcome hit)</t>
         </is>
       </c>
     </row>
@@ -2163,31 +2167,31 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>final</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>17.7</v>
+        <v>14.6</v>
       </c>
       <c r="K19" t="n">
-        <v>23.6</v>
+        <v>20.5</v>
       </c>
       <c r="L19" t="n">
-        <v>58.7</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="N19" t="n">
-        <v>1.82</v>
+        <v>2.11</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -2196,14 +2200,18 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr"/>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 53)</t>
+          <t>actual 1-4; model pick 0-2 (outcome hit)</t>
         </is>
       </c>
     </row>
@@ -2240,47 +2248,51 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>55</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="K20" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
           <t>1-0</t>
         </is>
       </c>
-      <c r="H20" t="n">
-        <v>52</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>scheduled</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="K20" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="L20" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 52)</t>
+          <t>actual 3-0; model pick 1-0 (outcome hit)</t>
         </is>
       </c>
     </row>
@@ -2317,31 +2329,31 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>final</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>44.7</v>
+        <v>49.2</v>
       </c>
       <c r="K21" t="n">
-        <v>27.1</v>
+        <v>25.6</v>
       </c>
       <c r="L21" t="n">
-        <v>28.3</v>
+        <v>25.2</v>
       </c>
       <c r="M21" t="n">
-        <v>1.46</v>
+        <v>1.63</v>
       </c>
       <c r="N21" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -2353,11 +2365,15 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 42)</t>
+          <t>actual 3-1; model pick 1-0 (outcome hit)</t>
         </is>
       </c>
     </row>
@@ -2394,47 +2410,51 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>56</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="K22" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
           <t>1-0</t>
         </is>
       </c>
-      <c r="H22" t="n">
-        <v>58</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>scheduled</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="K22" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="L22" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="M22" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 58)</t>
+          <t>actual 1-1; model pick 1-0 (outcome miss)</t>
         </is>
       </c>
     </row>
@@ -2548,31 +2568,31 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>final</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>44.2</v>
+        <v>49.7</v>
       </c>
       <c r="K24" t="n">
-        <v>27.1</v>
+        <v>24.5</v>
       </c>
       <c r="L24" t="n">
-        <v>28.6</v>
+        <v>25.8</v>
       </c>
       <c r="M24" t="n">
-        <v>1.45</v>
+        <v>1.74</v>
       </c>
       <c r="N24" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -2584,11 +2604,15 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 42)</t>
+          <t>actual 4-2; model pick 2-1 (outcome hit)</t>
         </is>
       </c>
     </row>
@@ -3938,7 +3962,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3946,19 +3970,19 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>69.40000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="K42" t="n">
-        <v>19.3</v>
+        <v>16.5</v>
       </c>
       <c r="L42" t="n">
-        <v>11.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="N42" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3974,7 +3998,7 @@
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 60)</t>
+          <t>maximises expected pool points (EV 63)</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4039,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -4023,16 +4047,16 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>40</v>
+        <v>44.6</v>
       </c>
       <c r="K43" t="n">
-        <v>27.6</v>
+        <v>26.2</v>
       </c>
       <c r="L43" t="n">
-        <v>32.4</v>
+        <v>29.3</v>
       </c>
       <c r="M43" t="n">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="N43" t="n">
         <v>1.2</v>
@@ -4051,7 +4075,7 @@
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 38)</t>
+          <t>maximises expected pool points (EV 42)</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4116,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -4100,19 +4124,19 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>56</v>
+        <v>57.2</v>
       </c>
       <c r="K44" t="n">
-        <v>24.5</v>
+        <v>23.8</v>
       </c>
       <c r="L44" t="n">
-        <v>19.5</v>
+        <v>19.1</v>
       </c>
       <c r="M44" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="N44" t="n">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -4128,7 +4152,7 @@
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 51)</t>
+          <t>maximises expected pool points (EV 52)</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4193,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -4177,19 +4201,19 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>28.7</v>
+        <v>29.4</v>
       </c>
       <c r="K45" t="n">
-        <v>27.1</v>
+        <v>26.7</v>
       </c>
       <c r="L45" t="n">
-        <v>44.1</v>
+        <v>43.9</v>
       </c>
       <c r="M45" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="N45" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -4205,7 +4229,7 @@
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 42)</t>
+          <t>maximises expected pool points (EV 41)</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4270,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -4254,16 +4278,16 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>53.1</v>
+        <v>51.4</v>
       </c>
       <c r="K46" t="n">
-        <v>25.3</v>
+        <v>25.9</v>
       </c>
       <c r="L46" t="n">
-        <v>21.6</v>
+        <v>22.7</v>
       </c>
       <c r="M46" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="N46" t="n">
         <v>0.98</v>
@@ -4282,7 +4306,7 @@
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 49)</t>
+          <t>maximises expected pool points (EV 48)</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4347,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -4331,16 +4355,16 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>65.09999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="K47" t="n">
-        <v>21.2</v>
+        <v>21.9</v>
       </c>
       <c r="L47" t="n">
-        <v>13.7</v>
+        <v>14.5</v>
       </c>
       <c r="M47" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="N47" t="n">
         <v>0.8100000000000001</v>
@@ -4359,7 +4383,7 @@
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 58)</t>
+          <t>maximises expected pool points (EV 57)</t>
         </is>
       </c>
     </row>
@@ -4396,11 +4420,11 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -4408,19 +4432,19 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>63.9</v>
+        <v>67</v>
       </c>
       <c r="K48" t="n">
-        <v>21.7</v>
+        <v>19.8</v>
       </c>
       <c r="L48" t="n">
-        <v>14.4</v>
+        <v>13.2</v>
       </c>
       <c r="M48" t="n">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="N48" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -4436,7 +4460,7 @@
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 57)</t>
+          <t>maximises expected pool points (EV 58)</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4501,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -4485,19 +4509,19 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>27.8</v>
+        <v>29.6</v>
       </c>
       <c r="K49" t="n">
-        <v>27</v>
+        <v>26.3</v>
       </c>
       <c r="L49" t="n">
-        <v>45.2</v>
+        <v>44.1</v>
       </c>
       <c r="M49" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="N49" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -4513,7 +4537,7 @@
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 43)</t>
+          <t>maximises expected pool points (EV 41)</t>
         </is>
       </c>
     </row>
@@ -5794,19 +5818,19 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>26.3</v>
+        <v>27.1</v>
       </c>
       <c r="K66" t="n">
-        <v>26.7</v>
+        <v>25.8</v>
       </c>
       <c r="L66" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
       <c r="M66" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="N66" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -5863,7 +5887,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -5871,19 +5895,19 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>54.7</v>
+        <v>56.5</v>
       </c>
       <c r="K67" t="n">
-        <v>24.9</v>
+        <v>23.6</v>
       </c>
       <c r="L67" t="n">
-        <v>20.5</v>
+        <v>19.9</v>
       </c>
       <c r="M67" t="n">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="N67" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -5899,7 +5923,7 @@
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 50)</t>
+          <t>maximises expected pool points (EV 51)</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5964,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -5948,19 +5972,19 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>35.6</v>
+        <v>31.8</v>
       </c>
       <c r="K68" t="n">
-        <v>27.7</v>
+        <v>27</v>
       </c>
       <c r="L68" t="n">
-        <v>36.6</v>
+        <v>41.2</v>
       </c>
       <c r="M68" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="N68" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -5976,7 +6000,7 @@
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 36)</t>
+          <t>maximises expected pool points (EV 39)</t>
         </is>
       </c>
     </row>
@@ -6013,11 +6037,11 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -6025,19 +6049,19 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="K69" t="n">
-        <v>21.3</v>
+        <v>19</v>
       </c>
       <c r="L69" t="n">
-        <v>64.7</v>
+        <v>69.5</v>
       </c>
       <c r="M69" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="N69" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -6053,7 +6077,7 @@
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 57)</t>
+          <t>maximises expected pool points (EV 60)</t>
         </is>
       </c>
     </row>
@@ -6090,7 +6114,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H70" t="n">
@@ -6102,23 +6126,23 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>35.6</v>
+        <v>36.8</v>
       </c>
       <c r="K70" t="n">
-        <v>27.7</v>
+        <v>28</v>
       </c>
       <c r="L70" t="n">
-        <v>36.6</v>
+        <v>35.2</v>
       </c>
       <c r="M70" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="N70" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -6171,7 +6195,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -6179,19 +6203,19 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>25</v>
+        <v>26.1</v>
       </c>
       <c r="K71" t="n">
-        <v>26.4</v>
+        <v>26.9</v>
       </c>
       <c r="L71" t="n">
-        <v>48.6</v>
+        <v>47</v>
       </c>
       <c r="M71" t="n">
         <v>1.05</v>
       </c>
       <c r="N71" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -6207,7 +6231,7 @@
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 45)</t>
+          <t>maximises expected pool points (EV 44)</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6272,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -6256,19 +6280,19 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>21.2</v>
+        <v>19.8</v>
       </c>
       <c r="K72" t="n">
-        <v>25.2</v>
+        <v>23.6</v>
       </c>
       <c r="L72" t="n">
-        <v>53.6</v>
+        <v>56.6</v>
       </c>
       <c r="M72" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="N72" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -6284,7 +6308,7 @@
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 49)</t>
+          <t>maximises expected pool points (EV 51)</t>
         </is>
       </c>
     </row>
@@ -6325,7 +6349,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -6333,19 +6357,19 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>55.7</v>
+        <v>54.8</v>
       </c>
       <c r="K73" t="n">
-        <v>24.6</v>
+        <v>24.1</v>
       </c>
       <c r="L73" t="n">
-        <v>19.8</v>
+        <v>21.1</v>
       </c>
       <c r="M73" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="N73" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -6361,7 +6385,7 @@
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 51)</t>
+          <t>maximises expected pool points (EV 50)</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6413,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -6398,7 +6422,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -6406,19 +6430,19 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>32.6</v>
+        <v>35.9</v>
       </c>
       <c r="K74" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="L74" t="n">
-        <v>39.7</v>
+        <v>36.3</v>
       </c>
       <c r="M74" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="N74" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -6432,11 +6456,11 @@
       </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>most-likely pairing (12%); Switzerland to advance</t>
+          <t>most-likely pairing (12%); Canada to advance</t>
         </is>
       </c>
     </row>
@@ -6507,7 +6531,7 @@
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -6582,7 +6606,7 @@
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -6657,7 +6681,7 @@
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -6698,7 +6722,7 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -6706,16 +6730,16 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>50.3</v>
+        <v>52.2</v>
       </c>
       <c r="K78" t="n">
-        <v>26.1</v>
+        <v>25.3</v>
       </c>
       <c r="L78" t="n">
-        <v>23.6</v>
+        <v>22.4</v>
       </c>
       <c r="M78" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="N78" t="n">
         <v>1.01</v>
@@ -6732,11 +6756,11 @@
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>most-likely pairing (4%); France to advance</t>
+          <t>most-likely pairing (5%); France to advance</t>
         </is>
       </c>
     </row>
@@ -6773,7 +6797,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -6781,19 +6805,19 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>30.2</v>
+        <v>28.4</v>
       </c>
       <c r="K79" t="n">
-        <v>27.9</v>
+        <v>26.9</v>
       </c>
       <c r="L79" t="n">
-        <v>41.9</v>
+        <v>44.7</v>
       </c>
       <c r="M79" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N79" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -6807,11 +6831,11 @@
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="n">
-        <v>14.5</v>
+        <v>20.6</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>most-likely pairing (14%); Norway to advance</t>
+          <t>most-likely pairing (21%); Norway to advance</t>
         </is>
       </c>
     </row>
@@ -6882,7 +6906,7 @@
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -6914,16 +6938,16 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -6931,19 +6955,19 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>55.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>24.6</v>
+        <v>18.8</v>
       </c>
       <c r="L81" t="n">
-        <v>19.8</v>
+        <v>11.6</v>
       </c>
       <c r="M81" t="n">
-        <v>1.73</v>
+        <v>2.23</v>
       </c>
       <c r="N81" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -6952,16 +6976,16 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="n">
-        <v>10.1</v>
+        <v>13.7</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>most-likely pairing (10%); England to advance</t>
+          <t>most-likely pairing (14%); England to advance</t>
         </is>
       </c>
     </row>
@@ -7032,7 +7056,7 @@
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -7107,7 +7131,7 @@
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -7134,7 +7158,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -7148,7 +7172,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -7156,19 +7180,19 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>41.1</v>
+        <v>42.7</v>
       </c>
       <c r="K84" t="n">
-        <v>27.5</v>
+        <v>26.6</v>
       </c>
       <c r="L84" t="n">
-        <v>31.4</v>
+        <v>30.7</v>
       </c>
       <c r="M84" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="N84" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -7182,11 +7206,11 @@
       </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="n">
-        <v>10.1</v>
+        <v>11.6</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>most-likely pairing (10%); Colombia to advance</t>
+          <t>most-likely pairing (12%); Portugal to advance</t>
         </is>
       </c>
     </row>
@@ -7223,7 +7247,7 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -7231,19 +7255,19 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>56.7</v>
+        <v>55.3</v>
       </c>
       <c r="K85" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="L85" t="n">
-        <v>18.5</v>
+        <v>19.7</v>
       </c>
       <c r="M85" t="n">
         <v>1.7</v>
       </c>
       <c r="N85" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -7257,11 +7281,11 @@
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="n">
-        <v>14.5</v>
+        <v>27.8</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>most-likely pairing (14%); Spain to advance</t>
+          <t>most-likely pairing (28%); Spain to advance</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7356,7 @@
       </c>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -7373,7 +7397,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -7381,19 +7405,19 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>63.5</v>
+        <v>66</v>
       </c>
       <c r="K87" t="n">
-        <v>22.3</v>
+        <v>21.2</v>
       </c>
       <c r="L87" t="n">
-        <v>14.2</v>
+        <v>12.8</v>
       </c>
       <c r="M87" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="N87" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
@@ -7402,16 +7426,16 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="n">
-        <v>15.5</v>
+        <v>21.6</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>most-likely pairing (15%); Argentina to advance</t>
+          <t>most-likely pairing (22%); Argentina to advance</t>
         </is>
       </c>
     </row>
@@ -7434,12 +7458,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -7448,7 +7472,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -7456,19 +7480,19 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>51</v>
+        <v>43.7</v>
       </c>
       <c r="K88" t="n">
-        <v>25.8</v>
+        <v>26.3</v>
       </c>
       <c r="L88" t="n">
-        <v>23.2</v>
+        <v>30</v>
       </c>
       <c r="M88" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="N88" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -7482,11 +7506,11 @@
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="n">
-        <v>8.300000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>most-likely pairing (8%); Portugal to advance</t>
+          <t>most-likely pairing (11%); Colombia to advance</t>
         </is>
       </c>
     </row>
@@ -7598,7 +7622,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -7606,19 +7630,19 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>32.6</v>
+        <v>31.3</v>
       </c>
       <c r="K90" t="n">
-        <v>26.2</v>
+        <v>25.6</v>
       </c>
       <c r="L90" t="n">
-        <v>41.2</v>
+        <v>43.1</v>
       </c>
       <c r="M90" t="n">
         <v>1.3</v>
       </c>
       <c r="N90" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -7632,11 +7656,11 @@
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="n">
-        <v>14.2</v>
+        <v>18.5</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>most-likely pairing (14%); France to advance</t>
+          <t>most-likely pairing (19%); France to advance</t>
         </is>
       </c>
     </row>
@@ -7707,7 +7731,7 @@
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -7739,7 +7763,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -7748,7 +7772,7 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -7756,19 +7780,19 @@
         </is>
       </c>
       <c r="J92" t="n">
-        <v>46.1</v>
+        <v>38.4</v>
       </c>
       <c r="K92" t="n">
-        <v>27.4</v>
+        <v>27.2</v>
       </c>
       <c r="L92" t="n">
-        <v>26.5</v>
+        <v>34.4</v>
       </c>
       <c r="M92" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="N92" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -7782,11 +7806,11 @@
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>most-likely pairing (4%); Brazil to advance</t>
+          <t>most-likely pairing (5%); Brazil to advance</t>
         </is>
       </c>
     </row>
@@ -7823,7 +7847,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -7831,19 +7855,19 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>27.7</v>
+        <v>26.3</v>
       </c>
       <c r="K93" t="n">
-        <v>27.2</v>
+        <v>25.9</v>
       </c>
       <c r="L93" t="n">
-        <v>45.1</v>
+        <v>47.9</v>
       </c>
       <c r="M93" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="N93" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -7857,11 +7881,11 @@
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="n">
-        <v>10.6</v>
+        <v>17.4</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>most-likely pairing (11%); England to advance</t>
+          <t>most-likely pairing (17%); England to advance</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7908,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -7898,7 +7922,7 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -7906,16 +7930,16 @@
         </is>
       </c>
       <c r="J94" t="n">
-        <v>25.8</v>
+        <v>25.1</v>
       </c>
       <c r="K94" t="n">
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
       <c r="L94" t="n">
-        <v>46.7</v>
+        <v>47.4</v>
       </c>
       <c r="M94" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="N94" t="n">
         <v>1.45</v>
@@ -7932,7 +7956,7 @@
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="n">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -8048,7 +8072,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -8056,19 +8080,19 @@
         </is>
       </c>
       <c r="J96" t="n">
-        <v>55.4</v>
+        <v>58</v>
       </c>
       <c r="K96" t="n">
-        <v>24.8</v>
+        <v>23.9</v>
       </c>
       <c r="L96" t="n">
-        <v>19.8</v>
+        <v>18.1</v>
       </c>
       <c r="M96" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="N96" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -8077,16 +8101,16 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="n">
-        <v>8.5</v>
+        <v>11.6</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>most-likely pairing (8%); Argentina to advance</t>
+          <t>most-likely pairing (12%); Argentina to advance</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8138,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -8131,19 +8155,19 @@
         </is>
       </c>
       <c r="J97" t="n">
-        <v>24.3</v>
+        <v>24.7</v>
       </c>
       <c r="K97" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="L97" t="n">
-        <v>49.4</v>
+        <v>48.8</v>
       </c>
       <c r="M97" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N97" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -8157,11 +8181,11 @@
       </c>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>most-likely pairing (5%); Portugal to advance</t>
+          <t>most-likely pairing (6%); Colombia to advance</t>
         </is>
       </c>
     </row>
@@ -8184,21 +8208,21 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -8206,19 +8230,19 @@
         </is>
       </c>
       <c r="J98" t="n">
-        <v>39.1</v>
+        <v>46.8</v>
       </c>
       <c r="K98" t="n">
-        <v>26.4</v>
+        <v>26</v>
       </c>
       <c r="L98" t="n">
-        <v>34.5</v>
+        <v>27.1</v>
       </c>
       <c r="M98" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="N98" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -8232,11 +8256,11 @@
       </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>most-likely pairing (3%); Germany to advance</t>
+          <t>most-likely pairing (3%); France to advance</t>
         </is>
       </c>
     </row>
@@ -8307,11 +8331,11 @@
       </c>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>most-likely pairing (4%); Spain to advance</t>
+          <t>most-likely pairing (5%); Spain to advance</t>
         </is>
       </c>
     </row>
@@ -8334,7 +8358,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -8344,11 +8368,11 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -8356,23 +8380,23 @@
         </is>
       </c>
       <c r="J100" t="n">
-        <v>32.6</v>
+        <v>39.4</v>
       </c>
       <c r="K100" t="n">
-        <v>27.8</v>
+        <v>26.3</v>
       </c>
       <c r="L100" t="n">
-        <v>39.6</v>
+        <v>34.3</v>
       </c>
       <c r="M100" t="n">
-        <v>1.19</v>
+        <v>1.45</v>
       </c>
       <c r="N100" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -8382,11 +8406,11 @@
       </c>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>most-likely pairing (2%); England to advance</t>
+          <t>most-likely pairing (4%); France to advance</t>
         </is>
       </c>
     </row>
@@ -8414,7 +8438,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -8423,7 +8447,7 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -8431,19 +8455,19 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>45.3</v>
+        <v>48.3</v>
       </c>
       <c r="K101" t="n">
-        <v>27</v>
+        <v>26.4</v>
       </c>
       <c r="L101" t="n">
-        <v>27.8</v>
+        <v>25.3</v>
       </c>
       <c r="M101" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="N101" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -8457,11 +8481,11 @@
       </c>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="n">
-        <v>4.7</v>
+        <v>7.9</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>most-likely pairing (5%); Argentina to advance</t>
+          <t>most-likely pairing (8%); Argentina to advance</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8508,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -8498,7 +8522,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -8506,19 +8530,19 @@
         </is>
       </c>
       <c r="J102" t="n">
-        <v>27.5</v>
+        <v>32.3</v>
       </c>
       <c r="K102" t="n">
-        <v>26.2</v>
+        <v>28</v>
       </c>
       <c r="L102" t="n">
-        <v>46.3</v>
+        <v>39.7</v>
       </c>
       <c r="M102" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="N102" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -8532,11 +8556,11 @@
       </c>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>most-likely pairing (3%); Spain to advance</t>
+          <t>most-likely pairing (4%); Spain to advance</t>
         </is>
       </c>
     </row>
@@ -8581,19 +8605,19 @@
         </is>
       </c>
       <c r="J103" t="n">
-        <v>30</v>
+        <v>29.7</v>
       </c>
       <c r="K103" t="n">
-        <v>27.3</v>
+        <v>26.2</v>
       </c>
       <c r="L103" t="n">
-        <v>42.7</v>
+        <v>44.1</v>
       </c>
       <c r="M103" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="N103" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -8607,11 +8631,11 @@
       </c>
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>most-likely pairing (2%); Argentina to advance</t>
+          <t>most-likely pairing (6%); Argentina to advance</t>
         </is>
       </c>
     </row>
@@ -8644,11 +8668,11 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -8656,23 +8680,23 @@
         </is>
       </c>
       <c r="J104" t="n">
-        <v>37.3</v>
+        <v>35</v>
       </c>
       <c r="K104" t="n">
         <v>28.5</v>
       </c>
       <c r="L104" t="n">
-        <v>34.2</v>
+        <v>36.5</v>
       </c>
       <c r="M104" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="N104" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -8682,11 +8706,11 @@
       </c>
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>most-likely pairing (1%); Spain to advance</t>
+          <t>most-likely pairing (1%); Argentina to advance</t>
         </is>
       </c>
     </row>
@@ -8719,11 +8743,11 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -8731,23 +8755,23 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>37.3</v>
+        <v>35</v>
       </c>
       <c r="K105" t="n">
         <v>28.5</v>
       </c>
       <c r="L105" t="n">
-        <v>34.2</v>
+        <v>36.5</v>
       </c>
       <c r="M105" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="N105" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -8757,11 +8781,11 @@
       </c>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>most-likely pairing (2%); Spain to advance</t>
+          <t>most-likely pairing (3%); Argentina to advance</t>
         </is>
       </c>
     </row>
@@ -10226,28 +10250,28 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>final</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K18" t="n">
-        <v>25.8</v>
+        <v>24.2</v>
       </c>
       <c r="L18" t="n">
-        <v>23.2</v>
+        <v>20.8</v>
       </c>
       <c r="M18" t="n">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="N18" t="n">
         <v>1.01</v>
@@ -10262,11 +10286,15 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 47)</t>
+          <t>actual 3-1; model pick 1-0 (outcome hit)</t>
         </is>
       </c>
     </row>
@@ -10303,31 +10331,31 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>final</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>17.7</v>
+        <v>14.6</v>
       </c>
       <c r="K19" t="n">
-        <v>23.6</v>
+        <v>20.5</v>
       </c>
       <c r="L19" t="n">
-        <v>58.7</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="N19" t="n">
-        <v>1.82</v>
+        <v>2.11</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -10336,14 +10364,18 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr"/>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 53)</t>
+          <t>actual 1-4; model pick 0-2 (outcome hit)</t>
         </is>
       </c>
     </row>
@@ -10380,47 +10412,51 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>55</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="K20" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
           <t>1-0</t>
         </is>
       </c>
-      <c r="H20" t="n">
-        <v>52</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>scheduled</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="K20" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="L20" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 52)</t>
+          <t>actual 3-0; model pick 1-0 (outcome hit)</t>
         </is>
       </c>
     </row>
@@ -10457,31 +10493,31 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>final</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>44.7</v>
+        <v>49.2</v>
       </c>
       <c r="K21" t="n">
-        <v>27.1</v>
+        <v>25.6</v>
       </c>
       <c r="L21" t="n">
-        <v>28.3</v>
+        <v>25.2</v>
       </c>
       <c r="M21" t="n">
-        <v>1.46</v>
+        <v>1.63</v>
       </c>
       <c r="N21" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -10493,11 +10529,15 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 42)</t>
+          <t>actual 3-1; model pick 1-0 (outcome hit)</t>
         </is>
       </c>
     </row>
@@ -10534,47 +10574,51 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>56</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="K22" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
           <t>1-0</t>
         </is>
       </c>
-      <c r="H22" t="n">
-        <v>58</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>scheduled</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="K22" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="L22" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="M22" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 58)</t>
+          <t>actual 1-1; model pick 1-0 (outcome miss)</t>
         </is>
       </c>
     </row>
@@ -10688,31 +10732,31 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>final</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>44.2</v>
+        <v>49.7</v>
       </c>
       <c r="K24" t="n">
-        <v>27.1</v>
+        <v>24.5</v>
       </c>
       <c r="L24" t="n">
-        <v>28.6</v>
+        <v>25.8</v>
       </c>
       <c r="M24" t="n">
-        <v>1.45</v>
+        <v>1.74</v>
       </c>
       <c r="N24" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -10724,11 +10768,15 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 42)</t>
+          <t>actual 4-2; model pick 2-1 (outcome hit)</t>
         </is>
       </c>
     </row>
@@ -12078,7 +12126,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -12086,19 +12134,19 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>69.40000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="K42" t="n">
-        <v>19.3</v>
+        <v>16.5</v>
       </c>
       <c r="L42" t="n">
-        <v>11.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="N42" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -12114,7 +12162,7 @@
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 60)</t>
+          <t>maximises expected pool points (EV 63)</t>
         </is>
       </c>
     </row>
@@ -12155,7 +12203,7 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -12163,16 +12211,16 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>40</v>
+        <v>44.6</v>
       </c>
       <c r="K43" t="n">
-        <v>27.6</v>
+        <v>26.2</v>
       </c>
       <c r="L43" t="n">
-        <v>32.4</v>
+        <v>29.3</v>
       </c>
       <c r="M43" t="n">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="N43" t="n">
         <v>1.2</v>
@@ -12191,7 +12239,7 @@
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 38)</t>
+          <t>maximises expected pool points (EV 42)</t>
         </is>
       </c>
     </row>
@@ -12232,7 +12280,7 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -12240,19 +12288,19 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>56</v>
+        <v>57.2</v>
       </c>
       <c r="K44" t="n">
-        <v>24.5</v>
+        <v>23.8</v>
       </c>
       <c r="L44" t="n">
-        <v>19.5</v>
+        <v>19.1</v>
       </c>
       <c r="M44" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="N44" t="n">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -12268,7 +12316,7 @@
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 51)</t>
+          <t>maximises expected pool points (EV 52)</t>
         </is>
       </c>
     </row>
@@ -12309,7 +12357,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -12317,19 +12365,19 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>28.7</v>
+        <v>29.4</v>
       </c>
       <c r="K45" t="n">
-        <v>27.1</v>
+        <v>26.7</v>
       </c>
       <c r="L45" t="n">
-        <v>44.1</v>
+        <v>43.9</v>
       </c>
       <c r="M45" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="N45" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -12345,7 +12393,7 @@
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 42)</t>
+          <t>maximises expected pool points (EV 41)</t>
         </is>
       </c>
     </row>
@@ -12386,7 +12434,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -12394,16 +12442,16 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>53.1</v>
+        <v>51.4</v>
       </c>
       <c r="K46" t="n">
-        <v>25.3</v>
+        <v>25.9</v>
       </c>
       <c r="L46" t="n">
-        <v>21.6</v>
+        <v>22.7</v>
       </c>
       <c r="M46" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="N46" t="n">
         <v>0.98</v>
@@ -12422,7 +12470,7 @@
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 49)</t>
+          <t>maximises expected pool points (EV 48)</t>
         </is>
       </c>
     </row>
@@ -12463,7 +12511,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -12471,16 +12519,16 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>65.09999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="K47" t="n">
-        <v>21.2</v>
+        <v>21.9</v>
       </c>
       <c r="L47" t="n">
-        <v>13.7</v>
+        <v>14.5</v>
       </c>
       <c r="M47" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="N47" t="n">
         <v>0.8100000000000001</v>
@@ -12499,7 +12547,7 @@
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 58)</t>
+          <t>maximises expected pool points (EV 57)</t>
         </is>
       </c>
     </row>
@@ -12536,11 +12584,11 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -12548,19 +12596,19 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>63.9</v>
+        <v>67</v>
       </c>
       <c r="K48" t="n">
-        <v>21.7</v>
+        <v>19.8</v>
       </c>
       <c r="L48" t="n">
-        <v>14.4</v>
+        <v>13.2</v>
       </c>
       <c r="M48" t="n">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="N48" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -12576,7 +12624,7 @@
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 57)</t>
+          <t>maximises expected pool points (EV 58)</t>
         </is>
       </c>
     </row>
@@ -12617,7 +12665,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -12625,19 +12673,19 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>27.8</v>
+        <v>29.6</v>
       </c>
       <c r="K49" t="n">
-        <v>27</v>
+        <v>26.3</v>
       </c>
       <c r="L49" t="n">
-        <v>45.2</v>
+        <v>44.1</v>
       </c>
       <c r="M49" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="N49" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -12653,7 +12701,7 @@
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 43)</t>
+          <t>maximises expected pool points (EV 41)</t>
         </is>
       </c>
     </row>
@@ -13934,19 +13982,19 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>26.3</v>
+        <v>27.1</v>
       </c>
       <c r="K66" t="n">
-        <v>26.7</v>
+        <v>25.8</v>
       </c>
       <c r="L66" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
       <c r="M66" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="N66" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -14003,7 +14051,7 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -14011,19 +14059,19 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>54.7</v>
+        <v>56.5</v>
       </c>
       <c r="K67" t="n">
-        <v>24.9</v>
+        <v>23.6</v>
       </c>
       <c r="L67" t="n">
-        <v>20.5</v>
+        <v>19.9</v>
       </c>
       <c r="M67" t="n">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="N67" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -14039,7 +14087,7 @@
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 50)</t>
+          <t>maximises expected pool points (EV 51)</t>
         </is>
       </c>
     </row>
@@ -14080,7 +14128,7 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -14088,19 +14136,19 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>35.6</v>
+        <v>31.8</v>
       </c>
       <c r="K68" t="n">
-        <v>27.7</v>
+        <v>27</v>
       </c>
       <c r="L68" t="n">
-        <v>36.6</v>
+        <v>41.2</v>
       </c>
       <c r="M68" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="N68" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -14116,7 +14164,7 @@
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 36)</t>
+          <t>maximises expected pool points (EV 39)</t>
         </is>
       </c>
     </row>
@@ -14153,11 +14201,11 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -14165,19 +14213,19 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="K69" t="n">
-        <v>21.3</v>
+        <v>19</v>
       </c>
       <c r="L69" t="n">
-        <v>64.7</v>
+        <v>69.5</v>
       </c>
       <c r="M69" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="N69" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -14193,7 +14241,7 @@
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 57)</t>
+          <t>maximises expected pool points (EV 60)</t>
         </is>
       </c>
     </row>
@@ -14230,7 +14278,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H70" t="n">
@@ -14242,23 +14290,23 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>35.6</v>
+        <v>36.8</v>
       </c>
       <c r="K70" t="n">
-        <v>27.7</v>
+        <v>28</v>
       </c>
       <c r="L70" t="n">
-        <v>36.6</v>
+        <v>35.2</v>
       </c>
       <c r="M70" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="N70" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -14311,7 +14359,7 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -14319,19 +14367,19 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>25</v>
+        <v>26.1</v>
       </c>
       <c r="K71" t="n">
-        <v>26.4</v>
+        <v>26.9</v>
       </c>
       <c r="L71" t="n">
-        <v>48.6</v>
+        <v>47</v>
       </c>
       <c r="M71" t="n">
         <v>1.05</v>
       </c>
       <c r="N71" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -14347,7 +14395,7 @@
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 45)</t>
+          <t>maximises expected pool points (EV 44)</t>
         </is>
       </c>
     </row>
@@ -14388,7 +14436,7 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -14396,19 +14444,19 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>21.2</v>
+        <v>19.8</v>
       </c>
       <c r="K72" t="n">
-        <v>25.2</v>
+        <v>23.6</v>
       </c>
       <c r="L72" t="n">
-        <v>53.6</v>
+        <v>56.6</v>
       </c>
       <c r="M72" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="N72" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -14424,7 +14472,7 @@
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 49)</t>
+          <t>maximises expected pool points (EV 51)</t>
         </is>
       </c>
     </row>
@@ -14465,7 +14513,7 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -14473,19 +14521,19 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>55.7</v>
+        <v>54.8</v>
       </c>
       <c r="K73" t="n">
-        <v>24.6</v>
+        <v>24.1</v>
       </c>
       <c r="L73" t="n">
-        <v>19.8</v>
+        <v>21.1</v>
       </c>
       <c r="M73" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="N73" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -14501,7 +14549,7 @@
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 51)</t>
+          <t>maximises expected pool points (EV 50)</t>
         </is>
       </c>
     </row>
@@ -14661,7 +14709,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -14670,7 +14718,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -14678,19 +14726,19 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>32.6</v>
+        <v>35.9</v>
       </c>
       <c r="K2" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="L2" t="n">
-        <v>39.7</v>
+        <v>36.3</v>
       </c>
       <c r="M2" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="N2" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -14704,11 +14752,11 @@
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>most-likely pairing (12%); Switzerland to advance</t>
+          <t>most-likely pairing (12%); Canada to advance</t>
         </is>
       </c>
     </row>
@@ -14779,7 +14827,7 @@
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -14854,7 +14902,7 @@
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -14929,7 +14977,7 @@
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -14970,7 +15018,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -14978,16 +15026,16 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>50.3</v>
+        <v>52.2</v>
       </c>
       <c r="K6" t="n">
-        <v>26.1</v>
+        <v>25.3</v>
       </c>
       <c r="L6" t="n">
-        <v>23.6</v>
+        <v>22.4</v>
       </c>
       <c r="M6" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="N6" t="n">
         <v>1.01</v>
@@ -15004,11 +15052,11 @@
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>most-likely pairing (4%); France to advance</t>
+          <t>most-likely pairing (5%); France to advance</t>
         </is>
       </c>
     </row>
@@ -15045,7 +15093,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -15053,19 +15101,19 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>30.2</v>
+        <v>28.4</v>
       </c>
       <c r="K7" t="n">
-        <v>27.9</v>
+        <v>26.9</v>
       </c>
       <c r="L7" t="n">
-        <v>41.9</v>
+        <v>44.7</v>
       </c>
       <c r="M7" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N7" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -15079,11 +15127,11 @@
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>14.5</v>
+        <v>20.6</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>most-likely pairing (14%); Norway to advance</t>
+          <t>most-likely pairing (21%); Norway to advance</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15202,7 @@
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -15186,16 +15234,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -15203,19 +15251,19 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>55.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>24.6</v>
+        <v>18.8</v>
       </c>
       <c r="L9" t="n">
-        <v>19.8</v>
+        <v>11.6</v>
       </c>
       <c r="M9" t="n">
-        <v>1.73</v>
+        <v>2.23</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -15224,16 +15272,16 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>10.1</v>
+        <v>13.7</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>most-likely pairing (10%); England to advance</t>
+          <t>most-likely pairing (14%); England to advance</t>
         </is>
       </c>
     </row>
@@ -15304,7 +15352,7 @@
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -15379,7 +15427,7 @@
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -15406,7 +15454,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -15420,7 +15468,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -15428,19 +15476,19 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>41.1</v>
+        <v>42.7</v>
       </c>
       <c r="K12" t="n">
-        <v>27.5</v>
+        <v>26.6</v>
       </c>
       <c r="L12" t="n">
-        <v>31.4</v>
+        <v>30.7</v>
       </c>
       <c r="M12" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="N12" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -15454,11 +15502,11 @@
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
-        <v>10.1</v>
+        <v>11.6</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>most-likely pairing (10%); Colombia to advance</t>
+          <t>most-likely pairing (12%); Portugal to advance</t>
         </is>
       </c>
     </row>
@@ -15495,7 +15543,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -15503,19 +15551,19 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>56.7</v>
+        <v>55.3</v>
       </c>
       <c r="K13" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="L13" t="n">
-        <v>18.5</v>
+        <v>19.7</v>
       </c>
       <c r="M13" t="n">
         <v>1.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -15529,11 +15577,11 @@
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
-        <v>14.5</v>
+        <v>27.8</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>most-likely pairing (14%); Spain to advance</t>
+          <t>most-likely pairing (28%); Spain to advance</t>
         </is>
       </c>
     </row>
@@ -15604,7 +15652,7 @@
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -15645,7 +15693,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -15653,19 +15701,19 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>63.5</v>
+        <v>66</v>
       </c>
       <c r="K15" t="n">
-        <v>22.3</v>
+        <v>21.2</v>
       </c>
       <c r="L15" t="n">
-        <v>14.2</v>
+        <v>12.8</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="N15" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -15674,16 +15722,16 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
-        <v>15.5</v>
+        <v>21.6</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>most-likely pairing (15%); Argentina to advance</t>
+          <t>most-likely pairing (22%); Argentina to advance</t>
         </is>
       </c>
     </row>
@@ -15706,12 +15754,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -15720,7 +15768,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -15728,19 +15776,19 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>51</v>
+        <v>43.7</v>
       </c>
       <c r="K16" t="n">
-        <v>25.8</v>
+        <v>26.3</v>
       </c>
       <c r="L16" t="n">
-        <v>23.2</v>
+        <v>30</v>
       </c>
       <c r="M16" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="N16" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -15754,11 +15802,11 @@
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
-        <v>8.300000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>most-likely pairing (8%); Portugal to advance</t>
+          <t>most-likely pairing (11%); Colombia to advance</t>
         </is>
       </c>
     </row>
@@ -15870,7 +15918,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -15878,19 +15926,19 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>32.6</v>
+        <v>31.3</v>
       </c>
       <c r="K18" t="n">
-        <v>26.2</v>
+        <v>25.6</v>
       </c>
       <c r="L18" t="n">
-        <v>41.2</v>
+        <v>43.1</v>
       </c>
       <c r="M18" t="n">
         <v>1.3</v>
       </c>
       <c r="N18" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -15904,11 +15952,11 @@
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
-        <v>14.2</v>
+        <v>18.5</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>most-likely pairing (14%); France to advance</t>
+          <t>most-likely pairing (19%); France to advance</t>
         </is>
       </c>
     </row>
@@ -15979,7 +16027,7 @@
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -16011,7 +16059,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -16020,7 +16068,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -16028,19 +16076,19 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>46.1</v>
+        <v>38.4</v>
       </c>
       <c r="K20" t="n">
-        <v>27.4</v>
+        <v>27.2</v>
       </c>
       <c r="L20" t="n">
-        <v>26.5</v>
+        <v>34.4</v>
       </c>
       <c r="M20" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="N20" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -16054,11 +16102,11 @@
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>most-likely pairing (4%); Brazil to advance</t>
+          <t>most-likely pairing (5%); Brazil to advance</t>
         </is>
       </c>
     </row>
@@ -16095,7 +16143,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -16103,19 +16151,19 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>27.7</v>
+        <v>26.3</v>
       </c>
       <c r="K21" t="n">
-        <v>27.2</v>
+        <v>25.9</v>
       </c>
       <c r="L21" t="n">
-        <v>45.1</v>
+        <v>47.9</v>
       </c>
       <c r="M21" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="N21" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -16129,11 +16177,11 @@
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
-        <v>10.6</v>
+        <v>17.4</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>most-likely pairing (11%); England to advance</t>
+          <t>most-likely pairing (17%); England to advance</t>
         </is>
       </c>
     </row>
@@ -16156,7 +16204,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -16170,7 +16218,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -16178,16 +16226,16 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>25.8</v>
+        <v>25.1</v>
       </c>
       <c r="K22" t="n">
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
       <c r="L22" t="n">
-        <v>46.7</v>
+        <v>47.4</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="N22" t="n">
         <v>1.45</v>
@@ -16204,7 +16252,7 @@
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -16320,7 +16368,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -16328,19 +16376,19 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>55.4</v>
+        <v>58</v>
       </c>
       <c r="K24" t="n">
-        <v>24.8</v>
+        <v>23.9</v>
       </c>
       <c r="L24" t="n">
-        <v>19.8</v>
+        <v>18.1</v>
       </c>
       <c r="M24" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="N24" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -16349,16 +16397,16 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="n">
-        <v>8.5</v>
+        <v>11.6</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>most-likely pairing (8%); Argentina to advance</t>
+          <t>most-likely pairing (12%); Argentina to advance</t>
         </is>
       </c>
     </row>
@@ -16386,7 +16434,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -16403,19 +16451,19 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>24.3</v>
+        <v>24.7</v>
       </c>
       <c r="K25" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="L25" t="n">
-        <v>49.4</v>
+        <v>48.8</v>
       </c>
       <c r="M25" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -16429,11 +16477,11 @@
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>most-likely pairing (5%); Portugal to advance</t>
+          <t>most-likely pairing (6%); Colombia to advance</t>
         </is>
       </c>
     </row>
@@ -16456,21 +16504,21 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -16478,19 +16526,19 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>39.1</v>
+        <v>46.8</v>
       </c>
       <c r="K26" t="n">
-        <v>26.4</v>
+        <v>26</v>
       </c>
       <c r="L26" t="n">
-        <v>34.5</v>
+        <v>27.1</v>
       </c>
       <c r="M26" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="N26" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -16504,11 +16552,11 @@
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>most-likely pairing (3%); Germany to advance</t>
+          <t>most-likely pairing (3%); France to advance</t>
         </is>
       </c>
     </row>
@@ -16579,11 +16627,11 @@
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>most-likely pairing (4%); Spain to advance</t>
+          <t>most-likely pairing (5%); Spain to advance</t>
         </is>
       </c>
     </row>
@@ -16606,7 +16654,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -16616,11 +16664,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -16628,23 +16676,23 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>32.6</v>
+        <v>39.4</v>
       </c>
       <c r="K28" t="n">
-        <v>27.8</v>
+        <v>26.3</v>
       </c>
       <c r="L28" t="n">
-        <v>39.6</v>
+        <v>34.3</v>
       </c>
       <c r="M28" t="n">
-        <v>1.19</v>
+        <v>1.45</v>
       </c>
       <c r="N28" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Away</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -16654,11 +16702,11 @@
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>most-likely pairing (2%); England to advance</t>
+          <t>most-likely pairing (4%); France to advance</t>
         </is>
       </c>
     </row>
@@ -16686,7 +16734,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -16695,7 +16743,7 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -16703,19 +16751,19 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>45.3</v>
+        <v>48.3</v>
       </c>
       <c r="K29" t="n">
-        <v>27</v>
+        <v>26.4</v>
       </c>
       <c r="L29" t="n">
-        <v>27.8</v>
+        <v>25.3</v>
       </c>
       <c r="M29" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="N29" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -16729,11 +16777,11 @@
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="n">
-        <v>4.7</v>
+        <v>7.9</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>most-likely pairing (5%); Argentina to advance</t>
+          <t>most-likely pairing (8%); Argentina to advance</t>
         </is>
       </c>
     </row>
@@ -16756,7 +16804,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -16770,7 +16818,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -16778,19 +16826,19 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>27.5</v>
+        <v>32.3</v>
       </c>
       <c r="K30" t="n">
-        <v>26.2</v>
+        <v>28</v>
       </c>
       <c r="L30" t="n">
-        <v>46.3</v>
+        <v>39.7</v>
       </c>
       <c r="M30" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="N30" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -16804,11 +16852,11 @@
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>most-likely pairing (3%); Spain to advance</t>
+          <t>most-likely pairing (4%); Spain to advance</t>
         </is>
       </c>
     </row>
@@ -16853,19 +16901,19 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>30</v>
+        <v>29.7</v>
       </c>
       <c r="K31" t="n">
-        <v>27.3</v>
+        <v>26.2</v>
       </c>
       <c r="L31" t="n">
-        <v>42.7</v>
+        <v>44.1</v>
       </c>
       <c r="M31" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="N31" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -16879,11 +16927,11 @@
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>most-likely pairing (2%); Argentina to advance</t>
+          <t>most-likely pairing (6%); Argentina to advance</t>
         </is>
       </c>
     </row>
@@ -16916,11 +16964,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -16928,23 +16976,23 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>37.3</v>
+        <v>35</v>
       </c>
       <c r="K32" t="n">
         <v>28.5</v>
       </c>
       <c r="L32" t="n">
-        <v>34.2</v>
+        <v>36.5</v>
       </c>
       <c r="M32" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="N32" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -16954,11 +17002,11 @@
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>most-likely pairing (1%); Spain to advance</t>
+          <t>most-likely pairing (1%); Argentina to advance</t>
         </is>
       </c>
     </row>
@@ -16991,11 +17039,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -17003,23 +17051,23 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>37.3</v>
+        <v>35</v>
       </c>
       <c r="K33" t="n">
         <v>28.5</v>
       </c>
       <c r="L33" t="n">
-        <v>34.2</v>
+        <v>36.5</v>
       </c>
       <c r="M33" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="N33" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -17029,11 +17077,11 @@
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>most-likely pairing (2%); Spain to advance</t>
+          <t>most-likely pairing (3%); Argentina to advance</t>
         </is>
       </c>
     </row>
@@ -17109,16 +17157,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>61</v>
+        <v>60.7</v>
       </c>
       <c r="D2" t="n">
         <v>27</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G2" t="n">
         <v>97.5</v>
@@ -17136,19 +17184,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>32.6</v>
+        <v>32.9</v>
       </c>
       <c r="D3" t="n">
         <v>44.5</v>
       </c>
       <c r="E3" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="G3" t="n">
-        <v>91.90000000000001</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="4">
@@ -17163,19 +17211,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="D4" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="E4" t="n">
         <v>42.8</v>
       </c>
       <c r="F4" t="n">
-        <v>36.3</v>
+        <v>36.1</v>
       </c>
       <c r="G4" t="n">
-        <v>47.2</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="5">
@@ -17193,16 +17241,16 @@
         <v>1.8</v>
       </c>
       <c r="D5" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="E5" t="n">
         <v>27.3</v>
       </c>
       <c r="F5" t="n">
-        <v>58.7</v>
+        <v>58.8</v>
       </c>
       <c r="G5" t="n">
-        <v>29.9</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="6">
@@ -17217,19 +17265,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37</v>
+        <v>36.5</v>
       </c>
       <c r="D6" t="n">
-        <v>26.6</v>
+        <v>26.8</v>
       </c>
       <c r="E6" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>14.3</v>
       </c>
       <c r="G6" t="n">
-        <v>77.59999999999999</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="7">
@@ -17244,19 +17292,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>32.7</v>
+        <v>33.5</v>
       </c>
       <c r="D7" t="n">
-        <v>27.2</v>
+        <v>26.9</v>
       </c>
       <c r="E7" t="n">
-        <v>24</v>
+        <v>23.7</v>
       </c>
       <c r="F7" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>74.7</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="8">
@@ -17271,19 +17319,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="D8" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="E8" t="n">
-        <v>27.1</v>
+        <v>27.3</v>
       </c>
       <c r="F8" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="G8" t="n">
-        <v>56</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="9">
@@ -17298,19 +17346,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14.8</v>
+        <v>14.4</v>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="E9" t="n">
-        <v>26.4</v>
+        <v>26.8</v>
       </c>
       <c r="F9" t="n">
-        <v>35.8</v>
+        <v>35.6</v>
       </c>
       <c r="G9" t="n">
-        <v>54.4</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="10">
@@ -17325,19 +17373,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>35.9</v>
+        <v>36.1</v>
       </c>
       <c r="D10" t="n">
-        <v>27.7</v>
+        <v>27.6</v>
       </c>
       <c r="E10" t="n">
-        <v>30.7</v>
+        <v>30.5</v>
       </c>
       <c r="F10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="G10" t="n">
-        <v>86.3</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="11">
@@ -17352,19 +17400,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>34.4</v>
+        <v>34.2</v>
       </c>
       <c r="D11" t="n">
         <v>33.1</v>
       </c>
       <c r="E11" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="F11" t="n">
         <v>10.7</v>
       </c>
       <c r="G11" t="n">
-        <v>83.40000000000001</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="12">
@@ -17379,19 +17427,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
       </c>
       <c r="D12" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="E12" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="F12" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="G12" t="n">
-        <v>77.8</v>
+        <v>77.7</v>
       </c>
     </row>
     <row r="13">
@@ -17406,19 +17454,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="D13" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="E13" t="n">
         <v>20.9</v>
       </c>
       <c r="F13" t="n">
-        <v>68.59999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>23.9</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="14">
@@ -17433,19 +17481,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>57.4</v>
+        <v>57.5</v>
       </c>
       <c r="D14" t="n">
         <v>28</v>
       </c>
       <c r="E14" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G14" t="n">
-        <v>97.2</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -17460,19 +17508,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>36.6</v>
+        <v>36.3</v>
       </c>
       <c r="D15" t="n">
-        <v>41.4</v>
+        <v>42</v>
       </c>
       <c r="E15" t="n">
-        <v>18.8</v>
+        <v>18.5</v>
       </c>
       <c r="F15" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G15" t="n">
-        <v>93.09999999999999</v>
+        <v>93.5</v>
       </c>
     </row>
     <row r="16">
@@ -17487,19 +17535,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>17.1</v>
+        <v>16.6</v>
       </c>
       <c r="E16" t="n">
-        <v>39.6</v>
+        <v>39.8</v>
       </c>
       <c r="F16" t="n">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
       <c r="G16" t="n">
-        <v>45.4</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="17">
@@ -17514,19 +17562,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="D17" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="E17" t="n">
-        <v>28.5</v>
+        <v>28.6</v>
       </c>
       <c r="F17" t="n">
         <v>55.8</v>
       </c>
       <c r="G17" t="n">
-        <v>33.3</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="18">
@@ -17541,13 +17589,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>63.6</v>
+        <v>63.8</v>
       </c>
       <c r="D18" t="n">
         <v>23.5</v>
       </c>
       <c r="E18" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="F18" t="n">
         <v>0.3</v>
@@ -17568,19 +17616,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>32.3</v>
+        <v>32.1</v>
       </c>
       <c r="D19" t="n">
-        <v>46.7</v>
+        <v>47</v>
       </c>
       <c r="E19" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="F19" t="n">
         <v>1.4</v>
       </c>
       <c r="G19" t="n">
-        <v>94.3</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="20">
@@ -17598,16 +17646,16 @@
         <v>3.7</v>
       </c>
       <c r="D20" t="n">
-        <v>25.7</v>
+        <v>25.3</v>
       </c>
       <c r="E20" t="n">
-        <v>54.1</v>
+        <v>54.3</v>
       </c>
       <c r="F20" t="n">
-        <v>16.5</v>
+        <v>16.8</v>
       </c>
       <c r="G20" t="n">
-        <v>67.2</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="21">
@@ -17625,16 +17673,16 @@
         <v>0.4</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="E21" t="n">
-        <v>13.7</v>
+        <v>14</v>
       </c>
       <c r="F21" t="n">
-        <v>81.90000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="G21" t="n">
-        <v>11.1</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="22">
@@ -17649,19 +17697,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="D22" t="n">
-        <v>26.7</v>
+        <v>27.1</v>
       </c>
       <c r="E22" t="n">
-        <v>33</v>
+        <v>32.6</v>
       </c>
       <c r="F22" t="n">
         <v>3.5</v>
       </c>
       <c r="G22" t="n">
-        <v>93.3</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="23">
@@ -17676,19 +17724,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="D23" t="n">
-        <v>33.9</v>
+        <v>33.4</v>
       </c>
       <c r="E23" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="F23" t="n">
-        <v>10.9</v>
+        <v>11.4</v>
       </c>
       <c r="G23" t="n">
-        <v>83.5</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="24">
@@ -17703,19 +17751,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>28.4</v>
+        <v>28.2</v>
       </c>
       <c r="D24" t="n">
         <v>33.8</v>
       </c>
       <c r="E24" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="F24" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="G24" t="n">
-        <v>81.2</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -17730,19 +17778,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="D25" t="n">
         <v>5.6</v>
       </c>
       <c r="E25" t="n">
-        <v>19</v>
+        <v>19.4</v>
       </c>
       <c r="F25" t="n">
-        <v>72.7</v>
+        <v>72.2</v>
       </c>
       <c r="G25" t="n">
-        <v>18.5</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="26">
@@ -17757,19 +17805,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>34.3</v>
+        <v>34.1</v>
       </c>
       <c r="D26" t="n">
-        <v>27.5</v>
+        <v>27.2</v>
       </c>
       <c r="E26" t="n">
-        <v>21.5</v>
+        <v>22.2</v>
       </c>
       <c r="F26" t="n">
-        <v>16.7</v>
+        <v>16.5</v>
       </c>
       <c r="G26" t="n">
-        <v>77.2</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="27">
@@ -17793,7 +17841,7 @@
         <v>23.6</v>
       </c>
       <c r="F27" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="G27" t="n">
         <v>70.5</v>
@@ -17811,19 +17859,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="D28" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="E28" t="n">
-        <v>27.8</v>
+        <v>27.6</v>
       </c>
       <c r="F28" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="G28" t="n">
-        <v>63.7</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="29">
@@ -17841,16 +17889,16 @@
         <v>14.9</v>
       </c>
       <c r="D29" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="E29" t="n">
-        <v>27</v>
+        <v>26.6</v>
       </c>
       <c r="F29" t="n">
-        <v>37.5</v>
+        <v>37.8</v>
       </c>
       <c r="G29" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="30">
@@ -17865,19 +17913,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>52.6</v>
+        <v>52.1</v>
       </c>
       <c r="D30" t="n">
-        <v>24.8</v>
+        <v>25.2</v>
       </c>
       <c r="E30" t="n">
-        <v>15.3</v>
+        <v>15.1</v>
       </c>
       <c r="F30" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="G30" t="n">
-        <v>88.5</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="31">
@@ -17892,19 +17940,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="D31" t="n">
         <v>26.6</v>
       </c>
       <c r="E31" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="F31" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="G31" t="n">
-        <v>63.9</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -17919,19 +17967,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="D32" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="E32" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="F32" t="n">
-        <v>30.9</v>
+        <v>30.6</v>
       </c>
       <c r="G32" t="n">
-        <v>60.7</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="33">
@@ -17946,19 +17994,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="D33" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="E33" t="n">
         <v>28.9</v>
       </c>
       <c r="F33" t="n">
-        <v>40</v>
+        <v>40.3</v>
       </c>
       <c r="G33" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="34">
@@ -17973,19 +18021,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>47.8</v>
+        <v>61.6</v>
       </c>
       <c r="D34" t="n">
-        <v>28.3</v>
+        <v>32.6</v>
       </c>
       <c r="E34" t="n">
-        <v>16.6</v>
+        <v>5.4</v>
       </c>
       <c r="F34" t="n">
-        <v>7.3</v>
+        <v>0.4</v>
       </c>
       <c r="G34" t="n">
-        <v>88.90000000000001</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35">
@@ -18000,19 +18048,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>26.2</v>
+        <v>35.6</v>
       </c>
       <c r="D35" t="n">
-        <v>31</v>
+        <v>43.8</v>
       </c>
       <c r="E35" t="n">
-        <v>27.2</v>
+        <v>19.9</v>
       </c>
       <c r="F35" t="n">
-        <v>15.7</v>
+        <v>0.6</v>
       </c>
       <c r="G35" t="n">
-        <v>75.8</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -18027,19 +18075,19 @@
         </is>
       </c>
       <c r="C36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D36" t="n">
         <v>20.5</v>
       </c>
-      <c r="D36" t="n">
-        <v>28.2</v>
-      </c>
       <c r="E36" t="n">
-        <v>31.1</v>
+        <v>54.4</v>
       </c>
       <c r="F36" t="n">
-        <v>20.2</v>
+        <v>22.7</v>
       </c>
       <c r="G36" t="n">
-        <v>69.2</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="37">
@@ -18054,19 +18102,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5.5</v>
+        <v>0.4</v>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>25.2</v>
+        <v>20.3</v>
       </c>
       <c r="F37" t="n">
-        <v>56.8</v>
+        <v>76.2</v>
       </c>
       <c r="G37" t="n">
-        <v>32</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="38">
@@ -18081,19 +18129,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>54.7</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>25.4</v>
+        <v>20.6</v>
       </c>
       <c r="E38" t="n">
-        <v>13.4</v>
+        <v>3.9</v>
       </c>
       <c r="F38" t="n">
-        <v>6.6</v>
+        <v>0.3</v>
       </c>
       <c r="G38" t="n">
-        <v>90.40000000000001</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -18108,19 +18156,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>18.2</v>
+        <v>22.6</v>
       </c>
       <c r="D39" t="n">
-        <v>27.4</v>
+        <v>53</v>
       </c>
       <c r="E39" t="n">
-        <v>28.8</v>
+        <v>22.5</v>
       </c>
       <c r="F39" t="n">
-        <v>25.6</v>
+        <v>2</v>
       </c>
       <c r="G39" t="n">
-        <v>64.3</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -18135,19 +18183,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>17.2</v>
+        <v>1.4</v>
       </c>
       <c r="D40" t="n">
-        <v>27.5</v>
+        <v>19.8</v>
       </c>
       <c r="E40" t="n">
-        <v>29.3</v>
+        <v>39.8</v>
       </c>
       <c r="F40" t="n">
-        <v>26</v>
+        <v>38.9</v>
       </c>
       <c r="G40" t="n">
-        <v>63.4</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="41">
@@ -18162,19 +18210,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>9.9</v>
+        <v>0.9</v>
       </c>
       <c r="D41" t="n">
-        <v>19.7</v>
+        <v>6.6</v>
       </c>
       <c r="E41" t="n">
-        <v>28.6</v>
+        <v>33.8</v>
       </c>
       <c r="F41" t="n">
-        <v>41.8</v>
+        <v>58.8</v>
       </c>
       <c r="G41" t="n">
-        <v>46.4</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="42">
@@ -18185,23 +18233,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>40.8</v>
+        <v>47</v>
       </c>
       <c r="D42" t="n">
-        <v>31</v>
+        <v>24.9</v>
       </c>
       <c r="E42" t="n">
-        <v>19.2</v>
+        <v>16.8</v>
       </c>
       <c r="F42" t="n">
-        <v>9</v>
+        <v>11.4</v>
       </c>
       <c r="G42" t="n">
-        <v>86.09999999999999</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -18212,23 +18260,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>38.8</v>
+        <v>27</v>
       </c>
       <c r="D43" t="n">
-        <v>32.2</v>
+        <v>33.1</v>
       </c>
       <c r="E43" t="n">
-        <v>19.6</v>
+        <v>26.3</v>
       </c>
       <c r="F43" t="n">
-        <v>9.300000000000001</v>
+        <v>13.6</v>
       </c>
       <c r="G43" t="n">
-        <v>85.5</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="44">
@@ -18243,16 +18291,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>14.6</v>
+        <v>18.4</v>
       </c>
       <c r="D44" t="n">
         <v>23.7</v>
       </c>
       <c r="E44" t="n">
-        <v>34</v>
+        <v>26.5</v>
       </c>
       <c r="F44" t="n">
-        <v>27.6</v>
+        <v>31.4</v>
       </c>
       <c r="G44" t="n">
         <v>59.5</v>
@@ -18270,19 +18318,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="D45" t="n">
-        <v>13</v>
+        <v>18.4</v>
       </c>
       <c r="E45" t="n">
-        <v>27.1</v>
+        <v>30.4</v>
       </c>
       <c r="F45" t="n">
-        <v>54</v>
+        <v>43.6</v>
       </c>
       <c r="G45" t="n">
-        <v>33.9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46">
@@ -18297,19 +18345,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>46.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>28</v>
+        <v>18.4</v>
       </c>
       <c r="E46" t="n">
-        <v>17</v>
+        <v>4.9</v>
       </c>
       <c r="F46" t="n">
-        <v>8.5</v>
+        <v>1.1</v>
       </c>
       <c r="G46" t="n">
-        <v>87.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -18324,19 +18372,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>29.2</v>
+        <v>5</v>
       </c>
       <c r="D47" t="n">
-        <v>31.1</v>
+        <v>35.2</v>
       </c>
       <c r="E47" t="n">
-        <v>24.2</v>
+        <v>35.3</v>
       </c>
       <c r="F47" t="n">
-        <v>15.5</v>
+        <v>24.5</v>
       </c>
       <c r="G47" t="n">
-        <v>77.09999999999999</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="48">
@@ -18351,19 +18399,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>16.3</v>
+        <v>13.4</v>
       </c>
       <c r="D48" t="n">
-        <v>25</v>
+        <v>28.3</v>
       </c>
       <c r="E48" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="F48" t="n">
-        <v>27.4</v>
+        <v>27</v>
       </c>
       <c r="G48" t="n">
-        <v>61.4</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="49">
@@ -18378,19 +18426,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D49" t="n">
-        <v>15.9</v>
+        <v>18.1</v>
       </c>
       <c r="E49" t="n">
-        <v>27.4</v>
+        <v>28.5</v>
       </c>
       <c r="F49" t="n">
-        <v>48.6</v>
+        <v>47.5</v>
       </c>
       <c r="G49" t="n">
-        <v>39.7</v>
+        <v>40.6</v>
       </c>
     </row>
   </sheetData>
@@ -18456,55 +18504,55 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>88.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>39.4</v>
+        <v>48.8</v>
       </c>
       <c r="E2" t="n">
-        <v>27.5</v>
+        <v>34.1</v>
       </c>
       <c r="F2" t="n">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="G2" t="n">
-        <v>11.4</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>90.40000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="D3" t="n">
-        <v>41.2</v>
+        <v>39.2</v>
       </c>
       <c r="E3" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="F3" t="n">
-        <v>17.6</v>
+        <v>17.9</v>
       </c>
       <c r="G3" t="n">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="4">
@@ -18519,19 +18567,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>88.90000000000001</v>
+        <v>99</v>
       </c>
       <c r="D4" t="n">
-        <v>37</v>
+        <v>42.6</v>
       </c>
       <c r="E4" t="n">
-        <v>23.5</v>
+        <v>27.7</v>
       </c>
       <c r="F4" t="n">
-        <v>13.9</v>
+        <v>16.6</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -18546,19 +18594,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>87.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>32.6</v>
+        <v>40.7</v>
       </c>
       <c r="E5" t="n">
-        <v>19.4</v>
+        <v>24.2</v>
       </c>
       <c r="F5" t="n">
-        <v>10.9</v>
+        <v>13.5</v>
       </c>
       <c r="G5" t="n">
-        <v>6.1</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="6">
@@ -18576,22 +18624,22 @@
         <v>99.40000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>33.8</v>
+        <v>32.6</v>
       </c>
       <c r="E6" t="n">
-        <v>20.2</v>
+        <v>19.1</v>
       </c>
       <c r="F6" t="n">
-        <v>10.9</v>
+        <v>10.5</v>
       </c>
       <c r="G6" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -18600,208 +18648,208 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>86.09999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>29.8</v>
+        <v>30.5</v>
       </c>
       <c r="E7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="G7" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>85.5</v>
+        <v>83.7</v>
       </c>
       <c r="D8" t="n">
-        <v>29.1</v>
+        <v>27.7</v>
       </c>
       <c r="E8" t="n">
-        <v>16.2</v>
+        <v>14.4</v>
       </c>
       <c r="F8" t="n">
-        <v>8.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="G8" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>83.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>28</v>
+        <v>28.9</v>
       </c>
       <c r="E9" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="F9" t="n">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>83.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>26.1</v>
+        <v>24.5</v>
       </c>
       <c r="E10" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="F10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="G10" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>75.8</v>
+        <v>83.2</v>
       </c>
       <c r="D11" t="n">
-        <v>22</v>
+        <v>25.4</v>
       </c>
       <c r="E11" t="n">
-        <v>11.5</v>
+        <v>12.9</v>
       </c>
       <c r="F11" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>81.2</v>
+        <v>97.5</v>
       </c>
       <c r="D12" t="n">
-        <v>22.5</v>
+        <v>25.7</v>
       </c>
       <c r="E12" t="n">
-        <v>10.9</v>
+        <v>11.8</v>
       </c>
       <c r="F12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>97.5</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E13" t="n">
-        <v>12.4</v>
+        <v>10.6</v>
       </c>
       <c r="F13" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>77.09999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>21.4</v>
+        <v>25.4</v>
       </c>
       <c r="E14" t="n">
         <v>11.1</v>
       </c>
       <c r="F14" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="15">
@@ -18816,19 +18864,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>67.2</v>
+        <v>67.8</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="E15" t="n">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="F15" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -18843,46 +18891,46 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>77.2</v>
+        <v>77.3</v>
       </c>
       <c r="D16" t="n">
-        <v>21.3</v>
+        <v>20.3</v>
       </c>
       <c r="E16" t="n">
-        <v>9.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>97.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>25.4</v>
+        <v>20.6</v>
       </c>
       <c r="E17" t="n">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="F17" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="G17" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="18">
@@ -18897,19 +18945,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>77.8</v>
+        <v>77.7</v>
       </c>
       <c r="D18" t="n">
-        <v>20</v>
+        <v>19.7</v>
       </c>
       <c r="E18" t="n">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="F18" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="19">
@@ -18924,19 +18972,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>93.09999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="D19" t="n">
-        <v>22.4</v>
+        <v>21.4</v>
       </c>
       <c r="E19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="20">
@@ -18951,73 +18999,73 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>63.9</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.2</v>
       </c>
       <c r="E20" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="F20" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="G20" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>74.7</v>
+        <v>63.7</v>
       </c>
       <c r="D21" t="n">
-        <v>18.6</v>
+        <v>15.9</v>
       </c>
       <c r="E21" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="F21" t="n">
         <v>3.6</v>
       </c>
       <c r="G21" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>69.2</v>
+        <v>75.3</v>
       </c>
       <c r="D22" t="n">
-        <v>17.2</v>
+        <v>18.7</v>
       </c>
       <c r="E22" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="F22" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="G22" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="23">
@@ -19032,178 +19080,178 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>94.3</v>
+        <v>94.5</v>
       </c>
       <c r="D23" t="n">
-        <v>19.2</v>
+        <v>18.2</v>
       </c>
       <c r="E23" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="G23" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>64.3</v>
+        <v>86.7</v>
       </c>
       <c r="D24" t="n">
-        <v>14.8</v>
+        <v>16.8</v>
       </c>
       <c r="E24" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="F24" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="G24" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>63.4</v>
+        <v>45.6</v>
       </c>
       <c r="D25" t="n">
-        <v>14</v>
+        <v>10.1</v>
       </c>
       <c r="E25" t="n">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="G25" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>86.3</v>
+        <v>77.5</v>
       </c>
       <c r="D26" t="n">
-        <v>17.4</v>
+        <v>16.8</v>
       </c>
       <c r="E26" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="F26" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="G26" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>91.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="D27" t="n">
-        <v>19.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="n">
-        <v>7.7</v>
+        <v>5.8</v>
       </c>
       <c r="F27" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="G27" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>77.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="D28" t="n">
-        <v>16.5</v>
+        <v>14.2</v>
       </c>
       <c r="E28" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="F28" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="G28" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>45.4</v>
+        <v>92.3</v>
       </c>
       <c r="D29" t="n">
-        <v>10.4</v>
+        <v>18.9</v>
       </c>
       <c r="E29" t="n">
-        <v>5.2</v>
+        <v>7.1</v>
       </c>
       <c r="F29" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -19212,22 +19260,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>63.7</v>
+        <v>56.6</v>
       </c>
       <c r="D30" t="n">
-        <v>13.7</v>
+        <v>12.8</v>
       </c>
       <c r="E30" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="F30" t="n">
         <v>2.4</v>
@@ -19239,52 +19287,52 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>70.5</v>
+        <v>93.7</v>
       </c>
       <c r="D31" t="n">
-        <v>14.4</v>
+        <v>16</v>
       </c>
       <c r="E31" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="F31" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>93.3</v>
+        <v>61.5</v>
       </c>
       <c r="D32" t="n">
-        <v>16.3</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="F32" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="G32" t="n">
         <v>0.8</v>
@@ -19293,52 +19341,52 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>61.4</v>
+        <v>44.1</v>
       </c>
       <c r="D33" t="n">
-        <v>11.3</v>
+        <v>8.6</v>
       </c>
       <c r="E33" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="F33" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="G33" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>47.2</v>
+        <v>59.5</v>
       </c>
       <c r="D34" t="n">
-        <v>9</v>
+        <v>10.2</v>
       </c>
       <c r="E34" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="F34" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="G34" t="n">
         <v>0.5</v>
@@ -19347,49 +19395,49 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>59.5</v>
+        <v>48.2</v>
       </c>
       <c r="D35" t="n">
-        <v>10.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="F35" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="G35" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>46.4</v>
+        <v>61.1</v>
       </c>
       <c r="D36" t="n">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="E36" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="F36" t="n">
         <v>1.1</v>
@@ -19401,25 +19449,25 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>60.7</v>
+        <v>33.9</v>
       </c>
       <c r="D37" t="n">
-        <v>8.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="E37" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="F37" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
         <v>0.4</v>
@@ -19428,52 +19476,52 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>33.3</v>
+        <v>46.6</v>
       </c>
       <c r="D38" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="E38" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="F38" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="G38" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>46.7</v>
+        <v>49.9</v>
       </c>
       <c r="D39" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="E39" t="n">
         <v>1.9</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G39" t="n">
         <v>0.2</v>
@@ -19482,28 +19530,28 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>50</v>
+        <v>24.1</v>
       </c>
       <c r="D40" t="n">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="E40" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G40" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="41">
@@ -19518,13 +19566,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>18.5</v>
+        <v>19.1</v>
       </c>
       <c r="D41" t="n">
         <v>2.5</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F41" t="n">
         <v>0.3</v>
@@ -19545,13 +19593,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>29.9</v>
+        <v>30.2</v>
       </c>
       <c r="D42" t="n">
         <v>3.6</v>
       </c>
       <c r="E42" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="F42" t="n">
         <v>0.3</v>
@@ -19563,19 +19611,19 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D43" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="E43" t="n">
         <v>1.1</v>
@@ -19590,25 +19638,25 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>33.9</v>
+        <v>54.6</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>5.6</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G44" t="n">
         <v>0.1</v>
@@ -19617,25 +19665,25 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>54.4</v>
+        <v>24.8</v>
       </c>
       <c r="D45" t="n">
-        <v>5.5</v>
+        <v>2.7</v>
       </c>
       <c r="E45" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G45" t="n">
         <v>0.1</v>
@@ -19644,25 +19692,25 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>23.9</v>
+        <v>40.6</v>
       </c>
       <c r="D46" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="F46" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G46" t="n">
         <v>0.1</v>
@@ -19671,22 +19719,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>39.7</v>
+        <v>56.2</v>
       </c>
       <c r="D47" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="E47" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="F47" t="n">
         <v>0.5</v>
@@ -19698,28 +19746,28 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>56</v>
+        <v>13.2</v>
       </c>
       <c r="D48" t="n">
-        <v>6.1</v>
+        <v>1.3</v>
       </c>
       <c r="E48" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="F48" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -19734,16 +19782,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>11.1</v>
+        <v>11.4</v>
       </c>
       <c r="D49" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E49" t="n">
         <v>0.2</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -19848,27 +19896,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>UEFA</t>
+          <t>CONMEBOL</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2157</v>
+        <v>2115</v>
       </c>
       <c r="E2" t="n">
-        <v>2137</v>
+        <v>2149</v>
       </c>
       <c r="F2" t="n">
-        <v>-20</v>
+        <v>34</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -19876,48 +19924,48 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>11.4</v>
+        <v>13.7</v>
       </c>
       <c r="L2" t="n">
-        <v>17.8</v>
+        <v>21.8</v>
       </c>
       <c r="M2" t="n">
-        <v>88.5</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CONMEBOL</t>
+          <t>UEFA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2115</v>
+        <v>2157</v>
       </c>
       <c r="E3" t="n">
-        <v>2115</v>
+        <v>2137</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -19925,22 +19973,22 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="L3" t="n">
-        <v>17.6</v>
+        <v>17.9</v>
       </c>
       <c r="M3" t="n">
-        <v>90.40000000000001</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="4">
@@ -19963,10 +20011,10 @@
         <v>2063</v>
       </c>
       <c r="E4" t="n">
-        <v>2063</v>
+        <v>2084</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -19980,16 +20028,16 @@
         <v>88</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>13.9</v>
+        <v>16.6</v>
       </c>
       <c r="M4" t="n">
-        <v>88.90000000000001</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5">
@@ -20012,10 +20060,10 @@
         <v>2024</v>
       </c>
       <c r="E5" t="n">
-        <v>2024</v>
+        <v>2049</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -20029,16 +20077,16 @@
         <v>85</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>6.1</v>
+        <v>7.6</v>
       </c>
       <c r="L5" t="n">
-        <v>10.9</v>
+        <v>13.5</v>
       </c>
       <c r="M5" t="n">
-        <v>87.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -20081,10 +20129,10 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="L6" t="n">
-        <v>10.9</v>
+        <v>10.5</v>
       </c>
       <c r="M6" t="n">
         <v>99.40000000000001</v>
@@ -20093,7 +20141,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -20103,14 +20151,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UEFA</t>
+          <t>CONMEBOL</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1989</v>
+        <v>1982</v>
       </c>
       <c r="E7" t="n">
-        <v>1989</v>
+        <v>1982</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -20121,33 +20169,33 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I7" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L7" t="n">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="M7" t="n">
-        <v>86.09999999999999</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -20156,13 +20204,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1982</v>
+        <v>1978</v>
       </c>
       <c r="E8" t="n">
-        <v>1982</v>
+        <v>1973</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -20170,48 +20218,48 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="L8" t="n">
-        <v>8.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="M8" t="n">
-        <v>85.5</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CONMEBOL</t>
+          <t>UEFA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1978</v>
+        <v>1989</v>
       </c>
       <c r="E9" t="n">
-        <v>1973</v>
+        <v>1970</v>
       </c>
       <c r="F9" t="n">
-        <v>-5</v>
+        <v>-19</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -20219,22 +20267,22 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="L9" t="n">
-        <v>7.9</v>
+        <v>7.2</v>
       </c>
       <c r="M9" t="n">
-        <v>83.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -20277,39 +20325,39 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L10" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="M10" t="n">
-        <v>83.5</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CONMEBOL</t>
+          <t>UEFA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1938</v>
+        <v>1914</v>
       </c>
       <c r="E11" t="n">
-        <v>1916</v>
+        <v>1945</v>
       </c>
       <c r="F11" t="n">
-        <v>-22</v>
+        <v>31</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -20317,46 +20365,48 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>23</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="I11" t="n">
+        <v>75</v>
+      </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="L11" t="n">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="M11" t="n">
-        <v>67.2</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UEFA</t>
+          <t>CONMEBOL</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1914</v>
+        <v>1938</v>
       </c>
       <c r="E12" t="n">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -20364,48 +20414,46 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>29</v>
-      </c>
-      <c r="I12" t="n">
-        <v>75</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="M12" t="n">
-        <v>75.8</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UEFA</t>
+          <t>AFC</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1912</v>
+        <v>1906</v>
       </c>
       <c r="E13" t="n">
-        <v>1912</v>
+        <v>1908</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -20413,46 +20461,46 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="L13" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="M13" t="n">
-        <v>77.09999999999999</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AFC</t>
+          <t>CONCACAF</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1906</v>
+        <v>1881</v>
       </c>
       <c r="E14" t="n">
-        <v>1908</v>
+        <v>1897</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -20460,46 +20508,48 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>18</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="I14" t="n">
+        <v>71</v>
+      </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="L14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="M14" t="n">
-        <v>81.2</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CONCACAF</t>
+          <t>UEFA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1881</v>
+        <v>1894</v>
       </c>
       <c r="E15" t="n">
-        <v>1897</v>
+        <v>1890</v>
       </c>
       <c r="F15" t="n">
-        <v>16</v>
+        <v>-4</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -20507,33 +20557,33 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I15" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="L15" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="M15" t="n">
-        <v>97.5</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -20542,13 +20592,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1894</v>
+        <v>1912</v>
       </c>
       <c r="E16" t="n">
-        <v>1890</v>
+        <v>1887</v>
       </c>
       <c r="F16" t="n">
-        <v>-4</v>
+        <v>-25</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -20556,22 +20606,20 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>8</v>
-      </c>
-      <c r="I16" t="n">
-        <v>77</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
         <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="L16" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="M16" t="n">
-        <v>77.2</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="17">
@@ -20614,13 +20662,13 @@
         <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="L17" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="M17" t="n">
-        <v>63.9</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -20661,24 +20709,24 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="L18" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="M18" t="n">
-        <v>77.8</v>
+        <v>77.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -20687,79 +20735,79 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1903</v>
+        <v>1846</v>
       </c>
       <c r="E19" t="n">
-        <v>1868</v>
+        <v>1871</v>
       </c>
       <c r="F19" t="n">
-        <v>-35</v>
+        <v>25</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>blend(metis)</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>blend(metis+fifa)</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>24</v>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
         <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="L19" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="M19" t="n">
-        <v>45.4</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>UEFA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1860</v>
+        <v>1903</v>
       </c>
       <c r="E20" t="n">
-        <v>1860</v>
+        <v>1868</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-35</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>eloratings.net</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>19</v>
-      </c>
+          <t>blend(metis)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="L20" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="M20" t="n">
-        <v>69.2</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="21">
@@ -20803,10 +20851,10 @@
         <v>2.1</v>
       </c>
       <c r="L21" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="M21" t="n">
-        <v>97.2</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -20847,13 +20895,13 @@
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="L22" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="M22" t="n">
-        <v>74.7</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="23">
@@ -20894,71 +20942,71 @@
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="L23" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="M23" t="n">
-        <v>93.09999999999999</v>
+        <v>93.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UEFA</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1846</v>
+        <v>1860</v>
       </c>
       <c r="E24" t="n">
-        <v>1846</v>
+        <v>1839</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>blend(metis+fifa)</t>
+          <t>eloratings.net</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="L24" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="M24" t="n">
-        <v>64.3</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -20967,13 +21015,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1839</v>
+        <v>1806</v>
       </c>
       <c r="E25" t="n">
-        <v>1839</v>
+        <v>1828</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -20981,46 +21029,46 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>1.3</v>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="M25" t="n">
-        <v>63.4</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>AFC</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1806</v>
+        <v>1824</v>
       </c>
       <c r="E26" t="n">
-        <v>1828</v>
+        <v>1816</v>
       </c>
       <c r="F26" t="n">
-        <v>22</v>
+        <v>-8</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -21028,46 +21076,46 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="M26" t="n">
-        <v>94.3</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AFC</t>
+          <t>UEFA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1824</v>
+        <v>1805</v>
       </c>
       <c r="E27" t="n">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="F27" t="n">
-        <v>-8</v>
+        <v>10</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -21075,46 +21123,46 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="L27" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="M27" t="n">
-        <v>63.7</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>UEFA</t>
+          <t>CONCACAF</t>
         </is>
       </c>
       <c r="D28" t="n">
+        <v>1820</v>
+      </c>
+      <c r="E28" t="n">
         <v>1805</v>
       </c>
-      <c r="E28" t="n">
-        <v>1815</v>
-      </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>-14</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -21122,46 +21170,46 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
         <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="M28" t="n">
-        <v>86.3</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CONCACAF</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1820</v>
+        <v>1839</v>
       </c>
       <c r="E29" t="n">
         <v>1805</v>
       </c>
       <c r="F29" t="n">
-        <v>-14</v>
+        <v>-34</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -21169,20 +21217,20 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
         <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="L29" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="M29" t="n">
-        <v>77.59999999999999</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="30">
@@ -21225,13 +21273,13 @@
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="M30" t="n">
-        <v>91.90000000000001</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="31">
@@ -21272,10 +21320,10 @@
         <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="M31" t="n">
         <v>70.5</v>
@@ -21322,10 +21370,10 @@
         <v>0.8</v>
       </c>
       <c r="L32" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>61.4</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="33">
@@ -21369,10 +21417,10 @@
         <v>0.4</v>
       </c>
       <c r="L33" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>33.3</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="34">
@@ -21414,10 +21462,10 @@
         <v>0.8</v>
       </c>
       <c r="L34" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="M34" t="n">
-        <v>93.3</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="35">
@@ -21461,7 +21509,7 @@
         <v>0.5</v>
       </c>
       <c r="L35" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="M35" t="n">
         <v>59.5</v>
@@ -21505,13 +21553,13 @@
         <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="L36" t="n">
         <v>1.3</v>
       </c>
       <c r="M36" t="n">
-        <v>47.2</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="37">
@@ -21555,10 +21603,10 @@
         <v>0.4</v>
       </c>
       <c r="L37" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="M37" t="n">
-        <v>60.7</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="38">
@@ -21581,10 +21629,10 @@
         <v>1728</v>
       </c>
       <c r="E38" t="n">
-        <v>1728</v>
+        <v>1702</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -21596,16 +21644,16 @@
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="L38" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="M38" t="n">
-        <v>46.4</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="39">
@@ -21652,7 +21700,7 @@
         <v>0.7</v>
       </c>
       <c r="M39" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="40">
@@ -21699,7 +21747,7 @@
         <v>0.3</v>
       </c>
       <c r="M40" t="n">
-        <v>18.5</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="41">
@@ -21743,10 +21791,10 @@
         <v>0.2</v>
       </c>
       <c r="L41" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="M41" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="42">
@@ -21790,10 +21838,10 @@
         <v>0.1</v>
       </c>
       <c r="L42" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="M42" t="n">
-        <v>39.7</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="43">
@@ -21840,7 +21888,7 @@
         <v>0.3</v>
       </c>
       <c r="M43" t="n">
-        <v>23.9</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="44">
@@ -21887,7 +21935,7 @@
         <v>0.5</v>
       </c>
       <c r="M44" t="n">
-        <v>56</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="45">
@@ -21936,33 +21984,33 @@
         <v>0.3</v>
       </c>
       <c r="M45" t="n">
-        <v>29.9</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AFC</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1608</v>
+        <v>1588</v>
       </c>
       <c r="E46" t="n">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -21972,7 +22020,7 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
         <v>0.1</v>
@@ -21981,7 +22029,7 @@
         <v>0.3</v>
       </c>
       <c r="M46" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47">
@@ -22026,33 +22074,33 @@
         <v>0.4</v>
       </c>
       <c r="M47" t="n">
-        <v>54.4</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>AFC</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1588</v>
+        <v>1608</v>
       </c>
       <c r="E48" t="n">
-        <v>1588</v>
+        <v>1578</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>-31</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -22062,16 +22110,16 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
         <v>0</v>
       </c>
-      <c r="K48" t="n">
+      <c r="L48" t="n">
         <v>0.1</v>
       </c>
-      <c r="L48" t="n">
-        <v>0.3</v>
-      </c>
       <c r="M48" t="n">
-        <v>33.9</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="49">
@@ -22115,10 +22163,10 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M49" t="n">
-        <v>11.1</v>
+        <v>11.4</v>
       </c>
     </row>
   </sheetData>
@@ -22132,7 +22180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -22785,6 +22833,228 @@
         <v>0</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Argentina 3-0 Algeria</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.5653447610298761</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.242932655319136</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.191722583650988</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1128413629229928</v>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Austria 3-1 Jordan</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.4465822656526882</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.270736216737822</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.2826815176094898</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.193090014544058</v>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>France 3-1 Senegal</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.5101967760009811</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.2582711067810726</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.2315321172179463</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.146757159771629</v>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Iraq 1-4 Norway</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.1771341674124645</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2358428959472877</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.587022936640248</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1009632840630759</v>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>England 4-2 Croatia</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.4421686007896301</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.2713758294277268</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.2864555697826432</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.196616331702249</v>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Portugal 1-1 DR Congo</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.6563191675226661</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.2094436649180234</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.1342371675593106</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2243872334059959</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/world_cup_2026_recommendations.xlsx
+++ b/outputs/world_cup_2026_recommendations.xlsx
@@ -549,7 +549,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>• Matches scored: 52   Outcome hit-rate: 60%   Mean RPS: 0.179  (good tournament forecasts ~0.17-0.18)</t>
+          <t>• Matches scored: 54   Outcome hit-rate: 59%   Mean RPS: 0.182  (good tournament forecasts ~0.17-0.18)</t>
         </is>
       </c>
     </row>
@@ -802,19 +802,19 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>61.5</v>
+        <v>62</v>
       </c>
       <c r="K2" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="L2" t="n">
-        <v>15.2</v>
+        <v>14.8</v>
       </c>
       <c r="M2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="N2" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -883,19 +883,19 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>39.5</v>
+        <v>40</v>
       </c>
       <c r="K3" t="n">
-        <v>27.9</v>
+        <v>28.2</v>
       </c>
       <c r="L3" t="n">
-        <v>32.6</v>
+        <v>31.8</v>
       </c>
       <c r="M3" t="n">
         <v>1.32</v>
       </c>
       <c r="N3" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2746,19 +2746,19 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>49.3</v>
+        <v>53</v>
       </c>
       <c r="K26" t="n">
-        <v>27.1</v>
+        <v>26.4</v>
       </c>
       <c r="L26" t="n">
-        <v>23.7</v>
+        <v>20.7</v>
       </c>
       <c r="M26" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="N26" t="n">
-        <v>0.96</v>
+        <v>0.88</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2827,19 +2827,19 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>44.5</v>
+        <v>40.4</v>
       </c>
       <c r="K27" t="n">
-        <v>27.4</v>
+        <v>28.2</v>
       </c>
       <c r="L27" t="n">
-        <v>28.1</v>
+        <v>31.5</v>
       </c>
       <c r="M27" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="N27" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -4678,31 +4678,31 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>final</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>25</v>
+        <v>27.4</v>
       </c>
       <c r="K50" t="n">
-        <v>27.1</v>
+        <v>28.6</v>
       </c>
       <c r="L50" t="n">
-        <v>47.9</v>
+        <v>44</v>
       </c>
       <c r="M50" t="n">
         <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -4714,11 +4714,15 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 45)</t>
+          <t>actual 1-0; model pick 0-1 (outcome miss)</t>
         </is>
       </c>
     </row>
@@ -4755,47 +4759,51 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>53</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="K51" t="n">
+        <v>24</v>
+      </c>
+      <c r="L51" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="H51" t="n">
-        <v>50</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>scheduled</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
-        <v>21</v>
-      </c>
-      <c r="K51" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="L51" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="N51" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 50)</t>
+          <t>actual 0-3; model pick 0-1 (outcome hit)</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6536,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -6542,7 +6550,7 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -6550,19 +6558,19 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>31.7</v>
+        <v>22.5</v>
       </c>
       <c r="K74" t="n">
-        <v>27.2</v>
+        <v>25.7</v>
       </c>
       <c r="L74" t="n">
-        <v>41.1</v>
+        <v>51.8</v>
       </c>
       <c r="M74" t="n">
-        <v>1.21</v>
+        <v>0.99</v>
       </c>
       <c r="N74" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -6576,11 +6584,11 @@
       </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="n">
-        <v>63.8</v>
+        <v>100</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>most-likely pairing (64%); Canada to advance</t>
+          <t>most-likely pairing (100%); Canada to advance</t>
         </is>
       </c>
     </row>
@@ -6651,11 +6659,11 @@
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="n">
-        <v>26.8</v>
+        <v>38.3</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>most-likely pairing (27%); Germany to advance</t>
+          <t>most-likely pairing (38%); Germany to advance</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6734,7 @@
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="n">
-        <v>55.1</v>
+        <v>55.3</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -6801,7 +6809,7 @@
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="n">
-        <v>43.7</v>
+        <v>43.5</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -6876,11 +6884,11 @@
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="n">
-        <v>20.7</v>
+        <v>19.9</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>most-likely pairing (21%); France to advance</t>
+          <t>most-likely pairing (20%); France to advance</t>
         </is>
       </c>
     </row>
@@ -6951,7 +6959,7 @@
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="n">
-        <v>55.3</v>
+        <v>55.2</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -6992,7 +7000,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -7000,19 +7008,19 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>45</v>
+        <v>47.5</v>
       </c>
       <c r="K80" t="n">
-        <v>28.4</v>
+        <v>27.8</v>
       </c>
       <c r="L80" t="n">
-        <v>26.5</v>
+        <v>24.7</v>
       </c>
       <c r="M80" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="N80" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -7026,11 +7034,11 @@
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="n">
-        <v>35.1</v>
+        <v>23.4</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>most-likely pairing (35%); Mexico to advance</t>
+          <t>most-likely pairing (23%); Mexico to advance</t>
         </is>
       </c>
     </row>
@@ -7101,7 +7109,7 @@
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -7176,11 +7184,11 @@
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="n">
-        <v>72.3</v>
+        <v>60.9</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>most-likely pairing (72%); United States to advance</t>
+          <t>most-likely pairing (61%); United States to advance</t>
         </is>
       </c>
     </row>
@@ -7217,7 +7225,7 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -7225,19 +7233,19 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>38.2</v>
+        <v>39.5</v>
       </c>
       <c r="K83" t="n">
-        <v>27.8</v>
+        <v>28.1</v>
       </c>
       <c r="L83" t="n">
-        <v>34.1</v>
+        <v>32.4</v>
       </c>
       <c r="M83" t="n">
         <v>1.31</v>
       </c>
       <c r="N83" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -7251,11 +7259,11 @@
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="n">
-        <v>12.1</v>
+        <v>53.9</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>most-likely pairing (12%); Egypt to advance</t>
+          <t>most-likely pairing (54%); Egypt to advance</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7334,7 @@
       </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="n">
-        <v>22.9</v>
+        <v>22.5</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -7476,11 +7484,11 @@
       </c>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="n">
-        <v>28.3</v>
+        <v>22.9</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>most-likely pairing (28%); Switzerland to advance</t>
+          <t>most-likely pairing (23%); Switzerland to advance</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7634,7 @@
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -7701,7 +7709,7 @@
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -7776,11 +7784,11 @@
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="n">
-        <v>37.3</v>
+        <v>37.7</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>most-likely pairing (37%); France to advance</t>
+          <t>most-likely pairing (38%); France to advance</t>
         </is>
       </c>
     </row>
@@ -7851,11 +7859,11 @@
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="n">
-        <v>25.1</v>
+        <v>29.6</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>most-likely pairing (25%); Morocco to advance</t>
+          <t>most-likely pairing (30%); Morocco to advance</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7934,7 @@
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="n">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -7967,7 +7975,7 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -7975,19 +7983,19 @@
         </is>
       </c>
       <c r="J93" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="K93" t="n">
         <v>27.6</v>
       </c>
-      <c r="K93" t="n">
-        <v>27.4</v>
-      </c>
       <c r="L93" t="n">
-        <v>45</v>
+        <v>42.7</v>
       </c>
       <c r="M93" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="N93" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -8001,11 +8009,11 @@
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="n">
-        <v>24.5</v>
+        <v>26.4</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>most-likely pairing (24%); England to advance</t>
+          <t>most-likely pairing (26%); England to advance</t>
         </is>
       </c>
     </row>
@@ -8076,7 +8084,7 @@
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="n">
-        <v>21.9</v>
+        <v>21.6</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -8108,7 +8116,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -8117,7 +8125,7 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -8125,19 +8133,19 @@
         </is>
       </c>
       <c r="J95" t="n">
-        <v>41.2</v>
+        <v>44.3</v>
       </c>
       <c r="K95" t="n">
-        <v>26.8</v>
+        <v>27.3</v>
       </c>
       <c r="L95" t="n">
-        <v>32.1</v>
+        <v>28.4</v>
       </c>
       <c r="M95" t="n">
         <v>1.44</v>
       </c>
       <c r="N95" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -8151,11 +8159,11 @@
       </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="n">
-        <v>21.6</v>
+        <v>26.6</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>most-likely pairing (22%); United States to advance</t>
+          <t>most-likely pairing (27%); United States to advance</t>
         </is>
       </c>
     </row>
@@ -8226,7 +8234,7 @@
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -8333,7 +8341,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -8342,7 +8350,7 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -8350,19 +8358,19 @@
         </is>
       </c>
       <c r="J98" t="n">
-        <v>44.8</v>
+        <v>49.2</v>
       </c>
       <c r="K98" t="n">
-        <v>25.4</v>
+        <v>24.4</v>
       </c>
       <c r="L98" t="n">
-        <v>29.8</v>
+        <v>26.4</v>
       </c>
       <c r="M98" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="N98" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -8376,11 +8384,11 @@
       </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="n">
-        <v>8.9</v>
+        <v>10.2</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>most-likely pairing (9%); Germany to advance</t>
+          <t>most-likely pairing (10%); Germany to advance</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8459,7 @@
       </c>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -8483,7 +8491,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -8492,7 +8500,7 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -8500,19 +8508,19 @@
         </is>
       </c>
       <c r="J100" t="n">
-        <v>36.5</v>
+        <v>42.7</v>
       </c>
       <c r="K100" t="n">
-        <v>27.5</v>
+        <v>27.9</v>
       </c>
       <c r="L100" t="n">
-        <v>36</v>
+        <v>29.4</v>
       </c>
       <c r="M100" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="N100" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
@@ -8526,7 +8534,7 @@
       </c>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -8601,7 +8609,7 @@
       </c>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -8676,7 +8684,7 @@
       </c>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -8751,11 +8759,11 @@
       </c>
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>most-likely pairing (7%); Argentina to advance</t>
+          <t>most-likely pairing (8%); Argentina to advance</t>
         </is>
       </c>
     </row>
@@ -8826,7 +8834,7 @@
       </c>
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -8901,7 +8909,7 @@
       </c>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -9086,19 +9094,19 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>61.5</v>
+        <v>62</v>
       </c>
       <c r="K2" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="L2" t="n">
-        <v>15.2</v>
+        <v>14.8</v>
       </c>
       <c r="M2" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="N2" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -9159,7 +9167,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -9167,19 +9175,19 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>39.5</v>
+        <v>40</v>
       </c>
       <c r="K3" t="n">
-        <v>27.9</v>
+        <v>28.2</v>
       </c>
       <c r="L3" t="n">
-        <v>32.6</v>
+        <v>31.8</v>
       </c>
       <c r="M3" t="n">
         <v>1.32</v>
       </c>
       <c r="N3" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -11022,7 +11030,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -11030,19 +11038,19 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>49.3</v>
+        <v>53</v>
       </c>
       <c r="K26" t="n">
-        <v>27.1</v>
+        <v>26.4</v>
       </c>
       <c r="L26" t="n">
-        <v>23.7</v>
+        <v>20.7</v>
       </c>
       <c r="M26" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="N26" t="n">
-        <v>0.96</v>
+        <v>0.88</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -11051,7 +11059,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -11103,7 +11111,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -11111,19 +11119,19 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>44.5</v>
+        <v>40.4</v>
       </c>
       <c r="K27" t="n">
-        <v>27.4</v>
+        <v>28.2</v>
       </c>
       <c r="L27" t="n">
-        <v>28.1</v>
+        <v>31.5</v>
       </c>
       <c r="M27" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="N27" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -12962,31 +12970,31 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>final</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>25</v>
+        <v>27.4</v>
       </c>
       <c r="K50" t="n">
-        <v>27.1</v>
+        <v>28.6</v>
       </c>
       <c r="L50" t="n">
-        <v>47.9</v>
+        <v>44</v>
       </c>
       <c r="M50" t="n">
         <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -12998,11 +13006,15 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 45)</t>
+          <t>actual 1-0; model pick 0-1 (outcome miss)</t>
         </is>
       </c>
     </row>
@@ -13039,47 +13051,51 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>53</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="K51" t="n">
+        <v>24</v>
+      </c>
+      <c r="L51" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="H51" t="n">
-        <v>50</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>scheduled</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
-        <v>21</v>
-      </c>
-      <c r="K51" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="L51" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="N51" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 50)</t>
+          <t>actual 0-3; model pick 0-1 (outcome hit)</t>
         </is>
       </c>
     </row>
@@ -14944,7 +14960,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -14958,7 +14974,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -14966,19 +14982,19 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>31.7</v>
+        <v>22.5</v>
       </c>
       <c r="K2" t="n">
-        <v>27.2</v>
+        <v>25.7</v>
       </c>
       <c r="L2" t="n">
-        <v>41.1</v>
+        <v>51.8</v>
       </c>
       <c r="M2" t="n">
-        <v>1.21</v>
+        <v>0.99</v>
       </c>
       <c r="N2" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -14992,11 +15008,11 @@
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>63.8</v>
+        <v>100</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>most-likely pairing (64%); Canada to advance</t>
+          <t>most-likely pairing (100%); Canada to advance</t>
         </is>
       </c>
     </row>
@@ -15067,11 +15083,11 @@
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>26.8</v>
+        <v>38.3</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>most-likely pairing (27%); Germany to advance</t>
+          <t>most-likely pairing (38%); Germany to advance</t>
         </is>
       </c>
     </row>
@@ -15142,7 +15158,7 @@
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>55.1</v>
+        <v>55.3</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -15217,7 +15233,7 @@
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>43.7</v>
+        <v>43.5</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -15292,11 +15308,11 @@
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>20.7</v>
+        <v>19.9</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>most-likely pairing (21%); France to advance</t>
+          <t>most-likely pairing (20%); France to advance</t>
         </is>
       </c>
     </row>
@@ -15367,7 +15383,7 @@
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>55.3</v>
+        <v>55.2</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -15408,7 +15424,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -15416,19 +15432,19 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>45</v>
+        <v>47.5</v>
       </c>
       <c r="K8" t="n">
-        <v>28.4</v>
+        <v>27.8</v>
       </c>
       <c r="L8" t="n">
-        <v>26.5</v>
+        <v>24.7</v>
       </c>
       <c r="M8" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="N8" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -15442,11 +15458,11 @@
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>35.1</v>
+        <v>23.4</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>most-likely pairing (35%); Mexico to advance</t>
+          <t>most-likely pairing (23%); Mexico to advance</t>
         </is>
       </c>
     </row>
@@ -15517,7 +15533,7 @@
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -15592,11 +15608,11 @@
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>72.3</v>
+        <v>60.9</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>most-likely pairing (72%); United States to advance</t>
+          <t>most-likely pairing (61%); United States to advance</t>
         </is>
       </c>
     </row>
@@ -15633,7 +15649,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -15641,19 +15657,19 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>38.2</v>
+        <v>39.5</v>
       </c>
       <c r="K11" t="n">
-        <v>27.8</v>
+        <v>28.1</v>
       </c>
       <c r="L11" t="n">
-        <v>34.1</v>
+        <v>32.4</v>
       </c>
       <c r="M11" t="n">
         <v>1.31</v>
       </c>
       <c r="N11" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -15667,11 +15683,11 @@
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
-        <v>12.1</v>
+        <v>53.9</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>most-likely pairing (12%); Egypt to advance</t>
+          <t>most-likely pairing (54%); Egypt to advance</t>
         </is>
       </c>
     </row>
@@ -15742,7 +15758,7 @@
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
-        <v>22.9</v>
+        <v>22.5</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -15892,11 +15908,11 @@
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
-        <v>28.3</v>
+        <v>22.9</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>most-likely pairing (28%); Switzerland to advance</t>
+          <t>most-likely pairing (23%); Switzerland to advance</t>
         </is>
       </c>
     </row>
@@ -16042,7 +16058,7 @@
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -16117,7 +16133,7 @@
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -16192,11 +16208,11 @@
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
-        <v>37.3</v>
+        <v>37.7</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>most-likely pairing (37%); France to advance</t>
+          <t>most-likely pairing (38%); France to advance</t>
         </is>
       </c>
     </row>
@@ -16267,11 +16283,11 @@
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
-        <v>25.1</v>
+        <v>29.6</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>most-likely pairing (25%); Morocco to advance</t>
+          <t>most-likely pairing (30%); Morocco to advance</t>
         </is>
       </c>
     </row>
@@ -16342,7 +16358,7 @@
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -16383,7 +16399,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -16391,19 +16407,19 @@
         </is>
       </c>
       <c r="J21" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="K21" t="n">
         <v>27.6</v>
       </c>
-      <c r="K21" t="n">
-        <v>27.4</v>
-      </c>
       <c r="L21" t="n">
-        <v>45</v>
+        <v>42.7</v>
       </c>
       <c r="M21" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="N21" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -16417,11 +16433,11 @@
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
-        <v>24.5</v>
+        <v>26.4</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>most-likely pairing (24%); England to advance</t>
+          <t>most-likely pairing (26%); England to advance</t>
         </is>
       </c>
     </row>
@@ -16492,7 +16508,7 @@
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>21.9</v>
+        <v>21.6</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -16524,7 +16540,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -16533,7 +16549,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -16541,19 +16557,19 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>41.2</v>
+        <v>44.3</v>
       </c>
       <c r="K23" t="n">
-        <v>26.8</v>
+        <v>27.3</v>
       </c>
       <c r="L23" t="n">
-        <v>32.1</v>
+        <v>28.4</v>
       </c>
       <c r="M23" t="n">
         <v>1.44</v>
       </c>
       <c r="N23" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -16567,11 +16583,11 @@
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>21.6</v>
+        <v>26.6</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>most-likely pairing (22%); United States to advance</t>
+          <t>most-likely pairing (27%); United States to advance</t>
         </is>
       </c>
     </row>
@@ -16642,7 +16658,7 @@
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -16749,7 +16765,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -16758,7 +16774,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -16766,19 +16782,19 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>44.8</v>
+        <v>49.2</v>
       </c>
       <c r="K26" t="n">
-        <v>25.4</v>
+        <v>24.4</v>
       </c>
       <c r="L26" t="n">
-        <v>29.8</v>
+        <v>26.4</v>
       </c>
       <c r="M26" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="N26" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -16792,11 +16808,11 @@
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="n">
-        <v>8.9</v>
+        <v>10.2</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>most-likely pairing (9%); Germany to advance</t>
+          <t>most-likely pairing (10%); Germany to advance</t>
         </is>
       </c>
     </row>
@@ -16867,7 +16883,7 @@
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -16899,7 +16915,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -16908,7 +16924,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -16916,19 +16932,19 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>36.5</v>
+        <v>42.7</v>
       </c>
       <c r="K28" t="n">
-        <v>27.5</v>
+        <v>27.9</v>
       </c>
       <c r="L28" t="n">
-        <v>36</v>
+        <v>29.4</v>
       </c>
       <c r="M28" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="N28" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -16942,7 +16958,7 @@
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -17017,7 +17033,7 @@
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -17092,7 +17108,7 @@
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -17167,11 +17183,11 @@
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>most-likely pairing (7%); Argentina to advance</t>
+          <t>most-likely pairing (8%); Argentina to advance</t>
         </is>
       </c>
     </row>
@@ -17242,7 +17258,7 @@
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -17317,7 +17333,7 @@
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -17397,10 +17413,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -17420,23 +17436,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>63.8</v>
+        <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>24.5</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>91.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -17447,23 +17463,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>21.2</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>23.6</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>55.2</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>26</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="5">
@@ -17481,16 +17497,16 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>39.1</v>
+        <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>22.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -17679,7 +17695,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>51.3</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="13">
@@ -17751,16 +17767,16 @@
         <v>0.9</v>
       </c>
       <c r="D15" t="n">
-        <v>63.7</v>
+        <v>63.6</v>
       </c>
       <c r="E15" t="n">
         <v>31.2</v>
       </c>
       <c r="F15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G15" t="n">
-        <v>92</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="16">
@@ -17778,16 +17794,16 @@
         <v>0.1</v>
       </c>
       <c r="D16" t="n">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="E16" t="n">
-        <v>53.4</v>
+        <v>53.1</v>
       </c>
       <c r="F16" t="n">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="G16" t="n">
-        <v>77.40000000000001</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="17">
@@ -17808,13 +17824,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>15.4</v>
+        <v>15.7</v>
       </c>
       <c r="F17" t="n">
-        <v>84.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="G17" t="n">
-        <v>14</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="18">
@@ -17859,16 +17875,16 @@
         <v>0.4</v>
       </c>
       <c r="D19" t="n">
-        <v>76.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="G19" t="n">
-        <v>92.3</v>
+        <v>91.59999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -17886,16 +17902,16 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="E20" t="n">
-        <v>66.40000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="F20" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="G20" t="n">
-        <v>29.8</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="21">
@@ -17913,16 +17929,16 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="E21" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="F21" t="n">
         <v>69.40000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="22">
@@ -17937,10 +17953,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>55.1</v>
+        <v>55.3</v>
       </c>
       <c r="D22" t="n">
-        <v>43.7</v>
+        <v>43.5</v>
       </c>
       <c r="E22" t="n">
         <v>1.2</v>
@@ -17964,13 +17980,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>37.5</v>
+        <v>37.3</v>
       </c>
       <c r="D23" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="E23" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -17994,16 +18010,16 @@
         <v>7.4</v>
       </c>
       <c r="D24" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="E24" t="n">
-        <v>77.90000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="F24" t="n">
         <v>0.1</v>
       </c>
       <c r="G24" t="n">
-        <v>92.59999999999999</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="25">
@@ -18045,13 +18061,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>59.1</v>
+        <v>58.6</v>
       </c>
       <c r="D26" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="E26" t="n">
-        <v>22.3</v>
+        <v>22.6</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -18072,19 +18088,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>13.2</v>
+        <v>13.5</v>
       </c>
       <c r="D27" t="n">
         <v>51.3</v>
       </c>
       <c r="E27" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="F27" t="n">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="G27" t="n">
-        <v>77.7</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="28">
@@ -18099,19 +18115,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27.6</v>
+        <v>27.9</v>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="E28" t="n">
-        <v>51.5</v>
+        <v>50.9</v>
       </c>
       <c r="F28" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="G28" t="n">
-        <v>63.9</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="29">
@@ -18129,16 +18145,16 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>16.3</v>
+        <v>15.9</v>
       </c>
       <c r="E29" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>74</v>
+        <v>74.3</v>
       </c>
       <c r="G29" t="n">
-        <v>22.3</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="30">
@@ -18153,13 +18169,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>80.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="D30" t="n">
-        <v>11.7</v>
+        <v>11.3</v>
       </c>
       <c r="E30" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -18186,13 +18202,13 @@
         <v>55.2</v>
       </c>
       <c r="E31" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="F31" t="n">
         <v>22.1</v>
       </c>
       <c r="G31" t="n">
-        <v>69.40000000000001</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -18207,19 +18223,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="D32" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>66.7</v>
+        <v>66.5</v>
       </c>
       <c r="F32" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>42.7</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="33">
@@ -18237,16 +18253,16 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>24.8</v>
+        <v>25.2</v>
       </c>
       <c r="E33" t="n">
         <v>6.8</v>
       </c>
       <c r="F33" t="n">
-        <v>68.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="G33" t="n">
-        <v>30.8</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="34">
@@ -18321,13 +18337,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="F36" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="G36" t="n">
-        <v>54.9</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="37">
@@ -18348,13 +18364,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="F37" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="G37" t="n">
-        <v>7.2</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="38">
@@ -18369,10 +18385,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -18399,16 +18415,16 @@
         <v>0.5</v>
       </c>
       <c r="D39" t="n">
-        <v>64.59999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="E39" t="n">
         <v>33</v>
       </c>
       <c r="F39" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="G39" t="n">
-        <v>94.5</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40">
@@ -18435,7 +18451,7 @@
         <v>4.7</v>
       </c>
       <c r="G40" t="n">
-        <v>80.40000000000001</v>
+        <v>74.8</v>
       </c>
     </row>
     <row r="41">
@@ -18456,13 +18472,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="F41" t="n">
-        <v>93.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="G41" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="42">
@@ -18477,13 +18493,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>39.7</v>
+        <v>39.5</v>
       </c>
       <c r="D42" t="n">
-        <v>60</v>
+        <v>60.2</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -18504,10 +18520,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>60.3</v>
+        <v>60.5</v>
       </c>
       <c r="D43" t="n">
-        <v>39.7</v>
+        <v>39.5</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -18534,16 +18550,16 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="E44" t="n">
-        <v>57.6</v>
+        <v>57.8</v>
       </c>
       <c r="F44" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="G44" t="n">
-        <v>33.8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45">
@@ -18564,13 +18580,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="F45" t="n">
-        <v>58</v>
+        <v>58.1</v>
       </c>
       <c r="G45" t="n">
-        <v>9.699999999999999</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="46">
@@ -18585,13 +18601,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>61</v>
+        <v>61.6</v>
       </c>
       <c r="D46" t="n">
-        <v>38.2</v>
+        <v>37.7</v>
       </c>
       <c r="E46" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -18612,13 +18628,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="D47" t="n">
         <v>32.9</v>
       </c>
       <c r="E47" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -18639,19 +18655,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>22.6</v>
+        <v>22.1</v>
       </c>
       <c r="D48" t="n">
-        <v>28.9</v>
+        <v>29.4</v>
       </c>
       <c r="E48" t="n">
-        <v>43.5</v>
+        <v>43.9</v>
       </c>
       <c r="F48" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="G48" t="n">
-        <v>91.90000000000001</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="49">
@@ -18672,13 +18688,13 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="F49" t="n">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="G49" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
     </row>
   </sheetData>
@@ -18756,13 +18772,13 @@
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>57</v>
+        <v>56.5</v>
       </c>
       <c r="E2" t="n">
         <v>38.2</v>
       </c>
       <c r="F2" t="n">
-        <v>24.7</v>
+        <v>24.3</v>
       </c>
       <c r="G2" t="n">
         <v>14.8</v>
@@ -18783,16 +18799,16 @@
         <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
       <c r="E3" t="n">
-        <v>34.6</v>
+        <v>34.9</v>
       </c>
       <c r="F3" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="G3" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -18810,40 +18826,40 @@
         <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="E4" t="n">
-        <v>28.3</v>
+        <v>28.6</v>
       </c>
       <c r="F4" t="n">
-        <v>16.1</v>
+        <v>16.5</v>
       </c>
       <c r="G4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>England</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>35.7</v>
+        <v>36.8</v>
       </c>
       <c r="E5" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="F5" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="G5" t="n">
         <v>5.9</v>
@@ -18852,82 +18868,82 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>37.5</v>
+        <v>35.1</v>
       </c>
       <c r="E6" t="n">
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>35.7</v>
+        <v>34.4</v>
       </c>
       <c r="E7" t="n">
-        <v>20.7</v>
+        <v>20.1</v>
       </c>
       <c r="F7" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="G7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>33.8</v>
+        <v>36.1</v>
       </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>21.1</v>
       </c>
       <c r="F8" t="n">
-        <v>10.2</v>
+        <v>11.1</v>
       </c>
       <c r="G8" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="9">
@@ -18945,16 +18961,16 @@
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>35.6</v>
+        <v>35.1</v>
       </c>
       <c r="E9" t="n">
-        <v>18.4</v>
+        <v>18.1</v>
       </c>
       <c r="F9" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="10">
@@ -18972,124 +18988,124 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>32.4</v>
+        <v>33.1</v>
       </c>
       <c r="E10" t="n">
         <v>17.1</v>
       </c>
       <c r="F10" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>29.5</v>
+        <v>27.8</v>
       </c>
       <c r="E11" t="n">
-        <v>15.8</v>
+        <v>13.8</v>
       </c>
       <c r="F11" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="G11" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>26.9</v>
+        <v>28.5</v>
       </c>
       <c r="E12" t="n">
-        <v>13.2</v>
+        <v>14.9</v>
       </c>
       <c r="F12" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>37.1</v>
+        <v>30.6</v>
       </c>
       <c r="E13" t="n">
-        <v>14</v>
+        <v>14.3</v>
       </c>
       <c r="F13" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>29.3</v>
+        <v>37.1</v>
       </c>
       <c r="E14" t="n">
-        <v>13.1</v>
+        <v>14.1</v>
       </c>
       <c r="F14" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="15">
@@ -19107,13 +19123,13 @@
         <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>25.2</v>
+        <v>26.4</v>
       </c>
       <c r="E15" t="n">
-        <v>10.9</v>
+        <v>11.4</v>
       </c>
       <c r="F15" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="G15" t="n">
         <v>2.1</v>
@@ -19134,40 +19150,40 @@
         <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="E16" t="n">
         <v>10.5</v>
       </c>
       <c r="F16" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>91.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>20.3</v>
+        <v>27.9</v>
       </c>
       <c r="E17" t="n">
-        <v>9.4</v>
+        <v>10.7</v>
       </c>
       <c r="F17" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="G17" t="n">
         <v>1.7</v>
@@ -19176,28 +19192,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>100</v>
+        <v>90.3</v>
       </c>
       <c r="D18" t="n">
-        <v>23.9</v>
+        <v>19.7</v>
       </c>
       <c r="E18" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="F18" t="n">
         <v>3.9</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="19">
@@ -19212,19 +19228,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>77.7</v>
+        <v>78.2</v>
       </c>
       <c r="D19" t="n">
-        <v>16.6</v>
+        <v>17.1</v>
       </c>
       <c r="E19" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="F19" t="n">
         <v>3.4</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="20">
@@ -19242,16 +19258,16 @@
         <v>100</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="E20" t="n">
         <v>7.8</v>
       </c>
       <c r="F20" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="21">
@@ -19266,19 +19282,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>94.5</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
-        <v>14.7</v>
+        <v>14.1</v>
       </c>
       <c r="E21" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="F21" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G21" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -19293,16 +19309,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>92</v>
+        <v>90.5</v>
       </c>
       <c r="D22" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="E22" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="F22" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G22" t="n">
         <v>0.9</v>
@@ -19320,13 +19336,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>92.3</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.5</v>
       </c>
       <c r="E23" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="F23" t="n">
         <v>2.2</v>
@@ -19347,43 +19363,43 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>42.7</v>
+        <v>41.6</v>
       </c>
       <c r="D24" t="n">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
       <c r="E24" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>29.8</v>
+        <v>52.9</v>
       </c>
       <c r="D25" t="n">
-        <v>7.4</v>
+        <v>10.8</v>
       </c>
       <c r="E25" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="F25" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="G25" t="n">
         <v>0.7</v>
@@ -19392,22 +19408,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>80.40000000000001</v>
+        <v>62.8</v>
       </c>
       <c r="D26" t="n">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="F26" t="n">
         <v>1.9</v>
@@ -19419,25 +19435,25 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>54.9</v>
+        <v>92.3</v>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>18.6</v>
       </c>
       <c r="E27" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="F27" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="G27" t="n">
         <v>0.7</v>
@@ -19446,55 +19462,55 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>63.9</v>
+        <v>74.8</v>
       </c>
       <c r="D28" t="n">
-        <v>13</v>
+        <v>11.4</v>
       </c>
       <c r="E28" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="F28" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>91.5</v>
+        <v>29.3</v>
       </c>
       <c r="D29" t="n">
-        <v>16.5</v>
+        <v>6.9</v>
       </c>
       <c r="E29" t="n">
-        <v>5.7</v>
+        <v>3.2</v>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="G29" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="30">
@@ -19509,19 +19525,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>77.40000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="D30" t="n">
-        <v>10.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="F30" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="G30" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="31">
@@ -19539,10 +19555,10 @@
         <v>100</v>
       </c>
       <c r="D31" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="E31" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="F31" t="n">
         <v>0.9</v>
@@ -19554,25 +19570,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>51.3</v>
+        <v>89.2</v>
       </c>
       <c r="D32" t="n">
-        <v>6.9</v>
+        <v>10</v>
       </c>
       <c r="E32" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
         <v>0.3</v>
@@ -19581,49 +19597,49 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>69.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="D33" t="n">
-        <v>6.7</v>
+        <v>9</v>
       </c>
       <c r="E33" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>22.8</v>
+        <v>33.8</v>
       </c>
       <c r="D34" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="F34" t="n">
         <v>0.5</v>
@@ -19635,25 +19651,25 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>92.59999999999999</v>
+        <v>13.4</v>
       </c>
       <c r="D35" t="n">
-        <v>10.2</v>
+        <v>2.1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="G35" t="n">
         <v>0.2</v>
@@ -19662,25 +19678,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>14</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>2.3</v>
+        <v>6.8</v>
       </c>
       <c r="E36" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="G36" t="n">
         <v>0.2</v>
@@ -19689,25 +19705,25 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="D37" t="n">
-        <v>2.5</v>
+        <v>7.2</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="G37" t="n">
         <v>0.1</v>
@@ -19716,22 +19732,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>33.8</v>
+        <v>31.1</v>
       </c>
       <c r="D38" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F38" t="n">
         <v>0.2</v>
@@ -19743,52 +19759,52 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>100</v>
+        <v>20.2</v>
       </c>
       <c r="D39" t="n">
-        <v>7.6</v>
+        <v>0.9</v>
       </c>
       <c r="E39" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -19797,25 +19813,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4.8</v>
+        <v>21.8</v>
       </c>
       <c r="D41" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="E41" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F41" t="n">
         <v>0.2</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.1</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -19824,25 +19840,25 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -19851,25 +19867,25 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -19878,25 +19894,25 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="D44" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F44" t="n">
         <v>0.1</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -19905,25 +19921,25 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>30.8</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -19932,22 +19948,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>22.3</v>
+        <v>5.6</v>
       </c>
       <c r="D46" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="F46" t="n">
         <v>0.1</v>
@@ -19959,12 +19975,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -19986,25 +20002,25 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>20.3</v>
+        <v>4.4</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -20173,10 +20189,10 @@
         <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="L2" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="M2" t="n">
         <v>100</v>
@@ -20225,7 +20241,7 @@
         <v>14.8</v>
       </c>
       <c r="L3" t="n">
-        <v>24.7</v>
+        <v>24.3</v>
       </c>
       <c r="M3" t="n">
         <v>100</v>
@@ -20271,10 +20287,10 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>16.1</v>
+        <v>16.5</v>
       </c>
       <c r="M4" t="n">
         <v>100</v>
@@ -20320,10 +20336,10 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="L5" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="M5" t="n">
         <v>100</v>
@@ -20369,7 +20385,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L6" t="n">
         <v>11.2</v>
@@ -20418,10 +20434,10 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="L7" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="M7" t="n">
         <v>100</v>
@@ -20467,10 +20483,10 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L8" t="n">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
@@ -20516,10 +20532,10 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M9" t="n">
         <v>100</v>
@@ -20565,10 +20581,10 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L10" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M10" t="n">
         <v>100</v>
@@ -20612,10 +20628,10 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="L11" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="M11" t="n">
         <v>100</v>
@@ -20661,10 +20677,10 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="L12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="M12" t="n">
         <v>100</v>
@@ -20673,45 +20689,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>CONCACAF</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1877</v>
+        <v>1881</v>
       </c>
       <c r="E13" t="n">
-        <v>1912</v>
+        <v>1939</v>
       </c>
       <c r="F13" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>blend(metis+fifa)</t>
+          <t>eloratings.net</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>11</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="I13" t="n">
+        <v>71</v>
+      </c>
       <c r="J13" t="n">
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="L13" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
@@ -20720,47 +20738,45 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CONCACAF</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1881</v>
+        <v>1877</v>
       </c>
       <c r="E14" t="n">
-        <v>1906</v>
+        <v>1912</v>
       </c>
       <c r="F14" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>eloratings.net</t>
+          <t>blend(metis+fifa)</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>15</v>
-      </c>
-      <c r="I14" t="n">
-        <v>71</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="L14" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
@@ -20804,13 +20820,13 @@
         <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="L15" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="M15" t="n">
-        <v>29.8</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="16">
@@ -20851,10 +20867,10 @@
         <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="L16" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="M16" t="n">
         <v>100</v>
@@ -20901,10 +20917,10 @@
         <v>1.7</v>
       </c>
       <c r="L17" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="M17" t="n">
-        <v>91.90000000000001</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="18">
@@ -20947,13 +20963,13 @@
         <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="L18" t="n">
         <v>3.4</v>
       </c>
       <c r="M18" t="n">
-        <v>77.7</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="19">
@@ -21043,13 +21059,13 @@
         <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="L20" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="M20" t="n">
-        <v>42.7</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="21">
@@ -21090,10 +21106,10 @@
         <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="L21" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="M21" t="n">
         <v>100</v>
@@ -21137,13 +21153,13 @@
         <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="M22" t="n">
-        <v>94.5</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23">
@@ -21185,10 +21201,10 @@
         <v>0.2</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="M23" t="n">
-        <v>14</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="24">
@@ -21232,10 +21248,10 @@
         <v>0.7</v>
       </c>
       <c r="L24" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="M24" t="n">
-        <v>54.9</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="25">
@@ -21279,10 +21295,10 @@
         <v>0.9</v>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="M25" t="n">
-        <v>92</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="26">
@@ -21323,10 +21339,10 @@
         <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="L26" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="M26" t="n">
         <v>100</v>
@@ -21376,7 +21392,7 @@
         <v>2.2</v>
       </c>
       <c r="M27" t="n">
-        <v>92.3</v>
+        <v>91.59999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -21423,7 +21439,7 @@
         <v>1.9</v>
       </c>
       <c r="M28" t="n">
-        <v>63.9</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="29">
@@ -21464,13 +21480,13 @@
         <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="L29" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="M29" t="n">
-        <v>80.40000000000001</v>
+        <v>74.8</v>
       </c>
     </row>
     <row r="30">
@@ -21511,13 +21527,13 @@
         <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="L30" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="M30" t="n">
-        <v>77.40000000000001</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="31">
@@ -21540,10 +21556,10 @@
         <v>1787</v>
       </c>
       <c r="E31" t="n">
-        <v>1793</v>
+        <v>1771</v>
       </c>
       <c r="F31" t="n">
-        <v>6</v>
+        <v>-16</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -21557,7 +21573,7 @@
         <v>64</v>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" t="n">
         <v>0.7</v>
@@ -21566,7 +21582,7 @@
         <v>2</v>
       </c>
       <c r="M31" t="n">
-        <v>91.5</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="32">
@@ -21607,13 +21623,13 @@
         <v>3</v>
       </c>
       <c r="K32" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="L32" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="M32" t="n">
-        <v>51.3</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="33">
@@ -21660,43 +21676,43 @@
         <v>0.1</v>
       </c>
       <c r="M33" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>UEFA</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1764</v>
+        <v>1710</v>
       </c>
       <c r="E34" t="n">
-        <v>1744</v>
+        <v>1738</v>
       </c>
       <c r="F34" t="n">
-        <v>-21</v>
+        <v>29</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>blend(metis+expert)</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="n">
-        <v>61</v>
-      </c>
+          <t>blend(metis+fifa)</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>68</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
         <v>2</v>
       </c>
@@ -21704,45 +21720,43 @@
         <v>0.2</v>
       </c>
       <c r="L34" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="M34" t="n">
-        <v>22.8</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>UEFA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1710</v>
+        <v>1703</v>
       </c>
       <c r="E35" t="n">
-        <v>1738</v>
+        <v>1715</v>
       </c>
       <c r="F35" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>blend(metis+fifa)</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>68</v>
-      </c>
+          <t>blend(metis)</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
         <v>2</v>
@@ -21751,21 +21765,21 @@
         <v>0.3</v>
       </c>
       <c r="L35" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>69.40000000000001</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -21774,32 +21788,34 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1703</v>
+        <v>1764</v>
       </c>
       <c r="E36" t="n">
-        <v>1715</v>
+        <v>1711</v>
       </c>
       <c r="F36" t="n">
-        <v>12</v>
+        <v>-54</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>blend(metis)</t>
+          <t>blend(metis+expert)</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>61</v>
+      </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K36" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>92.59999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -21846,7 +21862,7 @@
         <v>0.1</v>
       </c>
       <c r="M37" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="38">
@@ -21940,7 +21956,7 @@
         <v>0.1</v>
       </c>
       <c r="M39" t="n">
-        <v>9.699999999999999</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="40">
@@ -21981,109 +21997,109 @@
         <v>2</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L40" t="n">
         <v>0.2</v>
       </c>
       <c r="M40" t="n">
-        <v>30.8</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>OFC</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1657</v>
+        <v>1635</v>
       </c>
       <c r="E41" t="n">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="F41" t="n">
-        <v>-15</v>
+        <v>11</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>blend(metis+fifa)</t>
+          <t>blend(metis+fifa+expert)</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>86</v>
-      </c>
-      <c r="I41" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="I41" t="n">
+        <v>37</v>
+      </c>
       <c r="J41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L41" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="M41" t="n">
-        <v>22.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>OFC</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1635</v>
+        <v>1657</v>
       </c>
       <c r="E42" t="n">
-        <v>1624</v>
+        <v>1642</v>
       </c>
       <c r="F42" t="n">
-        <v>-11</v>
+        <v>-15</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>blend(metis+fifa+expert)</t>
+          <t>blend(metis+fifa)</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>61</v>
-      </c>
-      <c r="I42" t="n">
-        <v>37</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
         <v>2</v>
       </c>
       <c r="K42" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0.2</v>
       </c>
       <c r="M42" t="n">
-        <v>26</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="43">
@@ -22169,13 +22185,13 @@
         <v>2</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0.2</v>
       </c>
       <c r="M44" t="n">
-        <v>33.8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45">
@@ -22312,7 +22328,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>7.2</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="48">
@@ -22359,7 +22375,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="49">
@@ -22420,7 +22436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -22595,44 +22611,44 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>South Korea 2-1 Czechia</t>
+          <t>South Africa 1-0 South Korea</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.3775464057956682</v>
+        <v>0.26113755545355</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2770387146066375</v>
+        <v>0.2663778415879188</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3454148795976941</v>
+        <v>0.4724846029585311</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2533799579926903</v>
+        <v>0.3845797059970184</v>
       </c>
       <c r="I5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Canada 1-1 Bosnia and Herzegovina</t>
+          <t>South Korea 2-1 Czechia</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -22642,34 +22658,34 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.5935041775822631</v>
+        <v>0.3775464057956682</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2336119886651664</v>
+        <v>0.2770387146066375</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1728838337525705</v>
+        <v>0.3454148795976941</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1910680143902925</v>
+        <v>0.2533799579926903</v>
       </c>
       <c r="I6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>United States 4-1 Paraguay</t>
+          <t>Canada 1-1 Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -22679,39 +22695,39 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.4107699333529872</v>
+        <v>0.5935041775822631</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2750184355219605</v>
+        <v>0.2336119886651664</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3142116311250522</v>
+        <v>0.1728838337525705</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2229605102875545</v>
+        <v>0.1910680143902925</v>
       </c>
       <c r="I7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Australia 2-0 Turkey</t>
+          <t>United States 4-1 Paraguay</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -22725,53 +22741,53 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.3022966571991881</v>
+        <v>0.4107699333529872</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2736782656597276</v>
+        <v>0.2750184355219605</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4240250771410841</v>
+        <v>0.3142116311250522</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3332936102999648</v>
+        <v>0.2229605102875545</v>
       </c>
       <c r="I8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brazil 1-1 Morocco</t>
+          <t>Australia 2-0 Turkey</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.4339441725206395</v>
+        <v>0.3022966571991881</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2724853115528631</v>
+        <v>0.2736782656597276</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2935705159264974</v>
+        <v>0.4240250771410841</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1372455963429862</v>
+        <v>0.3332936102999648</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
@@ -22780,17 +22796,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Haiti 0-1 Scotland</t>
+          <t>Brazil 1-1 Morocco</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -22799,25 +22815,25 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.2606949315022876</v>
+        <v>0.4339441725206395</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2662752434568346</v>
+        <v>0.2724853115528631</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4730298250408779</v>
+        <v>0.2935705159264974</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1728297063037152</v>
+        <v>0.1372455963429862</v>
       </c>
       <c r="I10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Qatar 1-1 Switzerland</t>
+          <t>Haiti 0-1 Scotland</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -22827,7 +22843,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -22836,67 +22852,67 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.2021605238111649</v>
+        <v>0.2606949315022876</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2474960581873801</v>
+        <v>0.2662752434568346</v>
       </c>
       <c r="G11" t="n">
-        <v>0.550343418001455</v>
+        <v>0.4730298250408779</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1718733775625644</v>
+        <v>0.1728297063037152</v>
       </c>
       <c r="I11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Germany 7-1 Curaçao</t>
+          <t>Qatar 1-1 Switzerland</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.6099914400822092</v>
+        <v>0.2021605238111649</v>
       </c>
       <c r="F12" t="n">
-        <v>0.227710918612106</v>
+        <v>0.2474960581873801</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1622976413056849</v>
+        <v>0.550343418001455</v>
       </c>
       <c r="H12" t="n">
-        <v>0.08922360059126888</v>
+        <v>0.1718733775625644</v>
       </c>
       <c r="I12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ivory Coast 1-0 Ecuador</t>
+          <t>Germany 7-1 Curaçao</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -22906,57 +22922,57 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.2738762749141564</v>
+        <v>0.6099914400822092</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2691027275042267</v>
+        <v>0.227710918612106</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4570209975816171</v>
+        <v>0.1622976413056849</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3680619281815189</v>
+        <v>0.08922360059126888</v>
       </c>
       <c r="I13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Netherlands 2-2 Japan</t>
+          <t>Ivory Coast 1-0 Ecuador</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.3911107030923358</v>
+        <v>0.2738762749141564</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2764517043235625</v>
+        <v>0.2691027275042267</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3324375925841019</v>
+        <v>0.4570209975816171</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1317411675182472</v>
+        <v>0.3680619281815189</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
@@ -22965,17 +22981,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sweden 5-1 Tunisia</t>
+          <t>Netherlands 2-2 Japan</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -22984,16 +23000,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.3379351884295246</v>
+        <v>0.3911107030923358</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2767432920907087</v>
+        <v>0.2764517043235625</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3853215194797665</v>
+        <v>0.3324375925841019</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2934012440470226</v>
+        <v>0.1317411675182472</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
@@ -23002,35 +23018,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Belgium 1-1 Egypt</t>
+          <t>Sweden 5-1 Tunisia</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.4323227858568852</v>
+        <v>0.3379351884295246</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2726912470817157</v>
+        <v>0.2767432920907087</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2949859670613991</v>
+        <v>0.3853215194797665</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1369598559671035</v>
+        <v>0.2934012440470226</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
@@ -23039,7 +23055,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Iran 2-2 New Zealand</t>
+          <t>Belgium 1-1 Egypt</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -23058,16 +23074,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.4832027730434736</v>
+        <v>0.4323227858568852</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2642809230535665</v>
+        <v>0.2726912470817157</v>
       </c>
       <c r="G17" t="n">
-        <v>0.25251630390296</v>
+        <v>0.2949859670613991</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1486247018068573</v>
+        <v>0.1369598559671035</v>
       </c>
       <c r="I17" t="b">
         <v>0</v>
@@ -23076,12 +23092,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Saudi Arabia 1-1 Uruguay</t>
+          <t>Iran 2-2 New Zealand</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -23095,16 +23111,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.2240862560806894</v>
+        <v>0.4832027730434736</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2558123361101832</v>
+        <v>0.2642809230535665</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5201014078091272</v>
+        <v>0.25251630390296</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1603600622846482</v>
+        <v>0.1486247018068573</v>
       </c>
       <c r="I18" t="b">
         <v>0</v>
@@ -23113,12 +23129,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Spain 0-0 Cape Verde</t>
+          <t>Saudi Arabia 1-1 Uruguay</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -23128,20 +23144,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.6889149405831398</v>
+        <v>0.2240862560806894</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1951539809620534</v>
+        <v>0.2558123361101832</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1159310784548069</v>
+        <v>0.5201014078091272</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2440219051551828</v>
+        <v>0.1603600622846482</v>
       </c>
       <c r="I19" t="b">
         <v>0</v>
@@ -23150,7 +23166,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Argentina 3-0 Algeria</t>
+          <t>Spain 0-0 Cape Verde</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -23160,34 +23176,34 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.5653447610298761</v>
+        <v>0.6889149405831398</v>
       </c>
       <c r="F20" t="n">
-        <v>0.242932655319136</v>
+        <v>0.1951539809620534</v>
       </c>
       <c r="G20" t="n">
-        <v>0.191722583650988</v>
+        <v>0.1159310784548069</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1128413629229928</v>
+        <v>0.2440219051551828</v>
       </c>
       <c r="I20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Austria 3-1 Jordan</t>
+          <t>Argentina 3-0 Algeria</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -23206,16 +23222,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.4465822656526882</v>
+        <v>0.5653447610298761</v>
       </c>
       <c r="F21" t="n">
-        <v>0.270736216737822</v>
+        <v>0.242932655319136</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2826815176094898</v>
+        <v>0.191722583650988</v>
       </c>
       <c r="H21" t="n">
-        <v>0.193090014544058</v>
+        <v>0.1128413629229928</v>
       </c>
       <c r="I21" t="b">
         <v>1</v>
@@ -23224,7 +23240,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>France 3-1 Senegal</t>
+          <t>Austria 3-1 Jordan</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -23243,16 +23259,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.5101967760009811</v>
+        <v>0.4465822656526882</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2582711067810726</v>
+        <v>0.270736216737822</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2315321172179463</v>
+        <v>0.2826815176094898</v>
       </c>
       <c r="H22" t="n">
-        <v>0.146757159771629</v>
+        <v>0.193090014544058</v>
       </c>
       <c r="I22" t="b">
         <v>1</v>
@@ -23261,35 +23277,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Iraq 1-4 Norway</t>
+          <t>France 3-1 Senegal</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.1771341674124645</v>
+        <v>0.5101967760009811</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2358428959472877</v>
+        <v>0.2582711067810726</v>
       </c>
       <c r="G23" t="n">
-        <v>0.587022936640248</v>
+        <v>0.2315321172179463</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1009632840630759</v>
+        <v>0.146757159771629</v>
       </c>
       <c r="I23" t="b">
         <v>1</v>
@@ -23298,35 +23314,35 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>England 4-2 Croatia</t>
+          <t>Iraq 1-4 Norway</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.4421686007896301</v>
+        <v>0.1771341674124645</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2713758294277268</v>
+        <v>0.2358428959472877</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2864555697826432</v>
+        <v>0.587022936640248</v>
       </c>
       <c r="H24" t="n">
-        <v>0.196616331702249</v>
+        <v>0.1009632840630759</v>
       </c>
       <c r="I24" t="b">
         <v>1</v>
@@ -23335,12 +23351,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ghana 1-0 Panama</t>
+          <t>England 4-2 Croatia</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -23354,53 +23370,53 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.269445732840606</v>
+        <v>0.4421686007896301</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2682043756018556</v>
+        <v>0.2713758294277268</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4623498915575382</v>
+        <v>0.2864555697826432</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3737384797440333</v>
+        <v>0.196616331702249</v>
       </c>
       <c r="I25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Portugal 1-1 DR Congo</t>
+          <t>Ghana 1-0 Panama</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.6563191675226661</v>
+        <v>0.269445732840606</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2094436649180234</v>
+        <v>0.2682043756018556</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1342371675593106</v>
+        <v>0.4623498915575382</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2243872334059959</v>
+        <v>0.3737384797440333</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
@@ -23409,72 +23425,72 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Uzbekistan 1-3 Colombia</t>
+          <t>Portugal 1-1 DR Congo</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.2202298877346608</v>
+        <v>0.6563191675226661</v>
       </c>
       <c r="F27" t="n">
-        <v>0.254468243557875</v>
+        <v>0.2094436649180234</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5253018687074642</v>
+        <v>0.1342371675593106</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1369197596521234</v>
+        <v>0.2243872334059959</v>
       </c>
       <c r="I27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Canada 6-0 Qatar</t>
+          <t>Uzbekistan 1-3 Colombia</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.5764064554833523</v>
+        <v>0.2202298877346608</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2393871531850218</v>
+        <v>0.254468243557875</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1842063913316258</v>
+        <v>0.5253018687074642</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1066817427817986</v>
+        <v>0.1369197596521234</v>
       </c>
       <c r="I28" t="b">
         <v>1</v>
@@ -23483,7 +23499,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Czechia 1-1 South Africa</t>
+          <t>Canada 6-0 Qatar</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -23493,34 +23509,34 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.4553404858663942</v>
+        <v>0.5764064554833523</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2693770505519105</v>
+        <v>0.2393871531850218</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2752824635816952</v>
+        <v>0.1842063913316258</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1415576964123257</v>
+        <v>0.1066817427817986</v>
       </c>
       <c r="I29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mexico 1-0 South Korea</t>
+          <t>Czechia 1-1 South Africa</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -23530,7 +23546,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -23539,25 +23555,25 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.4881235585818711</v>
+        <v>0.4553404858663942</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2632623226473407</v>
+        <v>0.2693770505519105</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2486141187707883</v>
+        <v>0.2752824635816952</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1619132356655314</v>
+        <v>0.1415576964123257</v>
       </c>
       <c r="I30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Switzerland 4-1 Bosnia and Herzegovina</t>
+          <t>Mexico 1-0 South Korea</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -23572,20 +23588,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.5675807326327216</v>
+        <v>0.4881235585818711</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2422282277870113</v>
+        <v>0.2632623226473407</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1901910395802674</v>
+        <v>0.2486141187707883</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1115795271635383</v>
+        <v>0.1619132356655314</v>
       </c>
       <c r="I31" t="b">
         <v>1</v>
@@ -23594,7 +23610,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Brazil 3-0 Haiti</t>
+          <t>Switzerland 4-1 Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -23613,16 +23629,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.6024710043427424</v>
+        <v>0.5675807326327216</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2304425698918271</v>
+        <v>0.2422282277870113</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1670864257654306</v>
+        <v>0.1901910395802674</v>
       </c>
       <c r="H32" t="n">
-        <v>0.09297358803166735</v>
+        <v>0.1115795271635383</v>
       </c>
       <c r="I32" t="b">
         <v>1</v>
@@ -23631,35 +23647,35 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Scotland 0-1 Morocco</t>
+          <t>Brazil 3-0 Haiti</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.3123152964921898</v>
+        <v>0.6024710043427424</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2748269579337349</v>
+        <v>0.2304425698918271</v>
       </c>
       <c r="G33" t="n">
-        <v>0.4128577455740753</v>
+        <v>0.1670864257654306</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2211384356776808</v>
+        <v>0.09297358803166735</v>
       </c>
       <c r="I33" t="b">
         <v>1</v>
@@ -23668,12 +23684,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Turkey 0-1 Paraguay</t>
+          <t>Scotland 0-1 Morocco</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -23687,25 +23703,25 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.4158113794624096</v>
+        <v>0.3123152964921898</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2745434638141608</v>
+        <v>0.2748269579337349</v>
       </c>
       <c r="G34" t="n">
-        <v>0.3096451567234295</v>
+        <v>0.4128577455740753</v>
       </c>
       <c r="H34" t="n">
-        <v>0.324744456462925</v>
+        <v>0.2211384356776808</v>
       </c>
       <c r="I34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>United States 2-0 Australia</t>
+          <t>Turkey 0-1 Paraguay</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -23715,7 +23731,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -23724,25 +23740,25 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.4189589466211568</v>
+        <v>0.4158113794624096</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2742252024300777</v>
+        <v>0.2745434638141608</v>
       </c>
       <c r="G35" t="n">
-        <v>0.3068158509487656</v>
+        <v>0.3096451567234295</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2158723360525054</v>
+        <v>0.324744456462925</v>
       </c>
       <c r="I35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ecuador 0-0 Curaçao</t>
+          <t>United States 2-0 Australia</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -23752,34 +23768,34 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.614390105780561</v>
+        <v>0.4189589466211568</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2260824080030716</v>
+        <v>0.2742252024300777</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1595274862163676</v>
+        <v>0.3068158509487656</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2014621104697811</v>
+        <v>0.2158723360525054</v>
       </c>
       <c r="I36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Germany 2-1 Ivory Coast</t>
+          <t>Ecuador 0-0 Curaçao</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -23789,34 +23805,34 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.4525599494983835</v>
+        <v>0.614390105780561</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2698214154164175</v>
+        <v>0.2260824080030716</v>
       </c>
       <c r="G37" t="n">
-        <v>0.277618635085199</v>
+        <v>0.1595274862163676</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1883813577198906</v>
+        <v>0.2014621104697811</v>
       </c>
       <c r="I37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Netherlands 5-1 Sweden</t>
+          <t>Germany 2-1 Ivory Coast</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -23835,16 +23851,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.5419741522498547</v>
+        <v>0.4525599494983835</v>
       </c>
       <c r="F38" t="n">
-        <v>0.249917248195977</v>
+        <v>0.2698214154164175</v>
       </c>
       <c r="G38" t="n">
-        <v>0.2081085995541683</v>
+        <v>0.277618635085199</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1265484332078183</v>
+        <v>0.1883813577198906</v>
       </c>
       <c r="I38" t="b">
         <v>1</v>
@@ -23853,17 +23869,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Tunisia 0-4 Japan</t>
+          <t>Netherlands 5-1 Sweden</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -23872,16 +23888,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.2511552631390055</v>
+        <v>0.5419741522498547</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2639306340880528</v>
+        <v>0.249917248195977</v>
       </c>
       <c r="G39" t="n">
-        <v>0.4849141027729418</v>
+        <v>0.2081085995541683</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1641962238623133</v>
+        <v>0.1265484332078183</v>
       </c>
       <c r="I39" t="b">
         <v>1</v>
@@ -23890,17 +23906,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Belgium 0-0 Iran</t>
+          <t>Tunisia 0-4 Japan</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -23909,35 +23925,35 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.4110593987622102</v>
+        <v>0.2511552631390055</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2749923306348419</v>
+        <v>0.2639306340880528</v>
       </c>
       <c r="G40" t="n">
-        <v>0.3139482706029479</v>
+        <v>0.4849141027729418</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1337666729626658</v>
+        <v>0.1641962238623133</v>
       </c>
       <c r="I40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>New Zealand 1-3 Egypt</t>
+          <t>Belgium 0-0 Iran</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -23946,53 +23962,53 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.2701606709292552</v>
+        <v>0.4110593987622102</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2683528583888833</v>
+        <v>0.2749923306348419</v>
       </c>
       <c r="G41" t="n">
-        <v>0.4614864706818617</v>
+        <v>0.3139482706029479</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1814918046878114</v>
+        <v>0.1337666729626658</v>
       </c>
       <c r="I41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Spain 4-0 Saudi Arabia</t>
+          <t>New Zealand 1-3 Egypt</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.711801189694372</v>
+        <v>0.2701606709292552</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1844344879110749</v>
+        <v>0.2683528583888833</v>
       </c>
       <c r="G42" t="n">
-        <v>0.103764322394553</v>
+        <v>0.4614864706818617</v>
       </c>
       <c r="H42" t="n">
-        <v>0.04691279443179004</v>
+        <v>0.1814918046878114</v>
       </c>
       <c r="I42" t="b">
         <v>1</v>
@@ -24001,7 +24017,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Uruguay 2-2 Cape Verde</t>
+          <t>Spain 4-0 Saudi Arabia</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -24011,34 +24027,34 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.4946917415780235</v>
+        <v>0.711801189694372</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2618487176721053</v>
+        <v>0.1844344879110749</v>
       </c>
       <c r="G43" t="n">
-        <v>0.243459540749871</v>
+        <v>0.103764322394553</v>
       </c>
       <c r="H43" t="n">
-        <v>0.1519962335838181</v>
+        <v>0.04691279443179004</v>
       </c>
       <c r="I43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Argentina 2-0 Austria</t>
+          <t>Uruguay 2-2 Cape Verde</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -24048,7 +24064,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -24057,25 +24073,25 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.5600237883076568</v>
+        <v>0.4946917415780235</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2445838247676272</v>
+        <v>0.2618487176721053</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1953923869247162</v>
+        <v>0.243459540749871</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1158786258616418</v>
+        <v>0.1519962335838181</v>
       </c>
       <c r="I44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>France 3-0 Iraq</t>
+          <t>Argentina 2-0 Austria</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -24090,20 +24106,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.6938172051627756</v>
+        <v>0.5600237883076568</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1929050139558987</v>
+        <v>0.2445838247676272</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1132777808813258</v>
+        <v>0.1953923869247162</v>
       </c>
       <c r="H45" t="n">
-        <v>0.05328987974786575</v>
+        <v>0.1158786258616418</v>
       </c>
       <c r="I45" t="b">
         <v>1</v>
@@ -24112,35 +24128,35 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jordan 1-2 Algeria</t>
+          <t>France 3-0 Iraq</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.2871872150453605</v>
+        <v>0.6938172051627756</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2714956942424305</v>
+        <v>0.1929050139558987</v>
       </c>
       <c r="G46" t="n">
-        <v>0.4413170907122089</v>
+        <v>0.1132777808813258</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1973015448078901</v>
+        <v>0.05328987974786575</v>
       </c>
       <c r="I46" t="b">
         <v>1</v>
@@ -24149,17 +24165,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Norway 3-2 Senegal</t>
+          <t>Jordan 1-2 Algeria</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -24168,16 +24184,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.399746405577862</v>
+        <v>0.2871872150453605</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2759053625170023</v>
+        <v>0.2714956942424305</v>
       </c>
       <c r="G47" t="n">
-        <v>0.3243482319051358</v>
+        <v>0.4413170907122089</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2327530765783421</v>
+        <v>0.1973015448078901</v>
       </c>
       <c r="I47" t="b">
         <v>1</v>
@@ -24186,7 +24202,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Colombia 1-0 DR Congo</t>
+          <t>Norway 3-2 Senegal</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -24201,20 +24217,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.6513377464031052</v>
+        <v>0.399746405577862</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2115244400993148</v>
+        <v>0.2759053625170023</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1371378134975802</v>
+        <v>0.3243482319051358</v>
       </c>
       <c r="H48" t="n">
-        <v>0.07018607348708122</v>
+        <v>0.2327530765783421</v>
       </c>
       <c r="I48" t="b">
         <v>1</v>
@@ -24223,7 +24239,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>England 0-0 Ghana</t>
+          <t>Colombia 1-0 DR Congo</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -24233,7 +24249,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -24242,72 +24258,72 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.6391364229920049</v>
+        <v>0.6513377464031052</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2165036639184777</v>
+        <v>0.2115244400993148</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1443599130895173</v>
+        <v>0.1371378134975802</v>
       </c>
       <c r="H49" t="n">
-        <v>0.214667575851114</v>
+        <v>0.07018607348708122</v>
       </c>
       <c r="I49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Panama 0-1 Croatia</t>
+          <t>England 0-0 Ghana</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.2779192196934168</v>
+        <v>0.6391364229920049</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2698775634692422</v>
+        <v>0.2165036639184777</v>
       </c>
       <c r="G50" t="n">
-        <v>0.452203216837341</v>
+        <v>0.1443599130895173</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1886602041591775</v>
+        <v>0.214667575851114</v>
       </c>
       <c r="I50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Portugal 5-0 Uzbekistan</t>
+          <t>Panama 0-1 Croatia</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -24316,16 +24332,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.5305667905006943</v>
+        <v>0.2779192196934168</v>
       </c>
       <c r="F51" t="n">
-        <v>0.2530706921820465</v>
+        <v>0.2698775634692422</v>
       </c>
       <c r="G51" t="n">
-        <v>0.216362517317259</v>
+        <v>0.452203216837341</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1335901385403401</v>
+        <v>0.1886602041591775</v>
       </c>
       <c r="I51" t="b">
         <v>1</v>
@@ -24334,17 +24350,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Scotland 0-3 Brazil</t>
+          <t>Portugal 5-0 Uzbekistan</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -24353,16 +24369,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.24901815042318</v>
+        <v>0.5305667905006943</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2633698330694462</v>
+        <v>0.2530706921820465</v>
       </c>
       <c r="G52" t="n">
-        <v>0.4876120165073738</v>
+        <v>0.216362517317259</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1622757424339106</v>
+        <v>0.1335901385403401</v>
       </c>
       <c r="I52" t="b">
         <v>1</v>
@@ -24371,37 +24387,111 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>Czechia 0-3 Mexico</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0.2351921354348235</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.2594153894470163</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.5053924751181602</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.1499759721200661</v>
+      </c>
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Scotland 0-3 Brazil</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0.24901815042318</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.2633698330694462</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.4876120165073738</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.1622757424339106</v>
+      </c>
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>Switzerland 2-1 Canada</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="E53" t="n">
+      <c r="E55" t="n">
         <v>0.3372955421668554</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F55" t="n">
         <v>0.2767126361678793</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G55" t="n">
         <v>0.3859918216652653</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H55" t="n">
         <v>0.294083442412196</v>
       </c>
-      <c r="I53" t="b">
+      <c r="I55" t="b">
         <v>0</v>
       </c>
     </row>

--- a/outputs/world_cup_2026_recommendations.xlsx
+++ b/outputs/world_cup_2026_recommendations.xlsx
@@ -549,7 +549,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>• Matches scored: 54   Outcome hit-rate: 59%   Mean RPS: 0.182  (good tournament forecasts ~0.17-0.18)</t>
+          <t>• Matches scored: 60   Outcome hit-rate: 60%   Mean RPS: 0.182  (good tournament forecasts ~0.17-0.18)</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -1045,19 +1045,19 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>48.6</v>
+        <v>47.1</v>
       </c>
       <c r="K5" t="n">
-        <v>25.7</v>
+        <v>26</v>
       </c>
       <c r="L5" t="n">
-        <v>25.7</v>
+        <v>26.9</v>
       </c>
       <c r="M5" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="N5" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1369,19 +1369,19 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>34.1</v>
+        <v>32.8</v>
       </c>
       <c r="K9" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="L9" t="n">
-        <v>37.2</v>
+        <v>38.6</v>
       </c>
       <c r="M9" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="N9" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1450,16 +1450,16 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>73.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="L10" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="M10" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="N10" t="n">
         <v>0.84</v>
@@ -1531,16 +1531,16 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>30.3</v>
+        <v>30.1</v>
       </c>
       <c r="K11" t="n">
         <v>29.2</v>
       </c>
       <c r="L11" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
         <v>1.26</v>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1612,19 +1612,19 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>40</v>
+        <v>41.5</v>
       </c>
       <c r="K12" t="n">
         <v>25.8</v>
       </c>
       <c r="L12" t="n">
-        <v>34.2</v>
+        <v>32.7</v>
       </c>
       <c r="M12" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="N12" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1693,19 +1693,19 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>44.8</v>
+        <v>46.4</v>
       </c>
       <c r="K13" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="L13" t="n">
-        <v>30.8</v>
+        <v>29.3</v>
       </c>
       <c r="M13" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="N13" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -3232,19 +3232,19 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>46.6</v>
+        <v>45.2</v>
       </c>
       <c r="K32" t="n">
-        <v>26.6</v>
+        <v>26.8</v>
       </c>
       <c r="L32" t="n">
-        <v>26.8</v>
+        <v>28</v>
       </c>
       <c r="M32" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="N32" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -3313,19 +3313,19 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>38.9</v>
+        <v>40.3</v>
       </c>
       <c r="K33" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="L33" t="n">
-        <v>33</v>
+        <v>31.8</v>
       </c>
       <c r="M33" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="N33" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -3394,19 +3394,19 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>51.3</v>
+        <v>48.5</v>
       </c>
       <c r="K34" t="n">
-        <v>24.8</v>
+        <v>25.5</v>
       </c>
       <c r="L34" t="n">
-        <v>23.9</v>
+        <v>26</v>
       </c>
       <c r="M34" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="N34" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -3475,19 +3475,19 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>61.9</v>
+        <v>64.3</v>
       </c>
       <c r="K35" t="n">
-        <v>22.8</v>
+        <v>21.9</v>
       </c>
       <c r="L35" t="n">
-        <v>15.3</v>
+        <v>13.8</v>
       </c>
       <c r="M35" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="N35" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -3556,16 +3556,16 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>60.5</v>
+        <v>60.2</v>
       </c>
       <c r="K36" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="L36" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="M36" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="N36" t="n">
         <v>1.11</v>
@@ -3637,19 +3637,19 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="K37" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="L37" t="n">
-        <v>63.1</v>
+        <v>62.8</v>
       </c>
       <c r="M37" t="n">
         <v>0.97</v>
       </c>
       <c r="N37" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -5164,31 +5164,31 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>final</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>28.2</v>
+        <v>31.1</v>
       </c>
       <c r="K56" t="n">
-        <v>27.2</v>
+        <v>26.1</v>
       </c>
       <c r="L56" t="n">
-        <v>44.7</v>
+        <v>42.8</v>
       </c>
       <c r="M56" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="N56" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -5200,11 +5200,15 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 42)</t>
+          <t>actual 3-2; model pick 1-2 (outcome miss)</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5245,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -5249,23 +5253,23 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>final</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>34.7</v>
+        <v>34.1</v>
       </c>
       <c r="K57" t="n">
-        <v>27.8</v>
+        <v>29.3</v>
       </c>
       <c r="L57" t="n">
-        <v>37.5</v>
+        <v>36.6</v>
       </c>
       <c r="M57" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="N57" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -5277,11 +5281,15 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 36)</t>
+          <t>actual 0-0; model pick 0-1 (outcome miss)</t>
         </is>
       </c>
     </row>
@@ -5318,47 +5326,51 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>54</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="K58" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="L58" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N58" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="H58" t="n">
-        <v>52</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>scheduled</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="K58" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="L58" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="N58" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 52)</t>
+          <t>actual 0-2; model pick 0-1 (outcome hit)</t>
         </is>
       </c>
     </row>
@@ -5395,31 +5407,31 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H59" t="n">
+        <v>40</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="L59" t="n">
         <v>42</v>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>scheduled</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="K59" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="L59" t="n">
-        <v>44.6</v>
-      </c>
       <c r="M59" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="N59" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -5431,11 +5443,15 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 42)</t>
+          <t>actual 2-1; model pick 0-1 (outcome miss)</t>
         </is>
       </c>
     </row>
@@ -5472,31 +5488,31 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>final</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>56.7</v>
+        <v>54.2</v>
       </c>
       <c r="K60" t="n">
-        <v>22.5</v>
+        <v>23.6</v>
       </c>
       <c r="L60" t="n">
-        <v>20.8</v>
+        <v>22.2</v>
       </c>
       <c r="M60" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="N60" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -5508,11 +5524,15 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 50)</t>
+          <t>actual 1-1; model pick 2-1 (outcome miss)</t>
         </is>
       </c>
     </row>
@@ -5549,47 +5569,51 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>58</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="K61" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="L61" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="N61" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
           <t>0-2</t>
         </is>
       </c>
-      <c r="H61" t="n">
-        <v>57</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>scheduled</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="K61" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="L61" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="N61" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 57)</t>
+          <t>actual 1-3; model pick 0-2 (outcome hit)</t>
         </is>
       </c>
     </row>
@@ -6616,16 +6640,16 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -6633,19 +6657,19 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>69.5</v>
+        <v>59.5</v>
       </c>
       <c r="K75" t="n">
-        <v>18.1</v>
+        <v>21.2</v>
       </c>
       <c r="L75" t="n">
-        <v>12.4</v>
+        <v>19.3</v>
       </c>
       <c r="M75" t="n">
-        <v>2.37</v>
+        <v>2.12</v>
       </c>
       <c r="N75" t="n">
-        <v>0.91</v>
+        <v>1.14</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -6654,16 +6678,16 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="n">
-        <v>38.3</v>
+        <v>79</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>most-likely pairing (38%); Germany to advance</t>
+          <t>most-likely pairing (79%); Germany to advance</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6724,7 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -6708,19 +6732,19 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>43.4</v>
+        <v>44.2</v>
       </c>
       <c r="K76" t="n">
-        <v>25.8</v>
+        <v>25.6</v>
       </c>
       <c r="L76" t="n">
-        <v>30.8</v>
+        <v>30.2</v>
       </c>
       <c r="M76" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="N76" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -6734,11 +6758,11 @@
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="n">
-        <v>55.3</v>
+        <v>100</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>most-likely pairing (55%); Netherlands to advance</t>
+          <t>most-likely pairing (100%); Netherlands to advance</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6790,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -6775,7 +6799,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -6783,19 +6807,19 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>39.7</v>
+        <v>42.9</v>
       </c>
       <c r="K77" t="n">
-        <v>26.5</v>
+        <v>27</v>
       </c>
       <c r="L77" t="n">
-        <v>33.8</v>
+        <v>30.1</v>
       </c>
       <c r="M77" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="N77" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -6809,11 +6833,11 @@
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="n">
-        <v>43.5</v>
+        <v>100</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>most-likely pairing (44%); Brazil to advance</t>
+          <t>most-likely pairing (100%); Brazil to advance</t>
         </is>
       </c>
     </row>
@@ -6858,19 +6882,19 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>58.8</v>
+        <v>57.9</v>
       </c>
       <c r="K78" t="n">
-        <v>23.2</v>
+        <v>24</v>
       </c>
       <c r="L78" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="M78" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="N78" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -6879,16 +6903,16 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="n">
-        <v>19.9</v>
+        <v>58.4</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>most-likely pairing (20%); France to advance</t>
+          <t>most-likely pairing (58%); France to advance</t>
         </is>
       </c>
     </row>
@@ -6925,7 +6949,7 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -6933,19 +6957,19 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>27.6</v>
+        <v>28.6</v>
       </c>
       <c r="K79" t="n">
-        <v>26</v>
+        <v>26.4</v>
       </c>
       <c r="L79" t="n">
-        <v>46.4</v>
+        <v>45</v>
       </c>
       <c r="M79" t="n">
         <v>1.16</v>
       </c>
       <c r="N79" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -6959,11 +6983,11 @@
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="n">
-        <v>55.2</v>
+        <v>72.2</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>most-likely pairing (55%); Norway to advance</t>
+          <t>most-likely pairing (72%); Norway to advance</t>
         </is>
       </c>
     </row>
@@ -6991,7 +7015,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -7000,7 +7024,7 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -7008,19 +7032,19 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>47.5</v>
+        <v>36.7</v>
       </c>
       <c r="K80" t="n">
-        <v>27.8</v>
+        <v>29.5</v>
       </c>
       <c r="L80" t="n">
-        <v>24.7</v>
+        <v>33.8</v>
       </c>
       <c r="M80" t="n">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="N80" t="n">
-        <v>0.95</v>
+        <v>1.12</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -7034,11 +7058,11 @@
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="n">
-        <v>23.4</v>
+        <v>94.8</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>most-likely pairing (23%); Mexico to advance</t>
+          <t>most-likely pairing (95%); Mexico to advance</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7133,7 @@
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -7146,7 +7170,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H82" t="n">
@@ -7158,19 +7182,19 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>58.8</v>
+        <v>58.1</v>
       </c>
       <c r="K82" t="n">
-        <v>22.7</v>
+        <v>22.4</v>
       </c>
       <c r="L82" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="M82" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="N82" t="n">
-        <v>0.99</v>
+        <v>1.06</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -7184,11 +7208,11 @@
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="n">
-        <v>60.9</v>
+        <v>100</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>most-likely pairing (61%); United States to advance</t>
+          <t>most-likely pairing (100%); United States to advance</t>
         </is>
       </c>
     </row>
@@ -7259,11 +7283,11 @@
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="n">
-        <v>53.9</v>
+        <v>43.5</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>most-likely pairing (54%); Egypt to advance</t>
+          <t>most-likely pairing (43%); Egypt to advance</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7358,7 @@
       </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -7409,7 +7433,7 @@
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="n">
-        <v>51.9</v>
+        <v>51.6</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -7450,7 +7474,7 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -7458,19 +7482,19 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>51.6</v>
+        <v>50.5</v>
       </c>
       <c r="K86" t="n">
-        <v>23.9</v>
+        <v>24.4</v>
       </c>
       <c r="L86" t="n">
-        <v>24.4</v>
+        <v>25.1</v>
       </c>
       <c r="M86" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="N86" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -7484,11 +7508,11 @@
       </c>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="n">
-        <v>22.9</v>
+        <v>20.6</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>most-likely pairing (23%); Switzerland to advance</t>
+          <t>most-likely pairing (21%); Switzerland to advance</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7583,7 @@
       </c>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="n">
-        <v>54.9</v>
+        <v>54.8</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -7634,11 +7658,11 @@
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="n">
-        <v>30.7</v>
+        <v>30.4</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>most-likely pairing (31%); Colombia to advance</t>
+          <t>most-likely pairing (30%); Colombia to advance</t>
         </is>
       </c>
     </row>
@@ -7683,19 +7707,19 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>31.4</v>
+        <v>31.1</v>
       </c>
       <c r="K89" t="n">
-        <v>28.8</v>
+        <v>29.5</v>
       </c>
       <c r="L89" t="n">
-        <v>39.8</v>
+        <v>39.4</v>
       </c>
       <c r="M89" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="N89" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
@@ -7709,11 +7733,11 @@
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="n">
-        <v>32.8</v>
+        <v>50.8</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>most-likely pairing (33%); Belgium to advance</t>
+          <t>most-likely pairing (51%); Belgium to advance</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7774,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -7758,19 +7782,19 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>30.6</v>
+        <v>29.3</v>
       </c>
       <c r="K90" t="n">
-        <v>25.5</v>
+        <v>25.2</v>
       </c>
       <c r="L90" t="n">
-        <v>43.9</v>
+        <v>45.5</v>
       </c>
       <c r="M90" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="N90" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -7784,7 +7808,7 @@
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="n">
-        <v>37.7</v>
+        <v>37.5</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -7816,16 +7840,16 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -7833,19 +7857,19 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>32.9</v>
+        <v>26.8</v>
       </c>
       <c r="K91" t="n">
-        <v>26.6</v>
+        <v>24.6</v>
       </c>
       <c r="L91" t="n">
-        <v>40.4</v>
+        <v>48.6</v>
       </c>
       <c r="M91" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="N91" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -7859,11 +7883,11 @@
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="n">
-        <v>29.6</v>
+        <v>38.4</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>most-likely pairing (30%); Morocco to advance</t>
+          <t>most-likely pairing (38%); Netherlands to advance</t>
         </is>
       </c>
     </row>
@@ -7934,11 +7958,11 @@
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="n">
-        <v>25.7</v>
+        <v>24.2</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>most-likely pairing (26%); Brazil to advance</t>
+          <t>most-likely pairing (24%); Brazil to advance</t>
         </is>
       </c>
     </row>
@@ -8009,11 +8033,11 @@
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="n">
-        <v>26.4</v>
+        <v>22.6</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>most-likely pairing (26%); England to advance</t>
+          <t>most-likely pairing (23%); England to advance</t>
         </is>
       </c>
     </row>
@@ -8084,11 +8108,11 @@
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>most-likely pairing (22%); Spain to advance</t>
+          <t>most-likely pairing (21%); Spain to advance</t>
         </is>
       </c>
     </row>
@@ -8116,16 +8140,16 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -8133,19 +8157,19 @@
         </is>
       </c>
       <c r="J95" t="n">
-        <v>44.3</v>
+        <v>40.2</v>
       </c>
       <c r="K95" t="n">
-        <v>27.3</v>
+        <v>26.2</v>
       </c>
       <c r="L95" t="n">
-        <v>28.4</v>
+        <v>33.7</v>
       </c>
       <c r="M95" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="N95" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -8159,11 +8183,11 @@
       </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="n">
-        <v>26.6</v>
+        <v>22.8</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>most-likely pairing (27%); United States to advance</t>
+          <t>most-likely pairing (23%); United States to advance</t>
         </is>
       </c>
     </row>
@@ -8208,19 +8232,19 @@
         </is>
       </c>
       <c r="J96" t="n">
-        <v>60.8</v>
+        <v>59.9</v>
       </c>
       <c r="K96" t="n">
-        <v>23.2</v>
+        <v>24</v>
       </c>
       <c r="L96" t="n">
         <v>16.1</v>
       </c>
       <c r="M96" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="N96" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -8234,11 +8258,11 @@
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="n">
-        <v>24.6</v>
+        <v>37.6</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>most-likely pairing (25%); Argentina to advance</t>
+          <t>most-likely pairing (38%); Argentina to advance</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8333,7 @@
       </c>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -8341,16 +8365,16 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -8358,23 +8382,23 @@
         </is>
       </c>
       <c r="J98" t="n">
-        <v>49.2</v>
+        <v>36.7</v>
       </c>
       <c r="K98" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="L98" t="n">
-        <v>26.4</v>
+        <v>38.6</v>
       </c>
       <c r="M98" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="N98" t="n">
-        <v>1.23</v>
+        <v>1.57</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -8384,11 +8408,11 @@
       </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="n">
-        <v>10.2</v>
+        <v>13.3</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>most-likely pairing (10%); Germany to advance</t>
+          <t>most-likely pairing (13%); Netherlands to advance</t>
         </is>
       </c>
     </row>
@@ -8425,7 +8449,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -8433,19 +8457,19 @@
         </is>
       </c>
       <c r="J99" t="n">
-        <v>57.5</v>
+        <v>59.8</v>
       </c>
       <c r="K99" t="n">
-        <v>24</v>
+        <v>22.7</v>
       </c>
       <c r="L99" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="M99" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="N99" t="n">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -8454,12 +8478,12 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -8534,11 +8558,11 @@
       </c>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>most-likely pairing (10%); Brazil to advance</t>
+          <t>most-likely pairing (9%); Brazil to advance</t>
         </is>
       </c>
     </row>
@@ -8609,7 +8633,7 @@
       </c>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="n">
-        <v>15</v>
+        <v>14.6</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -8684,7 +8708,7 @@
       </c>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -8759,11 +8783,11 @@
       </c>
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>most-likely pairing (8%); Argentina to advance</t>
+          <t>most-likely pairing (7%); Argentina to advance</t>
         </is>
       </c>
     </row>
@@ -9329,7 +9353,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -9337,19 +9361,19 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>48.6</v>
+        <v>47.1</v>
       </c>
       <c r="K5" t="n">
-        <v>25.7</v>
+        <v>26</v>
       </c>
       <c r="L5" t="n">
-        <v>25.7</v>
+        <v>26.9</v>
       </c>
       <c r="M5" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="N5" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -9653,7 +9677,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -9661,19 +9685,19 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>34.1</v>
+        <v>32.8</v>
       </c>
       <c r="K9" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="L9" t="n">
-        <v>37.2</v>
+        <v>38.6</v>
       </c>
       <c r="M9" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="N9" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -9742,16 +9766,16 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>73.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="L10" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="M10" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="N10" t="n">
         <v>0.84</v>
@@ -9823,16 +9847,16 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>30.3</v>
+        <v>30.1</v>
       </c>
       <c r="K11" t="n">
         <v>29.2</v>
       </c>
       <c r="L11" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
         <v>1.26</v>
@@ -9896,7 +9920,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -9904,19 +9928,19 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>40</v>
+        <v>41.5</v>
       </c>
       <c r="K12" t="n">
         <v>25.8</v>
       </c>
       <c r="L12" t="n">
-        <v>34.2</v>
+        <v>32.7</v>
       </c>
       <c r="M12" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="N12" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -9977,7 +10001,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -9985,19 +10009,19 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>44.8</v>
+        <v>46.4</v>
       </c>
       <c r="K13" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="L13" t="n">
-        <v>30.8</v>
+        <v>29.3</v>
       </c>
       <c r="M13" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="N13" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -11516,7 +11540,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -11524,19 +11548,19 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>46.6</v>
+        <v>45.2</v>
       </c>
       <c r="K32" t="n">
-        <v>26.6</v>
+        <v>26.8</v>
       </c>
       <c r="L32" t="n">
-        <v>26.8</v>
+        <v>28</v>
       </c>
       <c r="M32" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="N32" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -11597,7 +11621,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -11605,19 +11629,19 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>38.9</v>
+        <v>40.3</v>
       </c>
       <c r="K33" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="L33" t="n">
-        <v>33</v>
+        <v>31.8</v>
       </c>
       <c r="M33" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="N33" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -11678,7 +11702,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -11686,19 +11710,19 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>51.3</v>
+        <v>48.5</v>
       </c>
       <c r="K34" t="n">
-        <v>24.8</v>
+        <v>25.5</v>
       </c>
       <c r="L34" t="n">
-        <v>23.9</v>
+        <v>26</v>
       </c>
       <c r="M34" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="N34" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -11759,7 +11783,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -11767,19 +11791,19 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>61.9</v>
+        <v>64.3</v>
       </c>
       <c r="K35" t="n">
-        <v>22.8</v>
+        <v>21.9</v>
       </c>
       <c r="L35" t="n">
-        <v>15.3</v>
+        <v>13.8</v>
       </c>
       <c r="M35" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="N35" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -11848,16 +11872,16 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>60.5</v>
+        <v>60.2</v>
       </c>
       <c r="K36" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="L36" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="M36" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="N36" t="n">
         <v>1.11</v>
@@ -11929,19 +11953,19 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="K37" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="L37" t="n">
-        <v>63.1</v>
+        <v>62.8</v>
       </c>
       <c r="M37" t="n">
         <v>0.97</v>
       </c>
       <c r="N37" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -13456,31 +13480,31 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>final</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>28.2</v>
+        <v>31.1</v>
       </c>
       <c r="K56" t="n">
-        <v>27.2</v>
+        <v>26.1</v>
       </c>
       <c r="L56" t="n">
-        <v>44.7</v>
+        <v>42.8</v>
       </c>
       <c r="M56" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="N56" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -13492,11 +13516,15 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 42)</t>
+          <t>actual 3-2; model pick 1-2 (outcome miss)</t>
         </is>
       </c>
     </row>
@@ -13533,7 +13561,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -13541,23 +13569,23 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>final</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>34.7</v>
+        <v>34.1</v>
       </c>
       <c r="K57" t="n">
-        <v>27.8</v>
+        <v>29.3</v>
       </c>
       <c r="L57" t="n">
-        <v>37.5</v>
+        <v>36.6</v>
       </c>
       <c r="M57" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="N57" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -13569,11 +13597,15 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 36)</t>
+          <t>actual 0-0; model pick 0-1 (outcome miss)</t>
         </is>
       </c>
     </row>
@@ -13610,47 +13642,51 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>54</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="K58" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="L58" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N58" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="H58" t="n">
-        <v>52</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>scheduled</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="K58" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="L58" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="N58" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 52)</t>
+          <t>actual 0-2; model pick 0-1 (outcome hit)</t>
         </is>
       </c>
     </row>
@@ -13687,31 +13723,31 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H59" t="n">
+        <v>40</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="L59" t="n">
         <v>42</v>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>scheduled</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="K59" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="L59" t="n">
-        <v>44.6</v>
-      </c>
       <c r="M59" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="N59" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -13723,11 +13759,15 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 42)</t>
+          <t>actual 2-1; model pick 0-1 (outcome miss)</t>
         </is>
       </c>
     </row>
@@ -13764,31 +13804,31 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>final</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>56.7</v>
+        <v>54.2</v>
       </c>
       <c r="K60" t="n">
-        <v>22.5</v>
+        <v>23.6</v>
       </c>
       <c r="L60" t="n">
-        <v>20.8</v>
+        <v>22.2</v>
       </c>
       <c r="M60" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="N60" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -13800,11 +13840,15 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 50)</t>
+          <t>actual 1-1; model pick 2-1 (outcome miss)</t>
         </is>
       </c>
     </row>
@@ -13841,47 +13885,51 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>58</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="K61" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="L61" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="N61" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
           <t>0-2</t>
         </is>
       </c>
-      <c r="H61" t="n">
-        <v>57</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>scheduled</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="K61" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="L61" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="N61" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
-          <t>maximises expected pool points (EV 57)</t>
+          <t>actual 1-3; model pick 0-2 (outcome hit)</t>
         </is>
       </c>
     </row>
@@ -15040,16 +15088,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -15057,19 +15105,19 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>69.5</v>
+        <v>59.5</v>
       </c>
       <c r="K3" t="n">
-        <v>18.1</v>
+        <v>21.2</v>
       </c>
       <c r="L3" t="n">
-        <v>12.4</v>
+        <v>19.3</v>
       </c>
       <c r="M3" t="n">
-        <v>2.37</v>
+        <v>2.12</v>
       </c>
       <c r="N3" t="n">
-        <v>0.91</v>
+        <v>1.14</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -15078,16 +15126,16 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>38.3</v>
+        <v>79</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>most-likely pairing (38%); Germany to advance</t>
+          <t>most-likely pairing (79%); Germany to advance</t>
         </is>
       </c>
     </row>
@@ -15124,7 +15172,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -15132,19 +15180,19 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>43.4</v>
+        <v>44.2</v>
       </c>
       <c r="K4" t="n">
-        <v>25.8</v>
+        <v>25.6</v>
       </c>
       <c r="L4" t="n">
-        <v>30.8</v>
+        <v>30.2</v>
       </c>
       <c r="M4" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="N4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -15158,11 +15206,11 @@
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>55.3</v>
+        <v>100</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>most-likely pairing (55%); Netherlands to advance</t>
+          <t>most-likely pairing (100%); Netherlands to advance</t>
         </is>
       </c>
     </row>
@@ -15190,7 +15238,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -15199,7 +15247,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -15207,19 +15255,19 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>39.7</v>
+        <v>42.9</v>
       </c>
       <c r="K5" t="n">
-        <v>26.5</v>
+        <v>27</v>
       </c>
       <c r="L5" t="n">
-        <v>33.8</v>
+        <v>30.1</v>
       </c>
       <c r="M5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="N5" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -15233,11 +15281,11 @@
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>43.5</v>
+        <v>100</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>most-likely pairing (44%); Brazil to advance</t>
+          <t>most-likely pairing (100%); Brazil to advance</t>
         </is>
       </c>
     </row>
@@ -15282,19 +15330,19 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>58.8</v>
+        <v>57.9</v>
       </c>
       <c r="K6" t="n">
-        <v>23.2</v>
+        <v>24</v>
       </c>
       <c r="L6" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="M6" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="N6" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -15303,16 +15351,16 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>19.9</v>
+        <v>58.4</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>most-likely pairing (20%); France to advance</t>
+          <t>most-likely pairing (58%); France to advance</t>
         </is>
       </c>
     </row>
@@ -15349,7 +15397,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -15357,19 +15405,19 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>27.6</v>
+        <v>28.6</v>
       </c>
       <c r="K7" t="n">
-        <v>26</v>
+        <v>26.4</v>
       </c>
       <c r="L7" t="n">
-        <v>46.4</v>
+        <v>45</v>
       </c>
       <c r="M7" t="n">
         <v>1.16</v>
       </c>
       <c r="N7" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -15383,11 +15431,11 @@
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>55.2</v>
+        <v>72.2</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>most-likely pairing (55%); Norway to advance</t>
+          <t>most-likely pairing (72%); Norway to advance</t>
         </is>
       </c>
     </row>
@@ -15415,7 +15463,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -15424,7 +15472,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -15432,19 +15480,19 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>47.5</v>
+        <v>36.7</v>
       </c>
       <c r="K8" t="n">
-        <v>27.8</v>
+        <v>29.5</v>
       </c>
       <c r="L8" t="n">
-        <v>24.7</v>
+        <v>33.8</v>
       </c>
       <c r="M8" t="n">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="N8" t="n">
-        <v>0.95</v>
+        <v>1.12</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -15458,11 +15506,11 @@
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>23.4</v>
+        <v>94.8</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>most-likely pairing (23%); Mexico to advance</t>
+          <t>most-likely pairing (95%); Mexico to advance</t>
         </is>
       </c>
     </row>
@@ -15533,7 +15581,7 @@
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -15570,7 +15618,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -15582,19 +15630,19 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>58.8</v>
+        <v>58.1</v>
       </c>
       <c r="K10" t="n">
-        <v>22.7</v>
+        <v>22.4</v>
       </c>
       <c r="L10" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="M10" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="N10" t="n">
-        <v>0.99</v>
+        <v>1.06</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -15608,11 +15656,11 @@
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>60.9</v>
+        <v>100</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>most-likely pairing (61%); United States to advance</t>
+          <t>most-likely pairing (100%); United States to advance</t>
         </is>
       </c>
     </row>
@@ -15683,11 +15731,11 @@
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
-        <v>53.9</v>
+        <v>43.5</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>most-likely pairing (54%); Egypt to advance</t>
+          <t>most-likely pairing (43%); Egypt to advance</t>
         </is>
       </c>
     </row>
@@ -15758,7 +15806,7 @@
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -15833,7 +15881,7 @@
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
-        <v>51.9</v>
+        <v>51.6</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -15874,7 +15922,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -15882,19 +15930,19 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>51.6</v>
+        <v>50.5</v>
       </c>
       <c r="K14" t="n">
-        <v>23.9</v>
+        <v>24.4</v>
       </c>
       <c r="L14" t="n">
-        <v>24.4</v>
+        <v>25.1</v>
       </c>
       <c r="M14" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="N14" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -15908,11 +15956,11 @@
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
-        <v>22.9</v>
+        <v>20.6</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>most-likely pairing (23%); Switzerland to advance</t>
+          <t>most-likely pairing (21%); Switzerland to advance</t>
         </is>
       </c>
     </row>
@@ -15983,7 +16031,7 @@
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
-        <v>54.9</v>
+        <v>54.8</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -16058,11 +16106,11 @@
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
-        <v>30.7</v>
+        <v>30.4</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>most-likely pairing (31%); Colombia to advance</t>
+          <t>most-likely pairing (30%); Colombia to advance</t>
         </is>
       </c>
     </row>
@@ -16107,19 +16155,19 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>31.4</v>
+        <v>31.1</v>
       </c>
       <c r="K17" t="n">
-        <v>28.8</v>
+        <v>29.5</v>
       </c>
       <c r="L17" t="n">
-        <v>39.8</v>
+        <v>39.4</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -16133,11 +16181,11 @@
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
-        <v>32.8</v>
+        <v>50.8</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>most-likely pairing (33%); Belgium to advance</t>
+          <t>most-likely pairing (51%); Belgium to advance</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16222,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -16182,19 +16230,19 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>30.6</v>
+        <v>29.3</v>
       </c>
       <c r="K18" t="n">
-        <v>25.5</v>
+        <v>25.2</v>
       </c>
       <c r="L18" t="n">
-        <v>43.9</v>
+        <v>45.5</v>
       </c>
       <c r="M18" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="N18" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -16208,7 +16256,7 @@
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
-        <v>37.7</v>
+        <v>37.5</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -16240,16 +16288,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -16257,19 +16305,19 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>32.9</v>
+        <v>26.8</v>
       </c>
       <c r="K19" t="n">
-        <v>26.6</v>
+        <v>24.6</v>
       </c>
       <c r="L19" t="n">
-        <v>40.4</v>
+        <v>48.6</v>
       </c>
       <c r="M19" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="N19" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -16283,11 +16331,11 @@
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
-        <v>29.6</v>
+        <v>38.4</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>most-likely pairing (30%); Morocco to advance</t>
+          <t>most-likely pairing (38%); Netherlands to advance</t>
         </is>
       </c>
     </row>
@@ -16358,11 +16406,11 @@
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
-        <v>25.7</v>
+        <v>24.2</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>most-likely pairing (26%); Brazil to advance</t>
+          <t>most-likely pairing (24%); Brazil to advance</t>
         </is>
       </c>
     </row>
@@ -16433,11 +16481,11 @@
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
-        <v>26.4</v>
+        <v>22.6</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>most-likely pairing (26%); England to advance</t>
+          <t>most-likely pairing (23%); England to advance</t>
         </is>
       </c>
     </row>
@@ -16508,11 +16556,11 @@
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>most-likely pairing (22%); Spain to advance</t>
+          <t>most-likely pairing (21%); Spain to advance</t>
         </is>
       </c>
     </row>
@@ -16540,16 +16588,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -16557,19 +16605,19 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>44.3</v>
+        <v>40.2</v>
       </c>
       <c r="K23" t="n">
-        <v>27.3</v>
+        <v>26.2</v>
       </c>
       <c r="L23" t="n">
-        <v>28.4</v>
+        <v>33.7</v>
       </c>
       <c r="M23" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="N23" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -16583,11 +16631,11 @@
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>26.6</v>
+        <v>22.8</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>most-likely pairing (27%); United States to advance</t>
+          <t>most-likely pairing (23%); United States to advance</t>
         </is>
       </c>
     </row>
@@ -16632,19 +16680,19 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>60.8</v>
+        <v>59.9</v>
       </c>
       <c r="K24" t="n">
-        <v>23.2</v>
+        <v>24</v>
       </c>
       <c r="L24" t="n">
         <v>16.1</v>
       </c>
       <c r="M24" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="N24" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -16658,11 +16706,11 @@
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="n">
-        <v>24.6</v>
+        <v>37.6</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>most-likely pairing (25%); Argentina to advance</t>
+          <t>most-likely pairing (38%); Argentina to advance</t>
         </is>
       </c>
     </row>
@@ -16733,7 +16781,7 @@
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -16765,16 +16813,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -16782,23 +16830,23 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>49.2</v>
+        <v>36.7</v>
       </c>
       <c r="K26" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="L26" t="n">
-        <v>26.4</v>
+        <v>38.6</v>
       </c>
       <c r="M26" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="N26" t="n">
-        <v>1.23</v>
+        <v>1.57</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -16808,11 +16856,11 @@
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="n">
-        <v>10.2</v>
+        <v>13.3</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>most-likely pairing (10%); Germany to advance</t>
+          <t>most-likely pairing (13%); Netherlands to advance</t>
         </is>
       </c>
     </row>
@@ -16849,7 +16897,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -16857,19 +16905,19 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>57.5</v>
+        <v>59.8</v>
       </c>
       <c r="K27" t="n">
-        <v>24</v>
+        <v>22.7</v>
       </c>
       <c r="L27" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="M27" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="N27" t="n">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -16878,12 +16926,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -16958,11 +17006,11 @@
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>most-likely pairing (10%); Brazil to advance</t>
+          <t>most-likely pairing (9%); Brazil to advance</t>
         </is>
       </c>
     </row>
@@ -17033,7 +17081,7 @@
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="n">
-        <v>15</v>
+        <v>14.6</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -17108,7 +17156,7 @@
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -17183,11 +17231,11 @@
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>most-likely pairing (8%); Argentina to advance</t>
+          <t>most-likely pairing (7%); Argentina to advance</t>
         </is>
       </c>
     </row>
@@ -17479,7 +17527,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>92.3</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -17695,7 +17743,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>33.8</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="13">
@@ -17733,14 +17781,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -17760,23 +17808,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9</v>
+        <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>63.6</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>31.2</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>90.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
@@ -17791,19 +17839,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>35.4</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>53.1</v>
+        <v>100</v>
       </c>
       <c r="F16" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>73.2</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -17824,13 +17872,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>15.7</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>84.3</v>
+        <v>100</v>
       </c>
       <c r="G17" t="n">
-        <v>13.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -17841,17 +17889,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>99.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -17868,23 +17916,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.4</v>
+        <v>100</v>
       </c>
       <c r="D19" t="n">
-        <v>76.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>17.3</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>91.59999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20">
@@ -17895,23 +17943,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>8.9</v>
+        <v>100</v>
       </c>
       <c r="E20" t="n">
-        <v>66.5</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>24.7</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>29.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
@@ -17929,16 +17977,16 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>16.3</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>69.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G21" t="n">
-        <v>20.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -17953,13 +18001,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>55.3</v>
+        <v>100</v>
       </c>
       <c r="D22" t="n">
-        <v>43.5</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -17980,13 +18028,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>37.3</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>41.7</v>
+        <v>100</v>
       </c>
       <c r="E23" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -18007,19 +18055,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>14.8</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>77.7</v>
+        <v>100</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>89.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25">
@@ -18040,10 +18088,10 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -18061,13 +18109,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>58.6</v>
+        <v>59.4</v>
       </c>
       <c r="D26" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="E26" t="n">
-        <v>22.6</v>
+        <v>22</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -18088,19 +18136,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="D27" t="n">
-        <v>51.3</v>
+        <v>50.8</v>
       </c>
       <c r="E27" t="n">
-        <v>16.8</v>
+        <v>17.1</v>
       </c>
       <c r="F27" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="G27" t="n">
-        <v>78.2</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28">
@@ -18115,19 +18163,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27.9</v>
+        <v>27.2</v>
       </c>
       <c r="D28" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="E28" t="n">
-        <v>50.9</v>
+        <v>51.4</v>
       </c>
       <c r="F28" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="G28" t="n">
-        <v>62.8</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="29">
@@ -18145,16 +18193,16 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>15.9</v>
+        <v>16.5</v>
       </c>
       <c r="E29" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="F29" t="n">
-        <v>74.3</v>
+        <v>74</v>
       </c>
       <c r="G29" t="n">
-        <v>21.8</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="30">
@@ -18172,10 +18220,10 @@
         <v>80.2</v>
       </c>
       <c r="D30" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="E30" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -18196,19 +18244,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="D31" t="n">
-        <v>55.2</v>
+        <v>55</v>
       </c>
       <c r="E31" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="F31" t="n">
         <v>22.1</v>
       </c>
       <c r="G31" t="n">
-        <v>68.90000000000001</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -18229,13 +18277,13 @@
         <v>8.300000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>66.5</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>41.6</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="33">
@@ -18256,13 +18304,13 @@
         <v>25.2</v>
       </c>
       <c r="E33" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="F33" t="n">
-        <v>68</v>
+        <v>68.2</v>
       </c>
       <c r="G33" t="n">
-        <v>31.1</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="34">
@@ -18277,10 +18325,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>72.3</v>
+        <v>72.2</v>
       </c>
       <c r="D34" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -18304,10 +18352,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="D35" t="n">
-        <v>72.3</v>
+        <v>72.2</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -18337,13 +18385,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="F36" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="G36" t="n">
-        <v>52.9</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="37">
@@ -18364,13 +18412,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="F37" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="G37" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="38">
@@ -18385,10 +18433,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>99.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="D38" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -18415,16 +18463,16 @@
         <v>0.5</v>
       </c>
       <c r="D39" t="n">
-        <v>64.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>33</v>
+        <v>33.3</v>
       </c>
       <c r="F39" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="G39" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40">
@@ -18442,16 +18490,16 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>34.8</v>
+        <v>35.1</v>
       </c>
       <c r="E40" t="n">
-        <v>60.5</v>
+        <v>60.2</v>
       </c>
       <c r="F40" t="n">
         <v>4.7</v>
       </c>
       <c r="G40" t="n">
-        <v>74.8</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="41">
@@ -18472,13 +18520,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="F41" t="n">
-        <v>93.5</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>5.6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="42">
@@ -18493,10 +18541,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>39.5</v>
+        <v>39.7</v>
       </c>
       <c r="D42" t="n">
-        <v>60.2</v>
+        <v>59.9</v>
       </c>
       <c r="E42" t="n">
         <v>0.3</v>
@@ -18520,10 +18568,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>60.5</v>
+        <v>60.3</v>
       </c>
       <c r="D43" t="n">
-        <v>39.5</v>
+        <v>39.7</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -18553,13 +18601,13 @@
         <v>0.3</v>
       </c>
       <c r="E44" t="n">
-        <v>57.8</v>
+        <v>57.9</v>
       </c>
       <c r="F44" t="n">
-        <v>41.9</v>
+        <v>41.7</v>
       </c>
       <c r="G44" t="n">
-        <v>33</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="45">
@@ -18580,13 +18628,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>41.9</v>
+        <v>41.7</v>
       </c>
       <c r="F45" t="n">
-        <v>58.1</v>
+        <v>58.3</v>
       </c>
       <c r="G45" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="46">
@@ -18601,10 +18649,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>61.6</v>
+        <v>61.2</v>
       </c>
       <c r="D46" t="n">
-        <v>37.7</v>
+        <v>38.1</v>
       </c>
       <c r="E46" t="n">
         <v>0.7</v>
@@ -18631,10 +18679,10 @@
         <v>16.4</v>
       </c>
       <c r="D47" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="E47" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -18655,19 +18703,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>22.1</v>
+        <v>22.4</v>
       </c>
       <c r="D48" t="n">
-        <v>29.4</v>
+        <v>29.2</v>
       </c>
       <c r="E48" t="n">
-        <v>43.9</v>
+        <v>43.7</v>
       </c>
       <c r="F48" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G48" t="n">
-        <v>90.3</v>
+        <v>84.7</v>
       </c>
     </row>
     <row r="49">
@@ -18688,13 +18736,13 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F49" t="n">
-        <v>95.3</v>
+        <v>95.2</v>
       </c>
       <c r="G49" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
     </row>
   </sheetData>
@@ -18772,10 +18820,10 @@
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>56.5</v>
+        <v>56.8</v>
       </c>
       <c r="E2" t="n">
-        <v>38.2</v>
+        <v>37.9</v>
       </c>
       <c r="F2" t="n">
         <v>24.3</v>
@@ -18799,13 +18847,13 @@
         <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>47.3</v>
+        <v>47.7</v>
       </c>
       <c r="E3" t="n">
-        <v>34.9</v>
+        <v>35.4</v>
       </c>
       <c r="F3" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="G3" t="n">
         <v>14</v>
@@ -18826,67 +18874,67 @@
         <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>43.8</v>
+        <v>45.1</v>
       </c>
       <c r="E4" t="n">
-        <v>28.6</v>
+        <v>28.9</v>
       </c>
       <c r="F4" t="n">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
       <c r="G4" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>36.8</v>
+        <v>35.5</v>
       </c>
       <c r="E5" t="n">
-        <v>21</v>
+        <v>20.6</v>
       </c>
       <c r="F5" t="n">
         <v>11.2</v>
       </c>
       <c r="G5" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>England</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>35.1</v>
+        <v>34.9</v>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>10.6</v>
       </c>
       <c r="G6" t="n">
         <v>5.6</v>
@@ -18907,43 +18955,43 @@
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>34.4</v>
+        <v>33.8</v>
       </c>
       <c r="E7" t="n">
-        <v>20.1</v>
+        <v>19.6</v>
       </c>
       <c r="F7" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="G7" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>36.1</v>
+        <v>38.5</v>
       </c>
       <c r="E8" t="n">
-        <v>21.1</v>
+        <v>19.5</v>
       </c>
       <c r="F8" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="9">
@@ -18961,175 +19009,175 @@
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>35.1</v>
+        <v>35.4</v>
       </c>
       <c r="E9" t="n">
-        <v>18.1</v>
+        <v>18.5</v>
       </c>
       <c r="F9" t="n">
-        <v>9.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>33.1</v>
+        <v>34.8</v>
       </c>
       <c r="E10" t="n">
-        <v>17.1</v>
+        <v>19.6</v>
       </c>
       <c r="F10" t="n">
-        <v>8.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="G10" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>27.8</v>
+        <v>29</v>
       </c>
       <c r="E11" t="n">
-        <v>13.8</v>
+        <v>15.1</v>
       </c>
       <c r="F11" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="G11" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>28.5</v>
+        <v>27.1</v>
       </c>
       <c r="E12" t="n">
-        <v>14.9</v>
+        <v>12.7</v>
       </c>
       <c r="F12" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="G12" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>30.6</v>
+        <v>21.8</v>
       </c>
       <c r="E13" t="n">
-        <v>14.3</v>
+        <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>37.1</v>
+        <v>25.2</v>
       </c>
       <c r="E14" t="n">
-        <v>14.1</v>
+        <v>11.2</v>
       </c>
       <c r="F14" t="n">
-        <v>6.1</v>
+        <v>5.1</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>26.4</v>
+        <v>37.1</v>
       </c>
       <c r="E15" t="n">
-        <v>11.4</v>
+        <v>13.3</v>
       </c>
       <c r="F15" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="G15" t="n">
         <v>2.1</v>
@@ -19138,34 +19186,34 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>26.4</v>
+        <v>24.1</v>
       </c>
       <c r="E16" t="n">
-        <v>10.5</v>
+        <v>10.9</v>
       </c>
       <c r="F16" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -19177,40 +19225,40 @@
         <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>27.9</v>
+        <v>25.7</v>
       </c>
       <c r="E17" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="F17" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>90.3</v>
+        <v>100</v>
       </c>
       <c r="D18" t="n">
-        <v>19.7</v>
+        <v>27.5</v>
       </c>
       <c r="E18" t="n">
-        <v>9.1</v>
+        <v>10.8</v>
       </c>
       <c r="F18" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="G18" t="n">
         <v>1.7</v>
@@ -19219,34 +19267,34 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>78.2</v>
+        <v>84.7</v>
       </c>
       <c r="D19" t="n">
-        <v>17.1</v>
+        <v>18.5</v>
       </c>
       <c r="E19" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="F19" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -19255,70 +19303,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="D20" t="n">
-        <v>22.2</v>
+        <v>17.2</v>
       </c>
       <c r="E20" t="n">
         <v>7.8</v>
       </c>
       <c r="F20" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>14.1</v>
+        <v>22.8</v>
       </c>
       <c r="E21" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>90.5</v>
+        <v>85</v>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>12.1</v>
       </c>
       <c r="E22" t="n">
         <v>5.7</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="G22" t="n">
         <v>0.9</v>
@@ -19327,103 +19375,103 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>91.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="D23" t="n">
-        <v>13.5</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="F23" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>41.6</v>
+        <v>100</v>
       </c>
       <c r="D24" t="n">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="E24" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="F24" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>52.9</v>
+        <v>40.9</v>
       </c>
       <c r="D25" t="n">
-        <v>10.8</v>
+        <v>9.5</v>
       </c>
       <c r="E25" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>62.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>13.1</v>
+        <v>12.1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="F26" t="n">
         <v>1.9</v>
@@ -19435,25 +19483,25 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>92.3</v>
+        <v>61.3</v>
       </c>
       <c r="D27" t="n">
-        <v>18.6</v>
+        <v>13.4</v>
       </c>
       <c r="E27" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="G27" t="n">
         <v>0.7</v>
@@ -19471,16 +19519,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>74.8</v>
+        <v>66.7</v>
       </c>
       <c r="D28" t="n">
-        <v>11.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="F28" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="G28" t="n">
         <v>0.6</v>
@@ -19489,52 +19537,52 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>29.3</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>6.9</v>
+        <v>14.3</v>
       </c>
       <c r="E29" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="F29" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>73.2</v>
+        <v>41.9</v>
       </c>
       <c r="D30" t="n">
-        <v>9.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="E30" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="F30" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="G30" t="n">
         <v>0.5</v>
@@ -19555,10 +19603,10 @@
         <v>100</v>
       </c>
       <c r="D31" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="F31" t="n">
         <v>0.9</v>
@@ -19570,25 +19618,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>89.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>6.9</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G32" t="n">
         <v>0.3</v>
@@ -19597,52 +19645,52 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>100</v>
       </c>
       <c r="D33" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="E33" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>33.8</v>
+        <v>100</v>
       </c>
       <c r="D34" t="n">
-        <v>4.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G34" t="n">
         <v>0.2</v>
@@ -19651,79 +19699,79 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>DR Congo</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>13.4</v>
+        <v>32.9</v>
       </c>
       <c r="D35" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>68.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="D36" t="n">
-        <v>6.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>100</v>
+        <v>10.8</v>
       </c>
       <c r="D37" t="n">
-        <v>7.2</v>
+        <v>1.2</v>
       </c>
       <c r="E37" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G37" t="n">
         <v>0.1</v>
@@ -19732,49 +19780,49 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>31.1</v>
+        <v>3.9</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F38" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>20.2</v>
+        <v>1.2</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="E39" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -19786,12 +19834,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -19813,25 +19861,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>21.8</v>
+        <v>3.8</v>
       </c>
       <c r="D41" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="E41" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -19840,22 +19888,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -19867,25 +19915,25 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DR Congo</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -19894,25 +19942,25 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="D44" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -19921,25 +19969,25 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>30.9</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -19948,22 +19996,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>5.6</v>
+        <v>22.3</v>
       </c>
       <c r="D46" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="F46" t="n">
         <v>0.1</v>
@@ -19975,12 +20023,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -20002,25 +20050,25 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -20192,7 +20240,7 @@
         <v>14</v>
       </c>
       <c r="L2" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="M2" t="n">
         <v>100</v>
@@ -20287,10 +20335,10 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="L4" t="n">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
       <c r="M4" t="n">
         <v>100</v>
@@ -20336,10 +20384,10 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="L5" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="M5" t="n">
         <v>100</v>
@@ -20385,10 +20433,10 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="L6" t="n">
-        <v>11.2</v>
+        <v>10.6</v>
       </c>
       <c r="M6" t="n">
         <v>100</v>
@@ -20434,10 +20482,10 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="L7" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="M7" t="n">
         <v>100</v>
@@ -20446,12 +20494,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -20460,13 +20508,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1932</v>
+        <v>1948</v>
       </c>
       <c r="E8" t="n">
-        <v>2013</v>
+        <v>2006</v>
       </c>
       <c r="F8" t="n">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -20474,19 +20522,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="L8" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
@@ -20532,10 +20580,10 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="L9" t="n">
-        <v>9.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M9" t="n">
         <v>100</v>
@@ -20544,12 +20592,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -20558,13 +20606,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1948</v>
+        <v>1932</v>
       </c>
       <c r="E10" t="n">
-        <v>1997</v>
+        <v>1994</v>
       </c>
       <c r="F10" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -20572,19 +20620,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="L10" t="n">
-        <v>8.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="M10" t="n">
         <v>100</v>
@@ -20593,27 +20641,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AFC</t>
+          <t>UEFA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1906</v>
+        <v>1914</v>
       </c>
       <c r="E11" t="n">
-        <v>1958</v>
+        <v>1953</v>
       </c>
       <c r="F11" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -20621,17 +20669,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>18</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="I11" t="n">
+        <v>75</v>
+      </c>
       <c r="J11" t="n">
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="L11" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="M11" t="n">
         <v>100</v>
@@ -20640,27 +20690,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UEFA</t>
+          <t>AFC</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1914</v>
+        <v>1906</v>
       </c>
       <c r="E12" t="n">
-        <v>1953</v>
+        <v>1946</v>
       </c>
       <c r="F12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -20668,19 +20718,17 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>29</v>
-      </c>
-      <c r="I12" t="n">
-        <v>75</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="L12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M12" t="n">
         <v>100</v>
@@ -20726,10 +20774,10 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="L13" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
@@ -20738,35 +20786,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>CONMEBOL</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1877</v>
+        <v>1938</v>
       </c>
       <c r="E14" t="n">
-        <v>1912</v>
+        <v>1917</v>
       </c>
       <c r="F14" t="n">
-        <v>35</v>
+        <v>-21</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>blend(metis+fifa)</t>
+          <t>eloratings.net</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
@@ -20776,7 +20824,7 @@
         <v>2.1</v>
       </c>
       <c r="L14" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
@@ -20785,48 +20833,48 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CONMEBOL</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1938</v>
+        <v>1877</v>
       </c>
       <c r="E15" t="n">
-        <v>1898</v>
+        <v>1912</v>
       </c>
       <c r="F15" t="n">
-        <v>-40</v>
+        <v>35</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>eloratings.net</t>
+          <t>blend(metis+fifa)</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="M15" t="n">
-        <v>29.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
@@ -20867,10 +20915,10 @@
         <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="M16" t="n">
         <v>100</v>
@@ -20914,13 +20962,13 @@
         <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="L17" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="M17" t="n">
-        <v>90.3</v>
+        <v>84.7</v>
       </c>
     </row>
     <row r="18">
@@ -20966,117 +21014,115 @@
         <v>1.5</v>
       </c>
       <c r="L18" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="M18" t="n">
-        <v>78.2</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CONCACAF</t>
+          <t>CONMEBOL</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1816</v>
+        <v>1892</v>
       </c>
       <c r="E19" t="n">
-        <v>1887</v>
+        <v>1873</v>
       </c>
       <c r="F19" t="n">
-        <v>70</v>
+        <v>-19</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>blend(metis+fifa)</t>
+          <t>eloratings.net</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>14</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="I19" t="n">
+        <v>77</v>
+      </c>
       <c r="J19" t="n">
         <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="L19" t="n">
-        <v>6.1</v>
+        <v>2.1</v>
       </c>
       <c r="M19" t="n">
-        <v>100</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CONMEBOL</t>
+          <t>UEFA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1892</v>
+        <v>1903</v>
       </c>
       <c r="E20" t="n">
-        <v>1873</v>
+        <v>1867</v>
       </c>
       <c r="F20" t="n">
-        <v>-19</v>
+        <v>-36</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>eloratings.net</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>16</v>
-      </c>
-      <c r="I20" t="n">
-        <v>77</v>
-      </c>
+          <t>blend(metis)</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>41.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -21085,13 +21131,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1820</v>
+        <v>1816</v>
       </c>
       <c r="E21" t="n">
-        <v>1860</v>
+        <v>1867</v>
       </c>
       <c r="F21" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -21099,17 +21145,17 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
         <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="L21" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="M21" t="n">
         <v>100</v>
@@ -21118,27 +21164,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UEFA</t>
+          <t>CONCACAF</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1846</v>
+        <v>1820</v>
       </c>
       <c r="E22" t="n">
-        <v>1853</v>
+        <v>1860</v>
       </c>
       <c r="F22" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -21146,31 +21192,31 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="L22" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="M22" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -21179,43 +21225,45 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1903</v>
+        <v>1846</v>
       </c>
       <c r="E23" t="n">
-        <v>1847</v>
+        <v>1853</v>
       </c>
       <c r="F23" t="n">
-        <v>-56</v>
+        <v>8</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>blend(metis)</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>blend(metis+fifa)</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>24</v>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
         <v>2</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>13.4</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -21224,107 +21272,107 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1860</v>
+        <v>1806</v>
       </c>
       <c r="E24" t="n">
-        <v>1831</v>
+        <v>1837</v>
       </c>
       <c r="F24" t="n">
-        <v>-29</v>
+        <v>31</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>eloratings.net</t>
+          <t>blend(metis+fifa)</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K24" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="L24" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>52.9</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AFC</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1816</v>
+        <v>1860</v>
       </c>
       <c r="E25" t="n">
-        <v>1825</v>
+        <v>1831</v>
       </c>
       <c r="F25" t="n">
-        <v>8</v>
+        <v>-29</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>blend(metis+fifa)</t>
+          <t>eloratings.net</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
         <v>2</v>
       </c>
       <c r="K25" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="L25" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="M25" t="n">
-        <v>90.5</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>AFC</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1795</v>
+        <v>1816</v>
       </c>
       <c r="E26" t="n">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="F26" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -21332,17 +21380,17 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="L26" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="M26" t="n">
         <v>100</v>
@@ -21351,12 +21399,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -21365,13 +21413,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1806</v>
+        <v>1795</v>
       </c>
       <c r="E27" t="n">
-        <v>1821</v>
+        <v>1823</v>
       </c>
       <c r="F27" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -21379,20 +21427,20 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
         <v>2</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="L27" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="M27" t="n">
-        <v>91.59999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -21439,7 +21487,7 @@
         <v>1.9</v>
       </c>
       <c r="M28" t="n">
-        <v>62.8</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="29">
@@ -21483,10 +21531,10 @@
         <v>0.6</v>
       </c>
       <c r="L29" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="M29" t="n">
-        <v>74.8</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="30">
@@ -21512,7 +21560,7 @@
         <v>1805</v>
       </c>
       <c r="F30" t="n">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -21524,16 +21572,16 @@
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="L30" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="M30" t="n">
-        <v>73.2</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -21576,13 +21624,13 @@
         <v>3</v>
       </c>
       <c r="K31" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="L31" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="M31" t="n">
-        <v>92.3</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -21623,13 +21671,13 @@
         <v>3</v>
       </c>
       <c r="K32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L32" t="n">
         <v>0.2</v>
       </c>
-      <c r="L32" t="n">
-        <v>0.5</v>
-      </c>
       <c r="M32" t="n">
-        <v>33.8</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="33">
@@ -21676,7 +21724,7 @@
         <v>0.1</v>
       </c>
       <c r="M33" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="34">
@@ -21717,13 +21765,13 @@
         <v>2</v>
       </c>
       <c r="K34" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="L34" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="M34" t="n">
-        <v>68.90000000000001</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -21746,10 +21794,10 @@
         <v>1703</v>
       </c>
       <c r="E35" t="n">
-        <v>1715</v>
+        <v>1726</v>
       </c>
       <c r="F35" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -21759,7 +21807,7 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K35" t="n">
         <v>0.3</v>
@@ -21768,7 +21816,7 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>89.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36">
@@ -21859,10 +21907,10 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>5.6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="38">
@@ -21953,10 +22001,10 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="40">
@@ -21997,13 +22045,13 @@
         <v>2</v>
       </c>
       <c r="K40" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0.2</v>
       </c>
       <c r="M40" t="n">
-        <v>31.1</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="41">
@@ -22096,10 +22144,10 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="M42" t="n">
-        <v>21.8</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="43">
@@ -22122,10 +22170,10 @@
         <v>1737</v>
       </c>
       <c r="E43" t="n">
-        <v>1624</v>
+        <v>1615</v>
       </c>
       <c r="F43" t="n">
-        <v>-113</v>
+        <v>-122</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -22137,7 +22185,7 @@
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -22185,13 +22233,13 @@
         <v>2</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L44" t="n">
         <v>0.2</v>
       </c>
       <c r="M44" t="n">
-        <v>33</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="45">
@@ -22233,7 +22281,7 @@
         <v>0.1</v>
       </c>
       <c r="L45" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="M45" t="n">
         <v>100</v>
@@ -22328,7 +22376,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="48">
@@ -22351,10 +22399,10 @@
         <v>1595</v>
       </c>
       <c r="E48" t="n">
-        <v>1539</v>
+        <v>1522</v>
       </c>
       <c r="F48" t="n">
-        <v>-56</v>
+        <v>-73</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -22366,7 +22414,7 @@
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -22375,7 +22423,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>20.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -22436,7 +22484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -22537,7 +22585,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mexico 2-0 South Africa</t>
+          <t>Ecuador 2-1 Germany</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -22552,20 +22600,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.6024361314750264</v>
+        <v>0.3655576724890429</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2304550812756662</v>
+        <v>0.2772729806587883</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1671087872493074</v>
+        <v>0.3571693468521687</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09299118816623837</v>
+        <v>0.2650435046341627</v>
       </c>
       <c r="I3" t="b">
         <v>1</v>
@@ -22574,7 +22622,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Morocco 4-2 Haiti</t>
+          <t>Mexico 2-0 South Africa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -22589,20 +22637,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.5271652709677939</v>
+        <v>0.6024361314750264</v>
       </c>
       <c r="F4" t="n">
-        <v>0.253977826748045</v>
+        <v>0.2304550812756662</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2188569022841612</v>
+        <v>0.1671087872493074</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1357355123281893</v>
+        <v>0.09299118816623837</v>
       </c>
       <c r="I4" t="b">
         <v>1</v>
@@ -22611,12 +22659,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>South Africa 1-0 South Korea</t>
+          <t>Morocco 4-2 Haiti</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -22630,25 +22678,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.26113755545355</v>
+        <v>0.5271652709677939</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2663778415879188</v>
+        <v>0.253977826748045</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4724846029585311</v>
+        <v>0.2188569022841612</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3845797059970184</v>
+        <v>0.1357355123281893</v>
       </c>
       <c r="I5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>South Korea 2-1 Czechia</t>
+          <t>Paraguay 0-0 Australia</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -22658,7 +22706,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -22667,53 +22715,53 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.3775464057956682</v>
+        <v>0.3692355958696349</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2770387146066375</v>
+        <v>0.2772300863797774</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3454148795976941</v>
+        <v>0.3535343177505875</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2533799579926903</v>
+        <v>0.1306607195422889</v>
       </c>
       <c r="I6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Canada 1-1 Bosnia and Herzegovina</t>
+          <t>South Africa 1-0 South Korea</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.5935041775822631</v>
+        <v>0.26113755545355</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2336119886651664</v>
+        <v>0.2663778415879188</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1728838337525705</v>
+        <v>0.4724846029585311</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1910680143902925</v>
+        <v>0.3845797059970184</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -22722,7 +22770,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>United States 4-1 Paraguay</t>
+          <t>South Korea 2-1 Czechia</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -22741,16 +22789,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.4107699333529872</v>
+        <v>0.3775464057956682</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2750184355219605</v>
+        <v>0.2770387146066375</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3142116311250522</v>
+        <v>0.3454148795976941</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2229605102875545</v>
+        <v>0.2533799579926903</v>
       </c>
       <c r="I8" t="b">
         <v>1</v>
@@ -22759,7 +22807,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Australia 2-0 Turkey</t>
+          <t>Tunisia 1-3 Netherlands</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -22769,7 +22817,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -22778,25 +22826,25 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.3022966571991881</v>
+        <v>0.2267976629606308</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2736782656597276</v>
+        <v>0.2567282829191442</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4240250771410841</v>
+        <v>0.5164740541202248</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3332936102999648</v>
+        <v>0.1426172601316675</v>
       </c>
       <c r="I9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Brazil 1-1 Morocco</t>
+          <t>Canada 1-1 Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -22811,20 +22859,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.4339441725206395</v>
+        <v>0.5935041775822631</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2724853115528631</v>
+        <v>0.2336119886651664</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2935705159264974</v>
+        <v>0.1728838337525705</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1372455963429862</v>
+        <v>0.1910680143902925</v>
       </c>
       <c r="I10" t="b">
         <v>0</v>
@@ -22833,17 +22881,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Haiti 0-1 Scotland</t>
+          <t>United States 4-1 Paraguay</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -22852,16 +22900,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.2606949315022876</v>
+        <v>0.4107699333529872</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2662752434568346</v>
+        <v>0.2750184355219605</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4730298250408779</v>
+        <v>0.3142116311250522</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1728297063037152</v>
+        <v>0.2229605102875545</v>
       </c>
       <c r="I11" t="b">
         <v>1</v>
@@ -22870,7 +22918,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Qatar 1-1 Switzerland</t>
+          <t>Australia 2-0 Turkey</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -22880,7 +22928,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -22889,16 +22937,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.2021605238111649</v>
+        <v>0.3022966571991881</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2474960581873801</v>
+        <v>0.2736782656597276</v>
       </c>
       <c r="G12" t="n">
-        <v>0.550343418001455</v>
+        <v>0.4240250771410841</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1718733775625644</v>
+        <v>0.3332936102999648</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
@@ -22907,7 +22955,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Germany 7-1 Curaçao</t>
+          <t>Brazil 1-1 Morocco</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -22917,34 +22965,34 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.6099914400822092</v>
+        <v>0.4339441725206395</v>
       </c>
       <c r="F13" t="n">
-        <v>0.227710918612106</v>
+        <v>0.2724853115528631</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1622976413056849</v>
+        <v>0.2935705159264974</v>
       </c>
       <c r="H13" t="n">
-        <v>0.08922360059126888</v>
+        <v>0.1372455963429862</v>
       </c>
       <c r="I13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ivory Coast 1-0 Ecuador</t>
+          <t>Haiti 0-1 Scotland</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -22954,7 +23002,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -22963,30 +23011,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.2738762749141564</v>
+        <v>0.2606949315022876</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2691027275042267</v>
+        <v>0.2662752434568346</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4570209975816171</v>
+        <v>0.4730298250408779</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3680619281815189</v>
+        <v>0.1728297063037152</v>
       </c>
       <c r="I14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Netherlands 2-2 Japan</t>
+          <t>Qatar 1-1 Switzerland</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -23000,16 +23048,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.3911107030923358</v>
+        <v>0.2021605238111649</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2764517043235625</v>
+        <v>0.2474960581873801</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3324375925841019</v>
+        <v>0.550343418001455</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1317411675182472</v>
+        <v>0.1718733775625644</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
@@ -23018,12 +23066,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sweden 5-1 Tunisia</t>
+          <t>Germany 7-1 Curaçao</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -23033,57 +23081,57 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.3379351884295246</v>
+        <v>0.6099914400822092</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2767432920907087</v>
+        <v>0.227710918612106</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3853215194797665</v>
+        <v>0.1622976413056849</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2934012440470226</v>
+        <v>0.08922360059126888</v>
       </c>
       <c r="I16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Belgium 1-1 Egypt</t>
+          <t>Ivory Coast 1-0 Ecuador</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.4323227858568852</v>
+        <v>0.2738762749141564</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2726912470817157</v>
+        <v>0.2691027275042267</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2949859670613991</v>
+        <v>0.4570209975816171</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1369598559671035</v>
+        <v>0.3680619281815189</v>
       </c>
       <c r="I17" t="b">
         <v>0</v>
@@ -23092,7 +23140,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Iran 2-2 New Zealand</t>
+          <t>Netherlands 2-2 Japan</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -23111,16 +23159,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.4832027730434736</v>
+        <v>0.3911107030923358</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2642809230535665</v>
+        <v>0.2764517043235625</v>
       </c>
       <c r="G18" t="n">
-        <v>0.25251630390296</v>
+        <v>0.3324375925841019</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1486247018068573</v>
+        <v>0.1317411675182472</v>
       </c>
       <c r="I18" t="b">
         <v>0</v>
@@ -23129,7 +23177,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Saudi Arabia 1-1 Uruguay</t>
+          <t>Sweden 5-1 Tunisia</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -23139,7 +23187,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -23148,16 +23196,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.2240862560806894</v>
+        <v>0.3379351884295246</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2558123361101832</v>
+        <v>0.2767432920907087</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5201014078091272</v>
+        <v>0.3853215194797665</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1603600622846482</v>
+        <v>0.2934012440470226</v>
       </c>
       <c r="I19" t="b">
         <v>0</v>
@@ -23166,7 +23214,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Spain 0-0 Cape Verde</t>
+          <t>Belgium 1-1 Egypt</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -23181,20 +23229,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.6889149405831398</v>
+        <v>0.4323227858568852</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1951539809620534</v>
+        <v>0.2726912470817157</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1159310784548069</v>
+        <v>0.2949859670613991</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2440219051551828</v>
+        <v>0.1369598559671035</v>
       </c>
       <c r="I20" t="b">
         <v>0</v>
@@ -23203,7 +23251,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Argentina 3-0 Algeria</t>
+          <t>Iran 2-2 New Zealand</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -23213,7 +23261,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -23222,35 +23270,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.5653447610298761</v>
+        <v>0.4832027730434736</v>
       </c>
       <c r="F21" t="n">
-        <v>0.242932655319136</v>
+        <v>0.2642809230535665</v>
       </c>
       <c r="G21" t="n">
-        <v>0.191722583650988</v>
+        <v>0.25251630390296</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1128413629229928</v>
+        <v>0.1486247018068573</v>
       </c>
       <c r="I21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Austria 3-1 Jordan</t>
+          <t>Saudi Arabia 1-1 Uruguay</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -23259,25 +23307,25 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.4465822656526882</v>
+        <v>0.2240862560806894</v>
       </c>
       <c r="F22" t="n">
-        <v>0.270736216737822</v>
+        <v>0.2558123361101832</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2826815176094898</v>
+        <v>0.5201014078091272</v>
       </c>
       <c r="H22" t="n">
-        <v>0.193090014544058</v>
+        <v>0.1603600622846482</v>
       </c>
       <c r="I22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>France 3-1 Senegal</t>
+          <t>Spain 0-0 Cape Verde</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -23287,62 +23335,62 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.5101967760009811</v>
+        <v>0.6889149405831398</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2582711067810726</v>
+        <v>0.1951539809620534</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2315321172179463</v>
+        <v>0.1159310784548069</v>
       </c>
       <c r="H23" t="n">
-        <v>0.146757159771629</v>
+        <v>0.2440219051551828</v>
       </c>
       <c r="I23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Iraq 1-4 Norway</t>
+          <t>Argentina 3-0 Algeria</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.1771341674124645</v>
+        <v>0.5653447610298761</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2358428959472877</v>
+        <v>0.242932655319136</v>
       </c>
       <c r="G24" t="n">
-        <v>0.587022936640248</v>
+        <v>0.191722583650988</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1009632840630759</v>
+        <v>0.1128413629229928</v>
       </c>
       <c r="I24" t="b">
         <v>1</v>
@@ -23351,7 +23399,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>England 4-2 Croatia</t>
+          <t>Austria 3-1 Jordan</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -23370,16 +23418,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.4421686007896301</v>
+        <v>0.4465822656526882</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2713758294277268</v>
+        <v>0.270736216737822</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2864555697826432</v>
+        <v>0.2826815176094898</v>
       </c>
       <c r="H25" t="n">
-        <v>0.196616331702249</v>
+        <v>0.193090014544058</v>
       </c>
       <c r="I25" t="b">
         <v>1</v>
@@ -23388,12 +23436,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ghana 1-0 Panama</t>
+          <t>France 3-1 Senegal</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -23407,72 +23455,72 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.269445732840606</v>
+        <v>0.5101967760009811</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2682043756018556</v>
+        <v>0.2582711067810726</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4623498915575382</v>
+        <v>0.2315321172179463</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3737384797440333</v>
+        <v>0.146757159771629</v>
       </c>
       <c r="I26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Portugal 1-1 DR Congo</t>
+          <t>Iraq 1-4 Norway</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.6563191675226661</v>
+        <v>0.1771341674124645</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2094436649180234</v>
+        <v>0.2358428959472877</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1342371675593106</v>
+        <v>0.587022936640248</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2243872334059959</v>
+        <v>0.1009632840630759</v>
       </c>
       <c r="I27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Uzbekistan 1-3 Colombia</t>
+          <t>England 4-2 Croatia</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -23481,16 +23529,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.2202298877346608</v>
+        <v>0.4421686007896301</v>
       </c>
       <c r="F28" t="n">
-        <v>0.254468243557875</v>
+        <v>0.2713758294277268</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5253018687074642</v>
+        <v>0.2864555697826432</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1369197596521234</v>
+        <v>0.196616331702249</v>
       </c>
       <c r="I28" t="b">
         <v>1</v>
@@ -23499,44 +23547,44 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Canada 6-0 Qatar</t>
+          <t>Ghana 1-0 Panama</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.5764064554833523</v>
+        <v>0.269445732840606</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2393871531850218</v>
+        <v>0.2682043756018556</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1842063913316258</v>
+        <v>0.4623498915575382</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1066817427817986</v>
+        <v>0.3737384797440333</v>
       </c>
       <c r="I29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Czechia 1-1 South Africa</t>
+          <t>Portugal 1-1 DR Congo</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -23551,20 +23599,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.4553404858663942</v>
+        <v>0.6563191675226661</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2693770505519105</v>
+        <v>0.2094436649180234</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2752824635816952</v>
+        <v>0.1342371675593106</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1415576964123257</v>
+        <v>0.2243872334059959</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
@@ -23573,17 +23621,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mexico 1-0 South Korea</t>
+          <t>Uzbekistan 1-3 Colombia</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -23592,16 +23640,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.4881235585818711</v>
+        <v>0.2202298877346608</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2632623226473407</v>
+        <v>0.254468243557875</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2486141187707883</v>
+        <v>0.5253018687074642</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1619132356655314</v>
+        <v>0.1369197596521234</v>
       </c>
       <c r="I31" t="b">
         <v>1</v>
@@ -23610,7 +23658,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Switzerland 4-1 Bosnia and Herzegovina</t>
+          <t>Canada 6-0 Qatar</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -23629,16 +23677,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.5675807326327216</v>
+        <v>0.5764064554833523</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2422282277870113</v>
+        <v>0.2393871531850218</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1901910395802674</v>
+        <v>0.1842063913316258</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1115795271635383</v>
+        <v>0.1066817427817986</v>
       </c>
       <c r="I32" t="b">
         <v>1</v>
@@ -23647,7 +23695,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Brazil 3-0 Haiti</t>
+          <t>Czechia 1-1 South Africa</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -23657,44 +23705,44 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.6024710043427424</v>
+        <v>0.4553404858663942</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2304425698918271</v>
+        <v>0.2693770505519105</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1670864257654306</v>
+        <v>0.2752824635816952</v>
       </c>
       <c r="H33" t="n">
-        <v>0.09297358803166735</v>
+        <v>0.1415576964123257</v>
       </c>
       <c r="I33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Scotland 0-1 Morocco</t>
+          <t>Mexico 1-0 South Korea</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -23703,16 +23751,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.3123152964921898</v>
+        <v>0.4881235585818711</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2748269579337349</v>
+        <v>0.2632623226473407</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4128577455740753</v>
+        <v>0.2486141187707883</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2211384356776808</v>
+        <v>0.1619132356655314</v>
       </c>
       <c r="I34" t="b">
         <v>1</v>
@@ -23721,7 +23769,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Turkey 0-1 Paraguay</t>
+          <t>Switzerland 4-1 Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -23731,34 +23779,34 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.4158113794624096</v>
+        <v>0.5675807326327216</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2745434638141608</v>
+        <v>0.2422282277870113</v>
       </c>
       <c r="G35" t="n">
-        <v>0.3096451567234295</v>
+        <v>0.1901910395802674</v>
       </c>
       <c r="H35" t="n">
-        <v>0.324744456462925</v>
+        <v>0.1115795271635383</v>
       </c>
       <c r="I35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>United States 2-0 Australia</t>
+          <t>Brazil 3-0 Haiti</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -23773,20 +23821,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.4189589466211568</v>
+        <v>0.6024710043427424</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2742252024300777</v>
+        <v>0.2304425698918271</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3068158509487656</v>
+        <v>0.1670864257654306</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2158723360525054</v>
+        <v>0.09297358803166735</v>
       </c>
       <c r="I36" t="b">
         <v>1</v>
@@ -23795,44 +23843,44 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ecuador 0-0 Curaçao</t>
+          <t>Scotland 0-1 Morocco</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.614390105780561</v>
+        <v>0.3123152964921898</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2260824080030716</v>
+        <v>0.2748269579337349</v>
       </c>
       <c r="G37" t="n">
-        <v>0.1595274862163676</v>
+        <v>0.4128577455740753</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2014621104697811</v>
+        <v>0.2211384356776808</v>
       </c>
       <c r="I37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Germany 2-1 Ivory Coast</t>
+          <t>Turkey 0-1 Paraguay</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -23842,7 +23890,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -23851,25 +23899,25 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.4525599494983835</v>
+        <v>0.4158113794624096</v>
       </c>
       <c r="F38" t="n">
-        <v>0.2698214154164175</v>
+        <v>0.2745434638141608</v>
       </c>
       <c r="G38" t="n">
-        <v>0.277618635085199</v>
+        <v>0.3096451567234295</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1883813577198906</v>
+        <v>0.324744456462925</v>
       </c>
       <c r="I38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Netherlands 5-1 Sweden</t>
+          <t>United States 2-0 Australia</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -23888,16 +23936,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.5419741522498547</v>
+        <v>0.4189589466211568</v>
       </c>
       <c r="F39" t="n">
-        <v>0.249917248195977</v>
+        <v>0.2742252024300777</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2081085995541683</v>
+        <v>0.3068158509487656</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1265484332078183</v>
+        <v>0.2158723360525054</v>
       </c>
       <c r="I39" t="b">
         <v>1</v>
@@ -23906,44 +23954,44 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Tunisia 0-4 Japan</t>
+          <t>Ecuador 0-0 Curaçao</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.2511552631390055</v>
+        <v>0.614390105780561</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2639306340880528</v>
+        <v>0.2260824080030716</v>
       </c>
       <c r="G40" t="n">
-        <v>0.4849141027729418</v>
+        <v>0.1595274862163676</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1641962238623133</v>
+        <v>0.2014621104697811</v>
       </c>
       <c r="I40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Belgium 0-0 Iran</t>
+          <t>Germany 2-1 Ivory Coast</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -23953,7 +24001,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -23962,35 +24010,35 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.4110593987622102</v>
+        <v>0.4525599494983835</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2749923306348419</v>
+        <v>0.2698214154164175</v>
       </c>
       <c r="G41" t="n">
-        <v>0.3139482706029479</v>
+        <v>0.277618635085199</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1337666729626658</v>
+        <v>0.1883813577198906</v>
       </c>
       <c r="I41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>New Zealand 1-3 Egypt</t>
+          <t>Netherlands 5-1 Sweden</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -23999,16 +24047,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.2701606709292552</v>
+        <v>0.5419741522498547</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2683528583888833</v>
+        <v>0.249917248195977</v>
       </c>
       <c r="G42" t="n">
-        <v>0.4614864706818617</v>
+        <v>0.2081085995541683</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1814918046878114</v>
+        <v>0.1265484332078183</v>
       </c>
       <c r="I42" t="b">
         <v>1</v>
@@ -24017,35 +24065,35 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Spain 4-0 Saudi Arabia</t>
+          <t>Tunisia 0-4 Japan</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.711801189694372</v>
+        <v>0.2511552631390055</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1844344879110749</v>
+        <v>0.2639306340880528</v>
       </c>
       <c r="G43" t="n">
-        <v>0.103764322394553</v>
+        <v>0.4849141027729418</v>
       </c>
       <c r="H43" t="n">
-        <v>0.04691279443179004</v>
+        <v>0.1641962238623133</v>
       </c>
       <c r="I43" t="b">
         <v>1</v>
@@ -24054,7 +24102,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Uruguay 2-2 Cape Verde</t>
+          <t>Belgium 0-0 Iran</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -24073,16 +24121,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.4946917415780235</v>
+        <v>0.4110593987622102</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2618487176721053</v>
+        <v>0.2749923306348419</v>
       </c>
       <c r="G44" t="n">
-        <v>0.243459540749871</v>
+        <v>0.3139482706029479</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1519962335838181</v>
+        <v>0.1337666729626658</v>
       </c>
       <c r="I44" t="b">
         <v>0</v>
@@ -24091,17 +24139,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Argentina 2-0 Austria</t>
+          <t>New Zealand 1-3 Egypt</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -24110,16 +24158,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.5600237883076568</v>
+        <v>0.2701606709292552</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2445838247676272</v>
+        <v>0.2683528583888833</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1953923869247162</v>
+        <v>0.4614864706818617</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1158786258616418</v>
+        <v>0.1814918046878114</v>
       </c>
       <c r="I45" t="b">
         <v>1</v>
@@ -24128,7 +24176,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>France 3-0 Iraq</t>
+          <t>Spain 4-0 Saudi Arabia</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -24147,16 +24195,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.6938172051627756</v>
+        <v>0.711801189694372</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1929050139558987</v>
+        <v>0.1844344879110749</v>
       </c>
       <c r="G46" t="n">
-        <v>0.1132777808813258</v>
+        <v>0.103764322394553</v>
       </c>
       <c r="H46" t="n">
-        <v>0.05328987974786575</v>
+        <v>0.04691279443179004</v>
       </c>
       <c r="I46" t="b">
         <v>1</v>
@@ -24165,17 +24213,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Jordan 1-2 Algeria</t>
+          <t>Uruguay 2-2 Cape Verde</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -24184,25 +24232,25 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.2871872150453605</v>
+        <v>0.4946917415780235</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2714956942424305</v>
+        <v>0.2618487176721053</v>
       </c>
       <c r="G47" t="n">
-        <v>0.4413170907122089</v>
+        <v>0.243459540749871</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1973015448078901</v>
+        <v>0.1519962335838181</v>
       </c>
       <c r="I47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Norway 3-2 Senegal</t>
+          <t>Argentina 2-0 Austria</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -24221,16 +24269,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.399746405577862</v>
+        <v>0.5600237883076568</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2759053625170023</v>
+        <v>0.2445838247676272</v>
       </c>
       <c r="G48" t="n">
-        <v>0.3243482319051358</v>
+        <v>0.1953923869247162</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2327530765783421</v>
+        <v>0.1158786258616418</v>
       </c>
       <c r="I48" t="b">
         <v>1</v>
@@ -24239,7 +24287,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Colombia 1-0 DR Congo</t>
+          <t>France 3-0 Iraq</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -24258,16 +24306,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.6513377464031052</v>
+        <v>0.6938172051627756</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2115244400993148</v>
+        <v>0.1929050139558987</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1371378134975802</v>
+        <v>0.1132777808813258</v>
       </c>
       <c r="H49" t="n">
-        <v>0.07018607348708122</v>
+        <v>0.05328987974786575</v>
       </c>
       <c r="I49" t="b">
         <v>1</v>
@@ -24276,54 +24324,54 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>England 0-0 Ghana</t>
+          <t>Jordan 1-2 Algeria</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.6391364229920049</v>
+        <v>0.2871872150453605</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2165036639184777</v>
+        <v>0.2714956942424305</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1443599130895173</v>
+        <v>0.4413170907122089</v>
       </c>
       <c r="H50" t="n">
-        <v>0.214667575851114</v>
+        <v>0.1973015448078901</v>
       </c>
       <c r="I50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Panama 0-1 Croatia</t>
+          <t>Norway 3-2 Senegal</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -24332,16 +24380,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.2779192196934168</v>
+        <v>0.399746405577862</v>
       </c>
       <c r="F51" t="n">
-        <v>0.2698775634692422</v>
+        <v>0.2759053625170023</v>
       </c>
       <c r="G51" t="n">
-        <v>0.452203216837341</v>
+        <v>0.3243482319051358</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1886602041591775</v>
+        <v>0.2327530765783421</v>
       </c>
       <c r="I51" t="b">
         <v>1</v>
@@ -24350,7 +24398,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Portugal 5-0 Uzbekistan</t>
+          <t>Colombia 1-0 DR Congo</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -24365,20 +24413,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.5305667905006943</v>
+        <v>0.6513377464031052</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2530706921820465</v>
+        <v>0.2115244400993148</v>
       </c>
       <c r="G52" t="n">
-        <v>0.216362517317259</v>
+        <v>0.1371378134975802</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1335901385403401</v>
+        <v>0.07018607348708122</v>
       </c>
       <c r="I52" t="b">
         <v>1</v>
@@ -24387,44 +24435,44 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Czechia 0-3 Mexico</t>
+          <t>England 0-0 Ghana</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.2351921354348235</v>
+        <v>0.6391364229920049</v>
       </c>
       <c r="F53" t="n">
-        <v>0.2594153894470163</v>
+        <v>0.2165036639184777</v>
       </c>
       <c r="G53" t="n">
-        <v>0.5053924751181602</v>
+        <v>0.1443599130895173</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1499759721200661</v>
+        <v>0.214667575851114</v>
       </c>
       <c r="I53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Scotland 0-3 Brazil</t>
+          <t>Panama 0-1 Croatia</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -24443,16 +24491,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.24901815042318</v>
+        <v>0.2779192196934168</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2633698330694462</v>
+        <v>0.2698775634692422</v>
       </c>
       <c r="G54" t="n">
-        <v>0.4876120165073738</v>
+        <v>0.452203216837341</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1622757424339106</v>
+        <v>0.1886602041591775</v>
       </c>
       <c r="I54" t="b">
         <v>1</v>
@@ -24461,38 +24509,260 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>Portugal 5-0 Uzbekistan</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0.5305667905006943</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.2530706921820465</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.216362517317259</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.1335901385403401</v>
+      </c>
+      <c r="I55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Czechia 0-3 Mexico</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0.2351921354348235</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.2594153894470163</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.5053924751181602</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.1499759721200661</v>
+      </c>
+      <c r="I56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Scotland 0-3 Brazil</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0.24901815042318</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.2633698330694462</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.4876120165073738</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.1622757424339106</v>
+      </c>
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>Switzerland 2-1 Canada</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="E55" t="n">
+      <c r="E58" t="n">
         <v>0.3372955421668554</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F58" t="n">
         <v>0.2767126361678793</v>
       </c>
-      <c r="G55" t="n">
+      <c r="G58" t="n">
         <v>0.3859918216652653</v>
       </c>
-      <c r="H55" t="n">
+      <c r="H58" t="n">
         <v>0.294083442412196</v>
       </c>
-      <c r="I55" t="b">
+      <c r="I58" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Curaçao 0-2 Ivory Coast</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0.2272040348991984</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.2568635144989577</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.515932450601844</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.1429715329274063</v>
+      </c>
+      <c r="I59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Japan 1-1 Sweden</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0.5103893669153626</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.2582245731851142</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.2313860598995233</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.1570184072880452</v>
+      </c>
+      <c r="I60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Turkey 3-2 United States</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0.366204275259826</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.2772673175853767</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.3565284071547971</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.2644047629036296</v>
+      </c>
+      <c r="I61" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/world_cup_2026_recommendations.xlsx
+++ b/outputs/world_cup_2026_recommendations.xlsx
@@ -549,7 +549,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>• Matches scored: 80   Outcome hit-rate: 62%   Mean RPS: 0.178  (good tournament forecasts ~0.17-0.18)</t>
+          <t>• Matches scored: 81   Outcome hit-rate: 63%   Mean RPS: 0.177  (good tournament forecasts ~0.17-0.18)</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>• Argentina 15%,  Spain 14%,  France 12%</t>
+          <t>• Argentina 15%,  Spain 15%,  France 13%</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1051,7 @@
         <v>26.3</v>
       </c>
       <c r="L5" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="M5" t="n">
         <v>1.52</v>
@@ -1774,19 +1774,19 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>47.4</v>
+        <v>47.2</v>
       </c>
       <c r="K14" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="L14" t="n">
-        <v>26.9</v>
+        <v>27.2</v>
       </c>
       <c r="M14" t="n">
         <v>1.61</v>
       </c>
       <c r="N14" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>51.9</v>
       </c>
       <c r="M16" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N16" t="n">
         <v>1.59</v>
@@ -2017,16 +2017,16 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>66.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="K17" t="n">
-        <v>21.9</v>
+        <v>21.6</v>
       </c>
       <c r="L17" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="M17" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="N17" t="n">
         <v>0.65</v>
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="K32" t="n">
         <v>26.6</v>
@@ -3718,19 +3718,19 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>46.9</v>
+        <v>46.6</v>
       </c>
       <c r="K38" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="L38" t="n">
-        <v>26.4</v>
+        <v>26.7</v>
       </c>
       <c r="M38" t="n">
         <v>1.51</v>
       </c>
       <c r="N38" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -3880,16 +3880,16 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>72.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="K40" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="L40" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="N40" t="n">
         <v>0.61</v>
@@ -5743,16 +5743,16 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="K63" t="n">
         <v>19.6</v>
       </c>
       <c r="L63" t="n">
-        <v>66</v>
+        <v>65.8</v>
       </c>
       <c r="M63" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="N63" t="n">
         <v>2.23</v>
@@ -5905,19 +5905,19 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="K65" t="n">
-        <v>24.9</v>
+        <v>24.6</v>
       </c>
       <c r="L65" t="n">
-        <v>58</v>
+        <v>58.4</v>
       </c>
       <c r="M65" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N65" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -7305,19 +7305,19 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>48.4</v>
+        <v>48.1</v>
       </c>
       <c r="K83" t="n">
         <v>25.1</v>
       </c>
       <c r="L83" t="n">
-        <v>26.5</v>
+        <v>26.8</v>
       </c>
       <c r="M83" t="n">
         <v>1.67</v>
       </c>
       <c r="N83" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -7455,16 +7455,16 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>60.8</v>
+        <v>61.3</v>
       </c>
       <c r="K85" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="L85" t="n">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="M85" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="N85" t="n">
         <v>0.85</v>
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>12.2</v>
       </c>
       <c r="M87" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="N87" t="n">
         <v>0.75</v>
@@ -7856,11 +7856,11 @@
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="n">
-        <v>54.4</v>
+        <v>55</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>most-likely pairing (54%); France to advance</t>
+          <t>most-likely pairing (55%); France to advance</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="n">
-        <v>35.9</v>
+        <v>36.2</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -8006,11 +8006,11 @@
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="n">
-        <v>32.4</v>
+        <v>32.7</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>most-likely pairing (32%); Brazil to advance</t>
+          <t>most-likely pairing (33%); Brazil to advance</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="n">
-        <v>41.5</v>
+        <v>41.2</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -8130,19 +8130,19 @@
         </is>
       </c>
       <c r="J94" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="K94" t="n">
-        <v>28.6</v>
+        <v>28.4</v>
       </c>
       <c r="L94" t="n">
-        <v>46.5</v>
+        <v>46.9</v>
       </c>
       <c r="M94" t="n">
         <v>0.93</v>
       </c>
       <c r="N94" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="n">
-        <v>45</v>
+        <v>45.5</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -8205,16 +8205,16 @@
         </is>
       </c>
       <c r="J95" t="n">
-        <v>27.3</v>
+        <v>27.6</v>
       </c>
       <c r="K95" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="L95" t="n">
-        <v>48.3</v>
+        <v>48</v>
       </c>
       <c r="M95" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="N95" t="n">
         <v>1.74</v>
@@ -8231,7 +8231,7 @@
       </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="n">
-        <v>43.1</v>
+        <v>42.5</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
       </c>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="n">
-        <v>37.2</v>
+        <v>36.8</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
       </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="n">
-        <v>20</v>
+        <v>20.3</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -8505,16 +8505,16 @@
         </is>
       </c>
       <c r="J99" t="n">
-        <v>51.7</v>
+        <v>52.6</v>
       </c>
       <c r="K99" t="n">
-        <v>26.3</v>
+        <v>25.9</v>
       </c>
       <c r="L99" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="M99" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="N99" t="n">
         <v>0.9399999999999999</v>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
       </c>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="n">
-        <v>25.7</v>
+        <v>25.5</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -8730,19 +8730,19 @@
         </is>
       </c>
       <c r="J102" t="n">
-        <v>33.2</v>
+        <v>33</v>
       </c>
       <c r="K102" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="L102" t="n">
-        <v>37.8</v>
+        <v>38.2</v>
       </c>
       <c r="M102" t="n">
         <v>1.14</v>
       </c>
       <c r="N102" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="n">
-        <v>12.7</v>
+        <v>13.2</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -8831,11 +8831,11 @@
       </c>
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="n">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>most-likely pairing (11%); Argentina to advance</t>
+          <t>most-likely pairing (12%); Argentina to advance</t>
         </is>
       </c>
     </row>
@@ -8858,7 +8858,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -8868,11 +8868,11 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -8880,23 +8880,23 @@
         </is>
       </c>
       <c r="J104" t="n">
-        <v>37.4</v>
+        <v>35.7</v>
       </c>
       <c r="K104" t="n">
-        <v>28.4</v>
+        <v>27.1</v>
       </c>
       <c r="L104" t="n">
-        <v>34.2</v>
+        <v>37.2</v>
       </c>
       <c r="M104" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="N104" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>most-likely pairing (2%); Spain to advance</t>
+          <t>most-likely pairing (2%); Argentina to advance</t>
         </is>
       </c>
     </row>
@@ -8955,16 +8955,16 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>37.4</v>
+        <v>37.8</v>
       </c>
       <c r="K105" t="n">
-        <v>28.4</v>
+        <v>28.3</v>
       </c>
       <c r="L105" t="n">
-        <v>34.2</v>
+        <v>33.9</v>
       </c>
       <c r="M105" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="N105" t="n">
         <v>1.19</v>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>26.3</v>
       </c>
       <c r="L5" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="M5" t="n">
         <v>1.52</v>
@@ -10138,19 +10138,19 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>47.4</v>
+        <v>47.2</v>
       </c>
       <c r="K14" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="L14" t="n">
-        <v>26.9</v>
+        <v>27.2</v>
       </c>
       <c r="M14" t="n">
         <v>1.61</v>
       </c>
       <c r="N14" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>51.9</v>
       </c>
       <c r="M16" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N16" t="n">
         <v>1.59</v>
@@ -10381,16 +10381,16 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>66.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="K17" t="n">
-        <v>21.9</v>
+        <v>21.6</v>
       </c>
       <c r="L17" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="M17" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="N17" t="n">
         <v>0.65</v>
@@ -11596,7 +11596,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="K32" t="n">
         <v>26.6</v>
@@ -12082,19 +12082,19 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>46.9</v>
+        <v>46.6</v>
       </c>
       <c r="K38" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="L38" t="n">
-        <v>26.4</v>
+        <v>26.7</v>
       </c>
       <c r="M38" t="n">
         <v>1.51</v>
       </c>
       <c r="N38" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -12244,16 +12244,16 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>72.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="K40" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="L40" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="N40" t="n">
         <v>0.61</v>
@@ -14107,16 +14107,16 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="K63" t="n">
         <v>19.6</v>
       </c>
       <c r="L63" t="n">
-        <v>66</v>
+        <v>65.8</v>
       </c>
       <c r="M63" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="N63" t="n">
         <v>2.23</v>
@@ -14269,19 +14269,19 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="K65" t="n">
-        <v>24.9</v>
+        <v>24.6</v>
       </c>
       <c r="L65" t="n">
-        <v>58</v>
+        <v>58.4</v>
       </c>
       <c r="M65" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N65" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -15801,19 +15801,19 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>48.4</v>
+        <v>48.1</v>
       </c>
       <c r="K11" t="n">
         <v>25.1</v>
       </c>
       <c r="L11" t="n">
-        <v>26.5</v>
+        <v>26.8</v>
       </c>
       <c r="M11" t="n">
         <v>1.67</v>
       </c>
       <c r="N11" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -15951,16 +15951,16 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>60.8</v>
+        <v>61.3</v>
       </c>
       <c r="K13" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="L13" t="n">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="M13" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="N13" t="n">
         <v>0.85</v>
@@ -16093,7 +16093,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>12.2</v>
       </c>
       <c r="M15" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="N15" t="n">
         <v>0.75</v>
@@ -16352,11 +16352,11 @@
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
-        <v>54.4</v>
+        <v>55</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>most-likely pairing (54%); France to advance</t>
+          <t>most-likely pairing (55%); France to advance</t>
         </is>
       </c>
     </row>
@@ -16427,7 +16427,7 @@
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
-        <v>35.9</v>
+        <v>36.2</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -16502,11 +16502,11 @@
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
-        <v>32.4</v>
+        <v>32.7</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>most-likely pairing (32%); Brazil to advance</t>
+          <t>most-likely pairing (33%); Brazil to advance</t>
         </is>
       </c>
     </row>
@@ -16577,7 +16577,7 @@
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
-        <v>41.5</v>
+        <v>41.2</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -16626,19 +16626,19 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="K22" t="n">
-        <v>28.6</v>
+        <v>28.4</v>
       </c>
       <c r="L22" t="n">
-        <v>46.5</v>
+        <v>46.9</v>
       </c>
       <c r="M22" t="n">
         <v>0.93</v>
       </c>
       <c r="N22" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>45</v>
+        <v>45.5</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -16701,16 +16701,16 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>27.3</v>
+        <v>27.6</v>
       </c>
       <c r="K23" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="L23" t="n">
-        <v>48.3</v>
+        <v>48</v>
       </c>
       <c r="M23" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="N23" t="n">
         <v>1.74</v>
@@ -16727,7 +16727,7 @@
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>43.1</v>
+        <v>42.5</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="n">
-        <v>37.2</v>
+        <v>36.8</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="n">
-        <v>20</v>
+        <v>20.3</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -17001,16 +17001,16 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>51.7</v>
+        <v>52.6</v>
       </c>
       <c r="K27" t="n">
-        <v>26.3</v>
+        <v>25.9</v>
       </c>
       <c r="L27" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="M27" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="N27" t="n">
         <v>0.9399999999999999</v>
@@ -17027,7 +17027,7 @@
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="n">
-        <v>25.7</v>
+        <v>25.5</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -17226,19 +17226,19 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>33.2</v>
+        <v>33</v>
       </c>
       <c r="K30" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="L30" t="n">
-        <v>37.8</v>
+        <v>38.2</v>
       </c>
       <c r="M30" t="n">
         <v>1.14</v>
       </c>
       <c r="N30" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="n">
-        <v>12.7</v>
+        <v>13.2</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -17327,11 +17327,11 @@
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="n">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>most-likely pairing (11%); Argentina to advance</t>
+          <t>most-likely pairing (12%); Argentina to advance</t>
         </is>
       </c>
     </row>
@@ -17354,7 +17354,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -17364,11 +17364,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -17376,23 +17376,23 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>37.4</v>
+        <v>35.7</v>
       </c>
       <c r="K32" t="n">
-        <v>28.4</v>
+        <v>27.1</v>
       </c>
       <c r="L32" t="n">
-        <v>34.2</v>
+        <v>37.2</v>
       </c>
       <c r="M32" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="N32" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -17406,7 +17406,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>most-likely pairing (2%); Spain to advance</t>
+          <t>most-likely pairing (2%); Argentina to advance</t>
         </is>
       </c>
     </row>
@@ -17451,16 +17451,16 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>37.4</v>
+        <v>37.8</v>
       </c>
       <c r="K33" t="n">
-        <v>28.4</v>
+        <v>28.3</v>
       </c>
       <c r="L33" t="n">
-        <v>34.2</v>
+        <v>33.9</v>
       </c>
       <c r="M33" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="N33" t="n">
         <v>1.19</v>
@@ -17477,7 +17477,7 @@
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -18916,16 +18916,16 @@
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>60.6</v>
+        <v>60.5</v>
       </c>
       <c r="E2" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="F2" t="n">
-        <v>26.5</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>15.5</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="3">
@@ -18943,16 +18943,16 @@
         <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>49.6</v>
+        <v>50.2</v>
       </c>
       <c r="E3" t="n">
-        <v>36.5</v>
+        <v>37.1</v>
       </c>
       <c r="F3" t="n">
-        <v>22.9</v>
+        <v>23.4</v>
       </c>
       <c r="G3" t="n">
-        <v>14.2</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="4">
@@ -18970,16 +18970,16 @@
         <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>51.6</v>
+        <v>52</v>
       </c>
       <c r="E4" t="n">
-        <v>34.9</v>
+        <v>35.5</v>
       </c>
       <c r="F4" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="G4" t="n">
-        <v>12.4</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="5">
@@ -18997,13 +18997,13 @@
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>47.8</v>
+        <v>48.4</v>
       </c>
       <c r="E5" t="n">
-        <v>27.6</v>
+        <v>28.1</v>
       </c>
       <c r="F5" t="n">
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
         <v>7.5</v>
@@ -19024,16 +19024,16 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>42.5</v>
+        <v>42.2</v>
       </c>
       <c r="E6" t="n">
-        <v>20.5</v>
+        <v>20.1</v>
       </c>
       <c r="F6" t="n">
-        <v>10.6</v>
+        <v>10.3</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="7">
@@ -19060,61 +19060,61 @@
         <v>9.1</v>
       </c>
       <c r="G7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>26.1</v>
+        <v>33.4</v>
       </c>
       <c r="E8" t="n">
-        <v>16.5</v>
+        <v>17.8</v>
       </c>
       <c r="F8" t="n">
-        <v>8.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>33.4</v>
+        <v>26</v>
       </c>
       <c r="E9" t="n">
-        <v>17.8</v>
+        <v>16.3</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="G9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="10">
@@ -19132,16 +19132,16 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>31.2</v>
+        <v>30.9</v>
       </c>
       <c r="E10" t="n">
-        <v>17.9</v>
+        <v>17.7</v>
       </c>
       <c r="F10" t="n">
         <v>8.5</v>
       </c>
       <c r="G10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="11">
@@ -19159,43 +19159,43 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>41.4</v>
+        <v>41</v>
       </c>
       <c r="E11" t="n">
-        <v>17.1</v>
+        <v>16.6</v>
       </c>
       <c r="F11" t="n">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="G11" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>24.1</v>
+        <v>27.9</v>
       </c>
       <c r="E12" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="F12" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="13">
@@ -19213,43 +19213,43 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="E13" t="n">
-        <v>12.7</v>
+        <v>12.4</v>
       </c>
       <c r="F13" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>27.8</v>
+        <v>23.9</v>
       </c>
       <c r="E14" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="F14" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="15">
@@ -19267,13 +19267,13 @@
         <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="E15" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="G15" t="n">
         <v>2.1</v>
@@ -19294,64 +19294,64 @@
         <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>22.4</v>
+        <v>22</v>
       </c>
       <c r="E16" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="F16" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>24.9</v>
+        <v>23.9</v>
       </c>
       <c r="E17" t="n">
-        <v>10.1</v>
+        <v>9.6</v>
       </c>
       <c r="F17" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>100</v>
       </c>
       <c r="D18" t="n">
-        <v>23.6</v>
+        <v>24.7</v>
       </c>
       <c r="E18" t="n">
-        <v>9.300000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="F18" t="n">
         <v>4.3</v>
@@ -19375,16 +19375,16 @@
         <v>100</v>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="E19" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="F19" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="20">
@@ -19408,10 +19408,10 @@
         <v>9.1</v>
       </c>
       <c r="F20" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="21">
@@ -19429,10 +19429,10 @@
         <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>23.4</v>
+        <v>23.9</v>
       </c>
       <c r="E21" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="F21" t="n">
         <v>2.8</v>
@@ -19444,52 +19444,52 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>100</v>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="E22" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="F22" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>100</v>
       </c>
       <c r="D23" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="E23" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="F23" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G23" t="n">
         <v>0.9</v>
@@ -19498,22 +19498,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>100</v>
       </c>
       <c r="D24" t="n">
-        <v>15.4</v>
+        <v>16.1</v>
       </c>
       <c r="E24" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="F24" t="n">
         <v>2.5</v>
@@ -19525,25 +19525,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>100</v>
       </c>
       <c r="D25" t="n">
-        <v>15.4</v>
+        <v>21.2</v>
       </c>
       <c r="E25" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="F25" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G25" t="n">
         <v>0.9</v>
@@ -19564,13 +19564,13 @@
         <v>100</v>
       </c>
       <c r="D26" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
         <v>5.1</v>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="G26" t="n">
         <v>0.8</v>
@@ -19591,40 +19591,40 @@
         <v>100</v>
       </c>
       <c r="D27" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="F27" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>100</v>
       </c>
       <c r="D28" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="E28" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
         <v>0.3</v>
@@ -19633,25 +19633,25 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>100</v>
       </c>
       <c r="D29" t="n">
-        <v>8.6</v>
+        <v>7.1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G29" t="n">
         <v>0.3</v>
@@ -19672,7 +19672,7 @@
         <v>100</v>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E30" t="n">
         <v>2.5</v>
@@ -19699,13 +19699,13 @@
         <v>100</v>
       </c>
       <c r="D31" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="E31" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G31" t="n">
         <v>0.1</v>
@@ -19726,10 +19726,10 @@
         <v>100</v>
       </c>
       <c r="D32" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="E32" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="F32" t="n">
         <v>0.4</v>
@@ -19753,13 +19753,13 @@
         <v>100</v>
       </c>
       <c r="D33" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="E33" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G33" t="n">
         <v>0.1</v>
@@ -19768,12 +19768,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -19795,12 +19795,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -19822,12 +19822,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -19849,12 +19849,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -19876,12 +19876,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -19930,12 +19930,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -20011,12 +20011,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -20038,12 +20038,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -20065,12 +20065,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -20092,12 +20092,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -20119,12 +20119,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -20313,10 +20313,10 @@
         <v>2157</v>
       </c>
       <c r="E2" t="n">
-        <v>2191</v>
+        <v>2196</v>
       </c>
       <c r="F2" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -20330,13 +20330,13 @@
         <v>90</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>14.2</v>
+        <v>14.8</v>
       </c>
       <c r="L2" t="n">
-        <v>22.9</v>
+        <v>23.4</v>
       </c>
       <c r="M2" t="n">
         <v>100</v>
@@ -20382,10 +20382,10 @@
         <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>15.5</v>
+        <v>15.1</v>
       </c>
       <c r="L3" t="n">
-        <v>26.5</v>
+        <v>26</v>
       </c>
       <c r="M3" t="n">
         <v>100</v>
@@ -20431,10 +20431,10 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>12.4</v>
+        <v>12.9</v>
       </c>
       <c r="L4" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="M4" t="n">
         <v>100</v>
@@ -20483,7 +20483,7 @@
         <v>7.5</v>
       </c>
       <c r="L5" t="n">
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="M5" t="n">
         <v>100</v>
@@ -20529,10 +20529,10 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L6" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="M6" t="n">
         <v>100</v>
@@ -20578,10 +20578,10 @@
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L7" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M7" t="n">
         <v>100</v>
@@ -20627,7 +20627,7 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L8" t="n">
         <v>9.1</v>
@@ -20676,10 +20676,10 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L9" t="n">
-        <v>10.6</v>
+        <v>10.3</v>
       </c>
       <c r="M9" t="n">
         <v>100</v>
@@ -20725,7 +20725,7 @@
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L10" t="n">
         <v>8.5</v>
@@ -20754,10 +20754,10 @@
         <v>1894</v>
       </c>
       <c r="E11" t="n">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="F11" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -20771,13 +20771,13 @@
         <v>77</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="M11" t="n">
         <v>100</v>
@@ -20821,7 +20821,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="L12" t="n">
         <v>5.3</v>
@@ -20870,10 +20870,10 @@
         <v>4</v>
       </c>
       <c r="K13" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="L13" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
@@ -20917,10 +20917,10 @@
         <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="L14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
@@ -20969,7 +20969,7 @@
         <v>2.1</v>
       </c>
       <c r="L15" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="M15" t="n">
         <v>100</v>
@@ -21013,10 +21013,10 @@
         <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="M16" t="n">
         <v>100</v>
@@ -21060,10 +21060,10 @@
         <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="L17" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="M17" t="n">
         <v>100</v>
@@ -21107,10 +21107,10 @@
         <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="L18" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="M18" t="n">
         <v>100</v>
@@ -21157,7 +21157,7 @@
         <v>1.7</v>
       </c>
       <c r="L19" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="M19" t="n">
         <v>100</v>
@@ -21298,7 +21298,7 @@
         <v>0.8</v>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="M22" t="n">
         <v>100</v>
@@ -21342,7 +21342,7 @@
         <v>3</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L23" t="n">
         <v>2.5</v>
@@ -21374,7 +21374,7 @@
         <v>1829</v>
       </c>
       <c r="F24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -21389,10 +21389,10 @@
         <v>4</v>
       </c>
       <c r="K24" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="L24" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
         <v>100</v>
@@ -21421,7 +21421,7 @@
         <v>1826</v>
       </c>
       <c r="F25" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -21627,7 +21627,7 @@
         <v>0.9</v>
       </c>
       <c r="L29" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="M29" t="n">
         <v>100</v>
@@ -21671,10 +21671,10 @@
         <v>4</v>
       </c>
       <c r="K30" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="L30" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="M30" t="n">
         <v>100</v>
@@ -21843,7 +21843,7 @@
         <v>1710</v>
       </c>
       <c r="E34" t="n">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="F34" t="n">
         <v>24</v>
@@ -22076,7 +22076,7 @@
         <v>1676</v>
       </c>
       <c r="E39" t="n">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="F39" t="n">
         <v>-27</v>
@@ -22146,7 +22146,7 @@
         <v>0.1</v>
       </c>
       <c r="L40" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M40" t="n">
         <v>100</v>
@@ -22238,7 +22238,7 @@
         <v>0.1</v>
       </c>
       <c r="L42" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="M42" t="n">
         <v>100</v>
@@ -22580,7 +22580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -22903,17 +22903,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>United States 1-4 Belgium</t>
+          <t>Spain 2-1 Belgium</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -22922,16 +22922,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.308742742240721</v>
+        <v>0.5552884311116757</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2744439586320889</v>
+        <v>0.2460232733026527</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4168132991271902</v>
+        <v>0.1986882955856716</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2177144044806162</v>
+        <v>0.118622709152927</v>
       </c>
       <c r="I9" t="b">
         <v>1</v>
@@ -22940,7 +22940,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina 3-1 Qatar</t>
+          <t>United States 1-4 Belgium</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -22959,67 +22959,67 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.3453920951054398</v>
+        <v>0.308742742240721</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2770379896168901</v>
+        <v>0.2744439586320889</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3775699152776701</v>
+        <v>0.4168132991271902</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2855352750366162</v>
+        <v>0.2177144044806162</v>
       </c>
       <c r="I10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Croatia 2-1 Ghana</t>
+          <t>Bosnia and Herzegovina 3-1 Qatar</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.5565688121684058</v>
+        <v>0.3453920951054398</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2456368639707376</v>
+        <v>0.2770379896168901</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1977943238608567</v>
+        <v>0.3775699152776701</v>
       </c>
       <c r="H11" t="n">
-        <v>0.117876906446656</v>
+        <v>0.2855352750366162</v>
       </c>
       <c r="I11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DR Congo 3-1 Uzbekistan</t>
+          <t>Croatia 2-1 Ghana</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -23033,90 +23033,90 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.2503767500746171</v>
+        <v>0.5565688121684058</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2637278732454056</v>
+        <v>0.2456368639707376</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4858953766799774</v>
+        <v>0.1977943238608567</v>
       </c>
       <c r="H12" t="n">
-        <v>0.399014666953835</v>
+        <v>0.117876906446656</v>
       </c>
       <c r="I12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ecuador 2-1 Germany</t>
+          <t>DR Congo 3-1 Uzbekistan</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.3655576724890429</v>
+        <v>0.2503767500746171</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2772729806587883</v>
+        <v>0.2637278732454056</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3571693468521687</v>
+        <v>0.4858953766799774</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2650435046341627</v>
+        <v>0.399014666953835</v>
       </c>
       <c r="I13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jordan 1-3 Argentina</t>
+          <t>Ecuador 2-1 Germany</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.139845943137528</v>
+        <v>0.3655576724890429</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2134247456256824</v>
+        <v>0.2772729806587883</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6467293112367896</v>
+        <v>0.3571693468521687</v>
       </c>
       <c r="H14" t="n">
-        <v>0.07217853367562886</v>
+        <v>0.2650435046341627</v>
       </c>
       <c r="I14" t="b">
         <v>1</v>
@@ -23125,35 +23125,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mexico 2-0 South Africa</t>
+          <t>Jordan 1-3 Argentina</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.6024361314750264</v>
+        <v>0.139845943137528</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2304550812756662</v>
+        <v>0.2134247456256824</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1671087872493074</v>
+        <v>0.6467293112367896</v>
       </c>
       <c r="H15" t="n">
-        <v>0.09299118816623837</v>
+        <v>0.07217853367562886</v>
       </c>
       <c r="I15" t="b">
         <v>1</v>
@@ -23162,35 +23162,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>New Zealand 1-5 Belgium</t>
+          <t>Mexico 2-0 South Africa</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.2127546061888779</v>
+        <v>0.6024361314750264</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2517212424245827</v>
+        <v>0.2304550812756662</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5355241513865395</v>
+        <v>0.1671087872493074</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1305011681998895</v>
+        <v>0.09299118816623837</v>
       </c>
       <c r="I16" t="b">
         <v>1</v>
@@ -23199,17 +23199,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Paraguay 0-0 Australia</t>
+          <t>New Zealand 1-5 Belgium</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -23218,25 +23218,25 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.3692355958696349</v>
+        <v>0.2127546061888779</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2772300863797774</v>
+        <v>0.2517212424245827</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3535343177505875</v>
+        <v>0.5355241513865395</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1306607195422889</v>
+        <v>0.1305011681998895</v>
       </c>
       <c r="I17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senegal 5-0 Iraq</t>
+          <t>Paraguay 0-0 Australia</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -23246,7 +23246,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -23255,25 +23255,25 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.5466858920536273</v>
+        <v>0.3692355958696349</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2485652655176322</v>
+        <v>0.2772300863797774</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2047488424287405</v>
+        <v>0.3535343177505875</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1237078844695625</v>
+        <v>0.1306607195422889</v>
       </c>
       <c r="I18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>South Korea 2-1 Czechia</t>
+          <t>Senegal 5-0 Iraq</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -23292,16 +23292,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.3775464057956682</v>
+        <v>0.5466858920536273</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2770387146066375</v>
+        <v>0.2485652655176322</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3454148795976941</v>
+        <v>0.2047488424287405</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2533799579926903</v>
+        <v>0.1237078844695625</v>
       </c>
       <c r="I19" t="b">
         <v>1</v>
@@ -23310,17 +23310,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tunisia 1-3 Netherlands</t>
+          <t>South Korea 2-1 Czechia</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -23329,16 +23329,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.2267976629606308</v>
+        <v>0.3775464057956682</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2567282829191442</v>
+        <v>0.2770387146066375</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5164740541202248</v>
+        <v>0.3454148795976941</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1426172601316675</v>
+        <v>0.2533799579926903</v>
       </c>
       <c r="I20" t="b">
         <v>1</v>
@@ -23347,7 +23347,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Uruguay 0-1 Spain</t>
+          <t>Tunisia 1-3 Netherlands</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -23366,16 +23366,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.1976421593034932</v>
+        <v>0.2267976629606308</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2455707955982245</v>
+        <v>0.2567282829191442</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5567870450982821</v>
+        <v>0.5164740541202248</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1177500732634297</v>
+        <v>0.1426172601316675</v>
       </c>
       <c r="I21" t="b">
         <v>1</v>
@@ -23384,72 +23384,72 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Canada 1-1 Bosnia and Herzegovina</t>
+          <t>Uruguay 0-1 Spain</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.5935041775822631</v>
+        <v>0.1976421593034932</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2336119886651664</v>
+        <v>0.2455707955982245</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1728838337525705</v>
+        <v>0.5567870450982821</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1910680143902925</v>
+        <v>0.1177500732634297</v>
       </c>
       <c r="I22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>South Africa 1-0 South Korea</t>
+          <t>Canada 1-1 Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.26113755545355</v>
+        <v>0.5935041775822631</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2663778415879188</v>
+        <v>0.2336119886651664</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4724846029585311</v>
+        <v>0.1728838337525705</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3845797059970184</v>
+        <v>0.1910680143902925</v>
       </c>
       <c r="I23" t="b">
         <v>0</v>
@@ -23458,49 +23458,49 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>United States 4-1 Paraguay</t>
+          <t>South Africa 1-0 South Korea</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.4107699333529872</v>
+        <v>0.26113755545355</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2750184355219605</v>
+        <v>0.2663778415879188</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3142116311250522</v>
+        <v>0.4724846029585311</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2229605102875545</v>
+        <v>0.3845797059970184</v>
       </c>
       <c r="I24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Australia 2-0 Turkey</t>
+          <t>United States 4-1 Paraguay</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -23514,53 +23514,53 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.3022966571991881</v>
+        <v>0.4107699333529872</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2736782656597276</v>
+        <v>0.2750184355219605</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4240250771410841</v>
+        <v>0.3142116311250522</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3332936102999648</v>
+        <v>0.2229605102875545</v>
       </c>
       <c r="I25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Brazil 1-1 Morocco</t>
+          <t>Australia 2-0 Turkey</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.4339441725206395</v>
+        <v>0.3022966571991881</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2724853115528631</v>
+        <v>0.2736782656597276</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2935705159264974</v>
+        <v>0.4240250771410841</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1372455963429862</v>
+        <v>0.3332936102999648</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
@@ -23569,17 +23569,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Haiti 0-1 Scotland</t>
+          <t>Brazil 1-1 Morocco</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -23588,25 +23588,25 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.2606949315022876</v>
+        <v>0.4339441725206395</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2662752434568346</v>
+        <v>0.2724853115528631</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4730298250408779</v>
+        <v>0.2935705159264974</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1728297063037152</v>
+        <v>0.1372455963429862</v>
       </c>
       <c r="I27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Qatar 1-1 Switzerland</t>
+          <t>Haiti 0-1 Scotland</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -23616,7 +23616,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -23625,67 +23625,67 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.2021605238111649</v>
+        <v>0.2606949315022876</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2474960581873801</v>
+        <v>0.2662752434568346</v>
       </c>
       <c r="G28" t="n">
-        <v>0.550343418001455</v>
+        <v>0.4730298250408779</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1718733775625644</v>
+        <v>0.1728297063037152</v>
       </c>
       <c r="I28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Germany 7-1 Curaçao</t>
+          <t>Qatar 1-1 Switzerland</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.6099914400822092</v>
+        <v>0.2021605238111649</v>
       </c>
       <c r="F29" t="n">
-        <v>0.227710918612106</v>
+        <v>0.2474960581873801</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1622976413056849</v>
+        <v>0.550343418001455</v>
       </c>
       <c r="H29" t="n">
-        <v>0.08922360059126888</v>
+        <v>0.1718733775625644</v>
       </c>
       <c r="I29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ivory Coast 1-0 Ecuador</t>
+          <t>Germany 7-1 Curaçao</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -23695,57 +23695,57 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.2738762749141564</v>
+        <v>0.6099914400822092</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2691027275042267</v>
+        <v>0.227710918612106</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4570209975816171</v>
+        <v>0.1622976413056849</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3680619281815189</v>
+        <v>0.08922360059126888</v>
       </c>
       <c r="I30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Netherlands 2-2 Japan</t>
+          <t>Ivory Coast 1-0 Ecuador</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.3911107030923358</v>
+        <v>0.2738762749141564</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2764517043235625</v>
+        <v>0.2691027275042267</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3324375925841019</v>
+        <v>0.4570209975816171</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1317411675182472</v>
+        <v>0.3680619281815189</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -23754,17 +23754,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sweden 5-1 Tunisia</t>
+          <t>Netherlands 2-2 Japan</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -23773,16 +23773,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.3379351884295246</v>
+        <v>0.3911107030923358</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2767432920907087</v>
+        <v>0.2764517043235625</v>
       </c>
       <c r="G32" t="n">
-        <v>0.3853215194797665</v>
+        <v>0.3324375925841019</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2934012440470226</v>
+        <v>0.1317411675182472</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -23791,35 +23791,35 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Belgium 1-1 Egypt</t>
+          <t>Sweden 5-1 Tunisia</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.4323227858568852</v>
+        <v>0.3379351884295246</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2726912470817157</v>
+        <v>0.2767432920907087</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2949859670613991</v>
+        <v>0.3853215194797665</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1369598559671035</v>
+        <v>0.2934012440470226</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
@@ -23828,7 +23828,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Iran 2-2 New Zealand</t>
+          <t>Belgium 1-1 Egypt</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -23847,16 +23847,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.4832027730434736</v>
+        <v>0.4323227858568852</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2642809230535665</v>
+        <v>0.2726912470817157</v>
       </c>
       <c r="G34" t="n">
-        <v>0.25251630390296</v>
+        <v>0.2949859670613991</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1486247018068573</v>
+        <v>0.1369598559671035</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
@@ -23865,12 +23865,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Saudi Arabia 1-1 Uruguay</t>
+          <t>Iran 2-2 New Zealand</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -23884,16 +23884,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.2240862560806894</v>
+        <v>0.4832027730434736</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2558123361101832</v>
+        <v>0.2642809230535665</v>
       </c>
       <c r="G35" t="n">
-        <v>0.5201014078091272</v>
+        <v>0.25251630390296</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1603600622846482</v>
+        <v>0.1486247018068573</v>
       </c>
       <c r="I35" t="b">
         <v>0</v>
@@ -23902,12 +23902,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Spain 0-0 Cape Verde</t>
+          <t>Saudi Arabia 1-1 Uruguay</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -23917,20 +23917,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.6889149405831398</v>
+        <v>0.2240862560806894</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1951539809620534</v>
+        <v>0.2558123361101832</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1159310784548069</v>
+        <v>0.5201014078091272</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2440219051551828</v>
+        <v>0.1603600622846482</v>
       </c>
       <c r="I36" t="b">
         <v>0</v>
@@ -23939,7 +23939,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Argentina 3-0 Algeria</t>
+          <t>Spain 0-0 Cape Verde</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -23949,34 +23949,34 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.5653447610298761</v>
+        <v>0.6889149405831398</v>
       </c>
       <c r="F37" t="n">
-        <v>0.242932655319136</v>
+        <v>0.1951539809620534</v>
       </c>
       <c r="G37" t="n">
-        <v>0.191722583650988</v>
+        <v>0.1159310784548069</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1128413629229928</v>
+        <v>0.2440219051551828</v>
       </c>
       <c r="I37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Austria 3-1 Jordan</t>
+          <t>Argentina 3-0 Algeria</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -23995,16 +23995,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.4465822656526882</v>
+        <v>0.5653447610298761</v>
       </c>
       <c r="F38" t="n">
-        <v>0.270736216737822</v>
+        <v>0.242932655319136</v>
       </c>
       <c r="G38" t="n">
-        <v>0.2826815176094898</v>
+        <v>0.191722583650988</v>
       </c>
       <c r="H38" t="n">
-        <v>0.193090014544058</v>
+        <v>0.1128413629229928</v>
       </c>
       <c r="I38" t="b">
         <v>1</v>
@@ -24013,7 +24013,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>France 3-1 Senegal</t>
+          <t>Austria 3-1 Jordan</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -24032,16 +24032,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.5101967760009811</v>
+        <v>0.4465822656526882</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2582711067810726</v>
+        <v>0.270736216737822</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2315321172179463</v>
+        <v>0.2826815176094898</v>
       </c>
       <c r="H39" t="n">
-        <v>0.146757159771629</v>
+        <v>0.193090014544058</v>
       </c>
       <c r="I39" t="b">
         <v>1</v>
@@ -24050,35 +24050,35 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Iraq 1-4 Norway</t>
+          <t>France 3-1 Senegal</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.1771341674124645</v>
+        <v>0.5101967760009811</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2358428959472877</v>
+        <v>0.2582711067810726</v>
       </c>
       <c r="G40" t="n">
-        <v>0.587022936640248</v>
+        <v>0.2315321172179463</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1009632840630759</v>
+        <v>0.146757159771629</v>
       </c>
       <c r="I40" t="b">
         <v>1</v>
@@ -24087,35 +24087,35 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>England 4-2 Croatia</t>
+          <t>Iraq 1-4 Norway</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.4421686007896301</v>
+        <v>0.1771341674124645</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2713758294277268</v>
+        <v>0.2358428959472877</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2864555697826432</v>
+        <v>0.587022936640248</v>
       </c>
       <c r="H41" t="n">
-        <v>0.196616331702249</v>
+        <v>0.1009632840630759</v>
       </c>
       <c r="I41" t="b">
         <v>1</v>
@@ -24124,12 +24124,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ghana 1-0 Panama</t>
+          <t>England 4-2 Croatia</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -24143,53 +24143,53 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.269445732840606</v>
+        <v>0.4421686007896301</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2682043756018556</v>
+        <v>0.2713758294277268</v>
       </c>
       <c r="G42" t="n">
-        <v>0.4623498915575382</v>
+        <v>0.2864555697826432</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3737384797440333</v>
+        <v>0.196616331702249</v>
       </c>
       <c r="I42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Portugal 1-1 DR Congo</t>
+          <t>Ghana 1-0 Panama</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.6563191675226661</v>
+        <v>0.269445732840606</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2094436649180234</v>
+        <v>0.2682043756018556</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1342371675593106</v>
+        <v>0.4623498915575382</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2243872334059959</v>
+        <v>0.3737384797440333</v>
       </c>
       <c r="I43" t="b">
         <v>0</v>
@@ -24198,72 +24198,72 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Uzbekistan 1-3 Colombia</t>
+          <t>Portugal 1-1 DR Congo</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.2202298877346608</v>
+        <v>0.6563191675226661</v>
       </c>
       <c r="F44" t="n">
-        <v>0.254468243557875</v>
+        <v>0.2094436649180234</v>
       </c>
       <c r="G44" t="n">
-        <v>0.5253018687074642</v>
+        <v>0.1342371675593106</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1369197596521234</v>
+        <v>0.2243872334059959</v>
       </c>
       <c r="I44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Canada 6-0 Qatar</t>
+          <t>Uzbekistan 1-3 Colombia</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.5764064554833523</v>
+        <v>0.2202298877346608</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2393871531850218</v>
+        <v>0.254468243557875</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1842063913316258</v>
+        <v>0.5253018687074642</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1066817427817986</v>
+        <v>0.1369197596521234</v>
       </c>
       <c r="I45" t="b">
         <v>1</v>
@@ -24272,7 +24272,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Czechia 1-1 South Africa</t>
+          <t>Canada 6-0 Qatar</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -24282,34 +24282,34 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.4553404858663942</v>
+        <v>0.5764064554833523</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2693770505519105</v>
+        <v>0.2393871531850218</v>
       </c>
       <c r="G46" t="n">
-        <v>0.2752824635816952</v>
+        <v>0.1842063913316258</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1415576964123257</v>
+        <v>0.1066817427817986</v>
       </c>
       <c r="I46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Mexico 1-0 South Korea</t>
+          <t>Czechia 1-1 South Africa</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -24319,7 +24319,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -24328,25 +24328,25 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.4881235585818711</v>
+        <v>0.4553404858663942</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2632623226473407</v>
+        <v>0.2693770505519105</v>
       </c>
       <c r="G47" t="n">
-        <v>0.2486141187707883</v>
+        <v>0.2752824635816952</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1619132356655314</v>
+        <v>0.1415576964123257</v>
       </c>
       <c r="I47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Switzerland 4-1 Bosnia and Herzegovina</t>
+          <t>Mexico 1-0 South Korea</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -24361,20 +24361,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.5675807326327216</v>
+        <v>0.4881235585818711</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2422282277870113</v>
+        <v>0.2632623226473407</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1901910395802674</v>
+        <v>0.2486141187707883</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1115795271635383</v>
+        <v>0.1619132356655314</v>
       </c>
       <c r="I48" t="b">
         <v>1</v>
@@ -24383,7 +24383,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Brazil 3-0 Haiti</t>
+          <t>Switzerland 4-1 Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -24402,16 +24402,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.6024710043427424</v>
+        <v>0.5675807326327216</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2304425698918271</v>
+        <v>0.2422282277870113</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1670864257654306</v>
+        <v>0.1901910395802674</v>
       </c>
       <c r="H49" t="n">
-        <v>0.09297358803166735</v>
+        <v>0.1115795271635383</v>
       </c>
       <c r="I49" t="b">
         <v>1</v>
@@ -24420,35 +24420,35 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Scotland 0-1 Morocco</t>
+          <t>Brazil 3-0 Haiti</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.3123152964921898</v>
+        <v>0.6024710043427424</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2748269579337349</v>
+        <v>0.2304425698918271</v>
       </c>
       <c r="G50" t="n">
-        <v>0.4128577455740753</v>
+        <v>0.1670864257654306</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2211384356776808</v>
+        <v>0.09297358803166735</v>
       </c>
       <c r="I50" t="b">
         <v>1</v>
@@ -24457,12 +24457,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Turkey 0-1 Paraguay</t>
+          <t>Scotland 0-1 Morocco</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -24476,25 +24476,25 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.4158113794624096</v>
+        <v>0.3123152964921898</v>
       </c>
       <c r="F51" t="n">
-        <v>0.2745434638141608</v>
+        <v>0.2748269579337349</v>
       </c>
       <c r="G51" t="n">
-        <v>0.3096451567234295</v>
+        <v>0.4128577455740753</v>
       </c>
       <c r="H51" t="n">
-        <v>0.324744456462925</v>
+        <v>0.2211384356776808</v>
       </c>
       <c r="I51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>United States 2-0 Australia</t>
+          <t>Turkey 0-1 Paraguay</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -24504,7 +24504,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -24513,25 +24513,25 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.4189589466211568</v>
+        <v>0.4158113794624096</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2742252024300777</v>
+        <v>0.2745434638141608</v>
       </c>
       <c r="G52" t="n">
-        <v>0.3068158509487656</v>
+        <v>0.3096451567234295</v>
       </c>
       <c r="H52" t="n">
-        <v>0.2158723360525054</v>
+        <v>0.324744456462925</v>
       </c>
       <c r="I52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ecuador 0-0 Curaçao</t>
+          <t>United States 2-0 Australia</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -24541,34 +24541,34 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.614390105780561</v>
+        <v>0.4189589466211568</v>
       </c>
       <c r="F53" t="n">
-        <v>0.2260824080030716</v>
+        <v>0.2742252024300777</v>
       </c>
       <c r="G53" t="n">
-        <v>0.1595274862163676</v>
+        <v>0.3068158509487656</v>
       </c>
       <c r="H53" t="n">
-        <v>0.2014621104697811</v>
+        <v>0.2158723360525054</v>
       </c>
       <c r="I53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Germany 2-1 Ivory Coast</t>
+          <t>Ecuador 0-0 Curaçao</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -24578,34 +24578,34 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.4525599494983835</v>
+        <v>0.614390105780561</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2698214154164175</v>
+        <v>0.2260824080030716</v>
       </c>
       <c r="G54" t="n">
-        <v>0.277618635085199</v>
+        <v>0.1595274862163676</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1883813577198906</v>
+        <v>0.2014621104697811</v>
       </c>
       <c r="I54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Netherlands 5-1 Sweden</t>
+          <t>Germany 2-1 Ivory Coast</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24624,16 +24624,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.5419741522498547</v>
+        <v>0.4525599494983835</v>
       </c>
       <c r="F55" t="n">
-        <v>0.249917248195977</v>
+        <v>0.2698214154164175</v>
       </c>
       <c r="G55" t="n">
-        <v>0.2081085995541683</v>
+        <v>0.277618635085199</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1265484332078183</v>
+        <v>0.1883813577198906</v>
       </c>
       <c r="I55" t="b">
         <v>1</v>
@@ -24642,17 +24642,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Tunisia 0-4 Japan</t>
+          <t>Netherlands 5-1 Sweden</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -24661,16 +24661,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.2511552631390055</v>
+        <v>0.5419741522498547</v>
       </c>
       <c r="F56" t="n">
-        <v>0.2639306340880528</v>
+        <v>0.249917248195977</v>
       </c>
       <c r="G56" t="n">
-        <v>0.4849141027729418</v>
+        <v>0.2081085995541683</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1641962238623133</v>
+        <v>0.1265484332078183</v>
       </c>
       <c r="I56" t="b">
         <v>1</v>
@@ -24679,17 +24679,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Belgium 0-0 Iran</t>
+          <t>Tunisia 0-4 Japan</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -24698,35 +24698,35 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.4110593987622102</v>
+        <v>0.2511552631390055</v>
       </c>
       <c r="F57" t="n">
-        <v>0.2749923306348419</v>
+        <v>0.2639306340880528</v>
       </c>
       <c r="G57" t="n">
-        <v>0.3139482706029479</v>
+        <v>0.4849141027729418</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1337666729626658</v>
+        <v>0.1641962238623133</v>
       </c>
       <c r="I57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>New Zealand 1-3 Egypt</t>
+          <t>Belgium 0-0 Iran</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -24735,53 +24735,53 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.2701606709292552</v>
+        <v>0.4110593987622102</v>
       </c>
       <c r="F58" t="n">
-        <v>0.2683528583888833</v>
+        <v>0.2749923306348419</v>
       </c>
       <c r="G58" t="n">
-        <v>0.4614864706818617</v>
+        <v>0.3139482706029479</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1814918046878114</v>
+        <v>0.1337666729626658</v>
       </c>
       <c r="I58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Spain 4-0 Saudi Arabia</t>
+          <t>New Zealand 1-3 Egypt</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.711801189694372</v>
+        <v>0.2701606709292552</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1844344879110749</v>
+        <v>0.2683528583888833</v>
       </c>
       <c r="G59" t="n">
-        <v>0.103764322394553</v>
+        <v>0.4614864706818617</v>
       </c>
       <c r="H59" t="n">
-        <v>0.04691279443179004</v>
+        <v>0.1814918046878114</v>
       </c>
       <c r="I59" t="b">
         <v>1</v>
@@ -24790,7 +24790,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Uruguay 2-2 Cape Verde</t>
+          <t>Spain 4-0 Saudi Arabia</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -24800,34 +24800,34 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.4946917415780235</v>
+        <v>0.711801189694372</v>
       </c>
       <c r="F60" t="n">
-        <v>0.2618487176721053</v>
+        <v>0.1844344879110749</v>
       </c>
       <c r="G60" t="n">
-        <v>0.243459540749871</v>
+        <v>0.103764322394553</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1519962335838181</v>
+        <v>0.04691279443179004</v>
       </c>
       <c r="I60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Argentina 2-0 Austria</t>
+          <t>Uruguay 2-2 Cape Verde</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -24837,7 +24837,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -24846,25 +24846,25 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.5600237883076568</v>
+        <v>0.4946917415780235</v>
       </c>
       <c r="F61" t="n">
-        <v>0.2445838247676272</v>
+        <v>0.2618487176721053</v>
       </c>
       <c r="G61" t="n">
-        <v>0.1953923869247162</v>
+        <v>0.243459540749871</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1158786258616418</v>
+        <v>0.1519962335838181</v>
       </c>
       <c r="I61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>France 3-0 Iraq</t>
+          <t>Argentina 2-0 Austria</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -24879,20 +24879,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.6938172051627756</v>
+        <v>0.5600237883076568</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1929050139558987</v>
+        <v>0.2445838247676272</v>
       </c>
       <c r="G62" t="n">
-        <v>0.1132777808813258</v>
+        <v>0.1953923869247162</v>
       </c>
       <c r="H62" t="n">
-        <v>0.05328987974786575</v>
+        <v>0.1158786258616418</v>
       </c>
       <c r="I62" t="b">
         <v>1</v>
@@ -24901,35 +24901,35 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Jordan 1-2 Algeria</t>
+          <t>France 3-0 Iraq</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.2871872150453605</v>
+        <v>0.6938172051627756</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2714956942424305</v>
+        <v>0.1929050139558987</v>
       </c>
       <c r="G63" t="n">
-        <v>0.4413170907122089</v>
+        <v>0.1132777808813258</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1973015448078901</v>
+        <v>0.05328987974786575</v>
       </c>
       <c r="I63" t="b">
         <v>1</v>
@@ -24938,17 +24938,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Norway 3-2 Senegal</t>
+          <t>Jordan 1-2 Algeria</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -24957,16 +24957,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.399746405577862</v>
+        <v>0.2871872150453605</v>
       </c>
       <c r="F64" t="n">
-        <v>0.2759053625170023</v>
+        <v>0.2714956942424305</v>
       </c>
       <c r="G64" t="n">
-        <v>0.3243482319051358</v>
+        <v>0.4413170907122089</v>
       </c>
       <c r="H64" t="n">
-        <v>0.2327530765783421</v>
+        <v>0.1973015448078901</v>
       </c>
       <c r="I64" t="b">
         <v>1</v>
@@ -24975,7 +24975,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Colombia 1-0 DR Congo</t>
+          <t>Norway 3-2 Senegal</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -24990,20 +24990,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.6513377464031052</v>
+        <v>0.399746405577862</v>
       </c>
       <c r="F65" t="n">
-        <v>0.2115244400993148</v>
+        <v>0.2759053625170023</v>
       </c>
       <c r="G65" t="n">
-        <v>0.1371378134975802</v>
+        <v>0.3243482319051358</v>
       </c>
       <c r="H65" t="n">
-        <v>0.07018607348708122</v>
+        <v>0.2327530765783421</v>
       </c>
       <c r="I65" t="b">
         <v>1</v>
@@ -25012,7 +25012,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>England 0-0 Ghana</t>
+          <t>Colombia 1-0 DR Congo</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -25022,7 +25022,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -25031,72 +25031,72 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.6391364229920049</v>
+        <v>0.6513377464031052</v>
       </c>
       <c r="F66" t="n">
-        <v>0.2165036639184777</v>
+        <v>0.2115244400993148</v>
       </c>
       <c r="G66" t="n">
-        <v>0.1443599130895173</v>
+        <v>0.1371378134975802</v>
       </c>
       <c r="H66" t="n">
-        <v>0.214667575851114</v>
+        <v>0.07018607348708122</v>
       </c>
       <c r="I66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Panama 0-1 Croatia</t>
+          <t>England 0-0 Ghana</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.2779192196934168</v>
+        <v>0.6391364229920049</v>
       </c>
       <c r="F67" t="n">
-        <v>0.2698775634692422</v>
+        <v>0.2165036639184777</v>
       </c>
       <c r="G67" t="n">
-        <v>0.452203216837341</v>
+        <v>0.1443599130895173</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1886602041591775</v>
+        <v>0.214667575851114</v>
       </c>
       <c r="I67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Portugal 5-0 Uzbekistan</t>
+          <t>Panama 0-1 Croatia</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -25105,16 +25105,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.5305667905006943</v>
+        <v>0.2779192196934168</v>
       </c>
       <c r="F68" t="n">
-        <v>0.2530706921820465</v>
+        <v>0.2698775634692422</v>
       </c>
       <c r="G68" t="n">
-        <v>0.216362517317259</v>
+        <v>0.452203216837341</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1335901385403401</v>
+        <v>0.1886602041591775</v>
       </c>
       <c r="I68" t="b">
         <v>1</v>
@@ -25123,17 +25123,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Czechia 0-3 Mexico</t>
+          <t>Portugal 5-0 Uzbekistan</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -25142,16 +25142,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.2351921354348235</v>
+        <v>0.5305667905006943</v>
       </c>
       <c r="F69" t="n">
-        <v>0.2594153894470163</v>
+        <v>0.2530706921820465</v>
       </c>
       <c r="G69" t="n">
-        <v>0.5053924751181602</v>
+        <v>0.216362517317259</v>
       </c>
       <c r="H69" t="n">
-        <v>0.1499759721200661</v>
+        <v>0.1335901385403401</v>
       </c>
       <c r="I69" t="b">
         <v>1</v>
@@ -25160,7 +25160,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Scotland 0-3 Brazil</t>
+          <t>Czechia 0-3 Mexico</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -25179,16 +25179,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.24901815042318</v>
+        <v>0.2351921354348235</v>
       </c>
       <c r="F70" t="n">
-        <v>0.2633698330694462</v>
+        <v>0.2594153894470163</v>
       </c>
       <c r="G70" t="n">
-        <v>0.4876120165073738</v>
+        <v>0.5053924751181602</v>
       </c>
       <c r="H70" t="n">
-        <v>0.1622757424339106</v>
+        <v>0.1499759721200661</v>
       </c>
       <c r="I70" t="b">
         <v>1</v>
@@ -25197,7 +25197,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Switzerland 2-1 Canada</t>
+          <t>Scotland 0-3 Brazil</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -25207,7 +25207,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -25216,25 +25216,25 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.3372955421668554</v>
+        <v>0.24901815042318</v>
       </c>
       <c r="F71" t="n">
-        <v>0.2767126361678793</v>
+        <v>0.2633698330694462</v>
       </c>
       <c r="G71" t="n">
-        <v>0.3859918216652653</v>
+        <v>0.4876120165073738</v>
       </c>
       <c r="H71" t="n">
-        <v>0.294083442412196</v>
+        <v>0.1622757424339106</v>
       </c>
       <c r="I71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Curaçao 0-2 Ivory Coast</t>
+          <t>Switzerland 2-1 Canada</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -25244,7 +25244,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -25253,35 +25253,35 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.2272040348991984</v>
+        <v>0.3372955421668554</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2568635144989577</v>
+        <v>0.2767126361678793</v>
       </c>
       <c r="G72" t="n">
-        <v>0.515932450601844</v>
+        <v>0.3859918216652653</v>
       </c>
       <c r="H72" t="n">
-        <v>0.1429715329274063</v>
+        <v>0.294083442412196</v>
       </c>
       <c r="I72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Japan 1-1 Sweden</t>
+          <t>Curaçao 0-2 Ivory Coast</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -25290,25 +25290,25 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.5103893669153626</v>
+        <v>0.2272040348991984</v>
       </c>
       <c r="F73" t="n">
-        <v>0.2582245731851142</v>
+        <v>0.2568635144989577</v>
       </c>
       <c r="G73" t="n">
-        <v>0.2313860598995233</v>
+        <v>0.515932450601844</v>
       </c>
       <c r="H73" t="n">
-        <v>0.1570184072880452</v>
+        <v>0.1429715329274063</v>
       </c>
       <c r="I73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Turkey 3-2 United States</t>
+          <t>Japan 1-1 Sweden</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -25318,7 +25318,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -25327,25 +25327,25 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.366204275259826</v>
+        <v>0.5103893669153626</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2772673175853767</v>
+        <v>0.2582245731851142</v>
       </c>
       <c r="G74" t="n">
-        <v>0.3565284071547971</v>
+        <v>0.2313860598995233</v>
       </c>
       <c r="H74" t="n">
-        <v>0.2644047629036296</v>
+        <v>0.1570184072880452</v>
       </c>
       <c r="I74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cape Verde 0-0 Saudi Arabia</t>
+          <t>Turkey 3-2 United States</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -25355,7 +25355,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -25364,30 +25364,30 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.3852371570345247</v>
+        <v>0.366204275259826</v>
       </c>
       <c r="F75" t="n">
-        <v>0.2767470924337009</v>
+        <v>0.2772673175853767</v>
       </c>
       <c r="G75" t="n">
-        <v>0.3380157505317744</v>
+        <v>0.3565284071547971</v>
       </c>
       <c r="H75" t="n">
-        <v>0.1313311573838009</v>
+        <v>0.2644047629036296</v>
       </c>
       <c r="I75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Egypt 1-1 Iran</t>
+          <t>Cape Verde 0-0 Saudi Arabia</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -25401,16 +25401,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.3412571427626345</v>
+        <v>0.3852371570345247</v>
       </c>
       <c r="F76" t="n">
-        <v>0.2768887787853823</v>
+        <v>0.2767470924337009</v>
       </c>
       <c r="G76" t="n">
-        <v>0.381854078451983</v>
+        <v>0.3380157505317744</v>
       </c>
       <c r="H76" t="n">
-        <v>0.1311344873584653</v>
+        <v>0.1313311573838009</v>
       </c>
       <c r="I76" t="b">
         <v>0</v>
@@ -25419,7 +25419,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Norway 1-4 France</t>
+          <t>Egypt 1-1 Iran</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -25429,7 +25429,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -25438,25 +25438,25 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.2634174763844304</v>
+        <v>0.3412571427626345</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2668977716683674</v>
+        <v>0.2768887787853823</v>
       </c>
       <c r="G77" t="n">
-        <v>0.4696847519472021</v>
+        <v>0.381854078451983</v>
       </c>
       <c r="H77" t="n">
-        <v>0.1753115145910212</v>
+        <v>0.1311344873584653</v>
       </c>
       <c r="I77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Algeria 3-3 Austria</t>
+          <t>Norway 1-4 France</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -25466,7 +25466,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -25475,25 +25475,25 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.3563952469271287</v>
+        <v>0.2634174763844304</v>
       </c>
       <c r="F78" t="n">
-        <v>0.2772660392601014</v>
+        <v>0.2668977716683674</v>
       </c>
       <c r="G78" t="n">
-        <v>0.3663387138127697</v>
+        <v>0.4696847519472021</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1306108126351218</v>
+        <v>0.1753115145910212</v>
       </c>
       <c r="I78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Colombia 0-0 Portugal</t>
+          <t>Algeria 3-3 Austria</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -25512,16 +25512,16 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.3564734412949417</v>
+        <v>0.3563952469271287</v>
       </c>
       <c r="F79" t="n">
-        <v>0.2772667941651129</v>
+        <v>0.2772660392601014</v>
       </c>
       <c r="G79" t="n">
-        <v>0.3662597645399454</v>
+        <v>0.3663387138127697</v>
       </c>
       <c r="H79" t="n">
-        <v>0.1306097647347573</v>
+        <v>0.1306108126351218</v>
       </c>
       <c r="I79" t="b">
         <v>0</v>
@@ -25530,17 +25530,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Morocco 4-2 Haiti</t>
+          <t>Colombia 0-0 Portugal</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -25549,55 +25549,92 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.5271652709677939</v>
+        <v>0.3564734412949417</v>
       </c>
       <c r="F80" t="n">
-        <v>0.253977826748045</v>
+        <v>0.2772667941651129</v>
       </c>
       <c r="G80" t="n">
-        <v>0.2188569022841612</v>
+        <v>0.3662597645399454</v>
       </c>
       <c r="H80" t="n">
-        <v>0.1357355123281893</v>
+        <v>0.1306097647347573</v>
       </c>
       <c r="I80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>Morocco 4-2 Haiti</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0.5271652709677939</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.253977826748045</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.2188569022841612</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.1357355123281893</v>
+      </c>
+      <c r="I81" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>Panama 0-2 England</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="E81" t="n">
+      <c r="E82" t="n">
         <v>0.2122842217813804</v>
       </c>
-      <c r="F81" t="n">
+      <c r="F82" t="n">
         <v>0.251542015288873</v>
       </c>
-      <c r="G81" t="n">
+      <c r="G82" t="n">
         <v>0.5361737629297465</v>
       </c>
-      <c r="H81" t="n">
+      <c r="H82" t="n">
         <v>0.1300996845060386</v>
       </c>
-      <c r="I81" t="b">
+      <c r="I82" t="b">
         <v>1</v>
       </c>
     </row>
